--- a/sacure_採算管理_v4_ルート別案件別.xlsx
+++ b/sacure_採算管理_v4_ルート別案件別.xlsx
@@ -1082,27 +1082,13 @@
         <f>D5+E5+F5+G5</f>
         <v/>
       </c>
-      <c r="I5" s="12" t="n">
-        <v>680000</v>
-      </c>
-      <c r="J5" s="12" t="n">
-        <v>185000</v>
-      </c>
-      <c r="K5" s="12" t="n">
-        <v>95000</v>
-      </c>
-      <c r="L5" s="12" t="n">
-        <v>620000</v>
-      </c>
-      <c r="M5" s="12" t="n">
-        <v>85000</v>
-      </c>
-      <c r="N5" s="12" t="n">
-        <v>45000</v>
-      </c>
-      <c r="O5" s="12" t="n">
-        <v>120000</v>
-      </c>
+      <c r="I5" s="12" t="n"/>
+      <c r="J5" s="12" t="n"/>
+      <c r="K5" s="12" t="n"/>
+      <c r="L5" s="12" t="n"/>
+      <c r="M5" s="12" t="n"/>
+      <c r="N5" s="12" t="n"/>
+      <c r="O5" s="12" t="n"/>
       <c r="P5" s="13">
         <f>I5+J5+K5+L5+M5+N5+O5</f>
         <v/>
@@ -1161,27 +1147,13 @@
         <f>D6+E6+F6+G6</f>
         <v/>
       </c>
-      <c r="I6" s="12" t="n">
-        <v>680000</v>
-      </c>
-      <c r="J6" s="12" t="n">
-        <v>185000</v>
-      </c>
-      <c r="K6" s="12" t="n">
-        <v>95000</v>
-      </c>
-      <c r="L6" s="12" t="n">
-        <v>620000</v>
-      </c>
-      <c r="M6" s="12" t="n">
-        <v>85000</v>
-      </c>
-      <c r="N6" s="12" t="n">
-        <v>45000</v>
-      </c>
-      <c r="O6" s="12" t="n">
-        <v>120000</v>
-      </c>
+      <c r="I6" s="12" t="n"/>
+      <c r="J6" s="12" t="n"/>
+      <c r="K6" s="12" t="n"/>
+      <c r="L6" s="12" t="n"/>
+      <c r="M6" s="12" t="n"/>
+      <c r="N6" s="12" t="n"/>
+      <c r="O6" s="12" t="n"/>
       <c r="P6" s="13">
         <f>I6+J6+K6+L6+M6+N6+O6</f>
         <v/>
@@ -1239,27 +1211,13 @@
         <f>D7+E7+F7+G7</f>
         <v/>
       </c>
-      <c r="I7" s="12" t="n">
-        <v>680000</v>
-      </c>
-      <c r="J7" s="12" t="n">
-        <v>185000</v>
-      </c>
-      <c r="K7" s="12" t="n">
-        <v>95000</v>
-      </c>
-      <c r="L7" s="12" t="n">
-        <v>620000</v>
-      </c>
-      <c r="M7" s="12" t="n">
-        <v>85000</v>
-      </c>
-      <c r="N7" s="12" t="n">
-        <v>45000</v>
-      </c>
-      <c r="O7" s="12" t="n">
-        <v>120000</v>
-      </c>
+      <c r="I7" s="12" t="n"/>
+      <c r="J7" s="12" t="n"/>
+      <c r="K7" s="12" t="n"/>
+      <c r="L7" s="12" t="n"/>
+      <c r="M7" s="12" t="n"/>
+      <c r="N7" s="12" t="n"/>
+      <c r="O7" s="12" t="n"/>
       <c r="P7" s="13">
         <f>I7+J7+K7+L7+M7+N7+O7</f>
         <v/>
@@ -1317,27 +1275,13 @@
         <f>D8+E8+F8+G8</f>
         <v/>
       </c>
-      <c r="I8" s="12" t="n">
-        <v>680000</v>
-      </c>
-      <c r="J8" s="12" t="n">
-        <v>185000</v>
-      </c>
-      <c r="K8" s="12" t="n">
-        <v>95000</v>
-      </c>
-      <c r="L8" s="12" t="n">
-        <v>620000</v>
-      </c>
-      <c r="M8" s="12" t="n">
-        <v>85000</v>
-      </c>
-      <c r="N8" s="12" t="n">
-        <v>45000</v>
-      </c>
-      <c r="O8" s="12" t="n">
-        <v>120000</v>
-      </c>
+      <c r="I8" s="12" t="n"/>
+      <c r="J8" s="12" t="n"/>
+      <c r="K8" s="12" t="n"/>
+      <c r="L8" s="12" t="n"/>
+      <c r="M8" s="12" t="n"/>
+      <c r="N8" s="12" t="n"/>
+      <c r="O8" s="12" t="n"/>
       <c r="P8" s="13">
         <f>I8+J8+K8+L8+M8+N8+O8</f>
         <v/>
@@ -1395,27 +1339,13 @@
         <f>D9+E9+F9+G9</f>
         <v/>
       </c>
-      <c r="I9" s="12" t="n">
-        <v>680000</v>
-      </c>
-      <c r="J9" s="12" t="n">
-        <v>185000</v>
-      </c>
-      <c r="K9" s="12" t="n">
-        <v>95000</v>
-      </c>
-      <c r="L9" s="12" t="n">
-        <v>620000</v>
-      </c>
-      <c r="M9" s="12" t="n">
-        <v>85000</v>
-      </c>
-      <c r="N9" s="12" t="n">
-        <v>45000</v>
-      </c>
-      <c r="O9" s="12" t="n">
-        <v>120000</v>
-      </c>
+      <c r="I9" s="12" t="n"/>
+      <c r="J9" s="12" t="n"/>
+      <c r="K9" s="12" t="n"/>
+      <c r="L9" s="12" t="n"/>
+      <c r="M9" s="12" t="n"/>
+      <c r="N9" s="12" t="n"/>
+      <c r="O9" s="12" t="n"/>
       <c r="P9" s="13">
         <f>I9+J9+K9+L9+M9+N9+O9</f>
         <v/>
@@ -1473,27 +1403,13 @@
         <f>D10+E10+F10+G10</f>
         <v/>
       </c>
-      <c r="I10" s="12" t="n">
-        <v>680000</v>
-      </c>
-      <c r="J10" s="12" t="n">
-        <v>185000</v>
-      </c>
-      <c r="K10" s="12" t="n">
-        <v>95000</v>
-      </c>
-      <c r="L10" s="12" t="n">
-        <v>620000</v>
-      </c>
-      <c r="M10" s="12" t="n">
-        <v>85000</v>
-      </c>
-      <c r="N10" s="12" t="n">
-        <v>45000</v>
-      </c>
-      <c r="O10" s="12" t="n">
-        <v>120000</v>
-      </c>
+      <c r="I10" s="12" t="n"/>
+      <c r="J10" s="12" t="n"/>
+      <c r="K10" s="12" t="n"/>
+      <c r="L10" s="12" t="n"/>
+      <c r="M10" s="12" t="n"/>
+      <c r="N10" s="12" t="n"/>
+      <c r="O10" s="12" t="n"/>
       <c r="P10" s="13">
         <f>I10+J10+K10+L10+M10+N10+O10</f>
         <v/>
@@ -1551,27 +1467,13 @@
         <f>D11+E11+F11+G11</f>
         <v/>
       </c>
-      <c r="I11" s="12" t="n">
-        <v>680000</v>
-      </c>
-      <c r="J11" s="12" t="n">
-        <v>185000</v>
-      </c>
-      <c r="K11" s="12" t="n">
-        <v>95000</v>
-      </c>
-      <c r="L11" s="12" t="n">
-        <v>620000</v>
-      </c>
-      <c r="M11" s="12" t="n">
-        <v>85000</v>
-      </c>
-      <c r="N11" s="12" t="n">
-        <v>45000</v>
-      </c>
-      <c r="O11" s="12" t="n">
-        <v>120000</v>
-      </c>
+      <c r="I11" s="12" t="n"/>
+      <c r="J11" s="12" t="n"/>
+      <c r="K11" s="12" t="n"/>
+      <c r="L11" s="12" t="n"/>
+      <c r="M11" s="12" t="n"/>
+      <c r="N11" s="12" t="n"/>
+      <c r="O11" s="12" t="n"/>
       <c r="P11" s="13">
         <f>I11+J11+K11+L11+M11+N11+O11</f>
         <v/>
@@ -1629,27 +1531,13 @@
         <f>D12+E12+F12+G12</f>
         <v/>
       </c>
-      <c r="I12" s="12" t="n">
-        <v>680000</v>
-      </c>
-      <c r="J12" s="12" t="n">
-        <v>185000</v>
-      </c>
-      <c r="K12" s="12" t="n">
-        <v>95000</v>
-      </c>
-      <c r="L12" s="12" t="n">
-        <v>620000</v>
-      </c>
-      <c r="M12" s="12" t="n">
-        <v>85000</v>
-      </c>
-      <c r="N12" s="12" t="n">
-        <v>45000</v>
-      </c>
-      <c r="O12" s="12" t="n">
-        <v>120000</v>
-      </c>
+      <c r="I12" s="12" t="n"/>
+      <c r="J12" s="12" t="n"/>
+      <c r="K12" s="12" t="n"/>
+      <c r="L12" s="12" t="n"/>
+      <c r="M12" s="12" t="n"/>
+      <c r="N12" s="12" t="n"/>
+      <c r="O12" s="12" t="n"/>
       <c r="P12" s="13">
         <f>I12+J12+K12+L12+M12+N12+O12</f>
         <v/>
@@ -1707,27 +1595,13 @@
         <f>D13+E13+F13+G13</f>
         <v/>
       </c>
-      <c r="I13" s="12" t="n">
-        <v>680000</v>
-      </c>
-      <c r="J13" s="12" t="n">
-        <v>185000</v>
-      </c>
-      <c r="K13" s="12" t="n">
-        <v>95000</v>
-      </c>
-      <c r="L13" s="12" t="n">
-        <v>620000</v>
-      </c>
-      <c r="M13" s="12" t="n">
-        <v>85000</v>
-      </c>
-      <c r="N13" s="12" t="n">
-        <v>45000</v>
-      </c>
-      <c r="O13" s="12" t="n">
-        <v>120000</v>
-      </c>
+      <c r="I13" s="12" t="n"/>
+      <c r="J13" s="12" t="n"/>
+      <c r="K13" s="12" t="n"/>
+      <c r="L13" s="12" t="n"/>
+      <c r="M13" s="12" t="n"/>
+      <c r="N13" s="12" t="n"/>
+      <c r="O13" s="12" t="n"/>
       <c r="P13" s="13">
         <f>I13+J13+K13+L13+M13+N13+O13</f>
         <v/>
@@ -1785,27 +1659,13 @@
         <f>D14+E14+F14+G14</f>
         <v/>
       </c>
-      <c r="I14" s="12" t="n">
-        <v>680000</v>
-      </c>
-      <c r="J14" s="12" t="n">
-        <v>185000</v>
-      </c>
-      <c r="K14" s="12" t="n">
-        <v>95000</v>
-      </c>
-      <c r="L14" s="12" t="n">
-        <v>620000</v>
-      </c>
-      <c r="M14" s="12" t="n">
-        <v>85000</v>
-      </c>
-      <c r="N14" s="12" t="n">
-        <v>45000</v>
-      </c>
-      <c r="O14" s="12" t="n">
-        <v>120000</v>
-      </c>
+      <c r="I14" s="12" t="n"/>
+      <c r="J14" s="12" t="n"/>
+      <c r="K14" s="12" t="n"/>
+      <c r="L14" s="12" t="n"/>
+      <c r="M14" s="12" t="n"/>
+      <c r="N14" s="12" t="n"/>
+      <c r="O14" s="12" t="n"/>
       <c r="P14" s="13">
         <f>I14+J14+K14+L14+M14+N14+O14</f>
         <v/>
@@ -1863,27 +1723,13 @@
         <f>D15+E15+F15+G15</f>
         <v/>
       </c>
-      <c r="I15" s="12" t="n">
-        <v>680000</v>
-      </c>
-      <c r="J15" s="12" t="n">
-        <v>185000</v>
-      </c>
-      <c r="K15" s="12" t="n">
-        <v>95000</v>
-      </c>
-      <c r="L15" s="12" t="n">
-        <v>620000</v>
-      </c>
-      <c r="M15" s="12" t="n">
-        <v>85000</v>
-      </c>
-      <c r="N15" s="12" t="n">
-        <v>45000</v>
-      </c>
-      <c r="O15" s="12" t="n">
-        <v>120000</v>
-      </c>
+      <c r="I15" s="12" t="n"/>
+      <c r="J15" s="12" t="n"/>
+      <c r="K15" s="12" t="n"/>
+      <c r="L15" s="12" t="n"/>
+      <c r="M15" s="12" t="n"/>
+      <c r="N15" s="12" t="n"/>
+      <c r="O15" s="12" t="n"/>
       <c r="P15" s="13">
         <f>I15+J15+K15+L15+M15+N15+O15</f>
         <v/>
@@ -1941,27 +1787,13 @@
         <f>D16+E16+F16+G16</f>
         <v/>
       </c>
-      <c r="I16" s="12" t="n">
-        <v>680000</v>
-      </c>
-      <c r="J16" s="12" t="n">
-        <v>185000</v>
-      </c>
-      <c r="K16" s="12" t="n">
-        <v>95000</v>
-      </c>
-      <c r="L16" s="12" t="n">
-        <v>620000</v>
-      </c>
-      <c r="M16" s="12" t="n">
-        <v>85000</v>
-      </c>
-      <c r="N16" s="12" t="n">
-        <v>45000</v>
-      </c>
-      <c r="O16" s="12" t="n">
-        <v>120000</v>
-      </c>
+      <c r="I16" s="12" t="n"/>
+      <c r="J16" s="12" t="n"/>
+      <c r="K16" s="12" t="n"/>
+      <c r="L16" s="12" t="n"/>
+      <c r="M16" s="12" t="n"/>
+      <c r="N16" s="12" t="n"/>
+      <c r="O16" s="12" t="n"/>
       <c r="P16" s="13">
         <f>I16+J16+K16+L16+M16+N16+O16</f>
         <v/>
@@ -2019,27 +1851,13 @@
         <f>D17+E17+F17+G17</f>
         <v/>
       </c>
-      <c r="I17" s="12" t="n">
-        <v>680000</v>
-      </c>
-      <c r="J17" s="12" t="n">
-        <v>185000</v>
-      </c>
-      <c r="K17" s="12" t="n">
-        <v>95000</v>
-      </c>
-      <c r="L17" s="12" t="n">
-        <v>620000</v>
-      </c>
-      <c r="M17" s="12" t="n">
-        <v>85000</v>
-      </c>
-      <c r="N17" s="12" t="n">
-        <v>45000</v>
-      </c>
-      <c r="O17" s="12" t="n">
-        <v>120000</v>
-      </c>
+      <c r="I17" s="12" t="n"/>
+      <c r="J17" s="12" t="n"/>
+      <c r="K17" s="12" t="n"/>
+      <c r="L17" s="12" t="n"/>
+      <c r="M17" s="12" t="n"/>
+      <c r="N17" s="12" t="n"/>
+      <c r="O17" s="12" t="n"/>
       <c r="P17" s="13">
         <f>I17+J17+K17+L17+M17+N17+O17</f>
         <v/>
@@ -2097,27 +1915,13 @@
         <f>D18+E18+F18+G18</f>
         <v/>
       </c>
-      <c r="I18" s="12" t="n">
-        <v>680000</v>
-      </c>
-      <c r="J18" s="12" t="n">
-        <v>185000</v>
-      </c>
-      <c r="K18" s="12" t="n">
-        <v>95000</v>
-      </c>
-      <c r="L18" s="12" t="n">
-        <v>620000</v>
-      </c>
-      <c r="M18" s="12" t="n">
-        <v>85000</v>
-      </c>
-      <c r="N18" s="12" t="n">
-        <v>45000</v>
-      </c>
-      <c r="O18" s="12" t="n">
-        <v>120000</v>
-      </c>
+      <c r="I18" s="12" t="n"/>
+      <c r="J18" s="12" t="n"/>
+      <c r="K18" s="12" t="n"/>
+      <c r="L18" s="12" t="n"/>
+      <c r="M18" s="12" t="n"/>
+      <c r="N18" s="12" t="n"/>
+      <c r="O18" s="12" t="n"/>
       <c r="P18" s="13">
         <f>I18+J18+K18+L18+M18+N18+O18</f>
         <v/>
@@ -2175,27 +1979,13 @@
         <f>D19+E19+F19+G19</f>
         <v/>
       </c>
-      <c r="I19" s="12" t="n">
-        <v>680000</v>
-      </c>
-      <c r="J19" s="12" t="n">
-        <v>185000</v>
-      </c>
-      <c r="K19" s="12" t="n">
-        <v>95000</v>
-      </c>
-      <c r="L19" s="12" t="n">
-        <v>620000</v>
-      </c>
-      <c r="M19" s="12" t="n">
-        <v>85000</v>
-      </c>
-      <c r="N19" s="12" t="n">
-        <v>45000</v>
-      </c>
-      <c r="O19" s="12" t="n">
-        <v>120000</v>
-      </c>
+      <c r="I19" s="12" t="n"/>
+      <c r="J19" s="12" t="n"/>
+      <c r="K19" s="12" t="n"/>
+      <c r="L19" s="12" t="n"/>
+      <c r="M19" s="12" t="n"/>
+      <c r="N19" s="12" t="n"/>
+      <c r="O19" s="12" t="n"/>
       <c r="P19" s="13">
         <f>I19+J19+K19+L19+M19+N19+O19</f>
         <v/>
@@ -2253,27 +2043,13 @@
         <f>D20+E20+F20+G20</f>
         <v/>
       </c>
-      <c r="I20" s="12" t="n">
-        <v>680000</v>
-      </c>
-      <c r="J20" s="12" t="n">
-        <v>185000</v>
-      </c>
-      <c r="K20" s="12" t="n">
-        <v>95000</v>
-      </c>
-      <c r="L20" s="12" t="n">
-        <v>620000</v>
-      </c>
-      <c r="M20" s="12" t="n">
-        <v>85000</v>
-      </c>
-      <c r="N20" s="12" t="n">
-        <v>45000</v>
-      </c>
-      <c r="O20" s="12" t="n">
-        <v>120000</v>
-      </c>
+      <c r="I20" s="12" t="n"/>
+      <c r="J20" s="12" t="n"/>
+      <c r="K20" s="12" t="n"/>
+      <c r="L20" s="12" t="n"/>
+      <c r="M20" s="12" t="n"/>
+      <c r="N20" s="12" t="n"/>
+      <c r="O20" s="12" t="n"/>
       <c r="P20" s="13">
         <f>I20+J20+K20+L20+M20+N20+O20</f>
         <v/>
@@ -2331,27 +2107,13 @@
         <f>D21+E21+F21+G21</f>
         <v/>
       </c>
-      <c r="I21" s="12" t="n">
-        <v>680000</v>
-      </c>
-      <c r="J21" s="12" t="n">
-        <v>185000</v>
-      </c>
-      <c r="K21" s="12" t="n">
-        <v>95000</v>
-      </c>
-      <c r="L21" s="12" t="n">
-        <v>620000</v>
-      </c>
-      <c r="M21" s="12" t="n">
-        <v>85000</v>
-      </c>
-      <c r="N21" s="12" t="n">
-        <v>45000</v>
-      </c>
-      <c r="O21" s="12" t="n">
-        <v>120000</v>
-      </c>
+      <c r="I21" s="12" t="n"/>
+      <c r="J21" s="12" t="n"/>
+      <c r="K21" s="12" t="n"/>
+      <c r="L21" s="12" t="n"/>
+      <c r="M21" s="12" t="n"/>
+      <c r="N21" s="12" t="n"/>
+      <c r="O21" s="12" t="n"/>
       <c r="P21" s="13">
         <f>I21+J21+K21+L21+M21+N21+O21</f>
         <v/>
@@ -2431,27 +2193,13 @@
         <f>D23+E23+F23+G23</f>
         <v/>
       </c>
-      <c r="I23" s="12" t="n">
-        <v>430000</v>
-      </c>
-      <c r="J23" s="12" t="n">
-        <v>125000</v>
-      </c>
-      <c r="K23" s="12" t="n">
-        <v>67000</v>
-      </c>
-      <c r="L23" s="12" t="n">
-        <v>385000</v>
-      </c>
-      <c r="M23" s="12" t="n">
-        <v>43000</v>
-      </c>
-      <c r="N23" s="12" t="n">
-        <v>29000</v>
-      </c>
-      <c r="O23" s="12" t="n">
-        <v>85000</v>
-      </c>
+      <c r="I23" s="12" t="n"/>
+      <c r="J23" s="12" t="n"/>
+      <c r="K23" s="12" t="n"/>
+      <c r="L23" s="12" t="n"/>
+      <c r="M23" s="12" t="n"/>
+      <c r="N23" s="12" t="n"/>
+      <c r="O23" s="12" t="n"/>
       <c r="P23" s="13">
         <f>I23+J23+K23+L23+M23+N23+O23</f>
         <v/>
@@ -2510,27 +2258,13 @@
         <f>D24+E24+F24+G24</f>
         <v/>
       </c>
-      <c r="I24" s="12" t="n">
-        <v>430000</v>
-      </c>
-      <c r="J24" s="12" t="n">
-        <v>125000</v>
-      </c>
-      <c r="K24" s="12" t="n">
-        <v>67000</v>
-      </c>
-      <c r="L24" s="12" t="n">
-        <v>385000</v>
-      </c>
-      <c r="M24" s="12" t="n">
-        <v>43000</v>
-      </c>
-      <c r="N24" s="12" t="n">
-        <v>29000</v>
-      </c>
-      <c r="O24" s="12" t="n">
-        <v>85000</v>
-      </c>
+      <c r="I24" s="12" t="n"/>
+      <c r="J24" s="12" t="n"/>
+      <c r="K24" s="12" t="n"/>
+      <c r="L24" s="12" t="n"/>
+      <c r="M24" s="12" t="n"/>
+      <c r="N24" s="12" t="n"/>
+      <c r="O24" s="12" t="n"/>
       <c r="P24" s="13">
         <f>I24+J24+K24+L24+M24+N24+O24</f>
         <v/>
@@ -2588,27 +2322,13 @@
         <f>D25+E25+F25+G25</f>
         <v/>
       </c>
-      <c r="I25" s="12" t="n">
-        <v>430000</v>
-      </c>
-      <c r="J25" s="12" t="n">
-        <v>125000</v>
-      </c>
-      <c r="K25" s="12" t="n">
-        <v>67000</v>
-      </c>
-      <c r="L25" s="12" t="n">
-        <v>385000</v>
-      </c>
-      <c r="M25" s="12" t="n">
-        <v>43000</v>
-      </c>
-      <c r="N25" s="12" t="n">
-        <v>29000</v>
-      </c>
-      <c r="O25" s="12" t="n">
-        <v>85000</v>
-      </c>
+      <c r="I25" s="12" t="n"/>
+      <c r="J25" s="12" t="n"/>
+      <c r="K25" s="12" t="n"/>
+      <c r="L25" s="12" t="n"/>
+      <c r="M25" s="12" t="n"/>
+      <c r="N25" s="12" t="n"/>
+      <c r="O25" s="12" t="n"/>
       <c r="P25" s="13">
         <f>I25+J25+K25+L25+M25+N25+O25</f>
         <v/>
@@ -2666,27 +2386,13 @@
         <f>D26+E26+F26+G26</f>
         <v/>
       </c>
-      <c r="I26" s="12" t="n">
-        <v>430000</v>
-      </c>
-      <c r="J26" s="12" t="n">
-        <v>125000</v>
-      </c>
-      <c r="K26" s="12" t="n">
-        <v>67000</v>
-      </c>
-      <c r="L26" s="12" t="n">
-        <v>385000</v>
-      </c>
-      <c r="M26" s="12" t="n">
-        <v>43000</v>
-      </c>
-      <c r="N26" s="12" t="n">
-        <v>29000</v>
-      </c>
-      <c r="O26" s="12" t="n">
-        <v>85000</v>
-      </c>
+      <c r="I26" s="12" t="n"/>
+      <c r="J26" s="12" t="n"/>
+      <c r="K26" s="12" t="n"/>
+      <c r="L26" s="12" t="n"/>
+      <c r="M26" s="12" t="n"/>
+      <c r="N26" s="12" t="n"/>
+      <c r="O26" s="12" t="n"/>
       <c r="P26" s="13">
         <f>I26+J26+K26+L26+M26+N26+O26</f>
         <v/>
@@ -2744,27 +2450,13 @@
         <f>D27+E27+F27+G27</f>
         <v/>
       </c>
-      <c r="I27" s="12" t="n">
-        <v>430000</v>
-      </c>
-      <c r="J27" s="12" t="n">
-        <v>125000</v>
-      </c>
-      <c r="K27" s="12" t="n">
-        <v>67000</v>
-      </c>
-      <c r="L27" s="12" t="n">
-        <v>385000</v>
-      </c>
-      <c r="M27" s="12" t="n">
-        <v>43000</v>
-      </c>
-      <c r="N27" s="12" t="n">
-        <v>29000</v>
-      </c>
-      <c r="O27" s="12" t="n">
-        <v>85000</v>
-      </c>
+      <c r="I27" s="12" t="n"/>
+      <c r="J27" s="12" t="n"/>
+      <c r="K27" s="12" t="n"/>
+      <c r="L27" s="12" t="n"/>
+      <c r="M27" s="12" t="n"/>
+      <c r="N27" s="12" t="n"/>
+      <c r="O27" s="12" t="n"/>
       <c r="P27" s="13">
         <f>I27+J27+K27+L27+M27+N27+O27</f>
         <v/>
@@ -2822,27 +2514,13 @@
         <f>D28+E28+F28+G28</f>
         <v/>
       </c>
-      <c r="I28" s="12" t="n">
-        <v>430000</v>
-      </c>
-      <c r="J28" s="12" t="n">
-        <v>125000</v>
-      </c>
-      <c r="K28" s="12" t="n">
-        <v>67000</v>
-      </c>
-      <c r="L28" s="12" t="n">
-        <v>385000</v>
-      </c>
-      <c r="M28" s="12" t="n">
-        <v>43000</v>
-      </c>
-      <c r="N28" s="12" t="n">
-        <v>29000</v>
-      </c>
-      <c r="O28" s="12" t="n">
-        <v>85000</v>
-      </c>
+      <c r="I28" s="12" t="n"/>
+      <c r="J28" s="12" t="n"/>
+      <c r="K28" s="12" t="n"/>
+      <c r="L28" s="12" t="n"/>
+      <c r="M28" s="12" t="n"/>
+      <c r="N28" s="12" t="n"/>
+      <c r="O28" s="12" t="n"/>
       <c r="P28" s="13">
         <f>I28+J28+K28+L28+M28+N28+O28</f>
         <v/>
@@ -2900,27 +2578,13 @@
         <f>D29+E29+F29+G29</f>
         <v/>
       </c>
-      <c r="I29" s="12" t="n">
-        <v>430000</v>
-      </c>
-      <c r="J29" s="12" t="n">
-        <v>125000</v>
-      </c>
-      <c r="K29" s="12" t="n">
-        <v>67000</v>
-      </c>
-      <c r="L29" s="12" t="n">
-        <v>385000</v>
-      </c>
-      <c r="M29" s="12" t="n">
-        <v>43000</v>
-      </c>
-      <c r="N29" s="12" t="n">
-        <v>29000</v>
-      </c>
-      <c r="O29" s="12" t="n">
-        <v>85000</v>
-      </c>
+      <c r="I29" s="12" t="n"/>
+      <c r="J29" s="12" t="n"/>
+      <c r="K29" s="12" t="n"/>
+      <c r="L29" s="12" t="n"/>
+      <c r="M29" s="12" t="n"/>
+      <c r="N29" s="12" t="n"/>
+      <c r="O29" s="12" t="n"/>
       <c r="P29" s="13">
         <f>I29+J29+K29+L29+M29+N29+O29</f>
         <v/>
@@ -2978,27 +2642,13 @@
         <f>D30+E30+F30+G30</f>
         <v/>
       </c>
-      <c r="I30" s="12" t="n">
-        <v>430000</v>
-      </c>
-      <c r="J30" s="12" t="n">
-        <v>125000</v>
-      </c>
-      <c r="K30" s="12" t="n">
-        <v>67000</v>
-      </c>
-      <c r="L30" s="12" t="n">
-        <v>385000</v>
-      </c>
-      <c r="M30" s="12" t="n">
-        <v>43000</v>
-      </c>
-      <c r="N30" s="12" t="n">
-        <v>29000</v>
-      </c>
-      <c r="O30" s="12" t="n">
-        <v>85000</v>
-      </c>
+      <c r="I30" s="12" t="n"/>
+      <c r="J30" s="12" t="n"/>
+      <c r="K30" s="12" t="n"/>
+      <c r="L30" s="12" t="n"/>
+      <c r="M30" s="12" t="n"/>
+      <c r="N30" s="12" t="n"/>
+      <c r="O30" s="12" t="n"/>
       <c r="P30" s="13">
         <f>I30+J30+K30+L30+M30+N30+O30</f>
         <v/>
@@ -3056,27 +2706,13 @@
         <f>D31+E31+F31+G31</f>
         <v/>
       </c>
-      <c r="I31" s="12" t="n">
-        <v>430000</v>
-      </c>
-      <c r="J31" s="12" t="n">
-        <v>125000</v>
-      </c>
-      <c r="K31" s="12" t="n">
-        <v>67000</v>
-      </c>
-      <c r="L31" s="12" t="n">
-        <v>385000</v>
-      </c>
-      <c r="M31" s="12" t="n">
-        <v>43000</v>
-      </c>
-      <c r="N31" s="12" t="n">
-        <v>29000</v>
-      </c>
-      <c r="O31" s="12" t="n">
-        <v>85000</v>
-      </c>
+      <c r="I31" s="12" t="n"/>
+      <c r="J31" s="12" t="n"/>
+      <c r="K31" s="12" t="n"/>
+      <c r="L31" s="12" t="n"/>
+      <c r="M31" s="12" t="n"/>
+      <c r="N31" s="12" t="n"/>
+      <c r="O31" s="12" t="n"/>
       <c r="P31" s="13">
         <f>I31+J31+K31+L31+M31+N31+O31</f>
         <v/>
@@ -3134,27 +2770,13 @@
         <f>D32+E32+F32+G32</f>
         <v/>
       </c>
-      <c r="I32" s="12" t="n">
-        <v>430000</v>
-      </c>
-      <c r="J32" s="12" t="n">
-        <v>125000</v>
-      </c>
-      <c r="K32" s="12" t="n">
-        <v>67000</v>
-      </c>
-      <c r="L32" s="12" t="n">
-        <v>385000</v>
-      </c>
-      <c r="M32" s="12" t="n">
-        <v>43000</v>
-      </c>
-      <c r="N32" s="12" t="n">
-        <v>29000</v>
-      </c>
-      <c r="O32" s="12" t="n">
-        <v>85000</v>
-      </c>
+      <c r="I32" s="12" t="n"/>
+      <c r="J32" s="12" t="n"/>
+      <c r="K32" s="12" t="n"/>
+      <c r="L32" s="12" t="n"/>
+      <c r="M32" s="12" t="n"/>
+      <c r="N32" s="12" t="n"/>
+      <c r="O32" s="12" t="n"/>
       <c r="P32" s="13">
         <f>I32+J32+K32+L32+M32+N32+O32</f>
         <v/>
@@ -3212,27 +2834,13 @@
         <f>D33+E33+F33+G33</f>
         <v/>
       </c>
-      <c r="I33" s="12" t="n">
-        <v>430000</v>
-      </c>
-      <c r="J33" s="12" t="n">
-        <v>125000</v>
-      </c>
-      <c r="K33" s="12" t="n">
-        <v>67000</v>
-      </c>
-      <c r="L33" s="12" t="n">
-        <v>385000</v>
-      </c>
-      <c r="M33" s="12" t="n">
-        <v>43000</v>
-      </c>
-      <c r="N33" s="12" t="n">
-        <v>29000</v>
-      </c>
-      <c r="O33" s="12" t="n">
-        <v>85000</v>
-      </c>
+      <c r="I33" s="12" t="n"/>
+      <c r="J33" s="12" t="n"/>
+      <c r="K33" s="12" t="n"/>
+      <c r="L33" s="12" t="n"/>
+      <c r="M33" s="12" t="n"/>
+      <c r="N33" s="12" t="n"/>
+      <c r="O33" s="12" t="n"/>
       <c r="P33" s="13">
         <f>I33+J33+K33+L33+M33+N33+O33</f>
         <v/>
@@ -3290,27 +2898,13 @@
         <f>D34+E34+F34+G34</f>
         <v/>
       </c>
-      <c r="I34" s="12" t="n">
-        <v>430000</v>
-      </c>
-      <c r="J34" s="12" t="n">
-        <v>125000</v>
-      </c>
-      <c r="K34" s="12" t="n">
-        <v>67000</v>
-      </c>
-      <c r="L34" s="12" t="n">
-        <v>385000</v>
-      </c>
-      <c r="M34" s="12" t="n">
-        <v>43000</v>
-      </c>
-      <c r="N34" s="12" t="n">
-        <v>29000</v>
-      </c>
-      <c r="O34" s="12" t="n">
-        <v>85000</v>
-      </c>
+      <c r="I34" s="12" t="n"/>
+      <c r="J34" s="12" t="n"/>
+      <c r="K34" s="12" t="n"/>
+      <c r="L34" s="12" t="n"/>
+      <c r="M34" s="12" t="n"/>
+      <c r="N34" s="12" t="n"/>
+      <c r="O34" s="12" t="n"/>
       <c r="P34" s="13">
         <f>I34+J34+K34+L34+M34+N34+O34</f>
         <v/>
@@ -3368,27 +2962,13 @@
         <f>D35+E35+F35+G35</f>
         <v/>
       </c>
-      <c r="I35" s="12" t="n">
-        <v>430000</v>
-      </c>
-      <c r="J35" s="12" t="n">
-        <v>125000</v>
-      </c>
-      <c r="K35" s="12" t="n">
-        <v>67000</v>
-      </c>
-      <c r="L35" s="12" t="n">
-        <v>385000</v>
-      </c>
-      <c r="M35" s="12" t="n">
-        <v>43000</v>
-      </c>
-      <c r="N35" s="12" t="n">
-        <v>29000</v>
-      </c>
-      <c r="O35" s="12" t="n">
-        <v>85000</v>
-      </c>
+      <c r="I35" s="12" t="n"/>
+      <c r="J35" s="12" t="n"/>
+      <c r="K35" s="12" t="n"/>
+      <c r="L35" s="12" t="n"/>
+      <c r="M35" s="12" t="n"/>
+      <c r="N35" s="12" t="n"/>
+      <c r="O35" s="12" t="n"/>
       <c r="P35" s="13">
         <f>I35+J35+K35+L35+M35+N35+O35</f>
         <v/>
@@ -3446,27 +3026,13 @@
         <f>D36+E36+F36+G36</f>
         <v/>
       </c>
-      <c r="I36" s="12" t="n">
-        <v>430000</v>
-      </c>
-      <c r="J36" s="12" t="n">
-        <v>125000</v>
-      </c>
-      <c r="K36" s="12" t="n">
-        <v>67000</v>
-      </c>
-      <c r="L36" s="12" t="n">
-        <v>385000</v>
-      </c>
-      <c r="M36" s="12" t="n">
-        <v>43000</v>
-      </c>
-      <c r="N36" s="12" t="n">
-        <v>29000</v>
-      </c>
-      <c r="O36" s="12" t="n">
-        <v>85000</v>
-      </c>
+      <c r="I36" s="12" t="n"/>
+      <c r="J36" s="12" t="n"/>
+      <c r="K36" s="12" t="n"/>
+      <c r="L36" s="12" t="n"/>
+      <c r="M36" s="12" t="n"/>
+      <c r="N36" s="12" t="n"/>
+      <c r="O36" s="12" t="n"/>
       <c r="P36" s="13">
         <f>I36+J36+K36+L36+M36+N36+O36</f>
         <v/>
@@ -3524,27 +3090,13 @@
         <f>D37+E37+F37+G37</f>
         <v/>
       </c>
-      <c r="I37" s="12" t="n">
-        <v>430000</v>
-      </c>
-      <c r="J37" s="12" t="n">
-        <v>125000</v>
-      </c>
-      <c r="K37" s="12" t="n">
-        <v>67000</v>
-      </c>
-      <c r="L37" s="12" t="n">
-        <v>385000</v>
-      </c>
-      <c r="M37" s="12" t="n">
-        <v>43000</v>
-      </c>
-      <c r="N37" s="12" t="n">
-        <v>29000</v>
-      </c>
-      <c r="O37" s="12" t="n">
-        <v>85000</v>
-      </c>
+      <c r="I37" s="12" t="n"/>
+      <c r="J37" s="12" t="n"/>
+      <c r="K37" s="12" t="n"/>
+      <c r="L37" s="12" t="n"/>
+      <c r="M37" s="12" t="n"/>
+      <c r="N37" s="12" t="n"/>
+      <c r="O37" s="12" t="n"/>
       <c r="P37" s="13">
         <f>I37+J37+K37+L37+M37+N37+O37</f>
         <v/>
@@ -3602,27 +3154,13 @@
         <f>D38+E38+F38+G38</f>
         <v/>
       </c>
-      <c r="I38" s="12" t="n">
-        <v>430000</v>
-      </c>
-      <c r="J38" s="12" t="n">
-        <v>125000</v>
-      </c>
-      <c r="K38" s="12" t="n">
-        <v>67000</v>
-      </c>
-      <c r="L38" s="12" t="n">
-        <v>385000</v>
-      </c>
-      <c r="M38" s="12" t="n">
-        <v>43000</v>
-      </c>
-      <c r="N38" s="12" t="n">
-        <v>29000</v>
-      </c>
-      <c r="O38" s="12" t="n">
-        <v>85000</v>
-      </c>
+      <c r="I38" s="12" t="n"/>
+      <c r="J38" s="12" t="n"/>
+      <c r="K38" s="12" t="n"/>
+      <c r="L38" s="12" t="n"/>
+      <c r="M38" s="12" t="n"/>
+      <c r="N38" s="12" t="n"/>
+      <c r="O38" s="12" t="n"/>
       <c r="P38" s="13">
         <f>I38+J38+K38+L38+M38+N38+O38</f>
         <v/>
@@ -3680,27 +3218,13 @@
         <f>D39+E39+F39+G39</f>
         <v/>
       </c>
-      <c r="I39" s="12" t="n">
-        <v>430000</v>
-      </c>
-      <c r="J39" s="12" t="n">
-        <v>125000</v>
-      </c>
-      <c r="K39" s="12" t="n">
-        <v>67000</v>
-      </c>
-      <c r="L39" s="12" t="n">
-        <v>385000</v>
-      </c>
-      <c r="M39" s="12" t="n">
-        <v>43000</v>
-      </c>
-      <c r="N39" s="12" t="n">
-        <v>29000</v>
-      </c>
-      <c r="O39" s="12" t="n">
-        <v>85000</v>
-      </c>
+      <c r="I39" s="12" t="n"/>
+      <c r="J39" s="12" t="n"/>
+      <c r="K39" s="12" t="n"/>
+      <c r="L39" s="12" t="n"/>
+      <c r="M39" s="12" t="n"/>
+      <c r="N39" s="12" t="n"/>
+      <c r="O39" s="12" t="n"/>
       <c r="P39" s="13">
         <f>I39+J39+K39+L39+M39+N39+O39</f>
         <v/>
@@ -3780,27 +3304,13 @@
         <f>D41+E41+F41+G41</f>
         <v/>
       </c>
-      <c r="I41" s="12" t="n">
-        <v>1360000</v>
-      </c>
-      <c r="J41" s="12" t="n">
-        <v>490000</v>
-      </c>
-      <c r="K41" s="12" t="n">
-        <v>220000</v>
-      </c>
-      <c r="L41" s="12" t="n">
-        <v>1180000</v>
-      </c>
-      <c r="M41" s="12" t="n">
-        <v>165000</v>
-      </c>
-      <c r="N41" s="12" t="n">
-        <v>84000</v>
-      </c>
-      <c r="O41" s="12" t="n">
-        <v>210000</v>
-      </c>
+      <c r="I41" s="12" t="n"/>
+      <c r="J41" s="12" t="n"/>
+      <c r="K41" s="12" t="n"/>
+      <c r="L41" s="12" t="n"/>
+      <c r="M41" s="12" t="n"/>
+      <c r="N41" s="12" t="n"/>
+      <c r="O41" s="12" t="n"/>
       <c r="P41" s="13">
         <f>I41+J41+K41+L41+M41+N41+O41</f>
         <v/>
@@ -3859,27 +3369,13 @@
         <f>D42+E42+F42+G42</f>
         <v/>
       </c>
-      <c r="I42" s="12" t="n">
-        <v>1360000</v>
-      </c>
-      <c r="J42" s="12" t="n">
-        <v>490000</v>
-      </c>
-      <c r="K42" s="12" t="n">
-        <v>220000</v>
-      </c>
-      <c r="L42" s="12" t="n">
-        <v>1180000</v>
-      </c>
-      <c r="M42" s="12" t="n">
-        <v>165000</v>
-      </c>
-      <c r="N42" s="12" t="n">
-        <v>84000</v>
-      </c>
-      <c r="O42" s="12" t="n">
-        <v>210000</v>
-      </c>
+      <c r="I42" s="12" t="n"/>
+      <c r="J42" s="12" t="n"/>
+      <c r="K42" s="12" t="n"/>
+      <c r="L42" s="12" t="n"/>
+      <c r="M42" s="12" t="n"/>
+      <c r="N42" s="12" t="n"/>
+      <c r="O42" s="12" t="n"/>
       <c r="P42" s="13">
         <f>I42+J42+K42+L42+M42+N42+O42</f>
         <v/>
@@ -3937,27 +3433,13 @@
         <f>D43+E43+F43+G43</f>
         <v/>
       </c>
-      <c r="I43" s="12" t="n">
-        <v>1360000</v>
-      </c>
-      <c r="J43" s="12" t="n">
-        <v>490000</v>
-      </c>
-      <c r="K43" s="12" t="n">
-        <v>220000</v>
-      </c>
-      <c r="L43" s="12" t="n">
-        <v>1180000</v>
-      </c>
-      <c r="M43" s="12" t="n">
-        <v>165000</v>
-      </c>
-      <c r="N43" s="12" t="n">
-        <v>84000</v>
-      </c>
-      <c r="O43" s="12" t="n">
-        <v>210000</v>
-      </c>
+      <c r="I43" s="12" t="n"/>
+      <c r="J43" s="12" t="n"/>
+      <c r="K43" s="12" t="n"/>
+      <c r="L43" s="12" t="n"/>
+      <c r="M43" s="12" t="n"/>
+      <c r="N43" s="12" t="n"/>
+      <c r="O43" s="12" t="n"/>
       <c r="P43" s="13">
         <f>I43+J43+K43+L43+M43+N43+O43</f>
         <v/>
@@ -4015,27 +3497,13 @@
         <f>D44+E44+F44+G44</f>
         <v/>
       </c>
-      <c r="I44" s="12" t="n">
-        <v>1360000</v>
-      </c>
-      <c r="J44" s="12" t="n">
-        <v>490000</v>
-      </c>
-      <c r="K44" s="12" t="n">
-        <v>220000</v>
-      </c>
-      <c r="L44" s="12" t="n">
-        <v>1180000</v>
-      </c>
-      <c r="M44" s="12" t="n">
-        <v>165000</v>
-      </c>
-      <c r="N44" s="12" t="n">
-        <v>84000</v>
-      </c>
-      <c r="O44" s="12" t="n">
-        <v>210000</v>
-      </c>
+      <c r="I44" s="12" t="n"/>
+      <c r="J44" s="12" t="n"/>
+      <c r="K44" s="12" t="n"/>
+      <c r="L44" s="12" t="n"/>
+      <c r="M44" s="12" t="n"/>
+      <c r="N44" s="12" t="n"/>
+      <c r="O44" s="12" t="n"/>
       <c r="P44" s="13">
         <f>I44+J44+K44+L44+M44+N44+O44</f>
         <v/>
@@ -4093,27 +3561,13 @@
         <f>D45+E45+F45+G45</f>
         <v/>
       </c>
-      <c r="I45" s="12" t="n">
-        <v>1360000</v>
-      </c>
-      <c r="J45" s="12" t="n">
-        <v>490000</v>
-      </c>
-      <c r="K45" s="12" t="n">
-        <v>220000</v>
-      </c>
-      <c r="L45" s="12" t="n">
-        <v>1180000</v>
-      </c>
-      <c r="M45" s="12" t="n">
-        <v>165000</v>
-      </c>
-      <c r="N45" s="12" t="n">
-        <v>84000</v>
-      </c>
-      <c r="O45" s="12" t="n">
-        <v>210000</v>
-      </c>
+      <c r="I45" s="12" t="n"/>
+      <c r="J45" s="12" t="n"/>
+      <c r="K45" s="12" t="n"/>
+      <c r="L45" s="12" t="n"/>
+      <c r="M45" s="12" t="n"/>
+      <c r="N45" s="12" t="n"/>
+      <c r="O45" s="12" t="n"/>
       <c r="P45" s="13">
         <f>I45+J45+K45+L45+M45+N45+O45</f>
         <v/>
@@ -4171,27 +3625,13 @@
         <f>D46+E46+F46+G46</f>
         <v/>
       </c>
-      <c r="I46" s="12" t="n">
-        <v>1360000</v>
-      </c>
-      <c r="J46" s="12" t="n">
-        <v>490000</v>
-      </c>
-      <c r="K46" s="12" t="n">
-        <v>220000</v>
-      </c>
-      <c r="L46" s="12" t="n">
-        <v>1180000</v>
-      </c>
-      <c r="M46" s="12" t="n">
-        <v>165000</v>
-      </c>
-      <c r="N46" s="12" t="n">
-        <v>84000</v>
-      </c>
-      <c r="O46" s="12" t="n">
-        <v>210000</v>
-      </c>
+      <c r="I46" s="12" t="n"/>
+      <c r="J46" s="12" t="n"/>
+      <c r="K46" s="12" t="n"/>
+      <c r="L46" s="12" t="n"/>
+      <c r="M46" s="12" t="n"/>
+      <c r="N46" s="12" t="n"/>
+      <c r="O46" s="12" t="n"/>
       <c r="P46" s="13">
         <f>I46+J46+K46+L46+M46+N46+O46</f>
         <v/>
@@ -4249,27 +3689,13 @@
         <f>D47+E47+F47+G47</f>
         <v/>
       </c>
-      <c r="I47" s="12" t="n">
-        <v>1360000</v>
-      </c>
-      <c r="J47" s="12" t="n">
-        <v>490000</v>
-      </c>
-      <c r="K47" s="12" t="n">
-        <v>220000</v>
-      </c>
-      <c r="L47" s="12" t="n">
-        <v>1180000</v>
-      </c>
-      <c r="M47" s="12" t="n">
-        <v>165000</v>
-      </c>
-      <c r="N47" s="12" t="n">
-        <v>84000</v>
-      </c>
-      <c r="O47" s="12" t="n">
-        <v>210000</v>
-      </c>
+      <c r="I47" s="12" t="n"/>
+      <c r="J47" s="12" t="n"/>
+      <c r="K47" s="12" t="n"/>
+      <c r="L47" s="12" t="n"/>
+      <c r="M47" s="12" t="n"/>
+      <c r="N47" s="12" t="n"/>
+      <c r="O47" s="12" t="n"/>
       <c r="P47" s="13">
         <f>I47+J47+K47+L47+M47+N47+O47</f>
         <v/>
@@ -4327,27 +3753,13 @@
         <f>D48+E48+F48+G48</f>
         <v/>
       </c>
-      <c r="I48" s="12" t="n">
-        <v>1360000</v>
-      </c>
-      <c r="J48" s="12" t="n">
-        <v>490000</v>
-      </c>
-      <c r="K48" s="12" t="n">
-        <v>220000</v>
-      </c>
-      <c r="L48" s="12" t="n">
-        <v>1180000</v>
-      </c>
-      <c r="M48" s="12" t="n">
-        <v>165000</v>
-      </c>
-      <c r="N48" s="12" t="n">
-        <v>84000</v>
-      </c>
-      <c r="O48" s="12" t="n">
-        <v>210000</v>
-      </c>
+      <c r="I48" s="12" t="n"/>
+      <c r="J48" s="12" t="n"/>
+      <c r="K48" s="12" t="n"/>
+      <c r="L48" s="12" t="n"/>
+      <c r="M48" s="12" t="n"/>
+      <c r="N48" s="12" t="n"/>
+      <c r="O48" s="12" t="n"/>
       <c r="P48" s="13">
         <f>I48+J48+K48+L48+M48+N48+O48</f>
         <v/>
@@ -4405,27 +3817,13 @@
         <f>D49+E49+F49+G49</f>
         <v/>
       </c>
-      <c r="I49" s="12" t="n">
-        <v>1360000</v>
-      </c>
-      <c r="J49" s="12" t="n">
-        <v>490000</v>
-      </c>
-      <c r="K49" s="12" t="n">
-        <v>220000</v>
-      </c>
-      <c r="L49" s="12" t="n">
-        <v>1180000</v>
-      </c>
-      <c r="M49" s="12" t="n">
-        <v>165000</v>
-      </c>
-      <c r="N49" s="12" t="n">
-        <v>84000</v>
-      </c>
-      <c r="O49" s="12" t="n">
-        <v>210000</v>
-      </c>
+      <c r="I49" s="12" t="n"/>
+      <c r="J49" s="12" t="n"/>
+      <c r="K49" s="12" t="n"/>
+      <c r="L49" s="12" t="n"/>
+      <c r="M49" s="12" t="n"/>
+      <c r="N49" s="12" t="n"/>
+      <c r="O49" s="12" t="n"/>
       <c r="P49" s="13">
         <f>I49+J49+K49+L49+M49+N49+O49</f>
         <v/>
@@ -4483,27 +3881,13 @@
         <f>D50+E50+F50+G50</f>
         <v/>
       </c>
-      <c r="I50" s="12" t="n">
-        <v>1360000</v>
-      </c>
-      <c r="J50" s="12" t="n">
-        <v>490000</v>
-      </c>
-      <c r="K50" s="12" t="n">
-        <v>220000</v>
-      </c>
-      <c r="L50" s="12" t="n">
-        <v>1180000</v>
-      </c>
-      <c r="M50" s="12" t="n">
-        <v>165000</v>
-      </c>
-      <c r="N50" s="12" t="n">
-        <v>84000</v>
-      </c>
-      <c r="O50" s="12" t="n">
-        <v>210000</v>
-      </c>
+      <c r="I50" s="12" t="n"/>
+      <c r="J50" s="12" t="n"/>
+      <c r="K50" s="12" t="n"/>
+      <c r="L50" s="12" t="n"/>
+      <c r="M50" s="12" t="n"/>
+      <c r="N50" s="12" t="n"/>
+      <c r="O50" s="12" t="n"/>
       <c r="P50" s="13">
         <f>I50+J50+K50+L50+M50+N50+O50</f>
         <v/>
@@ -4561,27 +3945,13 @@
         <f>D51+E51+F51+G51</f>
         <v/>
       </c>
-      <c r="I51" s="12" t="n">
-        <v>1360000</v>
-      </c>
-      <c r="J51" s="12" t="n">
-        <v>490000</v>
-      </c>
-      <c r="K51" s="12" t="n">
-        <v>220000</v>
-      </c>
-      <c r="L51" s="12" t="n">
-        <v>1180000</v>
-      </c>
-      <c r="M51" s="12" t="n">
-        <v>165000</v>
-      </c>
-      <c r="N51" s="12" t="n">
-        <v>84000</v>
-      </c>
-      <c r="O51" s="12" t="n">
-        <v>210000</v>
-      </c>
+      <c r="I51" s="12" t="n"/>
+      <c r="J51" s="12" t="n"/>
+      <c r="K51" s="12" t="n"/>
+      <c r="L51" s="12" t="n"/>
+      <c r="M51" s="12" t="n"/>
+      <c r="N51" s="12" t="n"/>
+      <c r="O51" s="12" t="n"/>
       <c r="P51" s="13">
         <f>I51+J51+K51+L51+M51+N51+O51</f>
         <v/>
@@ -4639,27 +4009,13 @@
         <f>D52+E52+F52+G52</f>
         <v/>
       </c>
-      <c r="I52" s="12" t="n">
-        <v>1360000</v>
-      </c>
-      <c r="J52" s="12" t="n">
-        <v>490000</v>
-      </c>
-      <c r="K52" s="12" t="n">
-        <v>220000</v>
-      </c>
-      <c r="L52" s="12" t="n">
-        <v>1180000</v>
-      </c>
-      <c r="M52" s="12" t="n">
-        <v>165000</v>
-      </c>
-      <c r="N52" s="12" t="n">
-        <v>84000</v>
-      </c>
-      <c r="O52" s="12" t="n">
-        <v>210000</v>
-      </c>
+      <c r="I52" s="12" t="n"/>
+      <c r="J52" s="12" t="n"/>
+      <c r="K52" s="12" t="n"/>
+      <c r="L52" s="12" t="n"/>
+      <c r="M52" s="12" t="n"/>
+      <c r="N52" s="12" t="n"/>
+      <c r="O52" s="12" t="n"/>
       <c r="P52" s="13">
         <f>I52+J52+K52+L52+M52+N52+O52</f>
         <v/>
@@ -4717,27 +4073,13 @@
         <f>D53+E53+F53+G53</f>
         <v/>
       </c>
-      <c r="I53" s="12" t="n">
-        <v>1360000</v>
-      </c>
-      <c r="J53" s="12" t="n">
-        <v>490000</v>
-      </c>
-      <c r="K53" s="12" t="n">
-        <v>220000</v>
-      </c>
-      <c r="L53" s="12" t="n">
-        <v>1180000</v>
-      </c>
-      <c r="M53" s="12" t="n">
-        <v>165000</v>
-      </c>
-      <c r="N53" s="12" t="n">
-        <v>84000</v>
-      </c>
-      <c r="O53" s="12" t="n">
-        <v>210000</v>
-      </c>
+      <c r="I53" s="12" t="n"/>
+      <c r="J53" s="12" t="n"/>
+      <c r="K53" s="12" t="n"/>
+      <c r="L53" s="12" t="n"/>
+      <c r="M53" s="12" t="n"/>
+      <c r="N53" s="12" t="n"/>
+      <c r="O53" s="12" t="n"/>
       <c r="P53" s="13">
         <f>I53+J53+K53+L53+M53+N53+O53</f>
         <v/>
@@ -4795,27 +4137,13 @@
         <f>D54+E54+F54+G54</f>
         <v/>
       </c>
-      <c r="I54" s="12" t="n">
-        <v>1360000</v>
-      </c>
-      <c r="J54" s="12" t="n">
-        <v>490000</v>
-      </c>
-      <c r="K54" s="12" t="n">
-        <v>220000</v>
-      </c>
-      <c r="L54" s="12" t="n">
-        <v>1180000</v>
-      </c>
-      <c r="M54" s="12" t="n">
-        <v>165000</v>
-      </c>
-      <c r="N54" s="12" t="n">
-        <v>84000</v>
-      </c>
-      <c r="O54" s="12" t="n">
-        <v>210000</v>
-      </c>
+      <c r="I54" s="12" t="n"/>
+      <c r="J54" s="12" t="n"/>
+      <c r="K54" s="12" t="n"/>
+      <c r="L54" s="12" t="n"/>
+      <c r="M54" s="12" t="n"/>
+      <c r="N54" s="12" t="n"/>
+      <c r="O54" s="12" t="n"/>
       <c r="P54" s="13">
         <f>I54+J54+K54+L54+M54+N54+O54</f>
         <v/>
@@ -4873,27 +4201,13 @@
         <f>D55+E55+F55+G55</f>
         <v/>
       </c>
-      <c r="I55" s="12" t="n">
-        <v>1360000</v>
-      </c>
-      <c r="J55" s="12" t="n">
-        <v>490000</v>
-      </c>
-      <c r="K55" s="12" t="n">
-        <v>220000</v>
-      </c>
-      <c r="L55" s="12" t="n">
-        <v>1180000</v>
-      </c>
-      <c r="M55" s="12" t="n">
-        <v>165000</v>
-      </c>
-      <c r="N55" s="12" t="n">
-        <v>84000</v>
-      </c>
-      <c r="O55" s="12" t="n">
-        <v>210000</v>
-      </c>
+      <c r="I55" s="12" t="n"/>
+      <c r="J55" s="12" t="n"/>
+      <c r="K55" s="12" t="n"/>
+      <c r="L55" s="12" t="n"/>
+      <c r="M55" s="12" t="n"/>
+      <c r="N55" s="12" t="n"/>
+      <c r="O55" s="12" t="n"/>
       <c r="P55" s="13">
         <f>I55+J55+K55+L55+M55+N55+O55</f>
         <v/>
@@ -4951,27 +4265,13 @@
         <f>D56+E56+F56+G56</f>
         <v/>
       </c>
-      <c r="I56" s="12" t="n">
-        <v>1360000</v>
-      </c>
-      <c r="J56" s="12" t="n">
-        <v>490000</v>
-      </c>
-      <c r="K56" s="12" t="n">
-        <v>220000</v>
-      </c>
-      <c r="L56" s="12" t="n">
-        <v>1180000</v>
-      </c>
-      <c r="M56" s="12" t="n">
-        <v>165000</v>
-      </c>
-      <c r="N56" s="12" t="n">
-        <v>84000</v>
-      </c>
-      <c r="O56" s="12" t="n">
-        <v>210000</v>
-      </c>
+      <c r="I56" s="12" t="n"/>
+      <c r="J56" s="12" t="n"/>
+      <c r="K56" s="12" t="n"/>
+      <c r="L56" s="12" t="n"/>
+      <c r="M56" s="12" t="n"/>
+      <c r="N56" s="12" t="n"/>
+      <c r="O56" s="12" t="n"/>
       <c r="P56" s="13">
         <f>I56+J56+K56+L56+M56+N56+O56</f>
         <v/>
@@ -5029,27 +4329,13 @@
         <f>D57+E57+F57+G57</f>
         <v/>
       </c>
-      <c r="I57" s="12" t="n">
-        <v>1360000</v>
-      </c>
-      <c r="J57" s="12" t="n">
-        <v>490000</v>
-      </c>
-      <c r="K57" s="12" t="n">
-        <v>220000</v>
-      </c>
-      <c r="L57" s="12" t="n">
-        <v>1180000</v>
-      </c>
-      <c r="M57" s="12" t="n">
-        <v>165000</v>
-      </c>
-      <c r="N57" s="12" t="n">
-        <v>84000</v>
-      </c>
-      <c r="O57" s="12" t="n">
-        <v>210000</v>
-      </c>
+      <c r="I57" s="12" t="n"/>
+      <c r="J57" s="12" t="n"/>
+      <c r="K57" s="12" t="n"/>
+      <c r="L57" s="12" t="n"/>
+      <c r="M57" s="12" t="n"/>
+      <c r="N57" s="12" t="n"/>
+      <c r="O57" s="12" t="n"/>
       <c r="P57" s="13">
         <f>I57+J57+K57+L57+M57+N57+O57</f>
         <v/>

--- a/sacure_採算管理_v4_ルート別案件別.xlsx
+++ b/sacure_採算管理_v4_ルート別案件別.xlsx
@@ -11,6 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ルート別採算" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="▼売上原票" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="▼マッピング設定" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="▼従業員マスター" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -23,7 +24,7 @@
     <numFmt numFmtId="164" formatCode="0.0%"/>
     <numFmt numFmtId="165" formatCode="+0.0%;-0.0%;0.0%"/>
   </numFmts>
-  <fonts count="16">
+  <fonts count="21">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -115,8 +116,36 @@
       <b val="1"/>
       <sz val="13"/>
     </font>
+    <font>
+      <name val="Yu Gothic UI"/>
+      <b val="1"/>
+      <color rgb="000D2B5E"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <name val="Yu Gothic UI"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Yu Gothic UI"/>
+      <color rgb="000D2B5E"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Yu Gothic UI"/>
+      <b val="1"/>
+      <color rgb="0055657A"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Yu Gothic UI"/>
+      <color rgb="00C0392B"/>
+      <sz val="9"/>
+    </font>
   </fonts>
-  <fills count="24">
+  <fills count="31">
     <fill>
       <patternFill/>
     </fill>
@@ -233,6 +262,41 @@
         <fgColor rgb="00E0F2F1"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFE0E0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E65100"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFE0B2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="002E7D32"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="004A148C"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="0037474F"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FAFAFA"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -260,7 +324,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="71">
+  <cellXfs count="127">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -467,6 +531,156 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="15" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="16" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="15" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="7" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="18" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="7" fillId="18" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="8" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="17" fillId="25" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="26" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="26" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="26" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="26" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="25" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="8" fillId="25" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="25" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="17" fillId="27" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="27" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="8" fillId="27" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="27" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="17" fillId="28" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="28" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="8" fillId="28" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="28" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="17" fillId="29" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="30" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="30" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="30" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="30" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="29" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="8" fillId="29" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="29" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="16" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="19" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -19542,4 +19756,6899 @@
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="00795548"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I187"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="24" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="71" t="inlineStr">
+        <is>
+          <t>従業員マスター（R6.10 新体系基準）　※給与データ機密 取扱注意</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="16" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>出典：令和6年10月変更 新体系　│　月給制=合計欄の固定額　│　日当制・時給制は稼働日数に応じて変動（E列入力）</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="72" t="inlineStr">
+        <is>
+          <t>▼ 月間稼働日数（日当制・時給制の計算基準）</t>
+        </is>
+      </c>
+      <c r="D3" s="73" t="n">
+        <v>22</v>
+      </c>
+      <c r="E3" s="74" t="inlineStr">
+        <is>
+          <t>← ここを変更すると日当制・時給制の月額が自動更新されます（時給制は×8時間/日で計算）</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="6" customHeight="1"/>
+    <row r="5" ht="34" customHeight="1">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>所属</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>氏名</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>雇用区分</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>月額/日当/時給</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>月間稼働日数
+(入力可)</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>月額人件費
+(自動計算)</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>直間
+区分</t>
+        </is>
+      </c>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>備考</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t>参考:年間</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="20" customHeight="1">
+      <c r="A6" s="75" t="inlineStr">
+        <is>
+          <t>■ 本社</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="20" customHeight="1">
+      <c r="A7" s="76" t="inlineStr">
+        <is>
+          <t>本社</t>
+        </is>
+      </c>
+      <c r="B7" s="77" t="inlineStr">
+        <is>
+          <t>横井 哲也</t>
+        </is>
+      </c>
+      <c r="C7" s="78" t="inlineStr">
+        <is>
+          <t>月給</t>
+        </is>
+      </c>
+      <c r="D7" s="60" t="n">
+        <v>269545</v>
+      </c>
+      <c r="E7" s="79" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F7" s="32" t="n">
+        <v>269545</v>
+      </c>
+      <c r="G7" s="80" t="inlineStr">
+        <is>
+          <t>直接</t>
+        </is>
+      </c>
+      <c r="H7" s="81" t="inlineStr"/>
+      <c r="I7" s="82" t="n">
+        <v>3234540</v>
+      </c>
+    </row>
+    <row r="8" ht="20" customHeight="1">
+      <c r="A8" s="76" t="inlineStr">
+        <is>
+          <t>本社</t>
+        </is>
+      </c>
+      <c r="B8" s="77" t="inlineStr">
+        <is>
+          <t>上林 幸二</t>
+        </is>
+      </c>
+      <c r="C8" s="78" t="inlineStr">
+        <is>
+          <t>月給</t>
+        </is>
+      </c>
+      <c r="D8" s="60" t="n">
+        <v>254545</v>
+      </c>
+      <c r="E8" s="79" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F8" s="32" t="n">
+        <v>254545</v>
+      </c>
+      <c r="G8" s="80" t="inlineStr">
+        <is>
+          <t>直接</t>
+        </is>
+      </c>
+      <c r="H8" s="81" t="inlineStr"/>
+      <c r="I8" s="82" t="n">
+        <v>3054540</v>
+      </c>
+    </row>
+    <row r="9" ht="20" customHeight="1">
+      <c r="A9" s="76" t="inlineStr">
+        <is>
+          <t>本社</t>
+        </is>
+      </c>
+      <c r="B9" s="77" t="inlineStr">
+        <is>
+          <t>加藤 光裕</t>
+        </is>
+      </c>
+      <c r="C9" s="78" t="inlineStr">
+        <is>
+          <t>月給</t>
+        </is>
+      </c>
+      <c r="D9" s="60" t="n">
+        <v>283545</v>
+      </c>
+      <c r="E9" s="79" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F9" s="32" t="n">
+        <v>283545</v>
+      </c>
+      <c r="G9" s="80" t="inlineStr">
+        <is>
+          <t>直接</t>
+        </is>
+      </c>
+      <c r="H9" s="81" t="inlineStr"/>
+      <c r="I9" s="82" t="n">
+        <v>3402540</v>
+      </c>
+    </row>
+    <row r="10" ht="20" customHeight="1">
+      <c r="A10" s="76" t="inlineStr">
+        <is>
+          <t>本社</t>
+        </is>
+      </c>
+      <c r="B10" s="77" t="inlineStr">
+        <is>
+          <t>吉田 創</t>
+        </is>
+      </c>
+      <c r="C10" s="78" t="inlineStr">
+        <is>
+          <t>月給</t>
+        </is>
+      </c>
+      <c r="D10" s="60" t="n">
+        <v>249395</v>
+      </c>
+      <c r="E10" s="79" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F10" s="32" t="n">
+        <v>249395</v>
+      </c>
+      <c r="G10" s="80" t="inlineStr">
+        <is>
+          <t>直接</t>
+        </is>
+      </c>
+      <c r="H10" s="81" t="inlineStr"/>
+      <c r="I10" s="82" t="n">
+        <v>2992740</v>
+      </c>
+    </row>
+    <row r="11" ht="20" customHeight="1">
+      <c r="A11" s="76" t="inlineStr">
+        <is>
+          <t>本社</t>
+        </is>
+      </c>
+      <c r="B11" s="77" t="inlineStr">
+        <is>
+          <t>原口 陽一</t>
+        </is>
+      </c>
+      <c r="C11" s="78" t="inlineStr">
+        <is>
+          <t>月給</t>
+        </is>
+      </c>
+      <c r="D11" s="60" t="n">
+        <v>243155</v>
+      </c>
+      <c r="E11" s="79" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F11" s="32" t="n">
+        <v>243155</v>
+      </c>
+      <c r="G11" s="80" t="inlineStr">
+        <is>
+          <t>直接</t>
+        </is>
+      </c>
+      <c r="H11" s="81" t="inlineStr"/>
+      <c r="I11" s="82" t="n">
+        <v>2917860</v>
+      </c>
+    </row>
+    <row r="12" ht="20" customHeight="1">
+      <c r="A12" s="76" t="inlineStr">
+        <is>
+          <t>本社</t>
+        </is>
+      </c>
+      <c r="B12" s="77" t="inlineStr">
+        <is>
+          <t>北川 善己</t>
+        </is>
+      </c>
+      <c r="C12" s="78" t="inlineStr">
+        <is>
+          <t>月給</t>
+        </is>
+      </c>
+      <c r="D12" s="60" t="n">
+        <v>266955</v>
+      </c>
+      <c r="E12" s="79" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F12" s="32" t="n">
+        <v>266955</v>
+      </c>
+      <c r="G12" s="80" t="inlineStr">
+        <is>
+          <t>直接</t>
+        </is>
+      </c>
+      <c r="H12" s="81" t="inlineStr">
+        <is>
+          <t>東京発送手当</t>
+        </is>
+      </c>
+      <c r="I12" s="82" t="n">
+        <v>3203460</v>
+      </c>
+    </row>
+    <row r="13" ht="20" customHeight="1">
+      <c r="A13" s="76" t="inlineStr">
+        <is>
+          <t>本社</t>
+        </is>
+      </c>
+      <c r="B13" s="77" t="inlineStr">
+        <is>
+          <t>平野 裕幸</t>
+        </is>
+      </c>
+      <c r="C13" s="78" t="inlineStr">
+        <is>
+          <t>月給</t>
+        </is>
+      </c>
+      <c r="D13" s="60" t="n">
+        <v>263155</v>
+      </c>
+      <c r="E13" s="79" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F13" s="32" t="n">
+        <v>263155</v>
+      </c>
+      <c r="G13" s="80" t="inlineStr">
+        <is>
+          <t>直接</t>
+        </is>
+      </c>
+      <c r="H13" s="81" t="inlineStr">
+        <is>
+          <t>渡邊ベニヤ</t>
+        </is>
+      </c>
+      <c r="I13" s="82" t="n">
+        <v>3157860</v>
+      </c>
+    </row>
+    <row r="14" ht="20" customHeight="1">
+      <c r="A14" s="76" t="inlineStr">
+        <is>
+          <t>本社</t>
+        </is>
+      </c>
+      <c r="B14" s="77" t="inlineStr">
+        <is>
+          <t>山口 晃司</t>
+        </is>
+      </c>
+      <c r="C14" s="78" t="inlineStr">
+        <is>
+          <t>月給</t>
+        </is>
+      </c>
+      <c r="D14" s="60" t="n">
+        <v>243155</v>
+      </c>
+      <c r="E14" s="79" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F14" s="32" t="n">
+        <v>243155</v>
+      </c>
+      <c r="G14" s="80" t="inlineStr">
+        <is>
+          <t>直接</t>
+        </is>
+      </c>
+      <c r="H14" s="81" t="inlineStr">
+        <is>
+          <t>いずみ</t>
+        </is>
+      </c>
+      <c r="I14" s="82" t="n">
+        <v>2917860</v>
+      </c>
+    </row>
+    <row r="15" ht="20" customHeight="1">
+      <c r="A15" s="76" t="inlineStr">
+        <is>
+          <t>本社</t>
+        </is>
+      </c>
+      <c r="B15" s="77" t="inlineStr">
+        <is>
+          <t>石垣眞一郎</t>
+        </is>
+      </c>
+      <c r="C15" s="78" t="inlineStr">
+        <is>
+          <t>月給</t>
+        </is>
+      </c>
+      <c r="D15" s="60" t="n">
+        <v>263155</v>
+      </c>
+      <c r="E15" s="79" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F15" s="32" t="n">
+        <v>263155</v>
+      </c>
+      <c r="G15" s="80" t="inlineStr">
+        <is>
+          <t>直接</t>
+        </is>
+      </c>
+      <c r="H15" s="81" t="inlineStr">
+        <is>
+          <t>菱倉</t>
+        </is>
+      </c>
+      <c r="I15" s="82" t="n">
+        <v>3157860</v>
+      </c>
+    </row>
+    <row r="16" ht="20" customHeight="1">
+      <c r="A16" s="76" t="inlineStr">
+        <is>
+          <t>本社</t>
+        </is>
+      </c>
+      <c r="B16" s="77" t="inlineStr">
+        <is>
+          <t>高島 正人</t>
+        </is>
+      </c>
+      <c r="C16" s="78" t="inlineStr">
+        <is>
+          <t>月給</t>
+        </is>
+      </c>
+      <c r="D16" s="60" t="n">
+        <v>246155</v>
+      </c>
+      <c r="E16" s="79" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F16" s="32" t="n">
+        <v>246155</v>
+      </c>
+      <c r="G16" s="80" t="inlineStr">
+        <is>
+          <t>直接</t>
+        </is>
+      </c>
+      <c r="H16" s="81" t="inlineStr">
+        <is>
+          <t>いずみ</t>
+        </is>
+      </c>
+      <c r="I16" s="82" t="n">
+        <v>2953860</v>
+      </c>
+    </row>
+    <row r="17" ht="20" customHeight="1">
+      <c r="A17" s="76" t="inlineStr">
+        <is>
+          <t>本社</t>
+        </is>
+      </c>
+      <c r="B17" s="77" t="inlineStr">
+        <is>
+          <t>綱島 博隆</t>
+        </is>
+      </c>
+      <c r="C17" s="78" t="inlineStr">
+        <is>
+          <t>月給</t>
+        </is>
+      </c>
+      <c r="D17" s="60" t="n">
+        <v>268155</v>
+      </c>
+      <c r="E17" s="79" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F17" s="32" t="n">
+        <v>268155</v>
+      </c>
+      <c r="G17" s="80" t="inlineStr">
+        <is>
+          <t>直接</t>
+        </is>
+      </c>
+      <c r="H17" s="81" t="inlineStr">
+        <is>
+          <t>千代田区</t>
+        </is>
+      </c>
+      <c r="I17" s="82" t="n">
+        <v>3217860</v>
+      </c>
+    </row>
+    <row r="18" ht="20" customHeight="1">
+      <c r="A18" s="76" t="inlineStr">
+        <is>
+          <t>本社</t>
+        </is>
+      </c>
+      <c r="B18" s="77" t="inlineStr">
+        <is>
+          <t>後藤 実</t>
+        </is>
+      </c>
+      <c r="C18" s="78" t="inlineStr">
+        <is>
+          <t>月給</t>
+        </is>
+      </c>
+      <c r="D18" s="60" t="n">
+        <v>243155</v>
+      </c>
+      <c r="E18" s="79" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F18" s="32" t="n">
+        <v>243155</v>
+      </c>
+      <c r="G18" s="80" t="inlineStr">
+        <is>
+          <t>直接</t>
+        </is>
+      </c>
+      <c r="H18" s="81" t="inlineStr"/>
+      <c r="I18" s="82" t="n">
+        <v>2917860</v>
+      </c>
+    </row>
+    <row r="19" ht="20" customHeight="1">
+      <c r="A19" s="76" t="inlineStr">
+        <is>
+          <t>本社</t>
+        </is>
+      </c>
+      <c r="B19" s="77" t="inlineStr">
+        <is>
+          <t>嶋村 真実</t>
+        </is>
+      </c>
+      <c r="C19" s="78" t="inlineStr">
+        <is>
+          <t>月給</t>
+        </is>
+      </c>
+      <c r="D19" s="60" t="n">
+        <v>243155</v>
+      </c>
+      <c r="E19" s="79" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F19" s="32" t="n">
+        <v>243155</v>
+      </c>
+      <c r="G19" s="80" t="inlineStr">
+        <is>
+          <t>直接</t>
+        </is>
+      </c>
+      <c r="H19" s="81" t="inlineStr"/>
+      <c r="I19" s="82" t="n">
+        <v>2917860</v>
+      </c>
+    </row>
+    <row r="20" ht="20" customHeight="1">
+      <c r="A20" s="76" t="inlineStr">
+        <is>
+          <t>本社</t>
+        </is>
+      </c>
+      <c r="B20" s="77" t="inlineStr">
+        <is>
+          <t>岡田 学</t>
+        </is>
+      </c>
+      <c r="C20" s="78" t="inlineStr">
+        <is>
+          <t>月給</t>
+        </is>
+      </c>
+      <c r="D20" s="60" t="n">
+        <v>243155</v>
+      </c>
+      <c r="E20" s="79" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F20" s="32" t="n">
+        <v>243155</v>
+      </c>
+      <c r="G20" s="83" t="inlineStr">
+        <is>
+          <t>間接</t>
+        </is>
+      </c>
+      <c r="H20" s="81" t="inlineStr">
+        <is>
+          <t>文書</t>
+        </is>
+      </c>
+      <c r="I20" s="82" t="n">
+        <v>2917860</v>
+      </c>
+    </row>
+    <row r="21" ht="20" customHeight="1">
+      <c r="A21" s="76" t="inlineStr">
+        <is>
+          <t>本社</t>
+        </is>
+      </c>
+      <c r="B21" s="77" t="inlineStr">
+        <is>
+          <t>横山 信廣</t>
+        </is>
+      </c>
+      <c r="C21" s="78" t="inlineStr">
+        <is>
+          <t>月給</t>
+        </is>
+      </c>
+      <c r="D21" s="60" t="n">
+        <v>243155</v>
+      </c>
+      <c r="E21" s="79" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F21" s="32" t="n">
+        <v>243155</v>
+      </c>
+      <c r="G21" s="80" t="inlineStr">
+        <is>
+          <t>直接</t>
+        </is>
+      </c>
+      <c r="H21" s="81" t="inlineStr"/>
+      <c r="I21" s="82" t="n">
+        <v>2917860</v>
+      </c>
+    </row>
+    <row r="22" ht="20" customHeight="1">
+      <c r="A22" s="76" t="inlineStr">
+        <is>
+          <t>本社</t>
+        </is>
+      </c>
+      <c r="B22" s="77" t="inlineStr">
+        <is>
+          <t>笹沼 信人</t>
+        </is>
+      </c>
+      <c r="C22" s="78" t="inlineStr">
+        <is>
+          <t>月給</t>
+        </is>
+      </c>
+      <c r="D22" s="60" t="n">
+        <v>263155</v>
+      </c>
+      <c r="E22" s="79" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F22" s="32" t="n">
+        <v>263155</v>
+      </c>
+      <c r="G22" s="80" t="inlineStr">
+        <is>
+          <t>直接</t>
+        </is>
+      </c>
+      <c r="H22" s="81" t="inlineStr">
+        <is>
+          <t>東京発送手当</t>
+        </is>
+      </c>
+      <c r="I22" s="82" t="n">
+        <v>3157860</v>
+      </c>
+    </row>
+    <row r="23" ht="20" customHeight="1">
+      <c r="A23" s="76" t="inlineStr">
+        <is>
+          <t>本社</t>
+        </is>
+      </c>
+      <c r="B23" s="77" t="inlineStr">
+        <is>
+          <t>諏訪 清行</t>
+        </is>
+      </c>
+      <c r="C23" s="78" t="inlineStr">
+        <is>
+          <t>月給</t>
+        </is>
+      </c>
+      <c r="D23" s="60" t="n">
+        <v>243155</v>
+      </c>
+      <c r="E23" s="79" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F23" s="32" t="n">
+        <v>243155</v>
+      </c>
+      <c r="G23" s="80" t="inlineStr">
+        <is>
+          <t>直接</t>
+        </is>
+      </c>
+      <c r="H23" s="81" t="inlineStr"/>
+      <c r="I23" s="82" t="n">
+        <v>2917860</v>
+      </c>
+    </row>
+    <row r="24" ht="20" customHeight="1">
+      <c r="A24" s="76" t="inlineStr">
+        <is>
+          <t>本社</t>
+        </is>
+      </c>
+      <c r="B24" s="77" t="inlineStr">
+        <is>
+          <t>清水 孝之</t>
+        </is>
+      </c>
+      <c r="C24" s="78" t="inlineStr">
+        <is>
+          <t>月給</t>
+        </is>
+      </c>
+      <c r="D24" s="60" t="n">
+        <v>246155</v>
+      </c>
+      <c r="E24" s="79" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F24" s="32" t="n">
+        <v>246155</v>
+      </c>
+      <c r="G24" s="80" t="inlineStr">
+        <is>
+          <t>直接</t>
+        </is>
+      </c>
+      <c r="H24" s="81" t="inlineStr">
+        <is>
+          <t>いずみ</t>
+        </is>
+      </c>
+      <c r="I24" s="82" t="n">
+        <v>2953860</v>
+      </c>
+    </row>
+    <row r="25" ht="20" customHeight="1">
+      <c r="A25" s="76" t="inlineStr">
+        <is>
+          <t>本社</t>
+        </is>
+      </c>
+      <c r="B25" s="77" t="inlineStr">
+        <is>
+          <t>山下 勝二</t>
+        </is>
+      </c>
+      <c r="C25" s="78" t="inlineStr">
+        <is>
+          <t>月給</t>
+        </is>
+      </c>
+      <c r="D25" s="60" t="n">
+        <v>243155</v>
+      </c>
+      <c r="E25" s="79" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F25" s="32" t="n">
+        <v>243155</v>
+      </c>
+      <c r="G25" s="80" t="inlineStr">
+        <is>
+          <t>直接</t>
+        </is>
+      </c>
+      <c r="H25" s="81" t="inlineStr"/>
+      <c r="I25" s="82" t="n">
+        <v>2917860</v>
+      </c>
+    </row>
+    <row r="26" ht="20" customHeight="1">
+      <c r="A26" s="76" t="inlineStr">
+        <is>
+          <t>本社</t>
+        </is>
+      </c>
+      <c r="B26" s="77" t="inlineStr">
+        <is>
+          <t>根本 純一</t>
+        </is>
+      </c>
+      <c r="C26" s="78" t="inlineStr">
+        <is>
+          <t>月給</t>
+        </is>
+      </c>
+      <c r="D26" s="60" t="n">
+        <v>278155</v>
+      </c>
+      <c r="E26" s="79" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F26" s="32" t="n">
+        <v>278155</v>
+      </c>
+      <c r="G26" s="80" t="inlineStr">
+        <is>
+          <t>直接</t>
+        </is>
+      </c>
+      <c r="H26" s="81" t="inlineStr">
+        <is>
+          <t>自転車撤去</t>
+        </is>
+      </c>
+      <c r="I26" s="82" t="n">
+        <v>3337860</v>
+      </c>
+    </row>
+    <row r="27" ht="20" customHeight="1">
+      <c r="A27" s="76" t="inlineStr">
+        <is>
+          <t>本社</t>
+        </is>
+      </c>
+      <c r="B27" s="77" t="inlineStr">
+        <is>
+          <t>花木 凌</t>
+        </is>
+      </c>
+      <c r="C27" s="78" t="inlineStr">
+        <is>
+          <t>月給</t>
+        </is>
+      </c>
+      <c r="D27" s="60" t="n">
+        <v>243155</v>
+      </c>
+      <c r="E27" s="79" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F27" s="32" t="n">
+        <v>243155</v>
+      </c>
+      <c r="G27" s="80" t="inlineStr">
+        <is>
+          <t>直接</t>
+        </is>
+      </c>
+      <c r="H27" s="81" t="inlineStr"/>
+      <c r="I27" s="82" t="n">
+        <v>2917860</v>
+      </c>
+    </row>
+    <row r="28" ht="20" customHeight="1">
+      <c r="A28" s="76" t="inlineStr">
+        <is>
+          <t>本社</t>
+        </is>
+      </c>
+      <c r="B28" s="77" t="inlineStr">
+        <is>
+          <t>川井 良之</t>
+        </is>
+      </c>
+      <c r="C28" s="78" t="inlineStr">
+        <is>
+          <t>月給</t>
+        </is>
+      </c>
+      <c r="D28" s="60" t="n">
+        <v>243155</v>
+      </c>
+      <c r="E28" s="79" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F28" s="32" t="n">
+        <v>243155</v>
+      </c>
+      <c r="G28" s="80" t="inlineStr">
+        <is>
+          <t>直接</t>
+        </is>
+      </c>
+      <c r="H28" s="81" t="inlineStr"/>
+      <c r="I28" s="82" t="n">
+        <v>2917860</v>
+      </c>
+    </row>
+    <row r="29" ht="20" customHeight="1">
+      <c r="A29" s="76" t="inlineStr">
+        <is>
+          <t>本社</t>
+        </is>
+      </c>
+      <c r="B29" s="77" t="inlineStr">
+        <is>
+          <t>岡村 栄</t>
+        </is>
+      </c>
+      <c r="C29" s="84" t="inlineStr">
+        <is>
+          <t>日当</t>
+        </is>
+      </c>
+      <c r="D29" s="12" t="n">
+        <v>10000</v>
+      </c>
+      <c r="E29" s="85">
+        <f>$D$3</f>
+        <v/>
+      </c>
+      <c r="F29" s="32">
+        <f>D29*$D$3</f>
+        <v/>
+      </c>
+      <c r="G29" s="80" t="inlineStr">
+        <is>
+          <t>直接</t>
+        </is>
+      </c>
+      <c r="H29" s="81" t="inlineStr"/>
+      <c r="I29" s="82">
+        <f>F29*12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30" ht="20" customHeight="1">
+      <c r="A30" s="76" t="inlineStr">
+        <is>
+          <t>本社</t>
+        </is>
+      </c>
+      <c r="B30" s="77" t="inlineStr">
+        <is>
+          <t>川端 保</t>
+        </is>
+      </c>
+      <c r="C30" s="84" t="inlineStr">
+        <is>
+          <t>日当</t>
+        </is>
+      </c>
+      <c r="D30" s="12" t="n">
+        <v>11000</v>
+      </c>
+      <c r="E30" s="85">
+        <f>$D$3</f>
+        <v/>
+      </c>
+      <c r="F30" s="32">
+        <f>D30*$D$3</f>
+        <v/>
+      </c>
+      <c r="G30" s="80" t="inlineStr">
+        <is>
+          <t>直接</t>
+        </is>
+      </c>
+      <c r="H30" s="81" t="inlineStr"/>
+      <c r="I30" s="82">
+        <f>F30*12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31" ht="20" customHeight="1">
+      <c r="A31" s="76" t="inlineStr">
+        <is>
+          <t>本社</t>
+        </is>
+      </c>
+      <c r="B31" s="77" t="inlineStr">
+        <is>
+          <t>鈴木 賢二</t>
+        </is>
+      </c>
+      <c r="C31" s="84" t="inlineStr">
+        <is>
+          <t>日当</t>
+        </is>
+      </c>
+      <c r="D31" s="12" t="n">
+        <v>10000</v>
+      </c>
+      <c r="E31" s="85">
+        <f>$D$3</f>
+        <v/>
+      </c>
+      <c r="F31" s="32">
+        <f>D31*$D$3</f>
+        <v/>
+      </c>
+      <c r="G31" s="80" t="inlineStr">
+        <is>
+          <t>直接</t>
+        </is>
+      </c>
+      <c r="H31" s="81" t="inlineStr"/>
+      <c r="I31" s="82">
+        <f>F31*12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32" ht="20" customHeight="1">
+      <c r="A32" s="76" t="inlineStr">
+        <is>
+          <t>本社</t>
+        </is>
+      </c>
+      <c r="B32" s="77" t="inlineStr">
+        <is>
+          <t>小西 正悦</t>
+        </is>
+      </c>
+      <c r="C32" s="84" t="inlineStr">
+        <is>
+          <t>日当</t>
+        </is>
+      </c>
+      <c r="D32" s="12" t="n">
+        <v>10000</v>
+      </c>
+      <c r="E32" s="85">
+        <f>$D$3</f>
+        <v/>
+      </c>
+      <c r="F32" s="32">
+        <f>D32*$D$3</f>
+        <v/>
+      </c>
+      <c r="G32" s="80" t="inlineStr">
+        <is>
+          <t>直接</t>
+        </is>
+      </c>
+      <c r="H32" s="81" t="inlineStr"/>
+      <c r="I32" s="82">
+        <f>F32*12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33" ht="20" customHeight="1">
+      <c r="A33" s="76" t="inlineStr">
+        <is>
+          <t>本社</t>
+        </is>
+      </c>
+      <c r="B33" s="77" t="inlineStr">
+        <is>
+          <t>西開地良二</t>
+        </is>
+      </c>
+      <c r="C33" s="84" t="inlineStr">
+        <is>
+          <t>日当</t>
+        </is>
+      </c>
+      <c r="D33" s="12" t="n">
+        <v>10000</v>
+      </c>
+      <c r="E33" s="85">
+        <f>$D$3</f>
+        <v/>
+      </c>
+      <c r="F33" s="32">
+        <f>D33*$D$3</f>
+        <v/>
+      </c>
+      <c r="G33" s="80" t="inlineStr">
+        <is>
+          <t>直接</t>
+        </is>
+      </c>
+      <c r="H33" s="81" t="inlineStr">
+        <is>
+          <t>いずみ手当</t>
+        </is>
+      </c>
+      <c r="I33" s="82">
+        <f>F33*12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34" ht="20" customHeight="1">
+      <c r="A34" s="76" t="inlineStr">
+        <is>
+          <t>本社</t>
+        </is>
+      </c>
+      <c r="B34" s="77" t="inlineStr">
+        <is>
+          <t>四位 宗光</t>
+        </is>
+      </c>
+      <c r="C34" s="84" t="inlineStr">
+        <is>
+          <t>日当</t>
+        </is>
+      </c>
+      <c r="D34" s="12" t="n">
+        <v>9320</v>
+      </c>
+      <c r="E34" s="85">
+        <f>$D$3</f>
+        <v/>
+      </c>
+      <c r="F34" s="32">
+        <f>D34*$D$3</f>
+        <v/>
+      </c>
+      <c r="G34" s="80" t="inlineStr">
+        <is>
+          <t>直接</t>
+        </is>
+      </c>
+      <c r="H34" s="81" t="inlineStr"/>
+      <c r="I34" s="82">
+        <f>F34*12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35" ht="20" customHeight="1">
+      <c r="A35" s="76" t="inlineStr">
+        <is>
+          <t>本社</t>
+        </is>
+      </c>
+      <c r="B35" s="77" t="inlineStr">
+        <is>
+          <t>赤崎 博隆</t>
+        </is>
+      </c>
+      <c r="C35" s="84" t="inlineStr">
+        <is>
+          <t>日当</t>
+        </is>
+      </c>
+      <c r="D35" s="12" t="n">
+        <v>10000</v>
+      </c>
+      <c r="E35" s="85">
+        <f>$D$3</f>
+        <v/>
+      </c>
+      <c r="F35" s="32">
+        <f>D35*$D$3</f>
+        <v/>
+      </c>
+      <c r="G35" s="80" t="inlineStr">
+        <is>
+          <t>直接</t>
+        </is>
+      </c>
+      <c r="H35" s="81" t="inlineStr"/>
+      <c r="I35" s="82">
+        <f>F35*12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36" ht="20" customHeight="1">
+      <c r="A36" s="76" t="inlineStr">
+        <is>
+          <t>本社</t>
+        </is>
+      </c>
+      <c r="B36" s="77" t="inlineStr">
+        <is>
+          <t>近藤 政夫</t>
+        </is>
+      </c>
+      <c r="C36" s="84" t="inlineStr">
+        <is>
+          <t>日当</t>
+        </is>
+      </c>
+      <c r="D36" s="12" t="n">
+        <v>10000</v>
+      </c>
+      <c r="E36" s="85">
+        <f>$D$3</f>
+        <v/>
+      </c>
+      <c r="F36" s="32">
+        <f>D36*$D$3</f>
+        <v/>
+      </c>
+      <c r="G36" s="80" t="inlineStr">
+        <is>
+          <t>直接</t>
+        </is>
+      </c>
+      <c r="H36" s="81" t="inlineStr"/>
+      <c r="I36" s="82">
+        <f>F36*12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37" ht="20" customHeight="1">
+      <c r="A37" s="76" t="inlineStr">
+        <is>
+          <t>本社</t>
+        </is>
+      </c>
+      <c r="B37" s="77" t="inlineStr">
+        <is>
+          <t>佐藤 淳司</t>
+        </is>
+      </c>
+      <c r="C37" s="84" t="inlineStr">
+        <is>
+          <t>日当</t>
+        </is>
+      </c>
+      <c r="D37" s="12" t="n">
+        <v>10000</v>
+      </c>
+      <c r="E37" s="85">
+        <f>$D$3</f>
+        <v/>
+      </c>
+      <c r="F37" s="32">
+        <f>D37*$D$3</f>
+        <v/>
+      </c>
+      <c r="G37" s="80" t="inlineStr">
+        <is>
+          <t>直接</t>
+        </is>
+      </c>
+      <c r="H37" s="81" t="inlineStr">
+        <is>
+          <t>自転車撤去</t>
+        </is>
+      </c>
+      <c r="I37" s="82">
+        <f>F37*12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38" ht="20" customHeight="1">
+      <c r="A38" s="76" t="inlineStr">
+        <is>
+          <t>本社</t>
+        </is>
+      </c>
+      <c r="B38" s="77" t="inlineStr">
+        <is>
+          <t>門脇 明敏</t>
+        </is>
+      </c>
+      <c r="C38" s="84" t="inlineStr">
+        <is>
+          <t>日当</t>
+        </is>
+      </c>
+      <c r="D38" s="12" t="n">
+        <v>10000</v>
+      </c>
+      <c r="E38" s="85">
+        <f>$D$3</f>
+        <v/>
+      </c>
+      <c r="F38" s="32">
+        <f>D38*$D$3</f>
+        <v/>
+      </c>
+      <c r="G38" s="80" t="inlineStr">
+        <is>
+          <t>直接</t>
+        </is>
+      </c>
+      <c r="H38" s="81" t="inlineStr">
+        <is>
+          <t>いずみ</t>
+        </is>
+      </c>
+      <c r="I38" s="82">
+        <f>F38*12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="39" ht="20" customHeight="1">
+      <c r="A39" s="76" t="inlineStr">
+        <is>
+          <t>本社</t>
+        </is>
+      </c>
+      <c r="B39" s="77" t="inlineStr">
+        <is>
+          <t>小島 一彦</t>
+        </is>
+      </c>
+      <c r="C39" s="84" t="inlineStr">
+        <is>
+          <t>日当</t>
+        </is>
+      </c>
+      <c r="D39" s="12" t="n">
+        <v>10000</v>
+      </c>
+      <c r="E39" s="85">
+        <f>$D$3</f>
+        <v/>
+      </c>
+      <c r="F39" s="32">
+        <f>D39*$D$3</f>
+        <v/>
+      </c>
+      <c r="G39" s="80" t="inlineStr">
+        <is>
+          <t>直接</t>
+        </is>
+      </c>
+      <c r="H39" s="81" t="inlineStr"/>
+      <c r="I39" s="82">
+        <f>F39*12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="40" ht="20" customHeight="1">
+      <c r="A40" s="76" t="inlineStr">
+        <is>
+          <t>本社</t>
+        </is>
+      </c>
+      <c r="B40" s="77" t="inlineStr">
+        <is>
+          <t>後藤 保幸</t>
+        </is>
+      </c>
+      <c r="C40" s="84" t="inlineStr">
+        <is>
+          <t>日当</t>
+        </is>
+      </c>
+      <c r="D40" s="12" t="n">
+        <v>10000</v>
+      </c>
+      <c r="E40" s="85">
+        <f>$D$3</f>
+        <v/>
+      </c>
+      <c r="F40" s="32">
+        <f>D40*$D$3</f>
+        <v/>
+      </c>
+      <c r="G40" s="80" t="inlineStr">
+        <is>
+          <t>直接</t>
+        </is>
+      </c>
+      <c r="H40" s="81" t="inlineStr"/>
+      <c r="I40" s="82">
+        <f>F40*12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="41" ht="20" customHeight="1">
+      <c r="A41" s="76" t="inlineStr">
+        <is>
+          <t>本社</t>
+        </is>
+      </c>
+      <c r="B41" s="77" t="inlineStr">
+        <is>
+          <t>昆野 良博</t>
+        </is>
+      </c>
+      <c r="C41" s="84" t="inlineStr">
+        <is>
+          <t>日当</t>
+        </is>
+      </c>
+      <c r="D41" s="12" t="n">
+        <v>10000</v>
+      </c>
+      <c r="E41" s="85">
+        <f>$D$3</f>
+        <v/>
+      </c>
+      <c r="F41" s="32">
+        <f>D41*$D$3</f>
+        <v/>
+      </c>
+      <c r="G41" s="80" t="inlineStr">
+        <is>
+          <t>直接</t>
+        </is>
+      </c>
+      <c r="H41" s="81" t="inlineStr"/>
+      <c r="I41" s="82">
+        <f>F41*12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="42" ht="20" customHeight="1">
+      <c r="A42" s="76" t="inlineStr">
+        <is>
+          <t>本社</t>
+        </is>
+      </c>
+      <c r="B42" s="77" t="inlineStr">
+        <is>
+          <t>伊藤 敏正</t>
+        </is>
+      </c>
+      <c r="C42" s="84" t="inlineStr">
+        <is>
+          <t>日当</t>
+        </is>
+      </c>
+      <c r="D42" s="12" t="n">
+        <v>10000</v>
+      </c>
+      <c r="E42" s="85">
+        <f>$D$3</f>
+        <v/>
+      </c>
+      <c r="F42" s="32">
+        <f>D42*$D$3</f>
+        <v/>
+      </c>
+      <c r="G42" s="80" t="inlineStr">
+        <is>
+          <t>直接</t>
+        </is>
+      </c>
+      <c r="H42" s="81" t="inlineStr"/>
+      <c r="I42" s="82">
+        <f>F42*12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="43" ht="20" customHeight="1">
+      <c r="A43" s="76" t="inlineStr">
+        <is>
+          <t>本社</t>
+        </is>
+      </c>
+      <c r="B43" s="77" t="inlineStr">
+        <is>
+          <t>石井 努</t>
+        </is>
+      </c>
+      <c r="C43" s="84" t="inlineStr">
+        <is>
+          <t>日当</t>
+        </is>
+      </c>
+      <c r="D43" s="12" t="n">
+        <v>10000</v>
+      </c>
+      <c r="E43" s="85">
+        <f>$D$3</f>
+        <v/>
+      </c>
+      <c r="F43" s="32">
+        <f>D43*$D$3</f>
+        <v/>
+      </c>
+      <c r="G43" s="80" t="inlineStr">
+        <is>
+          <t>直接</t>
+        </is>
+      </c>
+      <c r="H43" s="81" t="inlineStr">
+        <is>
+          <t>いずみ</t>
+        </is>
+      </c>
+      <c r="I43" s="82">
+        <f>F43*12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="44" ht="20" customHeight="1">
+      <c r="A44" s="76" t="inlineStr">
+        <is>
+          <t>本社</t>
+        </is>
+      </c>
+      <c r="B44" s="77" t="inlineStr">
+        <is>
+          <t>金川 裕</t>
+        </is>
+      </c>
+      <c r="C44" s="84" t="inlineStr">
+        <is>
+          <t>日当</t>
+        </is>
+      </c>
+      <c r="D44" s="12" t="n">
+        <v>10000</v>
+      </c>
+      <c r="E44" s="85">
+        <f>$D$3</f>
+        <v/>
+      </c>
+      <c r="F44" s="32">
+        <f>D44*$D$3</f>
+        <v/>
+      </c>
+      <c r="G44" s="80" t="inlineStr">
+        <is>
+          <t>直接</t>
+        </is>
+      </c>
+      <c r="H44" s="81" t="inlineStr">
+        <is>
+          <t>文書交換</t>
+        </is>
+      </c>
+      <c r="I44" s="82">
+        <f>F44*12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="45" ht="20" customHeight="1">
+      <c r="A45" s="76" t="inlineStr">
+        <is>
+          <t>本社</t>
+        </is>
+      </c>
+      <c r="B45" s="77" t="inlineStr">
+        <is>
+          <t>大澤 弘直</t>
+        </is>
+      </c>
+      <c r="C45" s="84" t="inlineStr">
+        <is>
+          <t>日当</t>
+        </is>
+      </c>
+      <c r="D45" s="12" t="n">
+        <v>8000</v>
+      </c>
+      <c r="E45" s="85">
+        <f>$D$3</f>
+        <v/>
+      </c>
+      <c r="F45" s="32">
+        <f>D45*$D$3</f>
+        <v/>
+      </c>
+      <c r="G45" s="80" t="inlineStr">
+        <is>
+          <t>直接</t>
+        </is>
+      </c>
+      <c r="H45" s="81" t="inlineStr">
+        <is>
+          <t>6.5h</t>
+        </is>
+      </c>
+      <c r="I45" s="82">
+        <f>F45*12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="46" ht="20" customHeight="1">
+      <c r="A46" s="76" t="inlineStr">
+        <is>
+          <t>本社</t>
+        </is>
+      </c>
+      <c r="B46" s="77" t="inlineStr">
+        <is>
+          <t>羽田 美惠</t>
+        </is>
+      </c>
+      <c r="C46" s="84" t="inlineStr">
+        <is>
+          <t>日当</t>
+        </is>
+      </c>
+      <c r="D46" s="12" t="n">
+        <v>10000</v>
+      </c>
+      <c r="E46" s="85">
+        <f>$D$3</f>
+        <v/>
+      </c>
+      <c r="F46" s="32">
+        <f>D46*$D$3</f>
+        <v/>
+      </c>
+      <c r="G46" s="83" t="inlineStr">
+        <is>
+          <t>間接</t>
+        </is>
+      </c>
+      <c r="H46" s="81" t="inlineStr"/>
+      <c r="I46" s="82">
+        <f>F46*12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="47" ht="20" customHeight="1">
+      <c r="A47" s="76" t="inlineStr">
+        <is>
+          <t>本社</t>
+        </is>
+      </c>
+      <c r="B47" s="77" t="inlineStr">
+        <is>
+          <t>赤石 政春</t>
+        </is>
+      </c>
+      <c r="C47" s="84" t="inlineStr">
+        <is>
+          <t>日当</t>
+        </is>
+      </c>
+      <c r="D47" s="12" t="n">
+        <v>10000</v>
+      </c>
+      <c r="E47" s="85">
+        <f>$D$3</f>
+        <v/>
+      </c>
+      <c r="F47" s="32">
+        <f>D47*$D$3</f>
+        <v/>
+      </c>
+      <c r="G47" s="80" t="inlineStr">
+        <is>
+          <t>直接</t>
+        </is>
+      </c>
+      <c r="H47" s="81" t="inlineStr">
+        <is>
+          <t>文書交換</t>
+        </is>
+      </c>
+      <c r="I47" s="82">
+        <f>F47*12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="48" ht="20" customHeight="1">
+      <c r="A48" s="76" t="inlineStr">
+        <is>
+          <t>本社</t>
+        </is>
+      </c>
+      <c r="B48" s="77" t="inlineStr">
+        <is>
+          <t>小山内文夫</t>
+        </is>
+      </c>
+      <c r="C48" s="84" t="inlineStr">
+        <is>
+          <t>日当</t>
+        </is>
+      </c>
+      <c r="D48" s="12" t="n">
+        <v>10000</v>
+      </c>
+      <c r="E48" s="85">
+        <f>$D$3</f>
+        <v/>
+      </c>
+      <c r="F48" s="32">
+        <f>D48*$D$3</f>
+        <v/>
+      </c>
+      <c r="G48" s="80" t="inlineStr">
+        <is>
+          <t>直接</t>
+        </is>
+      </c>
+      <c r="H48" s="81" t="inlineStr">
+        <is>
+          <t>千代田区</t>
+        </is>
+      </c>
+      <c r="I48" s="82">
+        <f>F48*12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="49" ht="20" customHeight="1">
+      <c r="A49" s="76" t="inlineStr">
+        <is>
+          <t>本社</t>
+        </is>
+      </c>
+      <c r="B49" s="77" t="inlineStr">
+        <is>
+          <t>林 重晴</t>
+        </is>
+      </c>
+      <c r="C49" s="84" t="inlineStr">
+        <is>
+          <t>日当</t>
+        </is>
+      </c>
+      <c r="D49" s="12" t="n">
+        <v>10000</v>
+      </c>
+      <c r="E49" s="85">
+        <f>$D$3</f>
+        <v/>
+      </c>
+      <c r="F49" s="32">
+        <f>D49*$D$3</f>
+        <v/>
+      </c>
+      <c r="G49" s="80" t="inlineStr">
+        <is>
+          <t>直接</t>
+        </is>
+      </c>
+      <c r="H49" s="81" t="inlineStr">
+        <is>
+          <t>いずみ</t>
+        </is>
+      </c>
+      <c r="I49" s="82">
+        <f>F49*12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="50" ht="20" customHeight="1">
+      <c r="A50" s="76" t="inlineStr">
+        <is>
+          <t>本社</t>
+        </is>
+      </c>
+      <c r="B50" s="77" t="inlineStr">
+        <is>
+          <t>中原 健一</t>
+        </is>
+      </c>
+      <c r="C50" s="84" t="inlineStr">
+        <is>
+          <t>日当</t>
+        </is>
+      </c>
+      <c r="D50" s="12" t="n">
+        <v>10000</v>
+      </c>
+      <c r="E50" s="85">
+        <f>$D$3</f>
+        <v/>
+      </c>
+      <c r="F50" s="32">
+        <f>D50*$D$3</f>
+        <v/>
+      </c>
+      <c r="G50" s="80" t="inlineStr">
+        <is>
+          <t>直接</t>
+        </is>
+      </c>
+      <c r="H50" s="81" t="inlineStr">
+        <is>
+          <t>文書交換</t>
+        </is>
+      </c>
+      <c r="I50" s="82">
+        <f>F50*12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="51" ht="20" customHeight="1">
+      <c r="A51" s="76" t="inlineStr">
+        <is>
+          <t>本社</t>
+        </is>
+      </c>
+      <c r="B51" s="77" t="inlineStr">
+        <is>
+          <t>樋口 隆一</t>
+        </is>
+      </c>
+      <c r="C51" s="84" t="inlineStr">
+        <is>
+          <t>日当</t>
+        </is>
+      </c>
+      <c r="D51" s="12" t="n">
+        <v>10000</v>
+      </c>
+      <c r="E51" s="85">
+        <f>$D$3</f>
+        <v/>
+      </c>
+      <c r="F51" s="32">
+        <f>D51*$D$3</f>
+        <v/>
+      </c>
+      <c r="G51" s="80" t="inlineStr">
+        <is>
+          <t>直接</t>
+        </is>
+      </c>
+      <c r="H51" s="81" t="inlineStr">
+        <is>
+          <t>自転車撤去</t>
+        </is>
+      </c>
+      <c r="I51" s="82">
+        <f>F51*12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="52" ht="20" customHeight="1">
+      <c r="A52" s="76" t="inlineStr">
+        <is>
+          <t>本社</t>
+        </is>
+      </c>
+      <c r="B52" s="77" t="inlineStr">
+        <is>
+          <t>中村 史德</t>
+        </is>
+      </c>
+      <c r="C52" s="84" t="inlineStr">
+        <is>
+          <t>日当</t>
+        </is>
+      </c>
+      <c r="D52" s="12" t="n">
+        <v>10000</v>
+      </c>
+      <c r="E52" s="85">
+        <f>$D$3</f>
+        <v/>
+      </c>
+      <c r="F52" s="32">
+        <f>D52*$D$3</f>
+        <v/>
+      </c>
+      <c r="G52" s="80" t="inlineStr">
+        <is>
+          <t>直接</t>
+        </is>
+      </c>
+      <c r="H52" s="81" t="inlineStr">
+        <is>
+          <t>自転車撤去</t>
+        </is>
+      </c>
+      <c r="I52" s="82">
+        <f>F52*12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="53" ht="20" customHeight="1">
+      <c r="A53" s="76" t="inlineStr">
+        <is>
+          <t>本社</t>
+        </is>
+      </c>
+      <c r="B53" s="77" t="inlineStr">
+        <is>
+          <t>金子 豊</t>
+        </is>
+      </c>
+      <c r="C53" s="84" t="inlineStr">
+        <is>
+          <t>日当</t>
+        </is>
+      </c>
+      <c r="D53" s="12" t="n">
+        <v>10000</v>
+      </c>
+      <c r="E53" s="85">
+        <f>$D$3</f>
+        <v/>
+      </c>
+      <c r="F53" s="32">
+        <f>D53*$D$3</f>
+        <v/>
+      </c>
+      <c r="G53" s="80" t="inlineStr">
+        <is>
+          <t>直接</t>
+        </is>
+      </c>
+      <c r="H53" s="81" t="inlineStr">
+        <is>
+          <t>自転車撤去</t>
+        </is>
+      </c>
+      <c r="I53" s="82">
+        <f>F53*12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="54" ht="20" customHeight="1">
+      <c r="A54" s="76" t="inlineStr">
+        <is>
+          <t>本社</t>
+        </is>
+      </c>
+      <c r="B54" s="77" t="inlineStr">
+        <is>
+          <t>斉藤 善</t>
+        </is>
+      </c>
+      <c r="C54" s="84" t="inlineStr">
+        <is>
+          <t>日当</t>
+        </is>
+      </c>
+      <c r="D54" s="12" t="n">
+        <v>10000</v>
+      </c>
+      <c r="E54" s="85">
+        <f>$D$3</f>
+        <v/>
+      </c>
+      <c r="F54" s="32">
+        <f>D54*$D$3</f>
+        <v/>
+      </c>
+      <c r="G54" s="80" t="inlineStr">
+        <is>
+          <t>直接</t>
+        </is>
+      </c>
+      <c r="H54" s="81" t="inlineStr">
+        <is>
+          <t>自転車撤去</t>
+        </is>
+      </c>
+      <c r="I54" s="82">
+        <f>F54*12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="55" ht="20" customHeight="1">
+      <c r="A55" s="76" t="inlineStr">
+        <is>
+          <t>本社</t>
+        </is>
+      </c>
+      <c r="B55" s="77" t="inlineStr">
+        <is>
+          <t>松崎 亨</t>
+        </is>
+      </c>
+      <c r="C55" s="84" t="inlineStr">
+        <is>
+          <t>日当</t>
+        </is>
+      </c>
+      <c r="D55" s="12" t="n">
+        <v>10000</v>
+      </c>
+      <c r="E55" s="85">
+        <f>$D$3</f>
+        <v/>
+      </c>
+      <c r="F55" s="32">
+        <f>D55*$D$3</f>
+        <v/>
+      </c>
+      <c r="G55" s="80" t="inlineStr">
+        <is>
+          <t>直接</t>
+        </is>
+      </c>
+      <c r="H55" s="81" t="inlineStr"/>
+      <c r="I55" s="82">
+        <f>F55*12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="56" ht="20" customHeight="1">
+      <c r="A56" s="76" t="inlineStr">
+        <is>
+          <t>本社</t>
+        </is>
+      </c>
+      <c r="B56" s="77" t="inlineStr">
+        <is>
+          <t>町田 昌明</t>
+        </is>
+      </c>
+      <c r="C56" s="84" t="inlineStr">
+        <is>
+          <t>日当</t>
+        </is>
+      </c>
+      <c r="D56" s="12" t="n">
+        <v>10000</v>
+      </c>
+      <c r="E56" s="85">
+        <f>$D$3</f>
+        <v/>
+      </c>
+      <c r="F56" s="32">
+        <f>D56*$D$3</f>
+        <v/>
+      </c>
+      <c r="G56" s="80" t="inlineStr">
+        <is>
+          <t>直接</t>
+        </is>
+      </c>
+      <c r="H56" s="81" t="inlineStr"/>
+      <c r="I56" s="82">
+        <f>F56*12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="57" ht="20" customHeight="1">
+      <c r="A57" s="76" t="inlineStr">
+        <is>
+          <t>本社</t>
+        </is>
+      </c>
+      <c r="B57" s="77" t="inlineStr">
+        <is>
+          <t>堀 富雄</t>
+        </is>
+      </c>
+      <c r="C57" s="84" t="inlineStr">
+        <is>
+          <t>日当</t>
+        </is>
+      </c>
+      <c r="D57" s="12" t="n">
+        <v>10000</v>
+      </c>
+      <c r="E57" s="85">
+        <f>$D$3</f>
+        <v/>
+      </c>
+      <c r="F57" s="32">
+        <f>D57*$D$3</f>
+        <v/>
+      </c>
+      <c r="G57" s="80" t="inlineStr">
+        <is>
+          <t>直接</t>
+        </is>
+      </c>
+      <c r="H57" s="81" t="inlineStr"/>
+      <c r="I57" s="82">
+        <f>F57*12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="58" ht="20" customHeight="1">
+      <c r="A58" s="76" t="inlineStr">
+        <is>
+          <t>本社</t>
+        </is>
+      </c>
+      <c r="B58" s="77" t="inlineStr">
+        <is>
+          <t>栗原文次郎</t>
+        </is>
+      </c>
+      <c r="C58" s="84" t="inlineStr">
+        <is>
+          <t>日当</t>
+        </is>
+      </c>
+      <c r="D58" s="12" t="n">
+        <v>10000</v>
+      </c>
+      <c r="E58" s="85">
+        <f>$D$3</f>
+        <v/>
+      </c>
+      <c r="F58" s="32">
+        <f>D58*$D$3</f>
+        <v/>
+      </c>
+      <c r="G58" s="80" t="inlineStr">
+        <is>
+          <t>直接</t>
+        </is>
+      </c>
+      <c r="H58" s="81" t="inlineStr"/>
+      <c r="I58" s="82">
+        <f>F58*12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="59" ht="20" customHeight="1">
+      <c r="A59" s="76" t="inlineStr">
+        <is>
+          <t>本社</t>
+        </is>
+      </c>
+      <c r="B59" s="77" t="inlineStr">
+        <is>
+          <t>高栁 恵州</t>
+        </is>
+      </c>
+      <c r="C59" s="84" t="inlineStr">
+        <is>
+          <t>日当</t>
+        </is>
+      </c>
+      <c r="D59" s="12" t="n">
+        <v>10000</v>
+      </c>
+      <c r="E59" s="85">
+        <f>$D$3</f>
+        <v/>
+      </c>
+      <c r="F59" s="32">
+        <f>D59*$D$3</f>
+        <v/>
+      </c>
+      <c r="G59" s="80" t="inlineStr">
+        <is>
+          <t>直接</t>
+        </is>
+      </c>
+      <c r="H59" s="81" t="inlineStr"/>
+      <c r="I59" s="82">
+        <f>F59*12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="60" ht="20" customHeight="1">
+      <c r="A60" s="76" t="inlineStr">
+        <is>
+          <t>本社</t>
+        </is>
+      </c>
+      <c r="B60" s="77" t="inlineStr">
+        <is>
+          <t>吉見 之男</t>
+        </is>
+      </c>
+      <c r="C60" s="84" t="inlineStr">
+        <is>
+          <t>日当</t>
+        </is>
+      </c>
+      <c r="D60" s="12" t="n">
+        <v>10000</v>
+      </c>
+      <c r="E60" s="85">
+        <f>$D$3</f>
+        <v/>
+      </c>
+      <c r="F60" s="32">
+        <f>D60*$D$3</f>
+        <v/>
+      </c>
+      <c r="G60" s="80" t="inlineStr">
+        <is>
+          <t>直接</t>
+        </is>
+      </c>
+      <c r="H60" s="81" t="inlineStr"/>
+      <c r="I60" s="82">
+        <f>F60*12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="61" ht="20" customHeight="1">
+      <c r="A61" s="76" t="inlineStr">
+        <is>
+          <t>本社</t>
+        </is>
+      </c>
+      <c r="B61" s="77" t="inlineStr">
+        <is>
+          <t>坂本 龍男</t>
+        </is>
+      </c>
+      <c r="C61" s="84" t="inlineStr">
+        <is>
+          <t>日当</t>
+        </is>
+      </c>
+      <c r="D61" s="12" t="n">
+        <v>10000</v>
+      </c>
+      <c r="E61" s="85">
+        <f>$D$3</f>
+        <v/>
+      </c>
+      <c r="F61" s="32">
+        <f>D61*$D$3</f>
+        <v/>
+      </c>
+      <c r="G61" s="80" t="inlineStr">
+        <is>
+          <t>直接</t>
+        </is>
+      </c>
+      <c r="H61" s="81" t="inlineStr"/>
+      <c r="I61" s="82">
+        <f>F61*12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="62" ht="20" customHeight="1">
+      <c r="A62" s="76" t="inlineStr">
+        <is>
+          <t>本社</t>
+        </is>
+      </c>
+      <c r="B62" s="77" t="inlineStr">
+        <is>
+          <t>桃谷 政良</t>
+        </is>
+      </c>
+      <c r="C62" s="84" t="inlineStr">
+        <is>
+          <t>日当</t>
+        </is>
+      </c>
+      <c r="D62" s="12" t="n">
+        <v>10000</v>
+      </c>
+      <c r="E62" s="85">
+        <f>$D$3</f>
+        <v/>
+      </c>
+      <c r="F62" s="32">
+        <f>D62*$D$3</f>
+        <v/>
+      </c>
+      <c r="G62" s="80" t="inlineStr">
+        <is>
+          <t>直接</t>
+        </is>
+      </c>
+      <c r="H62" s="81" t="inlineStr"/>
+      <c r="I62" s="82">
+        <f>F62*12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="63" ht="20" customHeight="1">
+      <c r="A63" s="76" t="inlineStr">
+        <is>
+          <t>本社</t>
+        </is>
+      </c>
+      <c r="B63" s="77" t="inlineStr">
+        <is>
+          <t>竹内 幸一</t>
+        </is>
+      </c>
+      <c r="C63" s="84" t="inlineStr">
+        <is>
+          <t>日当</t>
+        </is>
+      </c>
+      <c r="D63" s="12" t="n">
+        <v>10000</v>
+      </c>
+      <c r="E63" s="85">
+        <f>$D$3</f>
+        <v/>
+      </c>
+      <c r="F63" s="32">
+        <f>D63*$D$3</f>
+        <v/>
+      </c>
+      <c r="G63" s="80" t="inlineStr">
+        <is>
+          <t>直接</t>
+        </is>
+      </c>
+      <c r="H63" s="81" t="inlineStr"/>
+      <c r="I63" s="82">
+        <f>F63*12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="64" ht="20" customHeight="1">
+      <c r="A64" s="76" t="inlineStr">
+        <is>
+          <t>本社</t>
+        </is>
+      </c>
+      <c r="B64" s="77" t="inlineStr">
+        <is>
+          <t>林 幸夫</t>
+        </is>
+      </c>
+      <c r="C64" s="84" t="inlineStr">
+        <is>
+          <t>日当</t>
+        </is>
+      </c>
+      <c r="D64" s="12" t="n">
+        <v>10000</v>
+      </c>
+      <c r="E64" s="85">
+        <f>$D$3</f>
+        <v/>
+      </c>
+      <c r="F64" s="32">
+        <f>D64*$D$3</f>
+        <v/>
+      </c>
+      <c r="G64" s="80" t="inlineStr">
+        <is>
+          <t>直接</t>
+        </is>
+      </c>
+      <c r="H64" s="81" t="inlineStr"/>
+      <c r="I64" s="82">
+        <f>F64*12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="65" ht="20" customHeight="1">
+      <c r="A65" s="76" t="inlineStr">
+        <is>
+          <t>本社</t>
+        </is>
+      </c>
+      <c r="B65" s="77" t="inlineStr">
+        <is>
+          <t>加藤実都代</t>
+        </is>
+      </c>
+      <c r="C65" s="84" t="inlineStr">
+        <is>
+          <t>時給</t>
+        </is>
+      </c>
+      <c r="D65" s="12" t="n">
+        <v>1805</v>
+      </c>
+      <c r="E65" s="85">
+        <f>$D$3</f>
+        <v/>
+      </c>
+      <c r="F65" s="32">
+        <f>D65*$D$3*8</f>
+        <v/>
+      </c>
+      <c r="G65" s="83" t="inlineStr">
+        <is>
+          <t>間接</t>
+        </is>
+      </c>
+      <c r="H65" s="81" t="inlineStr"/>
+      <c r="I65" s="82">
+        <f>F65*12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="66" ht="20" customHeight="1">
+      <c r="A66" s="76" t="inlineStr">
+        <is>
+          <t>本社</t>
+        </is>
+      </c>
+      <c r="B66" s="77" t="inlineStr">
+        <is>
+          <t>林 典子</t>
+        </is>
+      </c>
+      <c r="C66" s="84" t="inlineStr">
+        <is>
+          <t>時給</t>
+        </is>
+      </c>
+      <c r="D66" s="12" t="n">
+        <v>1165</v>
+      </c>
+      <c r="E66" s="85">
+        <f>$D$3</f>
+        <v/>
+      </c>
+      <c r="F66" s="32">
+        <f>D66*$D$3*8</f>
+        <v/>
+      </c>
+      <c r="G66" s="83" t="inlineStr">
+        <is>
+          <t>間接</t>
+        </is>
+      </c>
+      <c r="H66" s="81" t="inlineStr"/>
+      <c r="I66" s="82">
+        <f>F66*12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="67" ht="20" customHeight="1">
+      <c r="A67" s="76" t="inlineStr">
+        <is>
+          <t>本社</t>
+        </is>
+      </c>
+      <c r="B67" s="77" t="inlineStr">
+        <is>
+          <t>足立秀次郎</t>
+        </is>
+      </c>
+      <c r="C67" s="84" t="inlineStr">
+        <is>
+          <t>時給</t>
+        </is>
+      </c>
+      <c r="D67" s="12" t="n">
+        <v>1165</v>
+      </c>
+      <c r="E67" s="85">
+        <f>$D$3</f>
+        <v/>
+      </c>
+      <c r="F67" s="32">
+        <f>D67*$D$3*8</f>
+        <v/>
+      </c>
+      <c r="G67" s="83" t="inlineStr">
+        <is>
+          <t>間接</t>
+        </is>
+      </c>
+      <c r="H67" s="81" t="inlineStr">
+        <is>
+          <t>文書交換室</t>
+        </is>
+      </c>
+      <c r="I67" s="82">
+        <f>F67*12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="68" ht="20" customHeight="1">
+      <c r="A68" s="76" t="inlineStr">
+        <is>
+          <t>本社</t>
+        </is>
+      </c>
+      <c r="B68" s="77" t="inlineStr">
+        <is>
+          <t>松原 光年</t>
+        </is>
+      </c>
+      <c r="C68" s="84" t="inlineStr">
+        <is>
+          <t>時給</t>
+        </is>
+      </c>
+      <c r="D68" s="12" t="n">
+        <v>1165</v>
+      </c>
+      <c r="E68" s="85">
+        <f>$D$3</f>
+        <v/>
+      </c>
+      <c r="F68" s="32">
+        <f>D68*$D$3*8</f>
+        <v/>
+      </c>
+      <c r="G68" s="83" t="inlineStr">
+        <is>
+          <t>間接</t>
+        </is>
+      </c>
+      <c r="H68" s="81" t="inlineStr">
+        <is>
+          <t>文書交換室</t>
+        </is>
+      </c>
+      <c r="I68" s="82">
+        <f>F68*12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="69" ht="20" customHeight="1">
+      <c r="A69" s="76" t="inlineStr">
+        <is>
+          <t>本社</t>
+        </is>
+      </c>
+      <c r="B69" s="77" t="inlineStr">
+        <is>
+          <t>吉川 洋平</t>
+        </is>
+      </c>
+      <c r="C69" s="84" t="inlineStr">
+        <is>
+          <t>時給</t>
+        </is>
+      </c>
+      <c r="D69" s="12" t="n">
+        <v>1165</v>
+      </c>
+      <c r="E69" s="85">
+        <f>$D$3</f>
+        <v/>
+      </c>
+      <c r="F69" s="32">
+        <f>D69*$D$3*8</f>
+        <v/>
+      </c>
+      <c r="G69" s="83" t="inlineStr">
+        <is>
+          <t>間接</t>
+        </is>
+      </c>
+      <c r="H69" s="81" t="inlineStr">
+        <is>
+          <t>文書交換室</t>
+        </is>
+      </c>
+      <c r="I69" s="82">
+        <f>F69*12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="70" ht="20" customHeight="1">
+      <c r="A70" s="76" t="inlineStr">
+        <is>
+          <t>本社</t>
+        </is>
+      </c>
+      <c r="B70" s="77" t="inlineStr">
+        <is>
+          <t>野村 正信</t>
+        </is>
+      </c>
+      <c r="C70" s="84" t="inlineStr">
+        <is>
+          <t>時給</t>
+        </is>
+      </c>
+      <c r="D70" s="12" t="n">
+        <v>1165</v>
+      </c>
+      <c r="E70" s="85">
+        <f>$D$3</f>
+        <v/>
+      </c>
+      <c r="F70" s="32">
+        <f>D70*$D$3*8</f>
+        <v/>
+      </c>
+      <c r="G70" s="83" t="inlineStr">
+        <is>
+          <t>間接</t>
+        </is>
+      </c>
+      <c r="H70" s="81" t="inlineStr">
+        <is>
+          <t>文書交換室</t>
+        </is>
+      </c>
+      <c r="I70" s="82">
+        <f>F70*12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="71" ht="20" customHeight="1">
+      <c r="A71" s="76" t="inlineStr">
+        <is>
+          <t>本社</t>
+        </is>
+      </c>
+      <c r="B71" s="77" t="inlineStr">
+        <is>
+          <t>野原 典子</t>
+        </is>
+      </c>
+      <c r="C71" s="84" t="inlineStr">
+        <is>
+          <t>時給</t>
+        </is>
+      </c>
+      <c r="D71" s="12" t="n">
+        <v>1165</v>
+      </c>
+      <c r="E71" s="85">
+        <f>$D$3</f>
+        <v/>
+      </c>
+      <c r="F71" s="32">
+        <f>D71*$D$3*8</f>
+        <v/>
+      </c>
+      <c r="G71" s="83" t="inlineStr">
+        <is>
+          <t>間接</t>
+        </is>
+      </c>
+      <c r="H71" s="81" t="inlineStr">
+        <is>
+          <t>文書交換室</t>
+        </is>
+      </c>
+      <c r="I71" s="82">
+        <f>F71*12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="72" ht="20" customHeight="1">
+      <c r="A72" s="76" t="inlineStr">
+        <is>
+          <t>本社</t>
+        </is>
+      </c>
+      <c r="B72" s="77" t="inlineStr">
+        <is>
+          <t>坂本多枝子</t>
+        </is>
+      </c>
+      <c r="C72" s="84" t="inlineStr">
+        <is>
+          <t>時給</t>
+        </is>
+      </c>
+      <c r="D72" s="12" t="n">
+        <v>1165</v>
+      </c>
+      <c r="E72" s="85">
+        <f>$D$3</f>
+        <v/>
+      </c>
+      <c r="F72" s="32">
+        <f>D72*$D$3*8</f>
+        <v/>
+      </c>
+      <c r="G72" s="83" t="inlineStr">
+        <is>
+          <t>間接</t>
+        </is>
+      </c>
+      <c r="H72" s="81" t="inlineStr">
+        <is>
+          <t>文書交換室</t>
+        </is>
+      </c>
+      <c r="I72" s="82">
+        <f>F72*12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="73" ht="20" customHeight="1">
+      <c r="A73" s="76" t="inlineStr">
+        <is>
+          <t>本社</t>
+        </is>
+      </c>
+      <c r="B73" s="77" t="inlineStr">
+        <is>
+          <t>矢作 明美</t>
+        </is>
+      </c>
+      <c r="C73" s="84" t="inlineStr">
+        <is>
+          <t>時給</t>
+        </is>
+      </c>
+      <c r="D73" s="12" t="n">
+        <v>1165</v>
+      </c>
+      <c r="E73" s="85">
+        <f>$D$3</f>
+        <v/>
+      </c>
+      <c r="F73" s="32">
+        <f>D73*$D$3*8</f>
+        <v/>
+      </c>
+      <c r="G73" s="83" t="inlineStr">
+        <is>
+          <t>間接</t>
+        </is>
+      </c>
+      <c r="H73" s="81" t="inlineStr">
+        <is>
+          <t>文書交換室</t>
+        </is>
+      </c>
+      <c r="I73" s="82">
+        <f>F73*12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="74" ht="20" customHeight="1">
+      <c r="A74" s="76" t="inlineStr">
+        <is>
+          <t>本社</t>
+        </is>
+      </c>
+      <c r="B74" s="77" t="inlineStr">
+        <is>
+          <t>木村 貴子</t>
+        </is>
+      </c>
+      <c r="C74" s="84" t="inlineStr">
+        <is>
+          <t>時給</t>
+        </is>
+      </c>
+      <c r="D74" s="12" t="n">
+        <v>1165</v>
+      </c>
+      <c r="E74" s="85">
+        <f>$D$3</f>
+        <v/>
+      </c>
+      <c r="F74" s="32">
+        <f>D74*$D$3*8</f>
+        <v/>
+      </c>
+      <c r="G74" s="83" t="inlineStr">
+        <is>
+          <t>間接</t>
+        </is>
+      </c>
+      <c r="H74" s="81" t="inlineStr">
+        <is>
+          <t>文書交換室</t>
+        </is>
+      </c>
+      <c r="I74" s="82">
+        <f>F74*12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="75" ht="20" customHeight="1">
+      <c r="A75" s="76" t="inlineStr">
+        <is>
+          <t>本社</t>
+        </is>
+      </c>
+      <c r="B75" s="77" t="inlineStr">
+        <is>
+          <t>稲富 笑子</t>
+        </is>
+      </c>
+      <c r="C75" s="84" t="inlineStr">
+        <is>
+          <t>時給</t>
+        </is>
+      </c>
+      <c r="D75" s="12" t="n">
+        <v>1165</v>
+      </c>
+      <c r="E75" s="85">
+        <f>$D$3</f>
+        <v/>
+      </c>
+      <c r="F75" s="32">
+        <f>D75*$D$3*8</f>
+        <v/>
+      </c>
+      <c r="G75" s="83" t="inlineStr">
+        <is>
+          <t>間接</t>
+        </is>
+      </c>
+      <c r="H75" s="81" t="inlineStr">
+        <is>
+          <t>文書交換室</t>
+        </is>
+      </c>
+      <c r="I75" s="82">
+        <f>F75*12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="76" ht="20" customHeight="1">
+      <c r="A76" s="76" t="inlineStr">
+        <is>
+          <t>本社</t>
+        </is>
+      </c>
+      <c r="B76" s="77" t="inlineStr">
+        <is>
+          <t>芳本 智代</t>
+        </is>
+      </c>
+      <c r="C76" s="84" t="inlineStr">
+        <is>
+          <t>時給</t>
+        </is>
+      </c>
+      <c r="D76" s="12" t="n">
+        <v>1165</v>
+      </c>
+      <c r="E76" s="85">
+        <f>$D$3</f>
+        <v/>
+      </c>
+      <c r="F76" s="32">
+        <f>D76*$D$3*8</f>
+        <v/>
+      </c>
+      <c r="G76" s="83" t="inlineStr">
+        <is>
+          <t>間接</t>
+        </is>
+      </c>
+      <c r="H76" s="81" t="inlineStr">
+        <is>
+          <t>文書交換室</t>
+        </is>
+      </c>
+      <c r="I76" s="82">
+        <f>F76*12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="77" ht="20" customHeight="1">
+      <c r="A77" s="76" t="inlineStr">
+        <is>
+          <t>本社</t>
+        </is>
+      </c>
+      <c r="B77" s="77" t="inlineStr">
+        <is>
+          <t>村上 博美</t>
+        </is>
+      </c>
+      <c r="C77" s="86" t="inlineStr">
+        <is>
+          <t>自転車</t>
+        </is>
+      </c>
+      <c r="D77" s="87" t="n">
+        <v>8447</v>
+      </c>
+      <c r="E77" s="85">
+        <f>$D$3</f>
+        <v/>
+      </c>
+      <c r="F77" s="32">
+        <f>D77*$D$3</f>
+        <v/>
+      </c>
+      <c r="G77" s="80" t="inlineStr">
+        <is>
+          <t>直接</t>
+        </is>
+      </c>
+      <c r="H77" s="81" t="inlineStr">
+        <is>
+          <t>7.25h</t>
+        </is>
+      </c>
+      <c r="I77" s="82">
+        <f>F77*12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="78" ht="20" customHeight="1">
+      <c r="A78" s="76" t="inlineStr">
+        <is>
+          <t>本社</t>
+        </is>
+      </c>
+      <c r="B78" s="77" t="inlineStr">
+        <is>
+          <t>渡邊 茂夫</t>
+        </is>
+      </c>
+      <c r="C78" s="86" t="inlineStr">
+        <is>
+          <t>自転車</t>
+        </is>
+      </c>
+      <c r="D78" s="87" t="n">
+        <v>8447</v>
+      </c>
+      <c r="E78" s="85">
+        <f>$D$3</f>
+        <v/>
+      </c>
+      <c r="F78" s="32">
+        <f>D78*$D$3</f>
+        <v/>
+      </c>
+      <c r="G78" s="80" t="inlineStr">
+        <is>
+          <t>直接</t>
+        </is>
+      </c>
+      <c r="H78" s="81" t="inlineStr">
+        <is>
+          <t>7.25h</t>
+        </is>
+      </c>
+      <c r="I78" s="82">
+        <f>F78*12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="79" ht="20" customHeight="1">
+      <c r="A79" s="76" t="inlineStr">
+        <is>
+          <t>本社</t>
+        </is>
+      </c>
+      <c r="B79" s="77" t="inlineStr">
+        <is>
+          <t>川満 俊一</t>
+        </is>
+      </c>
+      <c r="C79" s="86" t="inlineStr">
+        <is>
+          <t>自転車</t>
+        </is>
+      </c>
+      <c r="D79" s="87" t="n">
+        <v>8447</v>
+      </c>
+      <c r="E79" s="85">
+        <f>$D$3</f>
+        <v/>
+      </c>
+      <c r="F79" s="32">
+        <f>D79*$D$3</f>
+        <v/>
+      </c>
+      <c r="G79" s="80" t="inlineStr">
+        <is>
+          <t>直接</t>
+        </is>
+      </c>
+      <c r="H79" s="81" t="inlineStr">
+        <is>
+          <t>7.25h</t>
+        </is>
+      </c>
+      <c r="I79" s="82">
+        <f>F79*12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="80" ht="20" customHeight="1">
+      <c r="A80" s="76" t="inlineStr">
+        <is>
+          <t>本社</t>
+        </is>
+      </c>
+      <c r="B80" s="77" t="inlineStr">
+        <is>
+          <t>阿久津信介</t>
+        </is>
+      </c>
+      <c r="C80" s="86" t="inlineStr">
+        <is>
+          <t>自転車</t>
+        </is>
+      </c>
+      <c r="D80" s="87" t="n">
+        <v>8447</v>
+      </c>
+      <c r="E80" s="85">
+        <f>$D$3</f>
+        <v/>
+      </c>
+      <c r="F80" s="32">
+        <f>D80*$D$3</f>
+        <v/>
+      </c>
+      <c r="G80" s="80" t="inlineStr">
+        <is>
+          <t>直接</t>
+        </is>
+      </c>
+      <c r="H80" s="81" t="inlineStr">
+        <is>
+          <t>7.25h 班長手当</t>
+        </is>
+      </c>
+      <c r="I80" s="82">
+        <f>F80*12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="81" ht="20" customHeight="1">
+      <c r="A81" s="76" t="inlineStr">
+        <is>
+          <t>本社</t>
+        </is>
+      </c>
+      <c r="B81" s="77" t="inlineStr">
+        <is>
+          <t>竹内 和夫</t>
+        </is>
+      </c>
+      <c r="C81" s="86" t="inlineStr">
+        <is>
+          <t>自転車</t>
+        </is>
+      </c>
+      <c r="D81" s="87" t="n">
+        <v>8447</v>
+      </c>
+      <c r="E81" s="85">
+        <f>$D$3</f>
+        <v/>
+      </c>
+      <c r="F81" s="32">
+        <f>D81*$D$3</f>
+        <v/>
+      </c>
+      <c r="G81" s="80" t="inlineStr">
+        <is>
+          <t>直接</t>
+        </is>
+      </c>
+      <c r="H81" s="81" t="inlineStr">
+        <is>
+          <t>7.25h</t>
+        </is>
+      </c>
+      <c r="I81" s="82">
+        <f>F81*12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="82" ht="20" customHeight="1">
+      <c r="A82" s="76" t="inlineStr">
+        <is>
+          <t>本社</t>
+        </is>
+      </c>
+      <c r="B82" s="77" t="inlineStr">
+        <is>
+          <t>橋本富士夫</t>
+        </is>
+      </c>
+      <c r="C82" s="86" t="inlineStr">
+        <is>
+          <t>自転車</t>
+        </is>
+      </c>
+      <c r="D82" s="87" t="n">
+        <v>8447</v>
+      </c>
+      <c r="E82" s="85">
+        <f>$D$3</f>
+        <v/>
+      </c>
+      <c r="F82" s="32">
+        <f>D82*$D$3</f>
+        <v/>
+      </c>
+      <c r="G82" s="80" t="inlineStr">
+        <is>
+          <t>直接</t>
+        </is>
+      </c>
+      <c r="H82" s="81" t="inlineStr">
+        <is>
+          <t>7.25h</t>
+        </is>
+      </c>
+      <c r="I82" s="82">
+        <f>F82*12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="83" ht="20" customHeight="1">
+      <c r="A83" s="76" t="inlineStr">
+        <is>
+          <t>本社</t>
+        </is>
+      </c>
+      <c r="B83" s="77" t="inlineStr">
+        <is>
+          <t>三浦 勲</t>
+        </is>
+      </c>
+      <c r="C83" s="86" t="inlineStr">
+        <is>
+          <t>自転車</t>
+        </is>
+      </c>
+      <c r="D83" s="87" t="n">
+        <v>8447</v>
+      </c>
+      <c r="E83" s="85">
+        <f>$D$3</f>
+        <v/>
+      </c>
+      <c r="F83" s="32">
+        <f>D83*$D$3</f>
+        <v/>
+      </c>
+      <c r="G83" s="80" t="inlineStr">
+        <is>
+          <t>直接</t>
+        </is>
+      </c>
+      <c r="H83" s="81" t="inlineStr">
+        <is>
+          <t>7.25h</t>
+        </is>
+      </c>
+      <c r="I83" s="82">
+        <f>F83*12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="84" ht="20" customHeight="1">
+      <c r="A84" s="76" t="inlineStr">
+        <is>
+          <t>本社</t>
+        </is>
+      </c>
+      <c r="B84" s="77" t="inlineStr">
+        <is>
+          <t>青木 茂</t>
+        </is>
+      </c>
+      <c r="C84" s="86" t="inlineStr">
+        <is>
+          <t>自転車</t>
+        </is>
+      </c>
+      <c r="D84" s="87" t="n">
+        <v>8447</v>
+      </c>
+      <c r="E84" s="85">
+        <f>$D$3</f>
+        <v/>
+      </c>
+      <c r="F84" s="32">
+        <f>D84*$D$3</f>
+        <v/>
+      </c>
+      <c r="G84" s="80" t="inlineStr">
+        <is>
+          <t>直接</t>
+        </is>
+      </c>
+      <c r="H84" s="81" t="inlineStr">
+        <is>
+          <t>7.25h</t>
+        </is>
+      </c>
+      <c r="I84" s="82">
+        <f>F84*12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="85" ht="20" customHeight="1">
+      <c r="A85" s="76" t="inlineStr">
+        <is>
+          <t>本社</t>
+        </is>
+      </c>
+      <c r="B85" s="77" t="inlineStr">
+        <is>
+          <t>後藤 高広</t>
+        </is>
+      </c>
+      <c r="C85" s="86" t="inlineStr">
+        <is>
+          <t>自転車</t>
+        </is>
+      </c>
+      <c r="D85" s="87" t="n">
+        <v>8447</v>
+      </c>
+      <c r="E85" s="85">
+        <f>$D$3</f>
+        <v/>
+      </c>
+      <c r="F85" s="32">
+        <f>D85*$D$3</f>
+        <v/>
+      </c>
+      <c r="G85" s="80" t="inlineStr">
+        <is>
+          <t>直接</t>
+        </is>
+      </c>
+      <c r="H85" s="81" t="inlineStr">
+        <is>
+          <t>7.25h</t>
+        </is>
+      </c>
+      <c r="I85" s="82">
+        <f>F85*12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="86" ht="20" customHeight="1">
+      <c r="A86" s="76" t="inlineStr">
+        <is>
+          <t>本社</t>
+        </is>
+      </c>
+      <c r="B86" s="77" t="inlineStr">
+        <is>
+          <t>平山 進</t>
+        </is>
+      </c>
+      <c r="C86" s="86" t="inlineStr">
+        <is>
+          <t>自転車</t>
+        </is>
+      </c>
+      <c r="D86" s="87" t="n">
+        <v>8447</v>
+      </c>
+      <c r="E86" s="85">
+        <f>$D$3</f>
+        <v/>
+      </c>
+      <c r="F86" s="32">
+        <f>D86*$D$3</f>
+        <v/>
+      </c>
+      <c r="G86" s="80" t="inlineStr">
+        <is>
+          <t>直接</t>
+        </is>
+      </c>
+      <c r="H86" s="81" t="inlineStr">
+        <is>
+          <t>7.25h</t>
+        </is>
+      </c>
+      <c r="I86" s="82">
+        <f>F86*12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="87" ht="20" customHeight="1">
+      <c r="A87" s="76" t="inlineStr">
+        <is>
+          <t>本社</t>
+        </is>
+      </c>
+      <c r="B87" s="77" t="inlineStr">
+        <is>
+          <t>小松 真裕</t>
+        </is>
+      </c>
+      <c r="C87" s="86" t="inlineStr">
+        <is>
+          <t>自転車</t>
+        </is>
+      </c>
+      <c r="D87" s="87" t="n">
+        <v>8447</v>
+      </c>
+      <c r="E87" s="85">
+        <f>$D$3</f>
+        <v/>
+      </c>
+      <c r="F87" s="32">
+        <f>D87*$D$3</f>
+        <v/>
+      </c>
+      <c r="G87" s="80" t="inlineStr">
+        <is>
+          <t>直接</t>
+        </is>
+      </c>
+      <c r="H87" s="81" t="inlineStr">
+        <is>
+          <t>7.25h</t>
+        </is>
+      </c>
+      <c r="I87" s="82">
+        <f>F87*12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="88" ht="20" customHeight="1">
+      <c r="A88" s="76" t="inlineStr">
+        <is>
+          <t>本社</t>
+        </is>
+      </c>
+      <c r="B88" s="77" t="inlineStr">
+        <is>
+          <t>奥園 達雄</t>
+        </is>
+      </c>
+      <c r="C88" s="86" t="inlineStr">
+        <is>
+          <t>自転車</t>
+        </is>
+      </c>
+      <c r="D88" s="87" t="n">
+        <v>8447</v>
+      </c>
+      <c r="E88" s="85">
+        <f>$D$3</f>
+        <v/>
+      </c>
+      <c r="F88" s="32">
+        <f>D88*$D$3</f>
+        <v/>
+      </c>
+      <c r="G88" s="80" t="inlineStr">
+        <is>
+          <t>直接</t>
+        </is>
+      </c>
+      <c r="H88" s="81" t="inlineStr">
+        <is>
+          <t>7.25h</t>
+        </is>
+      </c>
+      <c r="I88" s="82">
+        <f>F88*12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="89" ht="20" customHeight="1">
+      <c r="A89" s="76" t="inlineStr">
+        <is>
+          <t>本社</t>
+        </is>
+      </c>
+      <c r="B89" s="77" t="inlineStr">
+        <is>
+          <t>伊藤 直道</t>
+        </is>
+      </c>
+      <c r="C89" s="86" t="inlineStr">
+        <is>
+          <t>自転車</t>
+        </is>
+      </c>
+      <c r="D89" s="87" t="n">
+        <v>8447</v>
+      </c>
+      <c r="E89" s="85">
+        <f>$D$3</f>
+        <v/>
+      </c>
+      <c r="F89" s="32">
+        <f>D89*$D$3</f>
+        <v/>
+      </c>
+      <c r="G89" s="80" t="inlineStr">
+        <is>
+          <t>直接</t>
+        </is>
+      </c>
+      <c r="H89" s="81" t="inlineStr">
+        <is>
+          <t>7.25h</t>
+        </is>
+      </c>
+      <c r="I89" s="82">
+        <f>F89*12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="90" ht="20" customHeight="1">
+      <c r="A90" s="76" t="inlineStr">
+        <is>
+          <t>本社</t>
+        </is>
+      </c>
+      <c r="B90" s="77" t="inlineStr">
+        <is>
+          <t>仲眞 栄治</t>
+        </is>
+      </c>
+      <c r="C90" s="86" t="inlineStr">
+        <is>
+          <t>自転車</t>
+        </is>
+      </c>
+      <c r="D90" s="87" t="n">
+        <v>8447</v>
+      </c>
+      <c r="E90" s="85">
+        <f>$D$3</f>
+        <v/>
+      </c>
+      <c r="F90" s="32">
+        <f>D90*$D$3</f>
+        <v/>
+      </c>
+      <c r="G90" s="80" t="inlineStr">
+        <is>
+          <t>直接</t>
+        </is>
+      </c>
+      <c r="H90" s="81" t="inlineStr">
+        <is>
+          <t>7.25h</t>
+        </is>
+      </c>
+      <c r="I90" s="82">
+        <f>F90*12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="91" ht="20" customHeight="1">
+      <c r="A91" s="76" t="inlineStr">
+        <is>
+          <t>本社</t>
+        </is>
+      </c>
+      <c r="B91" s="77" t="inlineStr">
+        <is>
+          <t>白井 久雄</t>
+        </is>
+      </c>
+      <c r="C91" s="86" t="inlineStr">
+        <is>
+          <t>自転車</t>
+        </is>
+      </c>
+      <c r="D91" s="87" t="n">
+        <v>8447</v>
+      </c>
+      <c r="E91" s="85">
+        <f>$D$3</f>
+        <v/>
+      </c>
+      <c r="F91" s="32">
+        <f>D91*$D$3</f>
+        <v/>
+      </c>
+      <c r="G91" s="80" t="inlineStr">
+        <is>
+          <t>直接</t>
+        </is>
+      </c>
+      <c r="H91" s="81" t="inlineStr">
+        <is>
+          <t>7.25h</t>
+        </is>
+      </c>
+      <c r="I91" s="82">
+        <f>F91*12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="92" ht="20" customHeight="1">
+      <c r="A92" s="76" t="inlineStr">
+        <is>
+          <t>本社</t>
+        </is>
+      </c>
+      <c r="B92" s="77" t="inlineStr">
+        <is>
+          <t>仲 宏樹</t>
+        </is>
+      </c>
+      <c r="C92" s="86" t="inlineStr">
+        <is>
+          <t>自転車</t>
+        </is>
+      </c>
+      <c r="D92" s="87" t="n">
+        <v>8447</v>
+      </c>
+      <c r="E92" s="85">
+        <f>$D$3</f>
+        <v/>
+      </c>
+      <c r="F92" s="32">
+        <f>D92*$D$3</f>
+        <v/>
+      </c>
+      <c r="G92" s="80" t="inlineStr">
+        <is>
+          <t>直接</t>
+        </is>
+      </c>
+      <c r="H92" s="81" t="inlineStr">
+        <is>
+          <t>7.25h 能率2</t>
+        </is>
+      </c>
+      <c r="I92" s="82">
+        <f>F92*12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="93" ht="20" customHeight="1">
+      <c r="A93" s="76" t="inlineStr">
+        <is>
+          <t>本社</t>
+        </is>
+      </c>
+      <c r="B93" s="77" t="inlineStr">
+        <is>
+          <t>石井 英明</t>
+        </is>
+      </c>
+      <c r="C93" s="86" t="inlineStr">
+        <is>
+          <t>自転車</t>
+        </is>
+      </c>
+      <c r="D93" s="87" t="n">
+        <v>8447</v>
+      </c>
+      <c r="E93" s="85">
+        <f>$D$3</f>
+        <v/>
+      </c>
+      <c r="F93" s="32">
+        <f>D93*$D$3</f>
+        <v/>
+      </c>
+      <c r="G93" s="80" t="inlineStr">
+        <is>
+          <t>直接</t>
+        </is>
+      </c>
+      <c r="H93" s="81" t="inlineStr">
+        <is>
+          <t>7.25h</t>
+        </is>
+      </c>
+      <c r="I93" s="82">
+        <f>F93*12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="94" ht="20" customHeight="1">
+      <c r="A94" s="76" t="inlineStr">
+        <is>
+          <t>本社</t>
+        </is>
+      </c>
+      <c r="B94" s="77" t="inlineStr">
+        <is>
+          <t>赤間 茂</t>
+        </is>
+      </c>
+      <c r="C94" s="86" t="inlineStr">
+        <is>
+          <t>自転車</t>
+        </is>
+      </c>
+      <c r="D94" s="87" t="n">
+        <v>8447</v>
+      </c>
+      <c r="E94" s="85">
+        <f>$D$3</f>
+        <v/>
+      </c>
+      <c r="F94" s="32">
+        <f>D94*$D$3</f>
+        <v/>
+      </c>
+      <c r="G94" s="80" t="inlineStr">
+        <is>
+          <t>直接</t>
+        </is>
+      </c>
+      <c r="H94" s="81" t="inlineStr">
+        <is>
+          <t>7.25h</t>
+        </is>
+      </c>
+      <c r="I94" s="82">
+        <f>F94*12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="95" ht="20" customHeight="1">
+      <c r="A95" s="76" t="inlineStr">
+        <is>
+          <t>本社</t>
+        </is>
+      </c>
+      <c r="B95" s="77" t="inlineStr">
+        <is>
+          <t>宇田川博之</t>
+        </is>
+      </c>
+      <c r="C95" s="86" t="inlineStr">
+        <is>
+          <t>自転車</t>
+        </is>
+      </c>
+      <c r="D95" s="87" t="n">
+        <v>8447</v>
+      </c>
+      <c r="E95" s="85">
+        <f>$D$3</f>
+        <v/>
+      </c>
+      <c r="F95" s="32">
+        <f>D95*$D$3</f>
+        <v/>
+      </c>
+      <c r="G95" s="80" t="inlineStr">
+        <is>
+          <t>直接</t>
+        </is>
+      </c>
+      <c r="H95" s="81" t="inlineStr">
+        <is>
+          <t>7.25h</t>
+        </is>
+      </c>
+      <c r="I95" s="82">
+        <f>F95*12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="96" ht="20" customHeight="1">
+      <c r="A96" s="76" t="inlineStr">
+        <is>
+          <t>本社</t>
+        </is>
+      </c>
+      <c r="B96" s="77" t="inlineStr">
+        <is>
+          <t>菊池 義一</t>
+        </is>
+      </c>
+      <c r="C96" s="86" t="inlineStr">
+        <is>
+          <t>自転車</t>
+        </is>
+      </c>
+      <c r="D96" s="87" t="n">
+        <v>8447</v>
+      </c>
+      <c r="E96" s="85">
+        <f>$D$3</f>
+        <v/>
+      </c>
+      <c r="F96" s="32">
+        <f>D96*$D$3</f>
+        <v/>
+      </c>
+      <c r="G96" s="80" t="inlineStr">
+        <is>
+          <t>直接</t>
+        </is>
+      </c>
+      <c r="H96" s="81" t="inlineStr">
+        <is>
+          <t>7.25h</t>
+        </is>
+      </c>
+      <c r="I96" s="82">
+        <f>F96*12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="97" ht="20" customHeight="1">
+      <c r="A97" s="76" t="inlineStr">
+        <is>
+          <t>本社</t>
+        </is>
+      </c>
+      <c r="B97" s="77" t="inlineStr">
+        <is>
+          <t>森 涼太</t>
+        </is>
+      </c>
+      <c r="C97" s="86" t="inlineStr">
+        <is>
+          <t>自転車</t>
+        </is>
+      </c>
+      <c r="D97" s="87" t="n">
+        <v>8447</v>
+      </c>
+      <c r="E97" s="85">
+        <f>$D$3</f>
+        <v/>
+      </c>
+      <c r="F97" s="32">
+        <f>D97*$D$3</f>
+        <v/>
+      </c>
+      <c r="G97" s="80" t="inlineStr">
+        <is>
+          <t>直接</t>
+        </is>
+      </c>
+      <c r="H97" s="81" t="inlineStr">
+        <is>
+          <t>7.25h 能率2</t>
+        </is>
+      </c>
+      <c r="I97" s="82">
+        <f>F97*12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="98" ht="18" customHeight="1">
+      <c r="A98" s="88" t="inlineStr">
+        <is>
+          <t>本社 合計  (92名)</t>
+        </is>
+      </c>
+      <c r="F98" s="89">
+        <f>SUMIF(A6:A97,"本社",F6:F97)</f>
+        <v/>
+      </c>
+      <c r="G98" s="90" t="n"/>
+      <c r="H98" s="90" t="n"/>
+      <c r="I98" s="90" t="n"/>
+    </row>
+    <row r="99" ht="20" customHeight="1">
+      <c r="A99" s="91" t="inlineStr">
+        <is>
+          <t>■ 板橋</t>
+        </is>
+      </c>
+    </row>
+    <row r="100" ht="20" customHeight="1">
+      <c r="A100" s="92" t="inlineStr">
+        <is>
+          <t>板橋</t>
+        </is>
+      </c>
+      <c r="B100" s="93" t="inlineStr">
+        <is>
+          <t>舟山 真純</t>
+        </is>
+      </c>
+      <c r="C100" s="78" t="inlineStr">
+        <is>
+          <t>月給</t>
+        </is>
+      </c>
+      <c r="D100" s="60" t="n">
+        <v>278155</v>
+      </c>
+      <c r="E100" s="94" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F100" s="32" t="n">
+        <v>278155</v>
+      </c>
+      <c r="G100" s="80" t="inlineStr">
+        <is>
+          <t>直接</t>
+        </is>
+      </c>
+      <c r="H100" s="95" t="inlineStr">
+        <is>
+          <t>KC</t>
+        </is>
+      </c>
+      <c r="I100" s="82" t="n">
+        <v>3337860</v>
+      </c>
+    </row>
+    <row r="101" ht="20" customHeight="1">
+      <c r="A101" s="92" t="inlineStr">
+        <is>
+          <t>板橋</t>
+        </is>
+      </c>
+      <c r="B101" s="93" t="inlineStr">
+        <is>
+          <t>真栄城玄昌</t>
+        </is>
+      </c>
+      <c r="C101" s="78" t="inlineStr">
+        <is>
+          <t>月給</t>
+        </is>
+      </c>
+      <c r="D101" s="60" t="n">
+        <v>278545</v>
+      </c>
+      <c r="E101" s="94" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F101" s="32" t="n">
+        <v>278545</v>
+      </c>
+      <c r="G101" s="80" t="inlineStr">
+        <is>
+          <t>直接</t>
+        </is>
+      </c>
+      <c r="H101" s="95" t="inlineStr"/>
+      <c r="I101" s="82" t="n">
+        <v>3342540</v>
+      </c>
+    </row>
+    <row r="102" ht="20" customHeight="1">
+      <c r="A102" s="92" t="inlineStr">
+        <is>
+          <t>板橋</t>
+        </is>
+      </c>
+      <c r="B102" s="93" t="inlineStr">
+        <is>
+          <t>長野 義昭</t>
+        </is>
+      </c>
+      <c r="C102" s="78" t="inlineStr">
+        <is>
+          <t>月給</t>
+        </is>
+      </c>
+      <c r="D102" s="60" t="n">
+        <v>269395</v>
+      </c>
+      <c r="E102" s="94" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F102" s="32" t="n">
+        <v>269395</v>
+      </c>
+      <c r="G102" s="80" t="inlineStr">
+        <is>
+          <t>直接</t>
+        </is>
+      </c>
+      <c r="H102" s="95" t="inlineStr">
+        <is>
+          <t>深夜</t>
+        </is>
+      </c>
+      <c r="I102" s="82" t="n">
+        <v>3232740</v>
+      </c>
+    </row>
+    <row r="103" ht="20" customHeight="1">
+      <c r="A103" s="92" t="inlineStr">
+        <is>
+          <t>板橋</t>
+        </is>
+      </c>
+      <c r="B103" s="93" t="inlineStr">
+        <is>
+          <t>大森 茂</t>
+        </is>
+      </c>
+      <c r="C103" s="78" t="inlineStr">
+        <is>
+          <t>月給</t>
+        </is>
+      </c>
+      <c r="D103" s="60" t="n">
+        <v>276395</v>
+      </c>
+      <c r="E103" s="94" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F103" s="32" t="n">
+        <v>276395</v>
+      </c>
+      <c r="G103" s="80" t="inlineStr">
+        <is>
+          <t>直接</t>
+        </is>
+      </c>
+      <c r="H103" s="95" t="inlineStr">
+        <is>
+          <t>深夜</t>
+        </is>
+      </c>
+      <c r="I103" s="82" t="n">
+        <v>3316740</v>
+      </c>
+    </row>
+    <row r="104" ht="20" customHeight="1">
+      <c r="A104" s="92" t="inlineStr">
+        <is>
+          <t>板橋</t>
+        </is>
+      </c>
+      <c r="B104" s="93" t="inlineStr">
+        <is>
+          <t>柳沼 清志</t>
+        </is>
+      </c>
+      <c r="C104" s="78" t="inlineStr">
+        <is>
+          <t>月給</t>
+        </is>
+      </c>
+      <c r="D104" s="60" t="n">
+        <v>276395</v>
+      </c>
+      <c r="E104" s="94" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F104" s="32" t="n">
+        <v>276395</v>
+      </c>
+      <c r="G104" s="80" t="inlineStr">
+        <is>
+          <t>直接</t>
+        </is>
+      </c>
+      <c r="H104" s="95" t="inlineStr"/>
+      <c r="I104" s="82" t="n">
+        <v>3316740</v>
+      </c>
+    </row>
+    <row r="105" ht="20" customHeight="1">
+      <c r="A105" s="92" t="inlineStr">
+        <is>
+          <t>板橋</t>
+        </is>
+      </c>
+      <c r="B105" s="93" t="inlineStr">
+        <is>
+          <t>内田 温城</t>
+        </is>
+      </c>
+      <c r="C105" s="78" t="inlineStr">
+        <is>
+          <t>月給</t>
+        </is>
+      </c>
+      <c r="D105" s="60" t="n">
+        <v>253155</v>
+      </c>
+      <c r="E105" s="94" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F105" s="32" t="n">
+        <v>253155</v>
+      </c>
+      <c r="G105" s="80" t="inlineStr">
+        <is>
+          <t>直接</t>
+        </is>
+      </c>
+      <c r="H105" s="95" t="inlineStr"/>
+      <c r="I105" s="82" t="n">
+        <v>3037860</v>
+      </c>
+    </row>
+    <row r="106" ht="20" customHeight="1">
+      <c r="A106" s="92" t="inlineStr">
+        <is>
+          <t>板橋</t>
+        </is>
+      </c>
+      <c r="B106" s="93" t="inlineStr">
+        <is>
+          <t>大迫 二郎</t>
+        </is>
+      </c>
+      <c r="C106" s="78" t="inlineStr">
+        <is>
+          <t>月給</t>
+        </is>
+      </c>
+      <c r="D106" s="60" t="n">
+        <v>253155</v>
+      </c>
+      <c r="E106" s="94" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F106" s="32" t="n">
+        <v>253155</v>
+      </c>
+      <c r="G106" s="80" t="inlineStr">
+        <is>
+          <t>直接</t>
+        </is>
+      </c>
+      <c r="H106" s="95" t="inlineStr">
+        <is>
+          <t>深夜</t>
+        </is>
+      </c>
+      <c r="I106" s="82" t="n">
+        <v>3037860</v>
+      </c>
+    </row>
+    <row r="107" ht="20" customHeight="1">
+      <c r="A107" s="92" t="inlineStr">
+        <is>
+          <t>板橋</t>
+        </is>
+      </c>
+      <c r="B107" s="93" t="inlineStr">
+        <is>
+          <t>黒澤栄次郎</t>
+        </is>
+      </c>
+      <c r="C107" s="78" t="inlineStr">
+        <is>
+          <t>月給</t>
+        </is>
+      </c>
+      <c r="D107" s="60" t="n">
+        <v>253155</v>
+      </c>
+      <c r="E107" s="94" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F107" s="32" t="n">
+        <v>253155</v>
+      </c>
+      <c r="G107" s="80" t="inlineStr">
+        <is>
+          <t>直接</t>
+        </is>
+      </c>
+      <c r="H107" s="95" t="inlineStr">
+        <is>
+          <t>深夜</t>
+        </is>
+      </c>
+      <c r="I107" s="82" t="n">
+        <v>3037860</v>
+      </c>
+    </row>
+    <row r="108" ht="20" customHeight="1">
+      <c r="A108" s="92" t="inlineStr">
+        <is>
+          <t>板橋</t>
+        </is>
+      </c>
+      <c r="B108" s="93" t="inlineStr">
+        <is>
+          <t>千葉 実</t>
+        </is>
+      </c>
+      <c r="C108" s="78" t="inlineStr">
+        <is>
+          <t>月給</t>
+        </is>
+      </c>
+      <c r="D108" s="60" t="n">
+        <v>253155</v>
+      </c>
+      <c r="E108" s="94" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F108" s="32" t="n">
+        <v>253155</v>
+      </c>
+      <c r="G108" s="80" t="inlineStr">
+        <is>
+          <t>直接</t>
+        </is>
+      </c>
+      <c r="H108" s="95" t="inlineStr">
+        <is>
+          <t>深夜</t>
+        </is>
+      </c>
+      <c r="I108" s="82" t="n">
+        <v>3037860</v>
+      </c>
+    </row>
+    <row r="109" ht="20" customHeight="1">
+      <c r="A109" s="92" t="inlineStr">
+        <is>
+          <t>板橋</t>
+        </is>
+      </c>
+      <c r="B109" s="93" t="inlineStr">
+        <is>
+          <t>宮原 茂</t>
+        </is>
+      </c>
+      <c r="C109" s="78" t="inlineStr">
+        <is>
+          <t>月給</t>
+        </is>
+      </c>
+      <c r="D109" s="60" t="n">
+        <v>253155</v>
+      </c>
+      <c r="E109" s="94" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F109" s="32" t="n">
+        <v>253155</v>
+      </c>
+      <c r="G109" s="80" t="inlineStr">
+        <is>
+          <t>直接</t>
+        </is>
+      </c>
+      <c r="H109" s="95" t="inlineStr">
+        <is>
+          <t>深夜</t>
+        </is>
+      </c>
+      <c r="I109" s="82" t="n">
+        <v>3037860</v>
+      </c>
+    </row>
+    <row r="110" ht="20" customHeight="1">
+      <c r="A110" s="92" t="inlineStr">
+        <is>
+          <t>板橋</t>
+        </is>
+      </c>
+      <c r="B110" s="93" t="inlineStr">
+        <is>
+          <t>堀 徳源</t>
+        </is>
+      </c>
+      <c r="C110" s="78" t="inlineStr">
+        <is>
+          <t>月給</t>
+        </is>
+      </c>
+      <c r="D110" s="60" t="n">
+        <v>263155</v>
+      </c>
+      <c r="E110" s="94" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F110" s="32" t="n">
+        <v>263155</v>
+      </c>
+      <c r="G110" s="80" t="inlineStr">
+        <is>
+          <t>直接</t>
+        </is>
+      </c>
+      <c r="H110" s="95" t="inlineStr"/>
+      <c r="I110" s="82" t="n">
+        <v>3157860</v>
+      </c>
+    </row>
+    <row r="111" ht="20" customHeight="1">
+      <c r="A111" s="92" t="inlineStr">
+        <is>
+          <t>板橋</t>
+        </is>
+      </c>
+      <c r="B111" s="93" t="inlineStr">
+        <is>
+          <t>青木 心一</t>
+        </is>
+      </c>
+      <c r="C111" s="78" t="inlineStr">
+        <is>
+          <t>月給</t>
+        </is>
+      </c>
+      <c r="D111" s="60" t="n">
+        <v>333155</v>
+      </c>
+      <c r="E111" s="94" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F111" s="32" t="n">
+        <v>333155</v>
+      </c>
+      <c r="G111" s="80" t="inlineStr">
+        <is>
+          <t>直接</t>
+        </is>
+      </c>
+      <c r="H111" s="95" t="inlineStr"/>
+      <c r="I111" s="82" t="n">
+        <v>3997860</v>
+      </c>
+    </row>
+    <row r="112" ht="20" customHeight="1">
+      <c r="A112" s="92" t="inlineStr">
+        <is>
+          <t>板橋</t>
+        </is>
+      </c>
+      <c r="B112" s="93" t="inlineStr">
+        <is>
+          <t>長谷川岳秀</t>
+        </is>
+      </c>
+      <c r="C112" s="78" t="inlineStr">
+        <is>
+          <t>月給</t>
+        </is>
+      </c>
+      <c r="D112" s="60" t="n">
+        <v>253155</v>
+      </c>
+      <c r="E112" s="94" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F112" s="32" t="n">
+        <v>253155</v>
+      </c>
+      <c r="G112" s="80" t="inlineStr">
+        <is>
+          <t>直接</t>
+        </is>
+      </c>
+      <c r="H112" s="95" t="inlineStr">
+        <is>
+          <t>深夜</t>
+        </is>
+      </c>
+      <c r="I112" s="82" t="n">
+        <v>3037860</v>
+      </c>
+    </row>
+    <row r="113" ht="20" customHeight="1">
+      <c r="A113" s="92" t="inlineStr">
+        <is>
+          <t>板橋</t>
+        </is>
+      </c>
+      <c r="B113" s="93" t="inlineStr">
+        <is>
+          <t>小林 司</t>
+        </is>
+      </c>
+      <c r="C113" s="78" t="inlineStr">
+        <is>
+          <t>月給</t>
+        </is>
+      </c>
+      <c r="D113" s="60" t="n">
+        <v>253155</v>
+      </c>
+      <c r="E113" s="94" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F113" s="32" t="n">
+        <v>253155</v>
+      </c>
+      <c r="G113" s="80" t="inlineStr">
+        <is>
+          <t>直接</t>
+        </is>
+      </c>
+      <c r="H113" s="95" t="inlineStr">
+        <is>
+          <t>深夜</t>
+        </is>
+      </c>
+      <c r="I113" s="82" t="n">
+        <v>3037860</v>
+      </c>
+    </row>
+    <row r="114" ht="20" customHeight="1">
+      <c r="A114" s="92" t="inlineStr">
+        <is>
+          <t>板橋</t>
+        </is>
+      </c>
+      <c r="B114" s="93" t="inlineStr">
+        <is>
+          <t>中條 順一</t>
+        </is>
+      </c>
+      <c r="C114" s="78" t="inlineStr">
+        <is>
+          <t>月給</t>
+        </is>
+      </c>
+      <c r="D114" s="60" t="n">
+        <v>253155</v>
+      </c>
+      <c r="E114" s="94" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F114" s="32" t="n">
+        <v>253155</v>
+      </c>
+      <c r="G114" s="80" t="inlineStr">
+        <is>
+          <t>直接</t>
+        </is>
+      </c>
+      <c r="H114" s="95" t="inlineStr">
+        <is>
+          <t>深夜</t>
+        </is>
+      </c>
+      <c r="I114" s="82" t="n">
+        <v>3037860</v>
+      </c>
+    </row>
+    <row r="115" ht="20" customHeight="1">
+      <c r="A115" s="92" t="inlineStr">
+        <is>
+          <t>板橋</t>
+        </is>
+      </c>
+      <c r="B115" s="93" t="inlineStr">
+        <is>
+          <t>吉橋 清</t>
+        </is>
+      </c>
+      <c r="C115" s="84" t="inlineStr">
+        <is>
+          <t>日当</t>
+        </is>
+      </c>
+      <c r="D115" s="12" t="n">
+        <v>10000</v>
+      </c>
+      <c r="E115" s="85">
+        <f>$D$3</f>
+        <v/>
+      </c>
+      <c r="F115" s="32">
+        <f>D115*$D$3</f>
+        <v/>
+      </c>
+      <c r="G115" s="80" t="inlineStr">
+        <is>
+          <t>直接</t>
+        </is>
+      </c>
+      <c r="H115" s="95" t="inlineStr">
+        <is>
+          <t>深夜手当</t>
+        </is>
+      </c>
+      <c r="I115" s="82">
+        <f>F115*12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="116" ht="20" customHeight="1">
+      <c r="A116" s="92" t="inlineStr">
+        <is>
+          <t>板橋</t>
+        </is>
+      </c>
+      <c r="B116" s="93" t="inlineStr">
+        <is>
+          <t>志村 貴子</t>
+        </is>
+      </c>
+      <c r="C116" s="84" t="inlineStr">
+        <is>
+          <t>時給</t>
+        </is>
+      </c>
+      <c r="D116" s="12" t="n">
+        <v>1165</v>
+      </c>
+      <c r="E116" s="85">
+        <f>$D$3</f>
+        <v/>
+      </c>
+      <c r="F116" s="32">
+        <f>D116*$D$3*8</f>
+        <v/>
+      </c>
+      <c r="G116" s="83" t="inlineStr">
+        <is>
+          <t>間接</t>
+        </is>
+      </c>
+      <c r="H116" s="95" t="inlineStr"/>
+      <c r="I116" s="82">
+        <f>F116*12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="117" ht="20" customHeight="1">
+      <c r="A117" s="92" t="inlineStr">
+        <is>
+          <t>板橋</t>
+        </is>
+      </c>
+      <c r="B117" s="93" t="inlineStr">
+        <is>
+          <t>加藤 裕子</t>
+        </is>
+      </c>
+      <c r="C117" s="84" t="inlineStr">
+        <is>
+          <t>時給</t>
+        </is>
+      </c>
+      <c r="D117" s="12" t="n">
+        <v>1165</v>
+      </c>
+      <c r="E117" s="85">
+        <f>$D$3</f>
+        <v/>
+      </c>
+      <c r="F117" s="32">
+        <f>D117*$D$3*8</f>
+        <v/>
+      </c>
+      <c r="G117" s="83" t="inlineStr">
+        <is>
+          <t>間接</t>
+        </is>
+      </c>
+      <c r="H117" s="95" t="inlineStr"/>
+      <c r="I117" s="82">
+        <f>F117*12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="118" ht="18" customHeight="1">
+      <c r="A118" s="96" t="inlineStr">
+        <is>
+          <t>板橋 合計  (19名)</t>
+        </is>
+      </c>
+      <c r="F118" s="97">
+        <f>SUMIF(A99:A117,"板橋",F99:F117)</f>
+        <v/>
+      </c>
+      <c r="G118" s="98" t="n"/>
+      <c r="H118" s="98" t="n"/>
+      <c r="I118" s="98" t="n"/>
+    </row>
+    <row r="119" ht="20" customHeight="1">
+      <c r="A119" s="99" t="inlineStr">
+        <is>
+          <t>■ 新横浜</t>
+        </is>
+      </c>
+    </row>
+    <row r="120" ht="20" customHeight="1">
+      <c r="A120" s="80" t="inlineStr">
+        <is>
+          <t>新横浜</t>
+        </is>
+      </c>
+      <c r="B120" s="100" t="inlineStr">
+        <is>
+          <t>富田 定夫</t>
+        </is>
+      </c>
+      <c r="C120" s="78" t="inlineStr">
+        <is>
+          <t>月給</t>
+        </is>
+      </c>
+      <c r="D120" s="60" t="n">
+        <v>248155</v>
+      </c>
+      <c r="E120" s="101" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F120" s="32" t="n">
+        <v>248155</v>
+      </c>
+      <c r="G120" s="80" t="inlineStr">
+        <is>
+          <t>直接</t>
+        </is>
+      </c>
+      <c r="H120" s="102" t="inlineStr"/>
+      <c r="I120" s="82" t="n">
+        <v>2977860</v>
+      </c>
+    </row>
+    <row r="121" ht="20" customHeight="1">
+      <c r="A121" s="80" t="inlineStr">
+        <is>
+          <t>新横浜</t>
+        </is>
+      </c>
+      <c r="B121" s="100" t="inlineStr">
+        <is>
+          <t>細野 篤史</t>
+        </is>
+      </c>
+      <c r="C121" s="78" t="inlineStr">
+        <is>
+          <t>月給</t>
+        </is>
+      </c>
+      <c r="D121" s="60" t="n">
+        <v>293155</v>
+      </c>
+      <c r="E121" s="101" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F121" s="32" t="n">
+        <v>293155</v>
+      </c>
+      <c r="G121" s="80" t="inlineStr">
+        <is>
+          <t>直接</t>
+        </is>
+      </c>
+      <c r="H121" s="102" t="inlineStr">
+        <is>
+          <t>サッポロ</t>
+        </is>
+      </c>
+      <c r="I121" s="82" t="n">
+        <v>3517860</v>
+      </c>
+    </row>
+    <row r="122" ht="20" customHeight="1">
+      <c r="A122" s="80" t="inlineStr">
+        <is>
+          <t>新横浜</t>
+        </is>
+      </c>
+      <c r="B122" s="100" t="inlineStr">
+        <is>
+          <t>麻生 和義</t>
+        </is>
+      </c>
+      <c r="C122" s="78" t="inlineStr">
+        <is>
+          <t>月給</t>
+        </is>
+      </c>
+      <c r="D122" s="60" t="n">
+        <v>263155</v>
+      </c>
+      <c r="E122" s="101" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F122" s="32" t="n">
+        <v>263155</v>
+      </c>
+      <c r="G122" s="80" t="inlineStr">
+        <is>
+          <t>直接</t>
+        </is>
+      </c>
+      <c r="H122" s="102" t="inlineStr">
+        <is>
+          <t>サッポロ</t>
+        </is>
+      </c>
+      <c r="I122" s="82" t="n">
+        <v>3157860</v>
+      </c>
+    </row>
+    <row r="123" ht="20" customHeight="1">
+      <c r="A123" s="80" t="inlineStr">
+        <is>
+          <t>新横浜</t>
+        </is>
+      </c>
+      <c r="B123" s="100" t="inlineStr">
+        <is>
+          <t>木幡 信行</t>
+        </is>
+      </c>
+      <c r="C123" s="84" t="inlineStr">
+        <is>
+          <t>日当</t>
+        </is>
+      </c>
+      <c r="D123" s="12" t="n">
+        <v>10000</v>
+      </c>
+      <c r="E123" s="85">
+        <f>$D$3</f>
+        <v/>
+      </c>
+      <c r="F123" s="32">
+        <f>D123*$D$3</f>
+        <v/>
+      </c>
+      <c r="G123" s="80" t="inlineStr">
+        <is>
+          <t>直接</t>
+        </is>
+      </c>
+      <c r="H123" s="102" t="inlineStr"/>
+      <c r="I123" s="82">
+        <f>F123*12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="124" ht="20" customHeight="1">
+      <c r="A124" s="80" t="inlineStr">
+        <is>
+          <t>新横浜</t>
+        </is>
+      </c>
+      <c r="B124" s="100" t="inlineStr">
+        <is>
+          <t>渡辺 義則</t>
+        </is>
+      </c>
+      <c r="C124" s="84" t="inlineStr">
+        <is>
+          <t>日当</t>
+        </is>
+      </c>
+      <c r="D124" s="12" t="n">
+        <v>10000</v>
+      </c>
+      <c r="E124" s="85">
+        <f>$D$3</f>
+        <v/>
+      </c>
+      <c r="F124" s="32">
+        <f>D124*$D$3</f>
+        <v/>
+      </c>
+      <c r="G124" s="80" t="inlineStr">
+        <is>
+          <t>直接</t>
+        </is>
+      </c>
+      <c r="H124" s="102" t="inlineStr"/>
+      <c r="I124" s="82">
+        <f>F124*12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="125" ht="20" customHeight="1">
+      <c r="A125" s="80" t="inlineStr">
+        <is>
+          <t>新横浜</t>
+        </is>
+      </c>
+      <c r="B125" s="100" t="inlineStr">
+        <is>
+          <t>府川 正明</t>
+        </is>
+      </c>
+      <c r="C125" s="84" t="inlineStr">
+        <is>
+          <t>日当</t>
+        </is>
+      </c>
+      <c r="D125" s="12" t="n">
+        <v>10000</v>
+      </c>
+      <c r="E125" s="85">
+        <f>$D$3</f>
+        <v/>
+      </c>
+      <c r="F125" s="32">
+        <f>D125*$D$3</f>
+        <v/>
+      </c>
+      <c r="G125" s="80" t="inlineStr">
+        <is>
+          <t>直接</t>
+        </is>
+      </c>
+      <c r="H125" s="102" t="inlineStr"/>
+      <c r="I125" s="82">
+        <f>F125*12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="126" ht="20" customHeight="1">
+      <c r="A126" s="80" t="inlineStr">
+        <is>
+          <t>新横浜</t>
+        </is>
+      </c>
+      <c r="B126" s="100" t="inlineStr">
+        <is>
+          <t>松尾 雅史</t>
+        </is>
+      </c>
+      <c r="C126" s="84" t="inlineStr">
+        <is>
+          <t>日当</t>
+        </is>
+      </c>
+      <c r="D126" s="12" t="n">
+        <v>10000</v>
+      </c>
+      <c r="E126" s="85">
+        <f>$D$3</f>
+        <v/>
+      </c>
+      <c r="F126" s="32">
+        <f>D126*$D$3</f>
+        <v/>
+      </c>
+      <c r="G126" s="80" t="inlineStr">
+        <is>
+          <t>直接</t>
+        </is>
+      </c>
+      <c r="H126" s="102" t="inlineStr">
+        <is>
+          <t>サッポロ</t>
+        </is>
+      </c>
+      <c r="I126" s="82">
+        <f>F126*12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="127" ht="20" customHeight="1">
+      <c r="A127" s="80" t="inlineStr">
+        <is>
+          <t>新横浜</t>
+        </is>
+      </c>
+      <c r="B127" s="100" t="inlineStr">
+        <is>
+          <t>古川 美光</t>
+        </is>
+      </c>
+      <c r="C127" s="84" t="inlineStr">
+        <is>
+          <t>日当</t>
+        </is>
+      </c>
+      <c r="D127" s="12" t="n">
+        <v>10000</v>
+      </c>
+      <c r="E127" s="85">
+        <f>$D$3</f>
+        <v/>
+      </c>
+      <c r="F127" s="32">
+        <f>D127*$D$3</f>
+        <v/>
+      </c>
+      <c r="G127" s="80" t="inlineStr">
+        <is>
+          <t>直接</t>
+        </is>
+      </c>
+      <c r="H127" s="102" t="inlineStr">
+        <is>
+          <t>深夜</t>
+        </is>
+      </c>
+      <c r="I127" s="82">
+        <f>F127*12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="128" ht="20" customHeight="1">
+      <c r="A128" s="80" t="inlineStr">
+        <is>
+          <t>新横浜</t>
+        </is>
+      </c>
+      <c r="B128" s="100" t="inlineStr">
+        <is>
+          <t>宮崎 守</t>
+        </is>
+      </c>
+      <c r="C128" s="84" t="inlineStr">
+        <is>
+          <t>日当</t>
+        </is>
+      </c>
+      <c r="D128" s="12" t="n">
+        <v>10000</v>
+      </c>
+      <c r="E128" s="85">
+        <f>$D$3</f>
+        <v/>
+      </c>
+      <c r="F128" s="32">
+        <f>D128*$D$3</f>
+        <v/>
+      </c>
+      <c r="G128" s="80" t="inlineStr">
+        <is>
+          <t>直接</t>
+        </is>
+      </c>
+      <c r="H128" s="102" t="inlineStr"/>
+      <c r="I128" s="82">
+        <f>F128*12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="129" ht="20" customHeight="1">
+      <c r="A129" s="80" t="inlineStr">
+        <is>
+          <t>新横浜</t>
+        </is>
+      </c>
+      <c r="B129" s="100" t="inlineStr">
+        <is>
+          <t>大矢 詔子</t>
+        </is>
+      </c>
+      <c r="C129" s="84" t="inlineStr">
+        <is>
+          <t>時給</t>
+        </is>
+      </c>
+      <c r="D129" s="12" t="n">
+        <v>1165</v>
+      </c>
+      <c r="E129" s="85">
+        <f>$D$3</f>
+        <v/>
+      </c>
+      <c r="F129" s="32">
+        <f>D129*$D$3*8</f>
+        <v/>
+      </c>
+      <c r="G129" s="83" t="inlineStr">
+        <is>
+          <t>間接</t>
+        </is>
+      </c>
+      <c r="H129" s="102" t="inlineStr"/>
+      <c r="I129" s="82">
+        <f>F129*12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="130" ht="18" customHeight="1">
+      <c r="A130" s="103" t="inlineStr">
+        <is>
+          <t>新横浜 合計  (11名)</t>
+        </is>
+      </c>
+      <c r="F130" s="104">
+        <f>SUMIF(A119:A129,"新横浜",F119:F129)</f>
+        <v/>
+      </c>
+      <c r="G130" s="105" t="n"/>
+      <c r="H130" s="105" t="n"/>
+      <c r="I130" s="105" t="n"/>
+    </row>
+    <row r="131" ht="20" customHeight="1">
+      <c r="A131" s="106" t="inlineStr">
+        <is>
+          <t>■ 埼玉</t>
+        </is>
+      </c>
+    </row>
+    <row r="132" ht="20" customHeight="1">
+      <c r="A132" s="107" t="inlineStr">
+        <is>
+          <t>埼玉</t>
+        </is>
+      </c>
+      <c r="B132" s="108" t="inlineStr">
+        <is>
+          <t>和田 康弘</t>
+        </is>
+      </c>
+      <c r="C132" s="78" t="inlineStr">
+        <is>
+          <t>月給</t>
+        </is>
+      </c>
+      <c r="D132" s="60" t="n">
+        <v>263155</v>
+      </c>
+      <c r="E132" s="109" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F132" s="32" t="n">
+        <v>263155</v>
+      </c>
+      <c r="G132" s="80" t="inlineStr">
+        <is>
+          <t>直接</t>
+        </is>
+      </c>
+      <c r="H132" s="110" t="inlineStr"/>
+      <c r="I132" s="82" t="n">
+        <v>3157860</v>
+      </c>
+    </row>
+    <row r="133" ht="20" customHeight="1">
+      <c r="A133" s="107" t="inlineStr">
+        <is>
+          <t>埼玉</t>
+        </is>
+      </c>
+      <c r="B133" s="108" t="inlineStr">
+        <is>
+          <t>藤内 順平</t>
+        </is>
+      </c>
+      <c r="C133" s="78" t="inlineStr">
+        <is>
+          <t>月給</t>
+        </is>
+      </c>
+      <c r="D133" s="60" t="n">
+        <v>253155</v>
+      </c>
+      <c r="E133" s="109" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F133" s="32" t="n">
+        <v>253155</v>
+      </c>
+      <c r="G133" s="80" t="inlineStr">
+        <is>
+          <t>直接</t>
+        </is>
+      </c>
+      <c r="H133" s="110" t="inlineStr">
+        <is>
+          <t>文京</t>
+        </is>
+      </c>
+      <c r="I133" s="82" t="n">
+        <v>3037860</v>
+      </c>
+    </row>
+    <row r="134" ht="20" customHeight="1">
+      <c r="A134" s="107" t="inlineStr">
+        <is>
+          <t>埼玉</t>
+        </is>
+      </c>
+      <c r="B134" s="108" t="inlineStr">
+        <is>
+          <t>土屋 紀元</t>
+        </is>
+      </c>
+      <c r="C134" s="78" t="inlineStr">
+        <is>
+          <t>月給</t>
+        </is>
+      </c>
+      <c r="D134" s="60" t="n">
+        <v>263155</v>
+      </c>
+      <c r="E134" s="109" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F134" s="32" t="n">
+        <v>263155</v>
+      </c>
+      <c r="G134" s="80" t="inlineStr">
+        <is>
+          <t>直接</t>
+        </is>
+      </c>
+      <c r="H134" s="110" t="inlineStr"/>
+      <c r="I134" s="82" t="n">
+        <v>3157860</v>
+      </c>
+    </row>
+    <row r="135" ht="20" customHeight="1">
+      <c r="A135" s="107" t="inlineStr">
+        <is>
+          <t>埼玉</t>
+        </is>
+      </c>
+      <c r="B135" s="108" t="inlineStr">
+        <is>
+          <t>玉山 賢雄</t>
+        </is>
+      </c>
+      <c r="C135" s="78" t="inlineStr">
+        <is>
+          <t>月給</t>
+        </is>
+      </c>
+      <c r="D135" s="60" t="n">
+        <v>243155</v>
+      </c>
+      <c r="E135" s="109" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F135" s="32" t="n">
+        <v>243155</v>
+      </c>
+      <c r="G135" s="80" t="inlineStr">
+        <is>
+          <t>直接</t>
+        </is>
+      </c>
+      <c r="H135" s="110" t="inlineStr"/>
+      <c r="I135" s="82" t="n">
+        <v>2917860</v>
+      </c>
+    </row>
+    <row r="136" ht="20" customHeight="1">
+      <c r="A136" s="107" t="inlineStr">
+        <is>
+          <t>埼玉</t>
+        </is>
+      </c>
+      <c r="B136" s="108" t="inlineStr">
+        <is>
+          <t>石橋 雅隆</t>
+        </is>
+      </c>
+      <c r="C136" s="78" t="inlineStr">
+        <is>
+          <t>月給</t>
+        </is>
+      </c>
+      <c r="D136" s="60" t="n">
+        <v>243155</v>
+      </c>
+      <c r="E136" s="109" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F136" s="32" t="n">
+        <v>243155</v>
+      </c>
+      <c r="G136" s="80" t="inlineStr">
+        <is>
+          <t>直接</t>
+        </is>
+      </c>
+      <c r="H136" s="110" t="inlineStr">
+        <is>
+          <t>ユニマテック</t>
+        </is>
+      </c>
+      <c r="I136" s="82" t="n">
+        <v>2917860</v>
+      </c>
+    </row>
+    <row r="137" ht="20" customHeight="1">
+      <c r="A137" s="107" t="inlineStr">
+        <is>
+          <t>埼玉</t>
+        </is>
+      </c>
+      <c r="B137" s="108" t="inlineStr">
+        <is>
+          <t>佐々木幸治</t>
+        </is>
+      </c>
+      <c r="C137" s="78" t="inlineStr">
+        <is>
+          <t>月給</t>
+        </is>
+      </c>
+      <c r="D137" s="60" t="n">
+        <v>263155</v>
+      </c>
+      <c r="E137" s="109" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F137" s="32" t="n">
+        <v>263155</v>
+      </c>
+      <c r="G137" s="80" t="inlineStr">
+        <is>
+          <t>直接</t>
+        </is>
+      </c>
+      <c r="H137" s="110" t="inlineStr"/>
+      <c r="I137" s="82" t="n">
+        <v>3157860</v>
+      </c>
+    </row>
+    <row r="138" ht="20" customHeight="1">
+      <c r="A138" s="107" t="inlineStr">
+        <is>
+          <t>埼玉</t>
+        </is>
+      </c>
+      <c r="B138" s="108" t="inlineStr">
+        <is>
+          <t>小堀 智由</t>
+        </is>
+      </c>
+      <c r="C138" s="78" t="inlineStr">
+        <is>
+          <t>月給</t>
+        </is>
+      </c>
+      <c r="D138" s="60" t="n">
+        <v>253155</v>
+      </c>
+      <c r="E138" s="109" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F138" s="32" t="n">
+        <v>253155</v>
+      </c>
+      <c r="G138" s="80" t="inlineStr">
+        <is>
+          <t>直接</t>
+        </is>
+      </c>
+      <c r="H138" s="110" t="inlineStr">
+        <is>
+          <t>文京</t>
+        </is>
+      </c>
+      <c r="I138" s="82" t="n">
+        <v>3037860</v>
+      </c>
+    </row>
+    <row r="139" ht="20" customHeight="1">
+      <c r="A139" s="107" t="inlineStr">
+        <is>
+          <t>埼玉</t>
+        </is>
+      </c>
+      <c r="B139" s="108" t="inlineStr">
+        <is>
+          <t>大森 翔太</t>
+        </is>
+      </c>
+      <c r="C139" s="78" t="inlineStr">
+        <is>
+          <t>月給</t>
+        </is>
+      </c>
+      <c r="D139" s="60" t="n">
+        <v>243155</v>
+      </c>
+      <c r="E139" s="109" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F139" s="32" t="n">
+        <v>243155</v>
+      </c>
+      <c r="G139" s="80" t="inlineStr">
+        <is>
+          <t>直接</t>
+        </is>
+      </c>
+      <c r="H139" s="110" t="inlineStr">
+        <is>
+          <t>ユニマテック</t>
+        </is>
+      </c>
+      <c r="I139" s="82" t="n">
+        <v>2917860</v>
+      </c>
+    </row>
+    <row r="140" ht="20" customHeight="1">
+      <c r="A140" s="107" t="inlineStr">
+        <is>
+          <t>埼玉</t>
+        </is>
+      </c>
+      <c r="B140" s="108" t="inlineStr">
+        <is>
+          <t>根岸 三鶴</t>
+        </is>
+      </c>
+      <c r="C140" s="78" t="inlineStr">
+        <is>
+          <t>月給</t>
+        </is>
+      </c>
+      <c r="D140" s="60" t="n">
+        <v>243155</v>
+      </c>
+      <c r="E140" s="109" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F140" s="32" t="n">
+        <v>243155</v>
+      </c>
+      <c r="G140" s="80" t="inlineStr">
+        <is>
+          <t>直接</t>
+        </is>
+      </c>
+      <c r="H140" s="110" t="inlineStr"/>
+      <c r="I140" s="82" t="n">
+        <v>2917860</v>
+      </c>
+    </row>
+    <row r="141" ht="20" customHeight="1">
+      <c r="A141" s="107" t="inlineStr">
+        <is>
+          <t>埼玉</t>
+        </is>
+      </c>
+      <c r="B141" s="108" t="inlineStr">
+        <is>
+          <t>平澤 隼</t>
+        </is>
+      </c>
+      <c r="C141" s="78" t="inlineStr">
+        <is>
+          <t>月給</t>
+        </is>
+      </c>
+      <c r="D141" s="60" t="n">
+        <v>253155</v>
+      </c>
+      <c r="E141" s="109" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F141" s="32" t="n">
+        <v>253155</v>
+      </c>
+      <c r="G141" s="80" t="inlineStr">
+        <is>
+          <t>直接</t>
+        </is>
+      </c>
+      <c r="H141" s="110" t="inlineStr">
+        <is>
+          <t>文京</t>
+        </is>
+      </c>
+      <c r="I141" s="82" t="n">
+        <v>3037860</v>
+      </c>
+    </row>
+    <row r="142" ht="20" customHeight="1">
+      <c r="A142" s="107" t="inlineStr">
+        <is>
+          <t>埼玉</t>
+        </is>
+      </c>
+      <c r="B142" s="108" t="inlineStr">
+        <is>
+          <t>八峠 知之</t>
+        </is>
+      </c>
+      <c r="C142" s="78" t="inlineStr">
+        <is>
+          <t>月給</t>
+        </is>
+      </c>
+      <c r="D142" s="60" t="n">
+        <v>243155</v>
+      </c>
+      <c r="E142" s="109" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F142" s="32" t="n">
+        <v>243155</v>
+      </c>
+      <c r="G142" s="80" t="inlineStr">
+        <is>
+          <t>直接</t>
+        </is>
+      </c>
+      <c r="H142" s="110" t="inlineStr"/>
+      <c r="I142" s="82" t="n">
+        <v>2917860</v>
+      </c>
+    </row>
+    <row r="143" ht="20" customHeight="1">
+      <c r="A143" s="107" t="inlineStr">
+        <is>
+          <t>埼玉</t>
+        </is>
+      </c>
+      <c r="B143" s="108" t="inlineStr">
+        <is>
+          <t>山田 和宏</t>
+        </is>
+      </c>
+      <c r="C143" s="78" t="inlineStr">
+        <is>
+          <t>月給</t>
+        </is>
+      </c>
+      <c r="D143" s="60" t="n">
+        <v>253155</v>
+      </c>
+      <c r="E143" s="109" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F143" s="32" t="n">
+        <v>253155</v>
+      </c>
+      <c r="G143" s="80" t="inlineStr">
+        <is>
+          <t>直接</t>
+        </is>
+      </c>
+      <c r="H143" s="110" t="inlineStr">
+        <is>
+          <t>文京</t>
+        </is>
+      </c>
+      <c r="I143" s="82" t="n">
+        <v>3037860</v>
+      </c>
+    </row>
+    <row r="144" ht="20" customHeight="1">
+      <c r="A144" s="107" t="inlineStr">
+        <is>
+          <t>埼玉</t>
+        </is>
+      </c>
+      <c r="B144" s="108" t="inlineStr">
+        <is>
+          <t>渡辺 貴之</t>
+        </is>
+      </c>
+      <c r="C144" s="78" t="inlineStr">
+        <is>
+          <t>月給</t>
+        </is>
+      </c>
+      <c r="D144" s="60" t="n">
+        <v>251155</v>
+      </c>
+      <c r="E144" s="109" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F144" s="32" t="n">
+        <v>251155</v>
+      </c>
+      <c r="G144" s="80" t="inlineStr">
+        <is>
+          <t>直接</t>
+        </is>
+      </c>
+      <c r="H144" s="110" t="inlineStr"/>
+      <c r="I144" s="82" t="n">
+        <v>3013860</v>
+      </c>
+    </row>
+    <row r="145" ht="20" customHeight="1">
+      <c r="A145" s="107" t="inlineStr">
+        <is>
+          <t>埼玉</t>
+        </is>
+      </c>
+      <c r="B145" s="108" t="inlineStr">
+        <is>
+          <t>大嶋 隆</t>
+        </is>
+      </c>
+      <c r="C145" s="78" t="inlineStr">
+        <is>
+          <t>月給</t>
+        </is>
+      </c>
+      <c r="D145" s="60" t="n">
+        <v>243155</v>
+      </c>
+      <c r="E145" s="109" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F145" s="32" t="n">
+        <v>243155</v>
+      </c>
+      <c r="G145" s="80" t="inlineStr">
+        <is>
+          <t>直接</t>
+        </is>
+      </c>
+      <c r="H145" s="110" t="inlineStr"/>
+      <c r="I145" s="82" t="n">
+        <v>2917860</v>
+      </c>
+    </row>
+    <row r="146" ht="20" customHeight="1">
+      <c r="A146" s="107" t="inlineStr">
+        <is>
+          <t>埼玉</t>
+        </is>
+      </c>
+      <c r="B146" s="108" t="inlineStr">
+        <is>
+          <t>日吉 眞次</t>
+        </is>
+      </c>
+      <c r="C146" s="78" t="inlineStr">
+        <is>
+          <t>月給</t>
+        </is>
+      </c>
+      <c r="D146" s="60" t="n">
+        <v>243155</v>
+      </c>
+      <c r="E146" s="109" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F146" s="32" t="n">
+        <v>243155</v>
+      </c>
+      <c r="G146" s="80" t="inlineStr">
+        <is>
+          <t>直接</t>
+        </is>
+      </c>
+      <c r="H146" s="110" t="inlineStr"/>
+      <c r="I146" s="82" t="n">
+        <v>2917860</v>
+      </c>
+    </row>
+    <row r="147" ht="20" customHeight="1">
+      <c r="A147" s="107" t="inlineStr">
+        <is>
+          <t>埼玉</t>
+        </is>
+      </c>
+      <c r="B147" s="108" t="inlineStr">
+        <is>
+          <t>西川 一美</t>
+        </is>
+      </c>
+      <c r="C147" s="78" t="inlineStr">
+        <is>
+          <t>月給</t>
+        </is>
+      </c>
+      <c r="D147" s="60" t="n">
+        <v>253155</v>
+      </c>
+      <c r="E147" s="109" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F147" s="32" t="n">
+        <v>253155</v>
+      </c>
+      <c r="G147" s="80" t="inlineStr">
+        <is>
+          <t>直接</t>
+        </is>
+      </c>
+      <c r="H147" s="110" t="inlineStr">
+        <is>
+          <t>文京</t>
+        </is>
+      </c>
+      <c r="I147" s="82" t="n">
+        <v>3037860</v>
+      </c>
+    </row>
+    <row r="148" ht="20" customHeight="1">
+      <c r="A148" s="107" t="inlineStr">
+        <is>
+          <t>埼玉</t>
+        </is>
+      </c>
+      <c r="B148" s="108" t="inlineStr">
+        <is>
+          <t>篠原 幸一</t>
+        </is>
+      </c>
+      <c r="C148" s="78" t="inlineStr">
+        <is>
+          <t>月給</t>
+        </is>
+      </c>
+      <c r="D148" s="60" t="n">
+        <v>253155</v>
+      </c>
+      <c r="E148" s="109" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F148" s="32" t="n">
+        <v>253155</v>
+      </c>
+      <c r="G148" s="80" t="inlineStr">
+        <is>
+          <t>直接</t>
+        </is>
+      </c>
+      <c r="H148" s="110" t="inlineStr">
+        <is>
+          <t>文京</t>
+        </is>
+      </c>
+      <c r="I148" s="82" t="n">
+        <v>3037860</v>
+      </c>
+    </row>
+    <row r="149" ht="20" customHeight="1">
+      <c r="A149" s="107" t="inlineStr">
+        <is>
+          <t>埼玉</t>
+        </is>
+      </c>
+      <c r="B149" s="108" t="inlineStr">
+        <is>
+          <t>前崎 厚志</t>
+        </is>
+      </c>
+      <c r="C149" s="78" t="inlineStr">
+        <is>
+          <t>月給</t>
+        </is>
+      </c>
+      <c r="D149" s="60" t="n">
+        <v>253155</v>
+      </c>
+      <c r="E149" s="109" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F149" s="32" t="n">
+        <v>253155</v>
+      </c>
+      <c r="G149" s="80" t="inlineStr">
+        <is>
+          <t>直接</t>
+        </is>
+      </c>
+      <c r="H149" s="110" t="inlineStr">
+        <is>
+          <t>文京</t>
+        </is>
+      </c>
+      <c r="I149" s="82" t="n">
+        <v>3037860</v>
+      </c>
+    </row>
+    <row r="150" ht="20" customHeight="1">
+      <c r="A150" s="107" t="inlineStr">
+        <is>
+          <t>埼玉</t>
+        </is>
+      </c>
+      <c r="B150" s="108" t="inlineStr">
+        <is>
+          <t>小笠原良孝</t>
+        </is>
+      </c>
+      <c r="C150" s="78" t="inlineStr">
+        <is>
+          <t>月給</t>
+        </is>
+      </c>
+      <c r="D150" s="60" t="n">
+        <v>243155</v>
+      </c>
+      <c r="E150" s="109" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F150" s="32" t="n">
+        <v>243155</v>
+      </c>
+      <c r="G150" s="80" t="inlineStr">
+        <is>
+          <t>直接</t>
+        </is>
+      </c>
+      <c r="H150" s="110" t="inlineStr"/>
+      <c r="I150" s="82" t="n">
+        <v>2917860</v>
+      </c>
+    </row>
+    <row r="151" ht="20" customHeight="1">
+      <c r="A151" s="107" t="inlineStr">
+        <is>
+          <t>埼玉</t>
+        </is>
+      </c>
+      <c r="B151" s="108" t="inlineStr">
+        <is>
+          <t>金子 修治</t>
+        </is>
+      </c>
+      <c r="C151" s="78" t="inlineStr">
+        <is>
+          <t>月給</t>
+        </is>
+      </c>
+      <c r="D151" s="60" t="n">
+        <v>243155</v>
+      </c>
+      <c r="E151" s="109" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F151" s="32" t="n">
+        <v>243155</v>
+      </c>
+      <c r="G151" s="80" t="inlineStr">
+        <is>
+          <t>直接</t>
+        </is>
+      </c>
+      <c r="H151" s="110" t="inlineStr"/>
+      <c r="I151" s="82" t="n">
+        <v>2917860</v>
+      </c>
+    </row>
+    <row r="152" ht="20" customHeight="1">
+      <c r="A152" s="107" t="inlineStr">
+        <is>
+          <t>埼玉</t>
+        </is>
+      </c>
+      <c r="B152" s="108" t="inlineStr">
+        <is>
+          <t>新海 善光</t>
+        </is>
+      </c>
+      <c r="C152" s="78" t="inlineStr">
+        <is>
+          <t>月給</t>
+        </is>
+      </c>
+      <c r="D152" s="60" t="n">
+        <v>258788</v>
+      </c>
+      <c r="E152" s="109" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F152" s="32" t="n">
+        <v>258788</v>
+      </c>
+      <c r="G152" s="80" t="inlineStr">
+        <is>
+          <t>直接</t>
+        </is>
+      </c>
+      <c r="H152" s="110" t="inlineStr">
+        <is>
+          <t>千代田区</t>
+        </is>
+      </c>
+      <c r="I152" s="82" t="n">
+        <v>3105456</v>
+      </c>
+    </row>
+    <row r="153" ht="20" customHeight="1">
+      <c r="A153" s="107" t="inlineStr">
+        <is>
+          <t>埼玉</t>
+        </is>
+      </c>
+      <c r="B153" s="108" t="inlineStr">
+        <is>
+          <t>北野 利春</t>
+        </is>
+      </c>
+      <c r="C153" s="78" t="inlineStr">
+        <is>
+          <t>月給</t>
+        </is>
+      </c>
+      <c r="D153" s="60" t="n">
+        <v>279288</v>
+      </c>
+      <c r="E153" s="109" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F153" s="32" t="n">
+        <v>279288</v>
+      </c>
+      <c r="G153" s="80" t="inlineStr">
+        <is>
+          <t>直接</t>
+        </is>
+      </c>
+      <c r="H153" s="110" t="inlineStr">
+        <is>
+          <t>千代田区</t>
+        </is>
+      </c>
+      <c r="I153" s="82" t="n">
+        <v>3351456</v>
+      </c>
+    </row>
+    <row r="154" ht="20" customHeight="1">
+      <c r="A154" s="107" t="inlineStr">
+        <is>
+          <t>埼玉</t>
+        </is>
+      </c>
+      <c r="B154" s="108" t="inlineStr">
+        <is>
+          <t>近藤 彰二</t>
+        </is>
+      </c>
+      <c r="C154" s="78" t="inlineStr">
+        <is>
+          <t>月給</t>
+        </is>
+      </c>
+      <c r="D154" s="60" t="n">
+        <v>272898</v>
+      </c>
+      <c r="E154" s="109" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F154" s="32" t="n">
+        <v>272898</v>
+      </c>
+      <c r="G154" s="80" t="inlineStr">
+        <is>
+          <t>直接</t>
+        </is>
+      </c>
+      <c r="H154" s="110" t="inlineStr">
+        <is>
+          <t>千代田区</t>
+        </is>
+      </c>
+      <c r="I154" s="82" t="n">
+        <v>3274776</v>
+      </c>
+    </row>
+    <row r="155" ht="20" customHeight="1">
+      <c r="A155" s="107" t="inlineStr">
+        <is>
+          <t>埼玉</t>
+        </is>
+      </c>
+      <c r="B155" s="108" t="inlineStr">
+        <is>
+          <t>和田 盛樹</t>
+        </is>
+      </c>
+      <c r="C155" s="78" t="inlineStr">
+        <is>
+          <t>月給</t>
+        </is>
+      </c>
+      <c r="D155" s="60" t="n">
+        <v>271898</v>
+      </c>
+      <c r="E155" s="109" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F155" s="32" t="n">
+        <v>271898</v>
+      </c>
+      <c r="G155" s="80" t="inlineStr">
+        <is>
+          <t>直接</t>
+        </is>
+      </c>
+      <c r="H155" s="110" t="inlineStr">
+        <is>
+          <t>千代田</t>
+        </is>
+      </c>
+      <c r="I155" s="82" t="n">
+        <v>3262776</v>
+      </c>
+    </row>
+    <row r="156" ht="20" customHeight="1">
+      <c r="A156" s="107" t="inlineStr">
+        <is>
+          <t>埼玉</t>
+        </is>
+      </c>
+      <c r="B156" s="108" t="inlineStr">
+        <is>
+          <t>折笠 良一</t>
+        </is>
+      </c>
+      <c r="C156" s="78" t="inlineStr">
+        <is>
+          <t>月給</t>
+        </is>
+      </c>
+      <c r="D156" s="60" t="n">
+        <v>272898</v>
+      </c>
+      <c r="E156" s="109" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F156" s="32" t="n">
+        <v>272898</v>
+      </c>
+      <c r="G156" s="80" t="inlineStr">
+        <is>
+          <t>直接</t>
+        </is>
+      </c>
+      <c r="H156" s="110" t="inlineStr">
+        <is>
+          <t>千代田区</t>
+        </is>
+      </c>
+      <c r="I156" s="82" t="n">
+        <v>3274776</v>
+      </c>
+    </row>
+    <row r="157" ht="20" customHeight="1">
+      <c r="A157" s="107" t="inlineStr">
+        <is>
+          <t>埼玉</t>
+        </is>
+      </c>
+      <c r="B157" s="108" t="inlineStr">
+        <is>
+          <t>山田 俊和</t>
+        </is>
+      </c>
+      <c r="C157" s="78" t="inlineStr">
+        <is>
+          <t>月給</t>
+        </is>
+      </c>
+      <c r="D157" s="60" t="n">
+        <v>266898</v>
+      </c>
+      <c r="E157" s="109" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F157" s="32" t="n">
+        <v>266898</v>
+      </c>
+      <c r="G157" s="80" t="inlineStr">
+        <is>
+          <t>直接</t>
+        </is>
+      </c>
+      <c r="H157" s="110" t="inlineStr">
+        <is>
+          <t>文京</t>
+        </is>
+      </c>
+      <c r="I157" s="82" t="n">
+        <v>3202776</v>
+      </c>
+    </row>
+    <row r="158" ht="20" customHeight="1">
+      <c r="A158" s="107" t="inlineStr">
+        <is>
+          <t>埼玉</t>
+        </is>
+      </c>
+      <c r="B158" s="108" t="inlineStr">
+        <is>
+          <t>荻野 泰宏</t>
+        </is>
+      </c>
+      <c r="C158" s="78" t="inlineStr">
+        <is>
+          <t>月給</t>
+        </is>
+      </c>
+      <c r="D158" s="60" t="n">
+        <v>266898</v>
+      </c>
+      <c r="E158" s="109" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F158" s="32" t="n">
+        <v>266898</v>
+      </c>
+      <c r="G158" s="80" t="inlineStr">
+        <is>
+          <t>直接</t>
+        </is>
+      </c>
+      <c r="H158" s="110" t="inlineStr">
+        <is>
+          <t>文京</t>
+        </is>
+      </c>
+      <c r="I158" s="82" t="n">
+        <v>3202776</v>
+      </c>
+    </row>
+    <row r="159" ht="20" customHeight="1">
+      <c r="A159" s="107" t="inlineStr">
+        <is>
+          <t>埼玉</t>
+        </is>
+      </c>
+      <c r="B159" s="108" t="inlineStr">
+        <is>
+          <t>寺木 達夫</t>
+        </is>
+      </c>
+      <c r="C159" s="78" t="inlineStr">
+        <is>
+          <t>月給</t>
+        </is>
+      </c>
+      <c r="D159" s="60" t="n">
+        <v>266898</v>
+      </c>
+      <c r="E159" s="109" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F159" s="32" t="n">
+        <v>266898</v>
+      </c>
+      <c r="G159" s="80" t="inlineStr">
+        <is>
+          <t>直接</t>
+        </is>
+      </c>
+      <c r="H159" s="110" t="inlineStr">
+        <is>
+          <t>文京</t>
+        </is>
+      </c>
+      <c r="I159" s="82" t="n">
+        <v>3202776</v>
+      </c>
+    </row>
+    <row r="160" ht="20" customHeight="1">
+      <c r="A160" s="107" t="inlineStr">
+        <is>
+          <t>埼玉</t>
+        </is>
+      </c>
+      <c r="B160" s="108" t="inlineStr">
+        <is>
+          <t>矢口 光春</t>
+        </is>
+      </c>
+      <c r="C160" s="78" t="inlineStr">
+        <is>
+          <t>月給</t>
+        </is>
+      </c>
+      <c r="D160" s="60" t="n">
+        <v>266898</v>
+      </c>
+      <c r="E160" s="109" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F160" s="32" t="n">
+        <v>266898</v>
+      </c>
+      <c r="G160" s="80" t="inlineStr">
+        <is>
+          <t>直接</t>
+        </is>
+      </c>
+      <c r="H160" s="110" t="inlineStr">
+        <is>
+          <t>文京</t>
+        </is>
+      </c>
+      <c r="I160" s="82" t="n">
+        <v>3202776</v>
+      </c>
+    </row>
+    <row r="161" ht="20" customHeight="1">
+      <c r="A161" s="107" t="inlineStr">
+        <is>
+          <t>埼玉</t>
+        </is>
+      </c>
+      <c r="B161" s="108" t="inlineStr">
+        <is>
+          <t>宇都宮一房</t>
+        </is>
+      </c>
+      <c r="C161" s="84" t="inlineStr">
+        <is>
+          <t>日当</t>
+        </is>
+      </c>
+      <c r="D161" s="12" t="n">
+        <v>10000</v>
+      </c>
+      <c r="E161" s="85">
+        <f>$D$3</f>
+        <v/>
+      </c>
+      <c r="F161" s="32">
+        <f>D161*$D$3</f>
+        <v/>
+      </c>
+      <c r="G161" s="80" t="inlineStr">
+        <is>
+          <t>直接</t>
+        </is>
+      </c>
+      <c r="H161" s="110" t="inlineStr"/>
+      <c r="I161" s="82">
+        <f>F161*12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="162" ht="20" customHeight="1">
+      <c r="A162" s="107" t="inlineStr">
+        <is>
+          <t>埼玉</t>
+        </is>
+      </c>
+      <c r="B162" s="108" t="inlineStr">
+        <is>
+          <t>大友 正昭</t>
+        </is>
+      </c>
+      <c r="C162" s="84" t="inlineStr">
+        <is>
+          <t>日当</t>
+        </is>
+      </c>
+      <c r="D162" s="12" t="n">
+        <v>10000</v>
+      </c>
+      <c r="E162" s="85">
+        <f>$D$3</f>
+        <v/>
+      </c>
+      <c r="F162" s="32">
+        <f>D162*$D$3</f>
+        <v/>
+      </c>
+      <c r="G162" s="80" t="inlineStr">
+        <is>
+          <t>直接</t>
+        </is>
+      </c>
+      <c r="H162" s="110" t="inlineStr">
+        <is>
+          <t>ユニマテック</t>
+        </is>
+      </c>
+      <c r="I162" s="82">
+        <f>F162*12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="163" ht="20" customHeight="1">
+      <c r="A163" s="107" t="inlineStr">
+        <is>
+          <t>埼玉</t>
+        </is>
+      </c>
+      <c r="B163" s="108" t="inlineStr">
+        <is>
+          <t>高井 孝行</t>
+        </is>
+      </c>
+      <c r="C163" s="84" t="inlineStr">
+        <is>
+          <t>日当</t>
+        </is>
+      </c>
+      <c r="D163" s="12" t="n">
+        <v>9000</v>
+      </c>
+      <c r="E163" s="85">
+        <f>$D$3</f>
+        <v/>
+      </c>
+      <c r="F163" s="32">
+        <f>D163*$D$3</f>
+        <v/>
+      </c>
+      <c r="G163" s="80" t="inlineStr">
+        <is>
+          <t>直接</t>
+        </is>
+      </c>
+      <c r="H163" s="110" t="inlineStr"/>
+      <c r="I163" s="82">
+        <f>F163*12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="164" ht="20" customHeight="1">
+      <c r="A164" s="107" t="inlineStr">
+        <is>
+          <t>埼玉</t>
+        </is>
+      </c>
+      <c r="B164" s="108" t="inlineStr">
+        <is>
+          <t>水野 敦夫</t>
+        </is>
+      </c>
+      <c r="C164" s="84" t="inlineStr">
+        <is>
+          <t>日当</t>
+        </is>
+      </c>
+      <c r="D164" s="12" t="n">
+        <v>9000</v>
+      </c>
+      <c r="E164" s="85">
+        <f>$D$3</f>
+        <v/>
+      </c>
+      <c r="F164" s="32">
+        <f>D164*$D$3</f>
+        <v/>
+      </c>
+      <c r="G164" s="80" t="inlineStr">
+        <is>
+          <t>直接</t>
+        </is>
+      </c>
+      <c r="H164" s="110" t="inlineStr"/>
+      <c r="I164" s="82">
+        <f>F164*12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="165" ht="20" customHeight="1">
+      <c r="A165" s="107" t="inlineStr">
+        <is>
+          <t>埼玉</t>
+        </is>
+      </c>
+      <c r="B165" s="108" t="inlineStr">
+        <is>
+          <t>岩波 孝</t>
+        </is>
+      </c>
+      <c r="C165" s="84" t="inlineStr">
+        <is>
+          <t>日当</t>
+        </is>
+      </c>
+      <c r="D165" s="12" t="n">
+        <v>10000</v>
+      </c>
+      <c r="E165" s="85">
+        <f>$D$3</f>
+        <v/>
+      </c>
+      <c r="F165" s="32">
+        <f>D165*$D$3</f>
+        <v/>
+      </c>
+      <c r="G165" s="80" t="inlineStr">
+        <is>
+          <t>直接</t>
+        </is>
+      </c>
+      <c r="H165" s="110" t="inlineStr"/>
+      <c r="I165" s="82">
+        <f>F165*12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="166" ht="20" customHeight="1">
+      <c r="A166" s="107" t="inlineStr">
+        <is>
+          <t>埼玉</t>
+        </is>
+      </c>
+      <c r="B166" s="108" t="inlineStr">
+        <is>
+          <t>河野 大地</t>
+        </is>
+      </c>
+      <c r="C166" s="84" t="inlineStr">
+        <is>
+          <t>日当</t>
+        </is>
+      </c>
+      <c r="D166" s="12" t="n">
+        <v>10000</v>
+      </c>
+      <c r="E166" s="85">
+        <f>$D$3</f>
+        <v/>
+      </c>
+      <c r="F166" s="32">
+        <f>D166*$D$3</f>
+        <v/>
+      </c>
+      <c r="G166" s="80" t="inlineStr">
+        <is>
+          <t>直接</t>
+        </is>
+      </c>
+      <c r="H166" s="110" t="inlineStr"/>
+      <c r="I166" s="82">
+        <f>F166*12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="167" ht="20" customHeight="1">
+      <c r="A167" s="107" t="inlineStr">
+        <is>
+          <t>埼玉</t>
+        </is>
+      </c>
+      <c r="B167" s="108" t="inlineStr">
+        <is>
+          <t>本田 智彦</t>
+        </is>
+      </c>
+      <c r="C167" s="84" t="inlineStr">
+        <is>
+          <t>日当</t>
+        </is>
+      </c>
+      <c r="D167" s="12" t="n">
+        <v>7500</v>
+      </c>
+      <c r="E167" s="85">
+        <f>$D$3</f>
+        <v/>
+      </c>
+      <c r="F167" s="32">
+        <f>D167*$D$3</f>
+        <v/>
+      </c>
+      <c r="G167" s="80" t="inlineStr">
+        <is>
+          <t>直接</t>
+        </is>
+      </c>
+      <c r="H167" s="110" t="inlineStr">
+        <is>
+          <t>点呼</t>
+        </is>
+      </c>
+      <c r="I167" s="82">
+        <f>F167*12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="168" ht="20" customHeight="1">
+      <c r="A168" s="107" t="inlineStr">
+        <is>
+          <t>埼玉</t>
+        </is>
+      </c>
+      <c r="B168" s="108" t="inlineStr">
+        <is>
+          <t>磐城 孝司</t>
+        </is>
+      </c>
+      <c r="C168" s="84" t="inlineStr">
+        <is>
+          <t>日当</t>
+        </is>
+      </c>
+      <c r="D168" s="12" t="n">
+        <v>7500</v>
+      </c>
+      <c r="E168" s="85">
+        <f>$D$3</f>
+        <v/>
+      </c>
+      <c r="F168" s="32">
+        <f>D168*$D$3</f>
+        <v/>
+      </c>
+      <c r="G168" s="80" t="inlineStr">
+        <is>
+          <t>直接</t>
+        </is>
+      </c>
+      <c r="H168" s="110" t="inlineStr">
+        <is>
+          <t>点呼</t>
+        </is>
+      </c>
+      <c r="I168" s="82">
+        <f>F168*12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="169" ht="20" customHeight="1">
+      <c r="A169" s="107" t="inlineStr">
+        <is>
+          <t>埼玉</t>
+        </is>
+      </c>
+      <c r="B169" s="108" t="inlineStr">
+        <is>
+          <t>石塚 正海</t>
+        </is>
+      </c>
+      <c r="C169" s="84" t="inlineStr">
+        <is>
+          <t>日当</t>
+        </is>
+      </c>
+      <c r="D169" s="12" t="n">
+        <v>7500</v>
+      </c>
+      <c r="E169" s="85">
+        <f>$D$3</f>
+        <v/>
+      </c>
+      <c r="F169" s="32">
+        <f>D169*$D$3</f>
+        <v/>
+      </c>
+      <c r="G169" s="80" t="inlineStr">
+        <is>
+          <t>直接</t>
+        </is>
+      </c>
+      <c r="H169" s="110" t="inlineStr">
+        <is>
+          <t>点呼</t>
+        </is>
+      </c>
+      <c r="I169" s="82">
+        <f>F169*12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="170" ht="20" customHeight="1">
+      <c r="A170" s="107" t="inlineStr">
+        <is>
+          <t>埼玉</t>
+        </is>
+      </c>
+      <c r="B170" s="108" t="inlineStr">
+        <is>
+          <t>佐藤 芳治</t>
+        </is>
+      </c>
+      <c r="C170" s="84" t="inlineStr">
+        <is>
+          <t>日当</t>
+        </is>
+      </c>
+      <c r="D170" s="12" t="n">
+        <v>7500</v>
+      </c>
+      <c r="E170" s="85">
+        <f>$D$3</f>
+        <v/>
+      </c>
+      <c r="F170" s="32">
+        <f>D170*$D$3</f>
+        <v/>
+      </c>
+      <c r="G170" s="80" t="inlineStr">
+        <is>
+          <t>直接</t>
+        </is>
+      </c>
+      <c r="H170" s="110" t="inlineStr"/>
+      <c r="I170" s="82">
+        <f>F170*12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="171" ht="18" customHeight="1">
+      <c r="A171" s="111" t="inlineStr">
+        <is>
+          <t>埼玉 合計  (40名)</t>
+        </is>
+      </c>
+      <c r="F171" s="112">
+        <f>SUMIF(A131:A170,"埼玉",F131:F170)</f>
+        <v/>
+      </c>
+      <c r="G171" s="113" t="n"/>
+      <c r="H171" s="113" t="n"/>
+      <c r="I171" s="113" t="n"/>
+    </row>
+    <row r="172" ht="20" customHeight="1">
+      <c r="A172" s="114" t="inlineStr">
+        <is>
+          <t>■ 管理</t>
+        </is>
+      </c>
+    </row>
+    <row r="173" ht="20" customHeight="1">
+      <c r="A173" s="115" t="inlineStr">
+        <is>
+          <t>管理</t>
+        </is>
+      </c>
+      <c r="B173" s="116" t="inlineStr">
+        <is>
+          <t>宇都宮 寛</t>
+        </is>
+      </c>
+      <c r="C173" s="78" t="inlineStr">
+        <is>
+          <t>月給</t>
+        </is>
+      </c>
+      <c r="D173" s="60" t="n">
+        <v>537000</v>
+      </c>
+      <c r="E173" s="117" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F173" s="32" t="n">
+        <v>537000</v>
+      </c>
+      <c r="G173" s="83" t="inlineStr">
+        <is>
+          <t>間接</t>
+        </is>
+      </c>
+      <c r="H173" s="118" t="inlineStr"/>
+      <c r="I173" s="82" t="n">
+        <v>6444000</v>
+      </c>
+    </row>
+    <row r="174" ht="20" customHeight="1">
+      <c r="A174" s="115" t="inlineStr">
+        <is>
+          <t>管理</t>
+        </is>
+      </c>
+      <c r="B174" s="116" t="inlineStr">
+        <is>
+          <t>遠藤 一栄</t>
+        </is>
+      </c>
+      <c r="C174" s="78" t="inlineStr">
+        <is>
+          <t>月給</t>
+        </is>
+      </c>
+      <c r="D174" s="60" t="n">
+        <v>337000</v>
+      </c>
+      <c r="E174" s="117" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F174" s="32" t="n">
+        <v>337000</v>
+      </c>
+      <c r="G174" s="83" t="inlineStr">
+        <is>
+          <t>間接</t>
+        </is>
+      </c>
+      <c r="H174" s="118" t="inlineStr"/>
+      <c r="I174" s="82" t="n">
+        <v>4044000</v>
+      </c>
+    </row>
+    <row r="175" ht="20" customHeight="1">
+      <c r="A175" s="115" t="inlineStr">
+        <is>
+          <t>管理</t>
+        </is>
+      </c>
+      <c r="B175" s="116" t="inlineStr">
+        <is>
+          <t>足立 孝子</t>
+        </is>
+      </c>
+      <c r="C175" s="78" t="inlineStr">
+        <is>
+          <t>月給</t>
+        </is>
+      </c>
+      <c r="D175" s="60" t="n">
+        <v>257993</v>
+      </c>
+      <c r="E175" s="117" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F175" s="32" t="n">
+        <v>257993</v>
+      </c>
+      <c r="G175" s="83" t="inlineStr">
+        <is>
+          <t>間接</t>
+        </is>
+      </c>
+      <c r="H175" s="118" t="inlineStr"/>
+      <c r="I175" s="82" t="n">
+        <v>3095916</v>
+      </c>
+    </row>
+    <row r="176" ht="20" customHeight="1">
+      <c r="A176" s="115" t="inlineStr">
+        <is>
+          <t>管理</t>
+        </is>
+      </c>
+      <c r="B176" s="116" t="inlineStr">
+        <is>
+          <t>滝田 豪</t>
+        </is>
+      </c>
+      <c r="C176" s="78" t="inlineStr">
+        <is>
+          <t>月給</t>
+        </is>
+      </c>
+      <c r="D176" s="60" t="n">
+        <v>307830</v>
+      </c>
+      <c r="E176" s="117" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F176" s="32" t="n">
+        <v>307830</v>
+      </c>
+      <c r="G176" s="83" t="inlineStr">
+        <is>
+          <t>間接</t>
+        </is>
+      </c>
+      <c r="H176" s="118" t="inlineStr"/>
+      <c r="I176" s="82" t="n">
+        <v>3693960</v>
+      </c>
+    </row>
+    <row r="177" ht="20" customHeight="1">
+      <c r="A177" s="115" t="inlineStr">
+        <is>
+          <t>管理</t>
+        </is>
+      </c>
+      <c r="B177" s="116" t="inlineStr">
+        <is>
+          <t>加藤 千明</t>
+        </is>
+      </c>
+      <c r="C177" s="78" t="inlineStr">
+        <is>
+          <t>月給</t>
+        </is>
+      </c>
+      <c r="D177" s="60" t="n">
+        <v>269601</v>
+      </c>
+      <c r="E177" s="117" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F177" s="32" t="n">
+        <v>269601</v>
+      </c>
+      <c r="G177" s="83" t="inlineStr">
+        <is>
+          <t>間接</t>
+        </is>
+      </c>
+      <c r="H177" s="118" t="inlineStr"/>
+      <c r="I177" s="82" t="n">
+        <v>3235212</v>
+      </c>
+    </row>
+    <row r="178" ht="20" customHeight="1">
+      <c r="A178" s="115" t="inlineStr">
+        <is>
+          <t>管理</t>
+        </is>
+      </c>
+      <c r="B178" s="116" t="inlineStr">
+        <is>
+          <t>山口 博文</t>
+        </is>
+      </c>
+      <c r="C178" s="78" t="inlineStr">
+        <is>
+          <t>月給</t>
+        </is>
+      </c>
+      <c r="D178" s="60" t="n">
+        <v>250500</v>
+      </c>
+      <c r="E178" s="117" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F178" s="32" t="n">
+        <v>250500</v>
+      </c>
+      <c r="G178" s="83" t="inlineStr">
+        <is>
+          <t>間接</t>
+        </is>
+      </c>
+      <c r="H178" s="118" t="inlineStr"/>
+      <c r="I178" s="82" t="n">
+        <v>3006000</v>
+      </c>
+    </row>
+    <row r="179" ht="20" customHeight="1">
+      <c r="A179" s="115" t="inlineStr">
+        <is>
+          <t>管理</t>
+        </is>
+      </c>
+      <c r="B179" s="116" t="inlineStr">
+        <is>
+          <t>佐藤 正美</t>
+        </is>
+      </c>
+      <c r="C179" s="78" t="inlineStr">
+        <is>
+          <t>月給</t>
+        </is>
+      </c>
+      <c r="D179" s="60" t="n">
+        <v>264500</v>
+      </c>
+      <c r="E179" s="117" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F179" s="32" t="n">
+        <v>264500</v>
+      </c>
+      <c r="G179" s="83" t="inlineStr">
+        <is>
+          <t>間接</t>
+        </is>
+      </c>
+      <c r="H179" s="118" t="inlineStr"/>
+      <c r="I179" s="82" t="n">
+        <v>3174000</v>
+      </c>
+    </row>
+    <row r="180" ht="20" customHeight="1">
+      <c r="A180" s="115" t="inlineStr">
+        <is>
+          <t>管理</t>
+        </is>
+      </c>
+      <c r="B180" s="116" t="inlineStr">
+        <is>
+          <t>戸塚 秀喜</t>
+        </is>
+      </c>
+      <c r="C180" s="78" t="inlineStr">
+        <is>
+          <t>月給</t>
+        </is>
+      </c>
+      <c r="D180" s="60" t="n">
+        <v>260600</v>
+      </c>
+      <c r="E180" s="117" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F180" s="32" t="n">
+        <v>260600</v>
+      </c>
+      <c r="G180" s="83" t="inlineStr">
+        <is>
+          <t>間接</t>
+        </is>
+      </c>
+      <c r="H180" s="118" t="inlineStr"/>
+      <c r="I180" s="82" t="n">
+        <v>3127200</v>
+      </c>
+    </row>
+    <row r="181" ht="20" customHeight="1">
+      <c r="A181" s="115" t="inlineStr">
+        <is>
+          <t>管理</t>
+        </is>
+      </c>
+      <c r="B181" s="116" t="inlineStr">
+        <is>
+          <t>落合 秋夫</t>
+        </is>
+      </c>
+      <c r="C181" s="78" t="inlineStr">
+        <is>
+          <t>月給</t>
+        </is>
+      </c>
+      <c r="D181" s="60" t="n">
+        <v>306298</v>
+      </c>
+      <c r="E181" s="117" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F181" s="32" t="n">
+        <v>306298</v>
+      </c>
+      <c r="G181" s="83" t="inlineStr">
+        <is>
+          <t>間接</t>
+        </is>
+      </c>
+      <c r="H181" s="118" t="inlineStr"/>
+      <c r="I181" s="82" t="n">
+        <v>3675576</v>
+      </c>
+    </row>
+    <row r="182" ht="18" customHeight="1">
+      <c r="A182" s="119" t="inlineStr">
+        <is>
+          <t>管理 合計  (10名)</t>
+        </is>
+      </c>
+      <c r="F182" s="120">
+        <f>SUMIF(A172:A181,"管理",F172:F181)</f>
+        <v/>
+      </c>
+      <c r="G182" s="121" t="n"/>
+      <c r="H182" s="121" t="n"/>
+      <c r="I182" s="121" t="n"/>
+    </row>
+    <row r="183"/>
+    <row r="184" ht="10" customHeight="1"/>
+    <row r="185">
+      <c r="A185" s="122" t="n"/>
+    </row>
+    <row r="186" ht="28" customHeight="1">
+      <c r="A186" s="123" t="inlineStr">
+        <is>
+          <t>▶ 月額人件費 総合計（全拠点）</t>
+        </is>
+      </c>
+      <c r="F186" s="124">
+        <f>SUMIF(A6:A184,"&lt;&gt;管理",F6:F184)</f>
+        <v/>
+      </c>
+      <c r="G186" s="122" t="n"/>
+      <c r="H186" s="122" t="n"/>
+      <c r="I186" s="125">
+        <f>F186*12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="187" ht="18" customHeight="1">
+      <c r="A187" s="126" t="inlineStr">
+        <is>
+          <t>※ 上記は月額固定部分のみ。社会保険料（会社負担・約15%）・賞与・退職積立等は別途加算が必要です。</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="17">
+    <mergeCell ref="E3:I3"/>
+    <mergeCell ref="A186:E186"/>
+    <mergeCell ref="A172:I172"/>
+    <mergeCell ref="A2:I2"/>
+    <mergeCell ref="A171:E171"/>
+    <mergeCell ref="A99:I99"/>
+    <mergeCell ref="A98:E98"/>
+    <mergeCell ref="A185:I185"/>
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A182:E182"/>
+    <mergeCell ref="A118:E118"/>
+    <mergeCell ref="A3:C3"/>
+    <mergeCell ref="A6:I6"/>
+    <mergeCell ref="A119:I119"/>
+    <mergeCell ref="A131:I131"/>
+    <mergeCell ref="A187:I187"/>
+    <mergeCell ref="A130:E130"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/sacure_採算管理_v4_ルート別案件別.xlsx
+++ b/sacure_採算管理_v4_ルート別案件別.xlsx
@@ -5352,22 +5352,12 @@
         <f>IFERROR(VLOOKUP(C5,▼売上原票!$A:$P,3,0),0)</f>
         <v/>
       </c>
-      <c r="E5" s="12" t="n">
-        <v>650000</v>
-      </c>
-      <c r="F5" s="12" t="n">
-        <v>190000</v>
-      </c>
-      <c r="G5" s="12" t="n">
-        <v>85000</v>
-      </c>
+      <c r="E5" s="12" t="n"/>
+      <c r="F5" s="12" t="n"/>
+      <c r="G5" s="12" t="n"/>
       <c r="H5" s="12" t="n"/>
-      <c r="I5" s="12" t="n">
-        <v>75000</v>
-      </c>
-      <c r="J5" s="12" t="n">
-        <v>45000</v>
-      </c>
+      <c r="I5" s="12" t="n"/>
+      <c r="J5" s="12" t="n"/>
       <c r="K5" s="13">
         <f>E5+F5+G5+H5+I5+J5</f>
         <v/>
@@ -5419,22 +5409,12 @@
         <f>IFERROR(VLOOKUP(C6,▼売上原票!$A:$P,3,0),0)</f>
         <v/>
       </c>
-      <c r="E6" s="12" t="n">
-        <v>650000</v>
-      </c>
-      <c r="F6" s="12" t="n">
-        <v>190000</v>
-      </c>
-      <c r="G6" s="12" t="n">
-        <v>85000</v>
-      </c>
+      <c r="E6" s="12" t="n"/>
+      <c r="F6" s="12" t="n"/>
+      <c r="G6" s="12" t="n"/>
       <c r="H6" s="12" t="n"/>
-      <c r="I6" s="12" t="n">
-        <v>75000</v>
-      </c>
-      <c r="J6" s="12" t="n">
-        <v>45000</v>
-      </c>
+      <c r="I6" s="12" t="n"/>
+      <c r="J6" s="12" t="n"/>
       <c r="K6" s="13">
         <f>E6+F6+G6+H6+I6+J6</f>
         <v/>
@@ -5485,22 +5465,12 @@
         <f>IFERROR(VLOOKUP(C7,▼売上原票!$A:$P,3,0),0)</f>
         <v/>
       </c>
-      <c r="E7" s="12" t="n">
-        <v>650000</v>
-      </c>
-      <c r="F7" s="12" t="n">
-        <v>190000</v>
-      </c>
-      <c r="G7" s="12" t="n">
-        <v>85000</v>
-      </c>
+      <c r="E7" s="12" t="n"/>
+      <c r="F7" s="12" t="n"/>
+      <c r="G7" s="12" t="n"/>
       <c r="H7" s="12" t="n"/>
-      <c r="I7" s="12" t="n">
-        <v>75000</v>
-      </c>
-      <c r="J7" s="12" t="n">
-        <v>45000</v>
-      </c>
+      <c r="I7" s="12" t="n"/>
+      <c r="J7" s="12" t="n"/>
       <c r="K7" s="13">
         <f>E7+F7+G7+H7+I7+J7</f>
         <v/>
@@ -5551,22 +5521,12 @@
         <f>IFERROR(VLOOKUP(C8,▼売上原票!$A:$P,3,0),0)</f>
         <v/>
       </c>
-      <c r="E8" s="12" t="n">
-        <v>650000</v>
-      </c>
-      <c r="F8" s="12" t="n">
-        <v>190000</v>
-      </c>
-      <c r="G8" s="12" t="n">
-        <v>85000</v>
-      </c>
+      <c r="E8" s="12" t="n"/>
+      <c r="F8" s="12" t="n"/>
+      <c r="G8" s="12" t="n"/>
       <c r="H8" s="12" t="n"/>
-      <c r="I8" s="12" t="n">
-        <v>75000</v>
-      </c>
-      <c r="J8" s="12" t="n">
-        <v>45000</v>
-      </c>
+      <c r="I8" s="12" t="n"/>
+      <c r="J8" s="12" t="n"/>
       <c r="K8" s="13">
         <f>E8+F8+G8+H8+I8+J8</f>
         <v/>
@@ -5617,22 +5577,12 @@
         <f>IFERROR(VLOOKUP(C9,▼売上原票!$A:$P,3,0),0)</f>
         <v/>
       </c>
-      <c r="E9" s="12" t="n">
-        <v>650000</v>
-      </c>
-      <c r="F9" s="12" t="n">
-        <v>190000</v>
-      </c>
-      <c r="G9" s="12" t="n">
-        <v>85000</v>
-      </c>
+      <c r="E9" s="12" t="n"/>
+      <c r="F9" s="12" t="n"/>
+      <c r="G9" s="12" t="n"/>
       <c r="H9" s="12" t="n"/>
-      <c r="I9" s="12" t="n">
-        <v>75000</v>
-      </c>
-      <c r="J9" s="12" t="n">
-        <v>45000</v>
-      </c>
+      <c r="I9" s="12" t="n"/>
+      <c r="J9" s="12" t="n"/>
       <c r="K9" s="13">
         <f>E9+F9+G9+H9+I9+J9</f>
         <v/>
@@ -5683,22 +5633,12 @@
         <f>IFERROR(VLOOKUP(C10,▼売上原票!$A:$P,3,0),0)</f>
         <v/>
       </c>
-      <c r="E10" s="12" t="n">
-        <v>650000</v>
-      </c>
-      <c r="F10" s="12" t="n">
-        <v>190000</v>
-      </c>
-      <c r="G10" s="12" t="n">
-        <v>85000</v>
-      </c>
+      <c r="E10" s="12" t="n"/>
+      <c r="F10" s="12" t="n"/>
+      <c r="G10" s="12" t="n"/>
       <c r="H10" s="12" t="n"/>
-      <c r="I10" s="12" t="n">
-        <v>75000</v>
-      </c>
-      <c r="J10" s="12" t="n">
-        <v>45000</v>
-      </c>
+      <c r="I10" s="12" t="n"/>
+      <c r="J10" s="12" t="n"/>
       <c r="K10" s="13">
         <f>E10+F10+G10+H10+I10+J10</f>
         <v/>
@@ -5749,22 +5689,12 @@
         <f>IFERROR(VLOOKUP(C11,▼売上原票!$A:$P,3,0),0)</f>
         <v/>
       </c>
-      <c r="E11" s="12" t="n">
-        <v>650000</v>
-      </c>
-      <c r="F11" s="12" t="n">
-        <v>190000</v>
-      </c>
-      <c r="G11" s="12" t="n">
-        <v>85000</v>
-      </c>
+      <c r="E11" s="12" t="n"/>
+      <c r="F11" s="12" t="n"/>
+      <c r="G11" s="12" t="n"/>
       <c r="H11" s="12" t="n"/>
-      <c r="I11" s="12" t="n">
-        <v>75000</v>
-      </c>
-      <c r="J11" s="12" t="n">
-        <v>45000</v>
-      </c>
+      <c r="I11" s="12" t="n"/>
+      <c r="J11" s="12" t="n"/>
       <c r="K11" s="13">
         <f>E11+F11+G11+H11+I11+J11</f>
         <v/>
@@ -5815,22 +5745,12 @@
         <f>IFERROR(VLOOKUP(C12,▼売上原票!$A:$P,3,0),0)</f>
         <v/>
       </c>
-      <c r="E12" s="12" t="n">
-        <v>650000</v>
-      </c>
-      <c r="F12" s="12" t="n">
-        <v>190000</v>
-      </c>
-      <c r="G12" s="12" t="n">
-        <v>85000</v>
-      </c>
+      <c r="E12" s="12" t="n"/>
+      <c r="F12" s="12" t="n"/>
+      <c r="G12" s="12" t="n"/>
       <c r="H12" s="12" t="n"/>
-      <c r="I12" s="12" t="n">
-        <v>75000</v>
-      </c>
-      <c r="J12" s="12" t="n">
-        <v>45000</v>
-      </c>
+      <c r="I12" s="12" t="n"/>
+      <c r="J12" s="12" t="n"/>
       <c r="K12" s="13">
         <f>E12+F12+G12+H12+I12+J12</f>
         <v/>
@@ -5881,22 +5801,12 @@
         <f>IFERROR(VLOOKUP(C13,▼売上原票!$A:$P,3,0),0)</f>
         <v/>
       </c>
-      <c r="E13" s="12" t="n">
-        <v>650000</v>
-      </c>
-      <c r="F13" s="12" t="n">
-        <v>190000</v>
-      </c>
-      <c r="G13" s="12" t="n">
-        <v>85000</v>
-      </c>
+      <c r="E13" s="12" t="n"/>
+      <c r="F13" s="12" t="n"/>
+      <c r="G13" s="12" t="n"/>
       <c r="H13" s="12" t="n"/>
-      <c r="I13" s="12" t="n">
-        <v>75000</v>
-      </c>
-      <c r="J13" s="12" t="n">
-        <v>45000</v>
-      </c>
+      <c r="I13" s="12" t="n"/>
+      <c r="J13" s="12" t="n"/>
       <c r="K13" s="13">
         <f>E13+F13+G13+H13+I13+J13</f>
         <v/>
@@ -5947,22 +5857,12 @@
         <f>IFERROR(VLOOKUP(C14,▼売上原票!$A:$P,3,0),0)</f>
         <v/>
       </c>
-      <c r="E14" s="12" t="n">
-        <v>650000</v>
-      </c>
-      <c r="F14" s="12" t="n">
-        <v>190000</v>
-      </c>
-      <c r="G14" s="12" t="n">
-        <v>85000</v>
-      </c>
+      <c r="E14" s="12" t="n"/>
+      <c r="F14" s="12" t="n"/>
+      <c r="G14" s="12" t="n"/>
       <c r="H14" s="12" t="n"/>
-      <c r="I14" s="12" t="n">
-        <v>75000</v>
-      </c>
-      <c r="J14" s="12" t="n">
-        <v>45000</v>
-      </c>
+      <c r="I14" s="12" t="n"/>
+      <c r="J14" s="12" t="n"/>
       <c r="K14" s="13">
         <f>E14+F14+G14+H14+I14+J14</f>
         <v/>
@@ -6013,22 +5913,12 @@
         <f>IFERROR(VLOOKUP(C15,▼売上原票!$A:$P,3,0),0)</f>
         <v/>
       </c>
-      <c r="E15" s="12" t="n">
-        <v>650000</v>
-      </c>
-      <c r="F15" s="12" t="n">
-        <v>190000</v>
-      </c>
-      <c r="G15" s="12" t="n">
-        <v>85000</v>
-      </c>
+      <c r="E15" s="12" t="n"/>
+      <c r="F15" s="12" t="n"/>
+      <c r="G15" s="12" t="n"/>
       <c r="H15" s="12" t="n"/>
-      <c r="I15" s="12" t="n">
-        <v>75000</v>
-      </c>
-      <c r="J15" s="12" t="n">
-        <v>45000</v>
-      </c>
+      <c r="I15" s="12" t="n"/>
+      <c r="J15" s="12" t="n"/>
       <c r="K15" s="13">
         <f>E15+F15+G15+H15+I15+J15</f>
         <v/>
@@ -6079,22 +5969,12 @@
         <f>IFERROR(VLOOKUP(C16,▼売上原票!$A:$P,3,0),0)</f>
         <v/>
       </c>
-      <c r="E16" s="12" t="n">
-        <v>650000</v>
-      </c>
-      <c r="F16" s="12" t="n">
-        <v>190000</v>
-      </c>
-      <c r="G16" s="12" t="n">
-        <v>85000</v>
-      </c>
+      <c r="E16" s="12" t="n"/>
+      <c r="F16" s="12" t="n"/>
+      <c r="G16" s="12" t="n"/>
       <c r="H16" s="12" t="n"/>
-      <c r="I16" s="12" t="n">
-        <v>75000</v>
-      </c>
-      <c r="J16" s="12" t="n">
-        <v>45000</v>
-      </c>
+      <c r="I16" s="12" t="n"/>
+      <c r="J16" s="12" t="n"/>
       <c r="K16" s="13">
         <f>E16+F16+G16+H16+I16+J16</f>
         <v/>
@@ -6145,22 +6025,12 @@
         <f>IFERROR(VLOOKUP(C17,▼売上原票!$A:$P,3,0),0)</f>
         <v/>
       </c>
-      <c r="E17" s="12" t="n">
-        <v>650000</v>
-      </c>
-      <c r="F17" s="12" t="n">
-        <v>190000</v>
-      </c>
-      <c r="G17" s="12" t="n">
-        <v>85000</v>
-      </c>
+      <c r="E17" s="12" t="n"/>
+      <c r="F17" s="12" t="n"/>
+      <c r="G17" s="12" t="n"/>
       <c r="H17" s="12" t="n"/>
-      <c r="I17" s="12" t="n">
-        <v>75000</v>
-      </c>
-      <c r="J17" s="12" t="n">
-        <v>45000</v>
-      </c>
+      <c r="I17" s="12" t="n"/>
+      <c r="J17" s="12" t="n"/>
       <c r="K17" s="13">
         <f>E17+F17+G17+H17+I17+J17</f>
         <v/>
@@ -6211,22 +6081,12 @@
         <f>IFERROR(VLOOKUP(C18,▼売上原票!$A:$P,3,0),0)</f>
         <v/>
       </c>
-      <c r="E18" s="12" t="n">
-        <v>650000</v>
-      </c>
-      <c r="F18" s="12" t="n">
-        <v>190000</v>
-      </c>
-      <c r="G18" s="12" t="n">
-        <v>85000</v>
-      </c>
+      <c r="E18" s="12" t="n"/>
+      <c r="F18" s="12" t="n"/>
+      <c r="G18" s="12" t="n"/>
       <c r="H18" s="12" t="n"/>
-      <c r="I18" s="12" t="n">
-        <v>75000</v>
-      </c>
-      <c r="J18" s="12" t="n">
-        <v>45000</v>
-      </c>
+      <c r="I18" s="12" t="n"/>
+      <c r="J18" s="12" t="n"/>
       <c r="K18" s="13">
         <f>E18+F18+G18+H18+I18+J18</f>
         <v/>
@@ -6277,22 +6137,12 @@
         <f>IFERROR(VLOOKUP(C19,▼売上原票!$A:$P,3,0),0)</f>
         <v/>
       </c>
-      <c r="E19" s="12" t="n">
-        <v>650000</v>
-      </c>
-      <c r="F19" s="12" t="n">
-        <v>190000</v>
-      </c>
-      <c r="G19" s="12" t="n">
-        <v>85000</v>
-      </c>
+      <c r="E19" s="12" t="n"/>
+      <c r="F19" s="12" t="n"/>
+      <c r="G19" s="12" t="n"/>
       <c r="H19" s="12" t="n"/>
-      <c r="I19" s="12" t="n">
-        <v>75000</v>
-      </c>
-      <c r="J19" s="12" t="n">
-        <v>45000</v>
-      </c>
+      <c r="I19" s="12" t="n"/>
+      <c r="J19" s="12" t="n"/>
       <c r="K19" s="13">
         <f>E19+F19+G19+H19+I19+J19</f>
         <v/>
@@ -6343,22 +6193,12 @@
         <f>IFERROR(VLOOKUP(C20,▼売上原票!$A:$P,3,0),0)</f>
         <v/>
       </c>
-      <c r="E20" s="12" t="n">
-        <v>650000</v>
-      </c>
-      <c r="F20" s="12" t="n">
-        <v>190000</v>
-      </c>
-      <c r="G20" s="12" t="n">
-        <v>85000</v>
-      </c>
+      <c r="E20" s="12" t="n"/>
+      <c r="F20" s="12" t="n"/>
+      <c r="G20" s="12" t="n"/>
       <c r="H20" s="12" t="n"/>
-      <c r="I20" s="12" t="n">
-        <v>75000</v>
-      </c>
-      <c r="J20" s="12" t="n">
-        <v>45000</v>
-      </c>
+      <c r="I20" s="12" t="n"/>
+      <c r="J20" s="12" t="n"/>
       <c r="K20" s="13">
         <f>E20+F20+G20+H20+I20+J20</f>
         <v/>
@@ -6409,22 +6249,12 @@
         <f>IFERROR(VLOOKUP(C21,▼売上原票!$A:$P,3,0),0)</f>
         <v/>
       </c>
-      <c r="E21" s="12" t="n">
-        <v>650000</v>
-      </c>
-      <c r="F21" s="12" t="n">
-        <v>190000</v>
-      </c>
-      <c r="G21" s="12" t="n">
-        <v>85000</v>
-      </c>
+      <c r="E21" s="12" t="n"/>
+      <c r="F21" s="12" t="n"/>
+      <c r="G21" s="12" t="n"/>
       <c r="H21" s="12" t="n"/>
-      <c r="I21" s="12" t="n">
-        <v>75000</v>
-      </c>
-      <c r="J21" s="12" t="n">
-        <v>45000</v>
-      </c>
+      <c r="I21" s="12" t="n"/>
+      <c r="J21" s="12" t="n"/>
       <c r="K21" s="13">
         <f>E21+F21+G21+H21+I21+J21</f>
         <v/>
@@ -6494,24 +6324,12 @@
         <f>IFERROR(VLOOKUP(C23,▼売上原票!$A:$P,4,0),0)</f>
         <v/>
       </c>
-      <c r="E23" s="12" t="n">
-        <v>1800000</v>
-      </c>
-      <c r="F23" s="12" t="n">
-        <v>520000</v>
-      </c>
-      <c r="G23" s="12" t="n">
-        <v>240000</v>
-      </c>
-      <c r="H23" s="12" t="n">
-        <v>1200000</v>
-      </c>
-      <c r="I23" s="12" t="n">
-        <v>180000</v>
-      </c>
-      <c r="J23" s="12" t="n">
-        <v>120000</v>
-      </c>
+      <c r="E23" s="12" t="n"/>
+      <c r="F23" s="12" t="n"/>
+      <c r="G23" s="12" t="n"/>
+      <c r="H23" s="12" t="n"/>
+      <c r="I23" s="12" t="n"/>
+      <c r="J23" s="12" t="n"/>
       <c r="K23" s="13">
         <f>E23+F23+G23+H23+I23+J23</f>
         <v/>
@@ -6563,24 +6381,12 @@
         <f>IFERROR(VLOOKUP(C24,▼売上原票!$A:$P,4,0),0)</f>
         <v/>
       </c>
-      <c r="E24" s="12" t="n">
-        <v>1800000</v>
-      </c>
-      <c r="F24" s="12" t="n">
-        <v>520000</v>
-      </c>
-      <c r="G24" s="12" t="n">
-        <v>240000</v>
-      </c>
-      <c r="H24" s="12" t="n">
-        <v>1200000</v>
-      </c>
-      <c r="I24" s="12" t="n">
-        <v>180000</v>
-      </c>
-      <c r="J24" s="12" t="n">
-        <v>120000</v>
-      </c>
+      <c r="E24" s="12" t="n"/>
+      <c r="F24" s="12" t="n"/>
+      <c r="G24" s="12" t="n"/>
+      <c r="H24" s="12" t="n"/>
+      <c r="I24" s="12" t="n"/>
+      <c r="J24" s="12" t="n"/>
       <c r="K24" s="13">
         <f>E24+F24+G24+H24+I24+J24</f>
         <v/>
@@ -6631,24 +6437,12 @@
         <f>IFERROR(VLOOKUP(C25,▼売上原票!$A:$P,4,0),0)</f>
         <v/>
       </c>
-      <c r="E25" s="12" t="n">
-        <v>1800000</v>
-      </c>
-      <c r="F25" s="12" t="n">
-        <v>520000</v>
-      </c>
-      <c r="G25" s="12" t="n">
-        <v>240000</v>
-      </c>
-      <c r="H25" s="12" t="n">
-        <v>1200000</v>
-      </c>
-      <c r="I25" s="12" t="n">
-        <v>180000</v>
-      </c>
-      <c r="J25" s="12" t="n">
-        <v>120000</v>
-      </c>
+      <c r="E25" s="12" t="n"/>
+      <c r="F25" s="12" t="n"/>
+      <c r="G25" s="12" t="n"/>
+      <c r="H25" s="12" t="n"/>
+      <c r="I25" s="12" t="n"/>
+      <c r="J25" s="12" t="n"/>
       <c r="K25" s="13">
         <f>E25+F25+G25+H25+I25+J25</f>
         <v/>
@@ -6699,24 +6493,12 @@
         <f>IFERROR(VLOOKUP(C26,▼売上原票!$A:$P,4,0),0)</f>
         <v/>
       </c>
-      <c r="E26" s="12" t="n">
-        <v>1800000</v>
-      </c>
-      <c r="F26" s="12" t="n">
-        <v>520000</v>
-      </c>
-      <c r="G26" s="12" t="n">
-        <v>240000</v>
-      </c>
-      <c r="H26" s="12" t="n">
-        <v>1200000</v>
-      </c>
-      <c r="I26" s="12" t="n">
-        <v>180000</v>
-      </c>
-      <c r="J26" s="12" t="n">
-        <v>120000</v>
-      </c>
+      <c r="E26" s="12" t="n"/>
+      <c r="F26" s="12" t="n"/>
+      <c r="G26" s="12" t="n"/>
+      <c r="H26" s="12" t="n"/>
+      <c r="I26" s="12" t="n"/>
+      <c r="J26" s="12" t="n"/>
       <c r="K26" s="13">
         <f>E26+F26+G26+H26+I26+J26</f>
         <v/>
@@ -6767,24 +6549,12 @@
         <f>IFERROR(VLOOKUP(C27,▼売上原票!$A:$P,4,0),0)</f>
         <v/>
       </c>
-      <c r="E27" s="12" t="n">
-        <v>1800000</v>
-      </c>
-      <c r="F27" s="12" t="n">
-        <v>520000</v>
-      </c>
-      <c r="G27" s="12" t="n">
-        <v>240000</v>
-      </c>
-      <c r="H27" s="12" t="n">
-        <v>1200000</v>
-      </c>
-      <c r="I27" s="12" t="n">
-        <v>180000</v>
-      </c>
-      <c r="J27" s="12" t="n">
-        <v>120000</v>
-      </c>
+      <c r="E27" s="12" t="n"/>
+      <c r="F27" s="12" t="n"/>
+      <c r="G27" s="12" t="n"/>
+      <c r="H27" s="12" t="n"/>
+      <c r="I27" s="12" t="n"/>
+      <c r="J27" s="12" t="n"/>
       <c r="K27" s="13">
         <f>E27+F27+G27+H27+I27+J27</f>
         <v/>
@@ -6835,24 +6605,12 @@
         <f>IFERROR(VLOOKUP(C28,▼売上原票!$A:$P,4,0),0)</f>
         <v/>
       </c>
-      <c r="E28" s="12" t="n">
-        <v>1800000</v>
-      </c>
-      <c r="F28" s="12" t="n">
-        <v>520000</v>
-      </c>
-      <c r="G28" s="12" t="n">
-        <v>240000</v>
-      </c>
-      <c r="H28" s="12" t="n">
-        <v>1200000</v>
-      </c>
-      <c r="I28" s="12" t="n">
-        <v>180000</v>
-      </c>
-      <c r="J28" s="12" t="n">
-        <v>120000</v>
-      </c>
+      <c r="E28" s="12" t="n"/>
+      <c r="F28" s="12" t="n"/>
+      <c r="G28" s="12" t="n"/>
+      <c r="H28" s="12" t="n"/>
+      <c r="I28" s="12" t="n"/>
+      <c r="J28" s="12" t="n"/>
       <c r="K28" s="13">
         <f>E28+F28+G28+H28+I28+J28</f>
         <v/>
@@ -6903,24 +6661,12 @@
         <f>IFERROR(VLOOKUP(C29,▼売上原票!$A:$P,4,0),0)</f>
         <v/>
       </c>
-      <c r="E29" s="12" t="n">
-        <v>1800000</v>
-      </c>
-      <c r="F29" s="12" t="n">
-        <v>520000</v>
-      </c>
-      <c r="G29" s="12" t="n">
-        <v>240000</v>
-      </c>
-      <c r="H29" s="12" t="n">
-        <v>1200000</v>
-      </c>
-      <c r="I29" s="12" t="n">
-        <v>180000</v>
-      </c>
-      <c r="J29" s="12" t="n">
-        <v>120000</v>
-      </c>
+      <c r="E29" s="12" t="n"/>
+      <c r="F29" s="12" t="n"/>
+      <c r="G29" s="12" t="n"/>
+      <c r="H29" s="12" t="n"/>
+      <c r="I29" s="12" t="n"/>
+      <c r="J29" s="12" t="n"/>
       <c r="K29" s="13">
         <f>E29+F29+G29+H29+I29+J29</f>
         <v/>
@@ -6971,24 +6717,12 @@
         <f>IFERROR(VLOOKUP(C30,▼売上原票!$A:$P,4,0),0)</f>
         <v/>
       </c>
-      <c r="E30" s="12" t="n">
-        <v>1800000</v>
-      </c>
-      <c r="F30" s="12" t="n">
-        <v>520000</v>
-      </c>
-      <c r="G30" s="12" t="n">
-        <v>240000</v>
-      </c>
-      <c r="H30" s="12" t="n">
-        <v>1200000</v>
-      </c>
-      <c r="I30" s="12" t="n">
-        <v>180000</v>
-      </c>
-      <c r="J30" s="12" t="n">
-        <v>120000</v>
-      </c>
+      <c r="E30" s="12" t="n"/>
+      <c r="F30" s="12" t="n"/>
+      <c r="G30" s="12" t="n"/>
+      <c r="H30" s="12" t="n"/>
+      <c r="I30" s="12" t="n"/>
+      <c r="J30" s="12" t="n"/>
       <c r="K30" s="13">
         <f>E30+F30+G30+H30+I30+J30</f>
         <v/>
@@ -7039,24 +6773,12 @@
         <f>IFERROR(VLOOKUP(C31,▼売上原票!$A:$P,4,0),0)</f>
         <v/>
       </c>
-      <c r="E31" s="12" t="n">
-        <v>1800000</v>
-      </c>
-      <c r="F31" s="12" t="n">
-        <v>520000</v>
-      </c>
-      <c r="G31" s="12" t="n">
-        <v>240000</v>
-      </c>
-      <c r="H31" s="12" t="n">
-        <v>1200000</v>
-      </c>
-      <c r="I31" s="12" t="n">
-        <v>180000</v>
-      </c>
-      <c r="J31" s="12" t="n">
-        <v>120000</v>
-      </c>
+      <c r="E31" s="12" t="n"/>
+      <c r="F31" s="12" t="n"/>
+      <c r="G31" s="12" t="n"/>
+      <c r="H31" s="12" t="n"/>
+      <c r="I31" s="12" t="n"/>
+      <c r="J31" s="12" t="n"/>
       <c r="K31" s="13">
         <f>E31+F31+G31+H31+I31+J31</f>
         <v/>
@@ -7107,24 +6829,12 @@
         <f>IFERROR(VLOOKUP(C32,▼売上原票!$A:$P,4,0),0)</f>
         <v/>
       </c>
-      <c r="E32" s="12" t="n">
-        <v>1800000</v>
-      </c>
-      <c r="F32" s="12" t="n">
-        <v>520000</v>
-      </c>
-      <c r="G32" s="12" t="n">
-        <v>240000</v>
-      </c>
-      <c r="H32" s="12" t="n">
-        <v>1200000</v>
-      </c>
-      <c r="I32" s="12" t="n">
-        <v>180000</v>
-      </c>
-      <c r="J32" s="12" t="n">
-        <v>120000</v>
-      </c>
+      <c r="E32" s="12" t="n"/>
+      <c r="F32" s="12" t="n"/>
+      <c r="G32" s="12" t="n"/>
+      <c r="H32" s="12" t="n"/>
+      <c r="I32" s="12" t="n"/>
+      <c r="J32" s="12" t="n"/>
       <c r="K32" s="13">
         <f>E32+F32+G32+H32+I32+J32</f>
         <v/>
@@ -7175,24 +6885,12 @@
         <f>IFERROR(VLOOKUP(C33,▼売上原票!$A:$P,4,0),0)</f>
         <v/>
       </c>
-      <c r="E33" s="12" t="n">
-        <v>1800000</v>
-      </c>
-      <c r="F33" s="12" t="n">
-        <v>520000</v>
-      </c>
-      <c r="G33" s="12" t="n">
-        <v>240000</v>
-      </c>
-      <c r="H33" s="12" t="n">
-        <v>1200000</v>
-      </c>
-      <c r="I33" s="12" t="n">
-        <v>180000</v>
-      </c>
-      <c r="J33" s="12" t="n">
-        <v>120000</v>
-      </c>
+      <c r="E33" s="12" t="n"/>
+      <c r="F33" s="12" t="n"/>
+      <c r="G33" s="12" t="n"/>
+      <c r="H33" s="12" t="n"/>
+      <c r="I33" s="12" t="n"/>
+      <c r="J33" s="12" t="n"/>
       <c r="K33" s="13">
         <f>E33+F33+G33+H33+I33+J33</f>
         <v/>
@@ -7243,24 +6941,12 @@
         <f>IFERROR(VLOOKUP(C34,▼売上原票!$A:$P,4,0),0)</f>
         <v/>
       </c>
-      <c r="E34" s="12" t="n">
-        <v>1800000</v>
-      </c>
-      <c r="F34" s="12" t="n">
-        <v>520000</v>
-      </c>
-      <c r="G34" s="12" t="n">
-        <v>240000</v>
-      </c>
-      <c r="H34" s="12" t="n">
-        <v>1200000</v>
-      </c>
-      <c r="I34" s="12" t="n">
-        <v>180000</v>
-      </c>
-      <c r="J34" s="12" t="n">
-        <v>120000</v>
-      </c>
+      <c r="E34" s="12" t="n"/>
+      <c r="F34" s="12" t="n"/>
+      <c r="G34" s="12" t="n"/>
+      <c r="H34" s="12" t="n"/>
+      <c r="I34" s="12" t="n"/>
+      <c r="J34" s="12" t="n"/>
       <c r="K34" s="13">
         <f>E34+F34+G34+H34+I34+J34</f>
         <v/>
@@ -7311,24 +6997,12 @@
         <f>IFERROR(VLOOKUP(C35,▼売上原票!$A:$P,4,0),0)</f>
         <v/>
       </c>
-      <c r="E35" s="12" t="n">
-        <v>1800000</v>
-      </c>
-      <c r="F35" s="12" t="n">
-        <v>520000</v>
-      </c>
-      <c r="G35" s="12" t="n">
-        <v>240000</v>
-      </c>
-      <c r="H35" s="12" t="n">
-        <v>1200000</v>
-      </c>
-      <c r="I35" s="12" t="n">
-        <v>180000</v>
-      </c>
-      <c r="J35" s="12" t="n">
-        <v>120000</v>
-      </c>
+      <c r="E35" s="12" t="n"/>
+      <c r="F35" s="12" t="n"/>
+      <c r="G35" s="12" t="n"/>
+      <c r="H35" s="12" t="n"/>
+      <c r="I35" s="12" t="n"/>
+      <c r="J35" s="12" t="n"/>
       <c r="K35" s="13">
         <f>E35+F35+G35+H35+I35+J35</f>
         <v/>
@@ -7379,24 +7053,12 @@
         <f>IFERROR(VLOOKUP(C36,▼売上原票!$A:$P,4,0),0)</f>
         <v/>
       </c>
-      <c r="E36" s="12" t="n">
-        <v>1800000</v>
-      </c>
-      <c r="F36" s="12" t="n">
-        <v>520000</v>
-      </c>
-      <c r="G36" s="12" t="n">
-        <v>240000</v>
-      </c>
-      <c r="H36" s="12" t="n">
-        <v>1200000</v>
-      </c>
-      <c r="I36" s="12" t="n">
-        <v>180000</v>
-      </c>
-      <c r="J36" s="12" t="n">
-        <v>120000</v>
-      </c>
+      <c r="E36" s="12" t="n"/>
+      <c r="F36" s="12" t="n"/>
+      <c r="G36" s="12" t="n"/>
+      <c r="H36" s="12" t="n"/>
+      <c r="I36" s="12" t="n"/>
+      <c r="J36" s="12" t="n"/>
       <c r="K36" s="13">
         <f>E36+F36+G36+H36+I36+J36</f>
         <v/>
@@ -7447,24 +7109,12 @@
         <f>IFERROR(VLOOKUP(C37,▼売上原票!$A:$P,4,0),0)</f>
         <v/>
       </c>
-      <c r="E37" s="12" t="n">
-        <v>1800000</v>
-      </c>
-      <c r="F37" s="12" t="n">
-        <v>520000</v>
-      </c>
-      <c r="G37" s="12" t="n">
-        <v>240000</v>
-      </c>
-      <c r="H37" s="12" t="n">
-        <v>1200000</v>
-      </c>
-      <c r="I37" s="12" t="n">
-        <v>180000</v>
-      </c>
-      <c r="J37" s="12" t="n">
-        <v>120000</v>
-      </c>
+      <c r="E37" s="12" t="n"/>
+      <c r="F37" s="12" t="n"/>
+      <c r="G37" s="12" t="n"/>
+      <c r="H37" s="12" t="n"/>
+      <c r="I37" s="12" t="n"/>
+      <c r="J37" s="12" t="n"/>
       <c r="K37" s="13">
         <f>E37+F37+G37+H37+I37+J37</f>
         <v/>
@@ -7515,24 +7165,12 @@
         <f>IFERROR(VLOOKUP(C38,▼売上原票!$A:$P,4,0),0)</f>
         <v/>
       </c>
-      <c r="E38" s="12" t="n">
-        <v>1800000</v>
-      </c>
-      <c r="F38" s="12" t="n">
-        <v>520000</v>
-      </c>
-      <c r="G38" s="12" t="n">
-        <v>240000</v>
-      </c>
-      <c r="H38" s="12" t="n">
-        <v>1200000</v>
-      </c>
-      <c r="I38" s="12" t="n">
-        <v>180000</v>
-      </c>
-      <c r="J38" s="12" t="n">
-        <v>120000</v>
-      </c>
+      <c r="E38" s="12" t="n"/>
+      <c r="F38" s="12" t="n"/>
+      <c r="G38" s="12" t="n"/>
+      <c r="H38" s="12" t="n"/>
+      <c r="I38" s="12" t="n"/>
+      <c r="J38" s="12" t="n"/>
       <c r="K38" s="13">
         <f>E38+F38+G38+H38+I38+J38</f>
         <v/>
@@ -7583,24 +7221,12 @@
         <f>IFERROR(VLOOKUP(C39,▼売上原票!$A:$P,4,0),0)</f>
         <v/>
       </c>
-      <c r="E39" s="12" t="n">
-        <v>1800000</v>
-      </c>
-      <c r="F39" s="12" t="n">
-        <v>520000</v>
-      </c>
-      <c r="G39" s="12" t="n">
-        <v>240000</v>
-      </c>
-      <c r="H39" s="12" t="n">
-        <v>1200000</v>
-      </c>
-      <c r="I39" s="12" t="n">
-        <v>180000</v>
-      </c>
-      <c r="J39" s="12" t="n">
-        <v>120000</v>
-      </c>
+      <c r="E39" s="12" t="n"/>
+      <c r="F39" s="12" t="n"/>
+      <c r="G39" s="12" t="n"/>
+      <c r="H39" s="12" t="n"/>
+      <c r="I39" s="12" t="n"/>
+      <c r="J39" s="12" t="n"/>
       <c r="K39" s="13">
         <f>E39+F39+G39+H39+I39+J39</f>
         <v/>
@@ -7670,22 +7296,12 @@
         <f>IFERROR(VLOOKUP(C41,▼売上原票!$A:$P,5,0),0)</f>
         <v/>
       </c>
-      <c r="E41" s="12" t="n">
-        <v>180000</v>
-      </c>
-      <c r="F41" s="12" t="n">
-        <v>55000</v>
-      </c>
-      <c r="G41" s="12" t="n">
-        <v>180000</v>
-      </c>
+      <c r="E41" s="12" t="n"/>
+      <c r="F41" s="12" t="n"/>
+      <c r="G41" s="12" t="n"/>
       <c r="H41" s="12" t="n"/>
-      <c r="I41" s="12" t="n">
-        <v>15000</v>
-      </c>
-      <c r="J41" s="12" t="n">
-        <v>20000</v>
-      </c>
+      <c r="I41" s="12" t="n"/>
+      <c r="J41" s="12" t="n"/>
       <c r="K41" s="13">
         <f>E41+F41+G41+H41+I41+J41</f>
         <v/>
@@ -7737,22 +7353,12 @@
         <f>IFERROR(VLOOKUP(C42,▼売上原票!$A:$P,5,0),0)</f>
         <v/>
       </c>
-      <c r="E42" s="12" t="n">
-        <v>180000</v>
-      </c>
-      <c r="F42" s="12" t="n">
-        <v>55000</v>
-      </c>
-      <c r="G42" s="12" t="n">
-        <v>180000</v>
-      </c>
+      <c r="E42" s="12" t="n"/>
+      <c r="F42" s="12" t="n"/>
+      <c r="G42" s="12" t="n"/>
       <c r="H42" s="12" t="n"/>
-      <c r="I42" s="12" t="n">
-        <v>15000</v>
-      </c>
-      <c r="J42" s="12" t="n">
-        <v>20000</v>
-      </c>
+      <c r="I42" s="12" t="n"/>
+      <c r="J42" s="12" t="n"/>
       <c r="K42" s="13">
         <f>E42+F42+G42+H42+I42+J42</f>
         <v/>
@@ -7803,22 +7409,12 @@
         <f>IFERROR(VLOOKUP(C43,▼売上原票!$A:$P,5,0),0)</f>
         <v/>
       </c>
-      <c r="E43" s="12" t="n">
-        <v>180000</v>
-      </c>
-      <c r="F43" s="12" t="n">
-        <v>55000</v>
-      </c>
-      <c r="G43" s="12" t="n">
-        <v>180000</v>
-      </c>
+      <c r="E43" s="12" t="n"/>
+      <c r="F43" s="12" t="n"/>
+      <c r="G43" s="12" t="n"/>
       <c r="H43" s="12" t="n"/>
-      <c r="I43" s="12" t="n">
-        <v>15000</v>
-      </c>
-      <c r="J43" s="12" t="n">
-        <v>20000</v>
-      </c>
+      <c r="I43" s="12" t="n"/>
+      <c r="J43" s="12" t="n"/>
       <c r="K43" s="13">
         <f>E43+F43+G43+H43+I43+J43</f>
         <v/>
@@ -7869,22 +7465,12 @@
         <f>IFERROR(VLOOKUP(C44,▼売上原票!$A:$P,5,0),0)</f>
         <v/>
       </c>
-      <c r="E44" s="12" t="n">
-        <v>180000</v>
-      </c>
-      <c r="F44" s="12" t="n">
-        <v>55000</v>
-      </c>
-      <c r="G44" s="12" t="n">
-        <v>180000</v>
-      </c>
+      <c r="E44" s="12" t="n"/>
+      <c r="F44" s="12" t="n"/>
+      <c r="G44" s="12" t="n"/>
       <c r="H44" s="12" t="n"/>
-      <c r="I44" s="12" t="n">
-        <v>15000</v>
-      </c>
-      <c r="J44" s="12" t="n">
-        <v>20000</v>
-      </c>
+      <c r="I44" s="12" t="n"/>
+      <c r="J44" s="12" t="n"/>
       <c r="K44" s="13">
         <f>E44+F44+G44+H44+I44+J44</f>
         <v/>
@@ -7935,22 +7521,12 @@
         <f>IFERROR(VLOOKUP(C45,▼売上原票!$A:$P,5,0),0)</f>
         <v/>
       </c>
-      <c r="E45" s="12" t="n">
-        <v>180000</v>
-      </c>
-      <c r="F45" s="12" t="n">
-        <v>55000</v>
-      </c>
-      <c r="G45" s="12" t="n">
-        <v>180000</v>
-      </c>
+      <c r="E45" s="12" t="n"/>
+      <c r="F45" s="12" t="n"/>
+      <c r="G45" s="12" t="n"/>
       <c r="H45" s="12" t="n"/>
-      <c r="I45" s="12" t="n">
-        <v>15000</v>
-      </c>
-      <c r="J45" s="12" t="n">
-        <v>20000</v>
-      </c>
+      <c r="I45" s="12" t="n"/>
+      <c r="J45" s="12" t="n"/>
       <c r="K45" s="13">
         <f>E45+F45+G45+H45+I45+J45</f>
         <v/>
@@ -8001,22 +7577,12 @@
         <f>IFERROR(VLOOKUP(C46,▼売上原票!$A:$P,5,0),0)</f>
         <v/>
       </c>
-      <c r="E46" s="12" t="n">
-        <v>180000</v>
-      </c>
-      <c r="F46" s="12" t="n">
-        <v>55000</v>
-      </c>
-      <c r="G46" s="12" t="n">
-        <v>180000</v>
-      </c>
+      <c r="E46" s="12" t="n"/>
+      <c r="F46" s="12" t="n"/>
+      <c r="G46" s="12" t="n"/>
       <c r="H46" s="12" t="n"/>
-      <c r="I46" s="12" t="n">
-        <v>15000</v>
-      </c>
-      <c r="J46" s="12" t="n">
-        <v>20000</v>
-      </c>
+      <c r="I46" s="12" t="n"/>
+      <c r="J46" s="12" t="n"/>
       <c r="K46" s="13">
         <f>E46+F46+G46+H46+I46+J46</f>
         <v/>
@@ -8067,22 +7633,12 @@
         <f>IFERROR(VLOOKUP(C47,▼売上原票!$A:$P,5,0),0)</f>
         <v/>
       </c>
-      <c r="E47" s="12" t="n">
-        <v>180000</v>
-      </c>
-      <c r="F47" s="12" t="n">
-        <v>55000</v>
-      </c>
-      <c r="G47" s="12" t="n">
-        <v>180000</v>
-      </c>
+      <c r="E47" s="12" t="n"/>
+      <c r="F47" s="12" t="n"/>
+      <c r="G47" s="12" t="n"/>
       <c r="H47" s="12" t="n"/>
-      <c r="I47" s="12" t="n">
-        <v>15000</v>
-      </c>
-      <c r="J47" s="12" t="n">
-        <v>20000</v>
-      </c>
+      <c r="I47" s="12" t="n"/>
+      <c r="J47" s="12" t="n"/>
       <c r="K47" s="13">
         <f>E47+F47+G47+H47+I47+J47</f>
         <v/>
@@ -8133,22 +7689,12 @@
         <f>IFERROR(VLOOKUP(C48,▼売上原票!$A:$P,5,0),0)</f>
         <v/>
       </c>
-      <c r="E48" s="12" t="n">
-        <v>180000</v>
-      </c>
-      <c r="F48" s="12" t="n">
-        <v>55000</v>
-      </c>
-      <c r="G48" s="12" t="n">
-        <v>180000</v>
-      </c>
+      <c r="E48" s="12" t="n"/>
+      <c r="F48" s="12" t="n"/>
+      <c r="G48" s="12" t="n"/>
       <c r="H48" s="12" t="n"/>
-      <c r="I48" s="12" t="n">
-        <v>15000</v>
-      </c>
-      <c r="J48" s="12" t="n">
-        <v>20000</v>
-      </c>
+      <c r="I48" s="12" t="n"/>
+      <c r="J48" s="12" t="n"/>
       <c r="K48" s="13">
         <f>E48+F48+G48+H48+I48+J48</f>
         <v/>
@@ -8199,22 +7745,12 @@
         <f>IFERROR(VLOOKUP(C49,▼売上原票!$A:$P,5,0),0)</f>
         <v/>
       </c>
-      <c r="E49" s="12" t="n">
-        <v>180000</v>
-      </c>
-      <c r="F49" s="12" t="n">
-        <v>55000</v>
-      </c>
-      <c r="G49" s="12" t="n">
-        <v>180000</v>
-      </c>
+      <c r="E49" s="12" t="n"/>
+      <c r="F49" s="12" t="n"/>
+      <c r="G49" s="12" t="n"/>
       <c r="H49" s="12" t="n"/>
-      <c r="I49" s="12" t="n">
-        <v>15000</v>
-      </c>
-      <c r="J49" s="12" t="n">
-        <v>20000</v>
-      </c>
+      <c r="I49" s="12" t="n"/>
+      <c r="J49" s="12" t="n"/>
       <c r="K49" s="13">
         <f>E49+F49+G49+H49+I49+J49</f>
         <v/>
@@ -8265,22 +7801,12 @@
         <f>IFERROR(VLOOKUP(C50,▼売上原票!$A:$P,5,0),0)</f>
         <v/>
       </c>
-      <c r="E50" s="12" t="n">
-        <v>180000</v>
-      </c>
-      <c r="F50" s="12" t="n">
-        <v>55000</v>
-      </c>
-      <c r="G50" s="12" t="n">
-        <v>180000</v>
-      </c>
+      <c r="E50" s="12" t="n"/>
+      <c r="F50" s="12" t="n"/>
+      <c r="G50" s="12" t="n"/>
       <c r="H50" s="12" t="n"/>
-      <c r="I50" s="12" t="n">
-        <v>15000</v>
-      </c>
-      <c r="J50" s="12" t="n">
-        <v>20000</v>
-      </c>
+      <c r="I50" s="12" t="n"/>
+      <c r="J50" s="12" t="n"/>
       <c r="K50" s="13">
         <f>E50+F50+G50+H50+I50+J50</f>
         <v/>
@@ -8331,22 +7857,12 @@
         <f>IFERROR(VLOOKUP(C51,▼売上原票!$A:$P,5,0),0)</f>
         <v/>
       </c>
-      <c r="E51" s="12" t="n">
-        <v>180000</v>
-      </c>
-      <c r="F51" s="12" t="n">
-        <v>55000</v>
-      </c>
-      <c r="G51" s="12" t="n">
-        <v>180000</v>
-      </c>
+      <c r="E51" s="12" t="n"/>
+      <c r="F51" s="12" t="n"/>
+      <c r="G51" s="12" t="n"/>
       <c r="H51" s="12" t="n"/>
-      <c r="I51" s="12" t="n">
-        <v>15000</v>
-      </c>
-      <c r="J51" s="12" t="n">
-        <v>20000</v>
-      </c>
+      <c r="I51" s="12" t="n"/>
+      <c r="J51" s="12" t="n"/>
       <c r="K51" s="13">
         <f>E51+F51+G51+H51+I51+J51</f>
         <v/>
@@ -8397,22 +7913,12 @@
         <f>IFERROR(VLOOKUP(C52,▼売上原票!$A:$P,5,0),0)</f>
         <v/>
       </c>
-      <c r="E52" s="12" t="n">
-        <v>180000</v>
-      </c>
-      <c r="F52" s="12" t="n">
-        <v>55000</v>
-      </c>
-      <c r="G52" s="12" t="n">
-        <v>180000</v>
-      </c>
+      <c r="E52" s="12" t="n"/>
+      <c r="F52" s="12" t="n"/>
+      <c r="G52" s="12" t="n"/>
       <c r="H52" s="12" t="n"/>
-      <c r="I52" s="12" t="n">
-        <v>15000</v>
-      </c>
-      <c r="J52" s="12" t="n">
-        <v>20000</v>
-      </c>
+      <c r="I52" s="12" t="n"/>
+      <c r="J52" s="12" t="n"/>
       <c r="K52" s="13">
         <f>E52+F52+G52+H52+I52+J52</f>
         <v/>
@@ -8463,22 +7969,12 @@
         <f>IFERROR(VLOOKUP(C53,▼売上原票!$A:$P,5,0),0)</f>
         <v/>
       </c>
-      <c r="E53" s="12" t="n">
-        <v>180000</v>
-      </c>
-      <c r="F53" s="12" t="n">
-        <v>55000</v>
-      </c>
-      <c r="G53" s="12" t="n">
-        <v>180000</v>
-      </c>
+      <c r="E53" s="12" t="n"/>
+      <c r="F53" s="12" t="n"/>
+      <c r="G53" s="12" t="n"/>
       <c r="H53" s="12" t="n"/>
-      <c r="I53" s="12" t="n">
-        <v>15000</v>
-      </c>
-      <c r="J53" s="12" t="n">
-        <v>20000</v>
-      </c>
+      <c r="I53" s="12" t="n"/>
+      <c r="J53" s="12" t="n"/>
       <c r="K53" s="13">
         <f>E53+F53+G53+H53+I53+J53</f>
         <v/>
@@ -8529,22 +8025,12 @@
         <f>IFERROR(VLOOKUP(C54,▼売上原票!$A:$P,5,0),0)</f>
         <v/>
       </c>
-      <c r="E54" s="12" t="n">
-        <v>180000</v>
-      </c>
-      <c r="F54" s="12" t="n">
-        <v>55000</v>
-      </c>
-      <c r="G54" s="12" t="n">
-        <v>180000</v>
-      </c>
+      <c r="E54" s="12" t="n"/>
+      <c r="F54" s="12" t="n"/>
+      <c r="G54" s="12" t="n"/>
       <c r="H54" s="12" t="n"/>
-      <c r="I54" s="12" t="n">
-        <v>15000</v>
-      </c>
-      <c r="J54" s="12" t="n">
-        <v>20000</v>
-      </c>
+      <c r="I54" s="12" t="n"/>
+      <c r="J54" s="12" t="n"/>
       <c r="K54" s="13">
         <f>E54+F54+G54+H54+I54+J54</f>
         <v/>
@@ -8595,22 +8081,12 @@
         <f>IFERROR(VLOOKUP(C55,▼売上原票!$A:$P,5,0),0)</f>
         <v/>
       </c>
-      <c r="E55" s="12" t="n">
-        <v>180000</v>
-      </c>
-      <c r="F55" s="12" t="n">
-        <v>55000</v>
-      </c>
-      <c r="G55" s="12" t="n">
-        <v>180000</v>
-      </c>
+      <c r="E55" s="12" t="n"/>
+      <c r="F55" s="12" t="n"/>
+      <c r="G55" s="12" t="n"/>
       <c r="H55" s="12" t="n"/>
-      <c r="I55" s="12" t="n">
-        <v>15000</v>
-      </c>
-      <c r="J55" s="12" t="n">
-        <v>20000</v>
-      </c>
+      <c r="I55" s="12" t="n"/>
+      <c r="J55" s="12" t="n"/>
       <c r="K55" s="13">
         <f>E55+F55+G55+H55+I55+J55</f>
         <v/>
@@ -8661,22 +8137,12 @@
         <f>IFERROR(VLOOKUP(C56,▼売上原票!$A:$P,5,0),0)</f>
         <v/>
       </c>
-      <c r="E56" s="12" t="n">
-        <v>180000</v>
-      </c>
-      <c r="F56" s="12" t="n">
-        <v>55000</v>
-      </c>
-      <c r="G56" s="12" t="n">
-        <v>180000</v>
-      </c>
+      <c r="E56" s="12" t="n"/>
+      <c r="F56" s="12" t="n"/>
+      <c r="G56" s="12" t="n"/>
       <c r="H56" s="12" t="n"/>
-      <c r="I56" s="12" t="n">
-        <v>15000</v>
-      </c>
-      <c r="J56" s="12" t="n">
-        <v>20000</v>
-      </c>
+      <c r="I56" s="12" t="n"/>
+      <c r="J56" s="12" t="n"/>
       <c r="K56" s="13">
         <f>E56+F56+G56+H56+I56+J56</f>
         <v/>
@@ -8727,22 +8193,12 @@
         <f>IFERROR(VLOOKUP(C57,▼売上原票!$A:$P,5,0),0)</f>
         <v/>
       </c>
-      <c r="E57" s="12" t="n">
-        <v>180000</v>
-      </c>
-      <c r="F57" s="12" t="n">
-        <v>55000</v>
-      </c>
-      <c r="G57" s="12" t="n">
-        <v>180000</v>
-      </c>
+      <c r="E57" s="12" t="n"/>
+      <c r="F57" s="12" t="n"/>
+      <c r="G57" s="12" t="n"/>
       <c r="H57" s="12" t="n"/>
-      <c r="I57" s="12" t="n">
-        <v>15000</v>
-      </c>
-      <c r="J57" s="12" t="n">
-        <v>20000</v>
-      </c>
+      <c r="I57" s="12" t="n"/>
+      <c r="J57" s="12" t="n"/>
       <c r="K57" s="13">
         <f>E57+F57+G57+H57+I57+J57</f>
         <v/>
@@ -9784,22 +9240,12 @@
         <f>IFERROR(VLOOKUP(C77,▼売上原票!$A:$P,7,0),0)</f>
         <v/>
       </c>
-      <c r="E77" s="12" t="n">
-        <v>85000</v>
-      </c>
-      <c r="F77" s="12" t="n">
-        <v>25000</v>
-      </c>
-      <c r="G77" s="12" t="n">
-        <v>15000</v>
-      </c>
+      <c r="E77" s="12" t="n"/>
+      <c r="F77" s="12" t="n"/>
+      <c r="G77" s="12" t="n"/>
       <c r="H77" s="12" t="n"/>
-      <c r="I77" s="12" t="n">
-        <v>20000</v>
-      </c>
-      <c r="J77" s="12" t="n">
-        <v>10000</v>
-      </c>
+      <c r="I77" s="12" t="n"/>
+      <c r="J77" s="12" t="n"/>
       <c r="K77" s="13">
         <f>E77+F77+G77+H77+I77+J77</f>
         <v/>
@@ -9851,22 +9297,12 @@
         <f>IFERROR(VLOOKUP(C78,▼売上原票!$A:$P,7,0),0)</f>
         <v/>
       </c>
-      <c r="E78" s="12" t="n">
-        <v>85000</v>
-      </c>
-      <c r="F78" s="12" t="n">
-        <v>25000</v>
-      </c>
-      <c r="G78" s="12" t="n">
-        <v>15000</v>
-      </c>
+      <c r="E78" s="12" t="n"/>
+      <c r="F78" s="12" t="n"/>
+      <c r="G78" s="12" t="n"/>
       <c r="H78" s="12" t="n"/>
-      <c r="I78" s="12" t="n">
-        <v>20000</v>
-      </c>
-      <c r="J78" s="12" t="n">
-        <v>10000</v>
-      </c>
+      <c r="I78" s="12" t="n"/>
+      <c r="J78" s="12" t="n"/>
       <c r="K78" s="13">
         <f>E78+F78+G78+H78+I78+J78</f>
         <v/>
@@ -9917,22 +9353,12 @@
         <f>IFERROR(VLOOKUP(C79,▼売上原票!$A:$P,7,0),0)</f>
         <v/>
       </c>
-      <c r="E79" s="12" t="n">
-        <v>85000</v>
-      </c>
-      <c r="F79" s="12" t="n">
-        <v>25000</v>
-      </c>
-      <c r="G79" s="12" t="n">
-        <v>15000</v>
-      </c>
+      <c r="E79" s="12" t="n"/>
+      <c r="F79" s="12" t="n"/>
+      <c r="G79" s="12" t="n"/>
       <c r="H79" s="12" t="n"/>
-      <c r="I79" s="12" t="n">
-        <v>20000</v>
-      </c>
-      <c r="J79" s="12" t="n">
-        <v>10000</v>
-      </c>
+      <c r="I79" s="12" t="n"/>
+      <c r="J79" s="12" t="n"/>
       <c r="K79" s="13">
         <f>E79+F79+G79+H79+I79+J79</f>
         <v/>
@@ -9983,22 +9409,12 @@
         <f>IFERROR(VLOOKUP(C80,▼売上原票!$A:$P,7,0),0)</f>
         <v/>
       </c>
-      <c r="E80" s="12" t="n">
-        <v>85000</v>
-      </c>
-      <c r="F80" s="12" t="n">
-        <v>25000</v>
-      </c>
-      <c r="G80" s="12" t="n">
-        <v>15000</v>
-      </c>
+      <c r="E80" s="12" t="n"/>
+      <c r="F80" s="12" t="n"/>
+      <c r="G80" s="12" t="n"/>
       <c r="H80" s="12" t="n"/>
-      <c r="I80" s="12" t="n">
-        <v>20000</v>
-      </c>
-      <c r="J80" s="12" t="n">
-        <v>10000</v>
-      </c>
+      <c r="I80" s="12" t="n"/>
+      <c r="J80" s="12" t="n"/>
       <c r="K80" s="13">
         <f>E80+F80+G80+H80+I80+J80</f>
         <v/>
@@ -10049,22 +9465,12 @@
         <f>IFERROR(VLOOKUP(C81,▼売上原票!$A:$P,7,0),0)</f>
         <v/>
       </c>
-      <c r="E81" s="12" t="n">
-        <v>85000</v>
-      </c>
-      <c r="F81" s="12" t="n">
-        <v>25000</v>
-      </c>
-      <c r="G81" s="12" t="n">
-        <v>15000</v>
-      </c>
+      <c r="E81" s="12" t="n"/>
+      <c r="F81" s="12" t="n"/>
+      <c r="G81" s="12" t="n"/>
       <c r="H81" s="12" t="n"/>
-      <c r="I81" s="12" t="n">
-        <v>20000</v>
-      </c>
-      <c r="J81" s="12" t="n">
-        <v>10000</v>
-      </c>
+      <c r="I81" s="12" t="n"/>
+      <c r="J81" s="12" t="n"/>
       <c r="K81" s="13">
         <f>E81+F81+G81+H81+I81+J81</f>
         <v/>
@@ -10115,22 +9521,12 @@
         <f>IFERROR(VLOOKUP(C82,▼売上原票!$A:$P,7,0),0)</f>
         <v/>
       </c>
-      <c r="E82" s="12" t="n">
-        <v>85000</v>
-      </c>
-      <c r="F82" s="12" t="n">
-        <v>25000</v>
-      </c>
-      <c r="G82" s="12" t="n">
-        <v>15000</v>
-      </c>
+      <c r="E82" s="12" t="n"/>
+      <c r="F82" s="12" t="n"/>
+      <c r="G82" s="12" t="n"/>
       <c r="H82" s="12" t="n"/>
-      <c r="I82" s="12" t="n">
-        <v>20000</v>
-      </c>
-      <c r="J82" s="12" t="n">
-        <v>10000</v>
-      </c>
+      <c r="I82" s="12" t="n"/>
+      <c r="J82" s="12" t="n"/>
       <c r="K82" s="13">
         <f>E82+F82+G82+H82+I82+J82</f>
         <v/>
@@ -10181,22 +9577,12 @@
         <f>IFERROR(VLOOKUP(C83,▼売上原票!$A:$P,7,0),0)</f>
         <v/>
       </c>
-      <c r="E83" s="12" t="n">
-        <v>85000</v>
-      </c>
-      <c r="F83" s="12" t="n">
-        <v>25000</v>
-      </c>
-      <c r="G83" s="12" t="n">
-        <v>15000</v>
-      </c>
+      <c r="E83" s="12" t="n"/>
+      <c r="F83" s="12" t="n"/>
+      <c r="G83" s="12" t="n"/>
       <c r="H83" s="12" t="n"/>
-      <c r="I83" s="12" t="n">
-        <v>20000</v>
-      </c>
-      <c r="J83" s="12" t="n">
-        <v>10000</v>
-      </c>
+      <c r="I83" s="12" t="n"/>
+      <c r="J83" s="12" t="n"/>
       <c r="K83" s="13">
         <f>E83+F83+G83+H83+I83+J83</f>
         <v/>
@@ -10247,22 +9633,12 @@
         <f>IFERROR(VLOOKUP(C84,▼売上原票!$A:$P,7,0),0)</f>
         <v/>
       </c>
-      <c r="E84" s="12" t="n">
-        <v>85000</v>
-      </c>
-      <c r="F84" s="12" t="n">
-        <v>25000</v>
-      </c>
-      <c r="G84" s="12" t="n">
-        <v>15000</v>
-      </c>
+      <c r="E84" s="12" t="n"/>
+      <c r="F84" s="12" t="n"/>
+      <c r="G84" s="12" t="n"/>
       <c r="H84" s="12" t="n"/>
-      <c r="I84" s="12" t="n">
-        <v>20000</v>
-      </c>
-      <c r="J84" s="12" t="n">
-        <v>10000</v>
-      </c>
+      <c r="I84" s="12" t="n"/>
+      <c r="J84" s="12" t="n"/>
       <c r="K84" s="13">
         <f>E84+F84+G84+H84+I84+J84</f>
         <v/>
@@ -10313,22 +9689,12 @@
         <f>IFERROR(VLOOKUP(C85,▼売上原票!$A:$P,7,0),0)</f>
         <v/>
       </c>
-      <c r="E85" s="12" t="n">
-        <v>85000</v>
-      </c>
-      <c r="F85" s="12" t="n">
-        <v>25000</v>
-      </c>
-      <c r="G85" s="12" t="n">
-        <v>15000</v>
-      </c>
+      <c r="E85" s="12" t="n"/>
+      <c r="F85" s="12" t="n"/>
+      <c r="G85" s="12" t="n"/>
       <c r="H85" s="12" t="n"/>
-      <c r="I85" s="12" t="n">
-        <v>20000</v>
-      </c>
-      <c r="J85" s="12" t="n">
-        <v>10000</v>
-      </c>
+      <c r="I85" s="12" t="n"/>
+      <c r="J85" s="12" t="n"/>
       <c r="K85" s="13">
         <f>E85+F85+G85+H85+I85+J85</f>
         <v/>
@@ -10379,22 +9745,12 @@
         <f>IFERROR(VLOOKUP(C86,▼売上原票!$A:$P,7,0),0)</f>
         <v/>
       </c>
-      <c r="E86" s="12" t="n">
-        <v>85000</v>
-      </c>
-      <c r="F86" s="12" t="n">
-        <v>25000</v>
-      </c>
-      <c r="G86" s="12" t="n">
-        <v>15000</v>
-      </c>
+      <c r="E86" s="12" t="n"/>
+      <c r="F86" s="12" t="n"/>
+      <c r="G86" s="12" t="n"/>
       <c r="H86" s="12" t="n"/>
-      <c r="I86" s="12" t="n">
-        <v>20000</v>
-      </c>
-      <c r="J86" s="12" t="n">
-        <v>10000</v>
-      </c>
+      <c r="I86" s="12" t="n"/>
+      <c r="J86" s="12" t="n"/>
       <c r="K86" s="13">
         <f>E86+F86+G86+H86+I86+J86</f>
         <v/>
@@ -10445,22 +9801,12 @@
         <f>IFERROR(VLOOKUP(C87,▼売上原票!$A:$P,7,0),0)</f>
         <v/>
       </c>
-      <c r="E87" s="12" t="n">
-        <v>85000</v>
-      </c>
-      <c r="F87" s="12" t="n">
-        <v>25000</v>
-      </c>
-      <c r="G87" s="12" t="n">
-        <v>15000</v>
-      </c>
+      <c r="E87" s="12" t="n"/>
+      <c r="F87" s="12" t="n"/>
+      <c r="G87" s="12" t="n"/>
       <c r="H87" s="12" t="n"/>
-      <c r="I87" s="12" t="n">
-        <v>20000</v>
-      </c>
-      <c r="J87" s="12" t="n">
-        <v>10000</v>
-      </c>
+      <c r="I87" s="12" t="n"/>
+      <c r="J87" s="12" t="n"/>
       <c r="K87" s="13">
         <f>E87+F87+G87+H87+I87+J87</f>
         <v/>
@@ -10511,22 +9857,12 @@
         <f>IFERROR(VLOOKUP(C88,▼売上原票!$A:$P,7,0),0)</f>
         <v/>
       </c>
-      <c r="E88" s="12" t="n">
-        <v>85000</v>
-      </c>
-      <c r="F88" s="12" t="n">
-        <v>25000</v>
-      </c>
-      <c r="G88" s="12" t="n">
-        <v>15000</v>
-      </c>
+      <c r="E88" s="12" t="n"/>
+      <c r="F88" s="12" t="n"/>
+      <c r="G88" s="12" t="n"/>
       <c r="H88" s="12" t="n"/>
-      <c r="I88" s="12" t="n">
-        <v>20000</v>
-      </c>
-      <c r="J88" s="12" t="n">
-        <v>10000</v>
-      </c>
+      <c r="I88" s="12" t="n"/>
+      <c r="J88" s="12" t="n"/>
       <c r="K88" s="13">
         <f>E88+F88+G88+H88+I88+J88</f>
         <v/>
@@ -10577,22 +9913,12 @@
         <f>IFERROR(VLOOKUP(C89,▼売上原票!$A:$P,7,0),0)</f>
         <v/>
       </c>
-      <c r="E89" s="12" t="n">
-        <v>85000</v>
-      </c>
-      <c r="F89" s="12" t="n">
-        <v>25000</v>
-      </c>
-      <c r="G89" s="12" t="n">
-        <v>15000</v>
-      </c>
+      <c r="E89" s="12" t="n"/>
+      <c r="F89" s="12" t="n"/>
+      <c r="G89" s="12" t="n"/>
       <c r="H89" s="12" t="n"/>
-      <c r="I89" s="12" t="n">
-        <v>20000</v>
-      </c>
-      <c r="J89" s="12" t="n">
-        <v>10000</v>
-      </c>
+      <c r="I89" s="12" t="n"/>
+      <c r="J89" s="12" t="n"/>
       <c r="K89" s="13">
         <f>E89+F89+G89+H89+I89+J89</f>
         <v/>
@@ -10643,22 +9969,12 @@
         <f>IFERROR(VLOOKUP(C90,▼売上原票!$A:$P,7,0),0)</f>
         <v/>
       </c>
-      <c r="E90" s="12" t="n">
-        <v>85000</v>
-      </c>
-      <c r="F90" s="12" t="n">
-        <v>25000</v>
-      </c>
-      <c r="G90" s="12" t="n">
-        <v>15000</v>
-      </c>
+      <c r="E90" s="12" t="n"/>
+      <c r="F90" s="12" t="n"/>
+      <c r="G90" s="12" t="n"/>
       <c r="H90" s="12" t="n"/>
-      <c r="I90" s="12" t="n">
-        <v>20000</v>
-      </c>
-      <c r="J90" s="12" t="n">
-        <v>10000</v>
-      </c>
+      <c r="I90" s="12" t="n"/>
+      <c r="J90" s="12" t="n"/>
       <c r="K90" s="13">
         <f>E90+F90+G90+H90+I90+J90</f>
         <v/>
@@ -10709,22 +10025,12 @@
         <f>IFERROR(VLOOKUP(C91,▼売上原票!$A:$P,7,0),0)</f>
         <v/>
       </c>
-      <c r="E91" s="12" t="n">
-        <v>85000</v>
-      </c>
-      <c r="F91" s="12" t="n">
-        <v>25000</v>
-      </c>
-      <c r="G91" s="12" t="n">
-        <v>15000</v>
-      </c>
+      <c r="E91" s="12" t="n"/>
+      <c r="F91" s="12" t="n"/>
+      <c r="G91" s="12" t="n"/>
       <c r="H91" s="12" t="n"/>
-      <c r="I91" s="12" t="n">
-        <v>20000</v>
-      </c>
-      <c r="J91" s="12" t="n">
-        <v>10000</v>
-      </c>
+      <c r="I91" s="12" t="n"/>
+      <c r="J91" s="12" t="n"/>
       <c r="K91" s="13">
         <f>E91+F91+G91+H91+I91+J91</f>
         <v/>
@@ -10775,22 +10081,12 @@
         <f>IFERROR(VLOOKUP(C92,▼売上原票!$A:$P,7,0),0)</f>
         <v/>
       </c>
-      <c r="E92" s="12" t="n">
-        <v>85000</v>
-      </c>
-      <c r="F92" s="12" t="n">
-        <v>25000</v>
-      </c>
-      <c r="G92" s="12" t="n">
-        <v>15000</v>
-      </c>
+      <c r="E92" s="12" t="n"/>
+      <c r="F92" s="12" t="n"/>
+      <c r="G92" s="12" t="n"/>
       <c r="H92" s="12" t="n"/>
-      <c r="I92" s="12" t="n">
-        <v>20000</v>
-      </c>
-      <c r="J92" s="12" t="n">
-        <v>10000</v>
-      </c>
+      <c r="I92" s="12" t="n"/>
+      <c r="J92" s="12" t="n"/>
       <c r="K92" s="13">
         <f>E92+F92+G92+H92+I92+J92</f>
         <v/>
@@ -10841,22 +10137,12 @@
         <f>IFERROR(VLOOKUP(C93,▼売上原票!$A:$P,7,0),0)</f>
         <v/>
       </c>
-      <c r="E93" s="12" t="n">
-        <v>85000</v>
-      </c>
-      <c r="F93" s="12" t="n">
-        <v>25000</v>
-      </c>
-      <c r="G93" s="12" t="n">
-        <v>15000</v>
-      </c>
+      <c r="E93" s="12" t="n"/>
+      <c r="F93" s="12" t="n"/>
+      <c r="G93" s="12" t="n"/>
       <c r="H93" s="12" t="n"/>
-      <c r="I93" s="12" t="n">
-        <v>20000</v>
-      </c>
-      <c r="J93" s="12" t="n">
-        <v>10000</v>
-      </c>
+      <c r="I93" s="12" t="n"/>
+      <c r="J93" s="12" t="n"/>
       <c r="K93" s="13">
         <f>E93+F93+G93+H93+I93+J93</f>
         <v/>
@@ -10926,22 +10212,12 @@
         <f>IFERROR(VLOOKUP(C95,▼売上原票!$A:$P,8,0),0)</f>
         <v/>
       </c>
-      <c r="E95" s="12" t="n">
-        <v>120000</v>
-      </c>
-      <c r="F95" s="12" t="n">
-        <v>38000</v>
-      </c>
-      <c r="G95" s="12" t="n">
-        <v>18000</v>
-      </c>
+      <c r="E95" s="12" t="n"/>
+      <c r="F95" s="12" t="n"/>
+      <c r="G95" s="12" t="n"/>
       <c r="H95" s="12" t="n"/>
-      <c r="I95" s="12" t="n">
-        <v>25000</v>
-      </c>
-      <c r="J95" s="12" t="n">
-        <v>12000</v>
-      </c>
+      <c r="I95" s="12" t="n"/>
+      <c r="J95" s="12" t="n"/>
       <c r="K95" s="13">
         <f>E95+F95+G95+H95+I95+J95</f>
         <v/>
@@ -10993,22 +10269,12 @@
         <f>IFERROR(VLOOKUP(C96,▼売上原票!$A:$P,8,0),0)</f>
         <v/>
       </c>
-      <c r="E96" s="12" t="n">
-        <v>120000</v>
-      </c>
-      <c r="F96" s="12" t="n">
-        <v>38000</v>
-      </c>
-      <c r="G96" s="12" t="n">
-        <v>18000</v>
-      </c>
+      <c r="E96" s="12" t="n"/>
+      <c r="F96" s="12" t="n"/>
+      <c r="G96" s="12" t="n"/>
       <c r="H96" s="12" t="n"/>
-      <c r="I96" s="12" t="n">
-        <v>25000</v>
-      </c>
-      <c r="J96" s="12" t="n">
-        <v>12000</v>
-      </c>
+      <c r="I96" s="12" t="n"/>
+      <c r="J96" s="12" t="n"/>
       <c r="K96" s="13">
         <f>E96+F96+G96+H96+I96+J96</f>
         <v/>
@@ -11059,22 +10325,12 @@
         <f>IFERROR(VLOOKUP(C97,▼売上原票!$A:$P,8,0),0)</f>
         <v/>
       </c>
-      <c r="E97" s="12" t="n">
-        <v>120000</v>
-      </c>
-      <c r="F97" s="12" t="n">
-        <v>38000</v>
-      </c>
-      <c r="G97" s="12" t="n">
-        <v>18000</v>
-      </c>
+      <c r="E97" s="12" t="n"/>
+      <c r="F97" s="12" t="n"/>
+      <c r="G97" s="12" t="n"/>
       <c r="H97" s="12" t="n"/>
-      <c r="I97" s="12" t="n">
-        <v>25000</v>
-      </c>
-      <c r="J97" s="12" t="n">
-        <v>12000</v>
-      </c>
+      <c r="I97" s="12" t="n"/>
+      <c r="J97" s="12" t="n"/>
       <c r="K97" s="13">
         <f>E97+F97+G97+H97+I97+J97</f>
         <v/>
@@ -11125,22 +10381,12 @@
         <f>IFERROR(VLOOKUP(C98,▼売上原票!$A:$P,8,0),0)</f>
         <v/>
       </c>
-      <c r="E98" s="12" t="n">
-        <v>120000</v>
-      </c>
-      <c r="F98" s="12" t="n">
-        <v>38000</v>
-      </c>
-      <c r="G98" s="12" t="n">
-        <v>18000</v>
-      </c>
+      <c r="E98" s="12" t="n"/>
+      <c r="F98" s="12" t="n"/>
+      <c r="G98" s="12" t="n"/>
       <c r="H98" s="12" t="n"/>
-      <c r="I98" s="12" t="n">
-        <v>25000</v>
-      </c>
-      <c r="J98" s="12" t="n">
-        <v>12000</v>
-      </c>
+      <c r="I98" s="12" t="n"/>
+      <c r="J98" s="12" t="n"/>
       <c r="K98" s="13">
         <f>E98+F98+G98+H98+I98+J98</f>
         <v/>
@@ -11191,22 +10437,12 @@
         <f>IFERROR(VLOOKUP(C99,▼売上原票!$A:$P,8,0),0)</f>
         <v/>
       </c>
-      <c r="E99" s="12" t="n">
-        <v>120000</v>
-      </c>
-      <c r="F99" s="12" t="n">
-        <v>38000</v>
-      </c>
-      <c r="G99" s="12" t="n">
-        <v>18000</v>
-      </c>
+      <c r="E99" s="12" t="n"/>
+      <c r="F99" s="12" t="n"/>
+      <c r="G99" s="12" t="n"/>
       <c r="H99" s="12" t="n"/>
-      <c r="I99" s="12" t="n">
-        <v>25000</v>
-      </c>
-      <c r="J99" s="12" t="n">
-        <v>12000</v>
-      </c>
+      <c r="I99" s="12" t="n"/>
+      <c r="J99" s="12" t="n"/>
       <c r="K99" s="13">
         <f>E99+F99+G99+H99+I99+J99</f>
         <v/>
@@ -11257,22 +10493,12 @@
         <f>IFERROR(VLOOKUP(C100,▼売上原票!$A:$P,8,0),0)</f>
         <v/>
       </c>
-      <c r="E100" s="12" t="n">
-        <v>120000</v>
-      </c>
-      <c r="F100" s="12" t="n">
-        <v>38000</v>
-      </c>
-      <c r="G100" s="12" t="n">
-        <v>18000</v>
-      </c>
+      <c r="E100" s="12" t="n"/>
+      <c r="F100" s="12" t="n"/>
+      <c r="G100" s="12" t="n"/>
       <c r="H100" s="12" t="n"/>
-      <c r="I100" s="12" t="n">
-        <v>25000</v>
-      </c>
-      <c r="J100" s="12" t="n">
-        <v>12000</v>
-      </c>
+      <c r="I100" s="12" t="n"/>
+      <c r="J100" s="12" t="n"/>
       <c r="K100" s="13">
         <f>E100+F100+G100+H100+I100+J100</f>
         <v/>
@@ -11323,22 +10549,12 @@
         <f>IFERROR(VLOOKUP(C101,▼売上原票!$A:$P,8,0),0)</f>
         <v/>
       </c>
-      <c r="E101" s="12" t="n">
-        <v>120000</v>
-      </c>
-      <c r="F101" s="12" t="n">
-        <v>38000</v>
-      </c>
-      <c r="G101" s="12" t="n">
-        <v>18000</v>
-      </c>
+      <c r="E101" s="12" t="n"/>
+      <c r="F101" s="12" t="n"/>
+      <c r="G101" s="12" t="n"/>
       <c r="H101" s="12" t="n"/>
-      <c r="I101" s="12" t="n">
-        <v>25000</v>
-      </c>
-      <c r="J101" s="12" t="n">
-        <v>12000</v>
-      </c>
+      <c r="I101" s="12" t="n"/>
+      <c r="J101" s="12" t="n"/>
       <c r="K101" s="13">
         <f>E101+F101+G101+H101+I101+J101</f>
         <v/>
@@ -11389,22 +10605,12 @@
         <f>IFERROR(VLOOKUP(C102,▼売上原票!$A:$P,8,0),0)</f>
         <v/>
       </c>
-      <c r="E102" s="12" t="n">
-        <v>120000</v>
-      </c>
-      <c r="F102" s="12" t="n">
-        <v>38000</v>
-      </c>
-      <c r="G102" s="12" t="n">
-        <v>18000</v>
-      </c>
+      <c r="E102" s="12" t="n"/>
+      <c r="F102" s="12" t="n"/>
+      <c r="G102" s="12" t="n"/>
       <c r="H102" s="12" t="n"/>
-      <c r="I102" s="12" t="n">
-        <v>25000</v>
-      </c>
-      <c r="J102" s="12" t="n">
-        <v>12000</v>
-      </c>
+      <c r="I102" s="12" t="n"/>
+      <c r="J102" s="12" t="n"/>
       <c r="K102" s="13">
         <f>E102+F102+G102+H102+I102+J102</f>
         <v/>
@@ -11455,22 +10661,12 @@
         <f>IFERROR(VLOOKUP(C103,▼売上原票!$A:$P,8,0),0)</f>
         <v/>
       </c>
-      <c r="E103" s="12" t="n">
-        <v>120000</v>
-      </c>
-      <c r="F103" s="12" t="n">
-        <v>38000</v>
-      </c>
-      <c r="G103" s="12" t="n">
-        <v>18000</v>
-      </c>
+      <c r="E103" s="12" t="n"/>
+      <c r="F103" s="12" t="n"/>
+      <c r="G103" s="12" t="n"/>
       <c r="H103" s="12" t="n"/>
-      <c r="I103" s="12" t="n">
-        <v>25000</v>
-      </c>
-      <c r="J103" s="12" t="n">
-        <v>12000</v>
-      </c>
+      <c r="I103" s="12" t="n"/>
+      <c r="J103" s="12" t="n"/>
       <c r="K103" s="13">
         <f>E103+F103+G103+H103+I103+J103</f>
         <v/>
@@ -11521,22 +10717,12 @@
         <f>IFERROR(VLOOKUP(C104,▼売上原票!$A:$P,8,0),0)</f>
         <v/>
       </c>
-      <c r="E104" s="12" t="n">
-        <v>120000</v>
-      </c>
-      <c r="F104" s="12" t="n">
-        <v>38000</v>
-      </c>
-      <c r="G104" s="12" t="n">
-        <v>18000</v>
-      </c>
+      <c r="E104" s="12" t="n"/>
+      <c r="F104" s="12" t="n"/>
+      <c r="G104" s="12" t="n"/>
       <c r="H104" s="12" t="n"/>
-      <c r="I104" s="12" t="n">
-        <v>25000</v>
-      </c>
-      <c r="J104" s="12" t="n">
-        <v>12000</v>
-      </c>
+      <c r="I104" s="12" t="n"/>
+      <c r="J104" s="12" t="n"/>
       <c r="K104" s="13">
         <f>E104+F104+G104+H104+I104+J104</f>
         <v/>
@@ -11587,22 +10773,12 @@
         <f>IFERROR(VLOOKUP(C105,▼売上原票!$A:$P,8,0),0)</f>
         <v/>
       </c>
-      <c r="E105" s="12" t="n">
-        <v>120000</v>
-      </c>
-      <c r="F105" s="12" t="n">
-        <v>38000</v>
-      </c>
-      <c r="G105" s="12" t="n">
-        <v>18000</v>
-      </c>
+      <c r="E105" s="12" t="n"/>
+      <c r="F105" s="12" t="n"/>
+      <c r="G105" s="12" t="n"/>
       <c r="H105" s="12" t="n"/>
-      <c r="I105" s="12" t="n">
-        <v>25000</v>
-      </c>
-      <c r="J105" s="12" t="n">
-        <v>12000</v>
-      </c>
+      <c r="I105" s="12" t="n"/>
+      <c r="J105" s="12" t="n"/>
       <c r="K105" s="13">
         <f>E105+F105+G105+H105+I105+J105</f>
         <v/>
@@ -11653,22 +10829,12 @@
         <f>IFERROR(VLOOKUP(C106,▼売上原票!$A:$P,8,0),0)</f>
         <v/>
       </c>
-      <c r="E106" s="12" t="n">
-        <v>120000</v>
-      </c>
-      <c r="F106" s="12" t="n">
-        <v>38000</v>
-      </c>
-      <c r="G106" s="12" t="n">
-        <v>18000</v>
-      </c>
+      <c r="E106" s="12" t="n"/>
+      <c r="F106" s="12" t="n"/>
+      <c r="G106" s="12" t="n"/>
       <c r="H106" s="12" t="n"/>
-      <c r="I106" s="12" t="n">
-        <v>25000</v>
-      </c>
-      <c r="J106" s="12" t="n">
-        <v>12000</v>
-      </c>
+      <c r="I106" s="12" t="n"/>
+      <c r="J106" s="12" t="n"/>
       <c r="K106" s="13">
         <f>E106+F106+G106+H106+I106+J106</f>
         <v/>
@@ -11719,22 +10885,12 @@
         <f>IFERROR(VLOOKUP(C107,▼売上原票!$A:$P,8,0),0)</f>
         <v/>
       </c>
-      <c r="E107" s="12" t="n">
-        <v>120000</v>
-      </c>
-      <c r="F107" s="12" t="n">
-        <v>38000</v>
-      </c>
-      <c r="G107" s="12" t="n">
-        <v>18000</v>
-      </c>
+      <c r="E107" s="12" t="n"/>
+      <c r="F107" s="12" t="n"/>
+      <c r="G107" s="12" t="n"/>
       <c r="H107" s="12" t="n"/>
-      <c r="I107" s="12" t="n">
-        <v>25000</v>
-      </c>
-      <c r="J107" s="12" t="n">
-        <v>12000</v>
-      </c>
+      <c r="I107" s="12" t="n"/>
+      <c r="J107" s="12" t="n"/>
       <c r="K107" s="13">
         <f>E107+F107+G107+H107+I107+J107</f>
         <v/>
@@ -11785,22 +10941,12 @@
         <f>IFERROR(VLOOKUP(C108,▼売上原票!$A:$P,8,0),0)</f>
         <v/>
       </c>
-      <c r="E108" s="12" t="n">
-        <v>120000</v>
-      </c>
-      <c r="F108" s="12" t="n">
-        <v>38000</v>
-      </c>
-      <c r="G108" s="12" t="n">
-        <v>18000</v>
-      </c>
+      <c r="E108" s="12" t="n"/>
+      <c r="F108" s="12" t="n"/>
+      <c r="G108" s="12" t="n"/>
       <c r="H108" s="12" t="n"/>
-      <c r="I108" s="12" t="n">
-        <v>25000</v>
-      </c>
-      <c r="J108" s="12" t="n">
-        <v>12000</v>
-      </c>
+      <c r="I108" s="12" t="n"/>
+      <c r="J108" s="12" t="n"/>
       <c r="K108" s="13">
         <f>E108+F108+G108+H108+I108+J108</f>
         <v/>
@@ -11851,22 +10997,12 @@
         <f>IFERROR(VLOOKUP(C109,▼売上原票!$A:$P,8,0),0)</f>
         <v/>
       </c>
-      <c r="E109" s="12" t="n">
-        <v>120000</v>
-      </c>
-      <c r="F109" s="12" t="n">
-        <v>38000</v>
-      </c>
-      <c r="G109" s="12" t="n">
-        <v>18000</v>
-      </c>
+      <c r="E109" s="12" t="n"/>
+      <c r="F109" s="12" t="n"/>
+      <c r="G109" s="12" t="n"/>
       <c r="H109" s="12" t="n"/>
-      <c r="I109" s="12" t="n">
-        <v>25000</v>
-      </c>
-      <c r="J109" s="12" t="n">
-        <v>12000</v>
-      </c>
+      <c r="I109" s="12" t="n"/>
+      <c r="J109" s="12" t="n"/>
       <c r="K109" s="13">
         <f>E109+F109+G109+H109+I109+J109</f>
         <v/>
@@ -11917,22 +11053,12 @@
         <f>IFERROR(VLOOKUP(C110,▼売上原票!$A:$P,8,0),0)</f>
         <v/>
       </c>
-      <c r="E110" s="12" t="n">
-        <v>120000</v>
-      </c>
-      <c r="F110" s="12" t="n">
-        <v>38000</v>
-      </c>
-      <c r="G110" s="12" t="n">
-        <v>18000</v>
-      </c>
+      <c r="E110" s="12" t="n"/>
+      <c r="F110" s="12" t="n"/>
+      <c r="G110" s="12" t="n"/>
       <c r="H110" s="12" t="n"/>
-      <c r="I110" s="12" t="n">
-        <v>25000</v>
-      </c>
-      <c r="J110" s="12" t="n">
-        <v>12000</v>
-      </c>
+      <c r="I110" s="12" t="n"/>
+      <c r="J110" s="12" t="n"/>
       <c r="K110" s="13">
         <f>E110+F110+G110+H110+I110+J110</f>
         <v/>
@@ -11983,22 +11109,12 @@
         <f>IFERROR(VLOOKUP(C111,▼売上原票!$A:$P,8,0),0)</f>
         <v/>
       </c>
-      <c r="E111" s="12" t="n">
-        <v>120000</v>
-      </c>
-      <c r="F111" s="12" t="n">
-        <v>38000</v>
-      </c>
-      <c r="G111" s="12" t="n">
-        <v>18000</v>
-      </c>
+      <c r="E111" s="12" t="n"/>
+      <c r="F111" s="12" t="n"/>
+      <c r="G111" s="12" t="n"/>
       <c r="H111" s="12" t="n"/>
-      <c r="I111" s="12" t="n">
-        <v>25000</v>
-      </c>
-      <c r="J111" s="12" t="n">
-        <v>12000</v>
-      </c>
+      <c r="I111" s="12" t="n"/>
+      <c r="J111" s="12" t="n"/>
       <c r="K111" s="13">
         <f>E111+F111+G111+H111+I111+J111</f>
         <v/>
@@ -12068,22 +11184,12 @@
         <f>IFERROR(VLOOKUP(C113,▼売上原票!$A:$P,9,0),0)</f>
         <v/>
       </c>
-      <c r="E113" s="12" t="n">
-        <v>20000</v>
-      </c>
-      <c r="F113" s="12" t="n">
-        <v>6000</v>
-      </c>
-      <c r="G113" s="12" t="n">
-        <v>3000</v>
-      </c>
+      <c r="E113" s="12" t="n"/>
+      <c r="F113" s="12" t="n"/>
+      <c r="G113" s="12" t="n"/>
       <c r="H113" s="12" t="n"/>
-      <c r="I113" s="12" t="n">
-        <v>5000</v>
-      </c>
-      <c r="J113" s="12" t="n">
-        <v>3000</v>
-      </c>
+      <c r="I113" s="12" t="n"/>
+      <c r="J113" s="12" t="n"/>
       <c r="K113" s="13">
         <f>E113+F113+G113+H113+I113+J113</f>
         <v/>
@@ -12135,22 +11241,12 @@
         <f>IFERROR(VLOOKUP(C114,▼売上原票!$A:$P,9,0),0)</f>
         <v/>
       </c>
-      <c r="E114" s="12" t="n">
-        <v>20000</v>
-      </c>
-      <c r="F114" s="12" t="n">
-        <v>6000</v>
-      </c>
-      <c r="G114" s="12" t="n">
-        <v>3000</v>
-      </c>
+      <c r="E114" s="12" t="n"/>
+      <c r="F114" s="12" t="n"/>
+      <c r="G114" s="12" t="n"/>
       <c r="H114" s="12" t="n"/>
-      <c r="I114" s="12" t="n">
-        <v>5000</v>
-      </c>
-      <c r="J114" s="12" t="n">
-        <v>3000</v>
-      </c>
+      <c r="I114" s="12" t="n"/>
+      <c r="J114" s="12" t="n"/>
       <c r="K114" s="13">
         <f>E114+F114+G114+H114+I114+J114</f>
         <v/>
@@ -12201,22 +11297,12 @@
         <f>IFERROR(VLOOKUP(C115,▼売上原票!$A:$P,9,0),0)</f>
         <v/>
       </c>
-      <c r="E115" s="12" t="n">
-        <v>20000</v>
-      </c>
-      <c r="F115" s="12" t="n">
-        <v>6000</v>
-      </c>
-      <c r="G115" s="12" t="n">
-        <v>3000</v>
-      </c>
+      <c r="E115" s="12" t="n"/>
+      <c r="F115" s="12" t="n"/>
+      <c r="G115" s="12" t="n"/>
       <c r="H115" s="12" t="n"/>
-      <c r="I115" s="12" t="n">
-        <v>5000</v>
-      </c>
-      <c r="J115" s="12" t="n">
-        <v>3000</v>
-      </c>
+      <c r="I115" s="12" t="n"/>
+      <c r="J115" s="12" t="n"/>
       <c r="K115" s="13">
         <f>E115+F115+G115+H115+I115+J115</f>
         <v/>
@@ -12267,22 +11353,12 @@
         <f>IFERROR(VLOOKUP(C116,▼売上原票!$A:$P,9,0),0)</f>
         <v/>
       </c>
-      <c r="E116" s="12" t="n">
-        <v>20000</v>
-      </c>
-      <c r="F116" s="12" t="n">
-        <v>6000</v>
-      </c>
-      <c r="G116" s="12" t="n">
-        <v>3000</v>
-      </c>
+      <c r="E116" s="12" t="n"/>
+      <c r="F116" s="12" t="n"/>
+      <c r="G116" s="12" t="n"/>
       <c r="H116" s="12" t="n"/>
-      <c r="I116" s="12" t="n">
-        <v>5000</v>
-      </c>
-      <c r="J116" s="12" t="n">
-        <v>3000</v>
-      </c>
+      <c r="I116" s="12" t="n"/>
+      <c r="J116" s="12" t="n"/>
       <c r="K116" s="13">
         <f>E116+F116+G116+H116+I116+J116</f>
         <v/>
@@ -12333,22 +11409,12 @@
         <f>IFERROR(VLOOKUP(C117,▼売上原票!$A:$P,9,0),0)</f>
         <v/>
       </c>
-      <c r="E117" s="12" t="n">
-        <v>20000</v>
-      </c>
-      <c r="F117" s="12" t="n">
-        <v>6000</v>
-      </c>
-      <c r="G117" s="12" t="n">
-        <v>3000</v>
-      </c>
+      <c r="E117" s="12" t="n"/>
+      <c r="F117" s="12" t="n"/>
+      <c r="G117" s="12" t="n"/>
       <c r="H117" s="12" t="n"/>
-      <c r="I117" s="12" t="n">
-        <v>5000</v>
-      </c>
-      <c r="J117" s="12" t="n">
-        <v>3000</v>
-      </c>
+      <c r="I117" s="12" t="n"/>
+      <c r="J117" s="12" t="n"/>
       <c r="K117" s="13">
         <f>E117+F117+G117+H117+I117+J117</f>
         <v/>
@@ -12399,22 +11465,12 @@
         <f>IFERROR(VLOOKUP(C118,▼売上原票!$A:$P,9,0),0)</f>
         <v/>
       </c>
-      <c r="E118" s="12" t="n">
-        <v>20000</v>
-      </c>
-      <c r="F118" s="12" t="n">
-        <v>6000</v>
-      </c>
-      <c r="G118" s="12" t="n">
-        <v>3000</v>
-      </c>
+      <c r="E118" s="12" t="n"/>
+      <c r="F118" s="12" t="n"/>
+      <c r="G118" s="12" t="n"/>
       <c r="H118" s="12" t="n"/>
-      <c r="I118" s="12" t="n">
-        <v>5000</v>
-      </c>
-      <c r="J118" s="12" t="n">
-        <v>3000</v>
-      </c>
+      <c r="I118" s="12" t="n"/>
+      <c r="J118" s="12" t="n"/>
       <c r="K118" s="13">
         <f>E118+F118+G118+H118+I118+J118</f>
         <v/>
@@ -12465,22 +11521,12 @@
         <f>IFERROR(VLOOKUP(C119,▼売上原票!$A:$P,9,0),0)</f>
         <v/>
       </c>
-      <c r="E119" s="12" t="n">
-        <v>20000</v>
-      </c>
-      <c r="F119" s="12" t="n">
-        <v>6000</v>
-      </c>
-      <c r="G119" s="12" t="n">
-        <v>3000</v>
-      </c>
+      <c r="E119" s="12" t="n"/>
+      <c r="F119" s="12" t="n"/>
+      <c r="G119" s="12" t="n"/>
       <c r="H119" s="12" t="n"/>
-      <c r="I119" s="12" t="n">
-        <v>5000</v>
-      </c>
-      <c r="J119" s="12" t="n">
-        <v>3000</v>
-      </c>
+      <c r="I119" s="12" t="n"/>
+      <c r="J119" s="12" t="n"/>
       <c r="K119" s="13">
         <f>E119+F119+G119+H119+I119+J119</f>
         <v/>
@@ -12531,22 +11577,12 @@
         <f>IFERROR(VLOOKUP(C120,▼売上原票!$A:$P,9,0),0)</f>
         <v/>
       </c>
-      <c r="E120" s="12" t="n">
-        <v>20000</v>
-      </c>
-      <c r="F120" s="12" t="n">
-        <v>6000</v>
-      </c>
-      <c r="G120" s="12" t="n">
-        <v>3000</v>
-      </c>
+      <c r="E120" s="12" t="n"/>
+      <c r="F120" s="12" t="n"/>
+      <c r="G120" s="12" t="n"/>
       <c r="H120" s="12" t="n"/>
-      <c r="I120" s="12" t="n">
-        <v>5000</v>
-      </c>
-      <c r="J120" s="12" t="n">
-        <v>3000</v>
-      </c>
+      <c r="I120" s="12" t="n"/>
+      <c r="J120" s="12" t="n"/>
       <c r="K120" s="13">
         <f>E120+F120+G120+H120+I120+J120</f>
         <v/>
@@ -12597,22 +11633,12 @@
         <f>IFERROR(VLOOKUP(C121,▼売上原票!$A:$P,9,0),0)</f>
         <v/>
       </c>
-      <c r="E121" s="12" t="n">
-        <v>20000</v>
-      </c>
-      <c r="F121" s="12" t="n">
-        <v>6000</v>
-      </c>
-      <c r="G121" s="12" t="n">
-        <v>3000</v>
-      </c>
+      <c r="E121" s="12" t="n"/>
+      <c r="F121" s="12" t="n"/>
+      <c r="G121" s="12" t="n"/>
       <c r="H121" s="12" t="n"/>
-      <c r="I121" s="12" t="n">
-        <v>5000</v>
-      </c>
-      <c r="J121" s="12" t="n">
-        <v>3000</v>
-      </c>
+      <c r="I121" s="12" t="n"/>
+      <c r="J121" s="12" t="n"/>
       <c r="K121" s="13">
         <f>E121+F121+G121+H121+I121+J121</f>
         <v/>
@@ -12663,22 +11689,12 @@
         <f>IFERROR(VLOOKUP(C122,▼売上原票!$A:$P,9,0),0)</f>
         <v/>
       </c>
-      <c r="E122" s="12" t="n">
-        <v>20000</v>
-      </c>
-      <c r="F122" s="12" t="n">
-        <v>6000</v>
-      </c>
-      <c r="G122" s="12" t="n">
-        <v>3000</v>
-      </c>
+      <c r="E122" s="12" t="n"/>
+      <c r="F122" s="12" t="n"/>
+      <c r="G122" s="12" t="n"/>
       <c r="H122" s="12" t="n"/>
-      <c r="I122" s="12" t="n">
-        <v>5000</v>
-      </c>
-      <c r="J122" s="12" t="n">
-        <v>3000</v>
-      </c>
+      <c r="I122" s="12" t="n"/>
+      <c r="J122" s="12" t="n"/>
       <c r="K122" s="13">
         <f>E122+F122+G122+H122+I122+J122</f>
         <v/>
@@ -12729,22 +11745,12 @@
         <f>IFERROR(VLOOKUP(C123,▼売上原票!$A:$P,9,0),0)</f>
         <v/>
       </c>
-      <c r="E123" s="12" t="n">
-        <v>20000</v>
-      </c>
-      <c r="F123" s="12" t="n">
-        <v>6000</v>
-      </c>
-      <c r="G123" s="12" t="n">
-        <v>3000</v>
-      </c>
+      <c r="E123" s="12" t="n"/>
+      <c r="F123" s="12" t="n"/>
+      <c r="G123" s="12" t="n"/>
       <c r="H123" s="12" t="n"/>
-      <c r="I123" s="12" t="n">
-        <v>5000</v>
-      </c>
-      <c r="J123" s="12" t="n">
-        <v>3000</v>
-      </c>
+      <c r="I123" s="12" t="n"/>
+      <c r="J123" s="12" t="n"/>
       <c r="K123" s="13">
         <f>E123+F123+G123+H123+I123+J123</f>
         <v/>
@@ -12795,22 +11801,12 @@
         <f>IFERROR(VLOOKUP(C124,▼売上原票!$A:$P,9,0),0)</f>
         <v/>
       </c>
-      <c r="E124" s="12" t="n">
-        <v>20000</v>
-      </c>
-      <c r="F124" s="12" t="n">
-        <v>6000</v>
-      </c>
-      <c r="G124" s="12" t="n">
-        <v>3000</v>
-      </c>
+      <c r="E124" s="12" t="n"/>
+      <c r="F124" s="12" t="n"/>
+      <c r="G124" s="12" t="n"/>
       <c r="H124" s="12" t="n"/>
-      <c r="I124" s="12" t="n">
-        <v>5000</v>
-      </c>
-      <c r="J124" s="12" t="n">
-        <v>3000</v>
-      </c>
+      <c r="I124" s="12" t="n"/>
+      <c r="J124" s="12" t="n"/>
       <c r="K124" s="13">
         <f>E124+F124+G124+H124+I124+J124</f>
         <v/>
@@ -12861,22 +11857,12 @@
         <f>IFERROR(VLOOKUP(C125,▼売上原票!$A:$P,9,0),0)</f>
         <v/>
       </c>
-      <c r="E125" s="12" t="n">
-        <v>20000</v>
-      </c>
-      <c r="F125" s="12" t="n">
-        <v>6000</v>
-      </c>
-      <c r="G125" s="12" t="n">
-        <v>3000</v>
-      </c>
+      <c r="E125" s="12" t="n"/>
+      <c r="F125" s="12" t="n"/>
+      <c r="G125" s="12" t="n"/>
       <c r="H125" s="12" t="n"/>
-      <c r="I125" s="12" t="n">
-        <v>5000</v>
-      </c>
-      <c r="J125" s="12" t="n">
-        <v>3000</v>
-      </c>
+      <c r="I125" s="12" t="n"/>
+      <c r="J125" s="12" t="n"/>
       <c r="K125" s="13">
         <f>E125+F125+G125+H125+I125+J125</f>
         <v/>
@@ -12927,22 +11913,12 @@
         <f>IFERROR(VLOOKUP(C126,▼売上原票!$A:$P,9,0),0)</f>
         <v/>
       </c>
-      <c r="E126" s="12" t="n">
-        <v>20000</v>
-      </c>
-      <c r="F126" s="12" t="n">
-        <v>6000</v>
-      </c>
-      <c r="G126" s="12" t="n">
-        <v>3000</v>
-      </c>
+      <c r="E126" s="12" t="n"/>
+      <c r="F126" s="12" t="n"/>
+      <c r="G126" s="12" t="n"/>
       <c r="H126" s="12" t="n"/>
-      <c r="I126" s="12" t="n">
-        <v>5000</v>
-      </c>
-      <c r="J126" s="12" t="n">
-        <v>3000</v>
-      </c>
+      <c r="I126" s="12" t="n"/>
+      <c r="J126" s="12" t="n"/>
       <c r="K126" s="13">
         <f>E126+F126+G126+H126+I126+J126</f>
         <v/>
@@ -12993,22 +11969,12 @@
         <f>IFERROR(VLOOKUP(C127,▼売上原票!$A:$P,9,0),0)</f>
         <v/>
       </c>
-      <c r="E127" s="12" t="n">
-        <v>20000</v>
-      </c>
-      <c r="F127" s="12" t="n">
-        <v>6000</v>
-      </c>
-      <c r="G127" s="12" t="n">
-        <v>3000</v>
-      </c>
+      <c r="E127" s="12" t="n"/>
+      <c r="F127" s="12" t="n"/>
+      <c r="G127" s="12" t="n"/>
       <c r="H127" s="12" t="n"/>
-      <c r="I127" s="12" t="n">
-        <v>5000</v>
-      </c>
-      <c r="J127" s="12" t="n">
-        <v>3000</v>
-      </c>
+      <c r="I127" s="12" t="n"/>
+      <c r="J127" s="12" t="n"/>
       <c r="K127" s="13">
         <f>E127+F127+G127+H127+I127+J127</f>
         <v/>
@@ -13059,22 +12025,12 @@
         <f>IFERROR(VLOOKUP(C128,▼売上原票!$A:$P,9,0),0)</f>
         <v/>
       </c>
-      <c r="E128" s="12" t="n">
-        <v>20000</v>
-      </c>
-      <c r="F128" s="12" t="n">
-        <v>6000</v>
-      </c>
-      <c r="G128" s="12" t="n">
-        <v>3000</v>
-      </c>
+      <c r="E128" s="12" t="n"/>
+      <c r="F128" s="12" t="n"/>
+      <c r="G128" s="12" t="n"/>
       <c r="H128" s="12" t="n"/>
-      <c r="I128" s="12" t="n">
-        <v>5000</v>
-      </c>
-      <c r="J128" s="12" t="n">
-        <v>3000</v>
-      </c>
+      <c r="I128" s="12" t="n"/>
+      <c r="J128" s="12" t="n"/>
       <c r="K128" s="13">
         <f>E128+F128+G128+H128+I128+J128</f>
         <v/>
@@ -13125,22 +12081,12 @@
         <f>IFERROR(VLOOKUP(C129,▼売上原票!$A:$P,9,0),0)</f>
         <v/>
       </c>
-      <c r="E129" s="12" t="n">
-        <v>20000</v>
-      </c>
-      <c r="F129" s="12" t="n">
-        <v>6000</v>
-      </c>
-      <c r="G129" s="12" t="n">
-        <v>3000</v>
-      </c>
+      <c r="E129" s="12" t="n"/>
+      <c r="F129" s="12" t="n"/>
+      <c r="G129" s="12" t="n"/>
       <c r="H129" s="12" t="n"/>
-      <c r="I129" s="12" t="n">
-        <v>5000</v>
-      </c>
-      <c r="J129" s="12" t="n">
-        <v>3000</v>
-      </c>
+      <c r="I129" s="12" t="n"/>
+      <c r="J129" s="12" t="n"/>
       <c r="K129" s="13">
         <f>E129+F129+G129+H129+I129+J129</f>
         <v/>
@@ -13210,24 +12156,12 @@
         <f>IFERROR(VLOOKUP(C131,▼売上原票!$A:$P,10,0),0)</f>
         <v/>
       </c>
-      <c r="E131" s="12" t="n">
-        <v>850000</v>
-      </c>
-      <c r="F131" s="12" t="n">
-        <v>248000</v>
-      </c>
-      <c r="G131" s="12" t="n">
-        <v>118000</v>
-      </c>
-      <c r="H131" s="12" t="n">
-        <v>580000</v>
-      </c>
-      <c r="I131" s="12" t="n">
-        <v>95000</v>
-      </c>
-      <c r="J131" s="12" t="n">
-        <v>62000</v>
-      </c>
+      <c r="E131" s="12" t="n"/>
+      <c r="F131" s="12" t="n"/>
+      <c r="G131" s="12" t="n"/>
+      <c r="H131" s="12" t="n"/>
+      <c r="I131" s="12" t="n"/>
+      <c r="J131" s="12" t="n"/>
       <c r="K131" s="13">
         <f>E131+F131+G131+H131+I131+J131</f>
         <v/>
@@ -13279,24 +12213,12 @@
         <f>IFERROR(VLOOKUP(C132,▼売上原票!$A:$P,10,0),0)</f>
         <v/>
       </c>
-      <c r="E132" s="12" t="n">
-        <v>850000</v>
-      </c>
-      <c r="F132" s="12" t="n">
-        <v>248000</v>
-      </c>
-      <c r="G132" s="12" t="n">
-        <v>118000</v>
-      </c>
-      <c r="H132" s="12" t="n">
-        <v>580000</v>
-      </c>
-      <c r="I132" s="12" t="n">
-        <v>95000</v>
-      </c>
-      <c r="J132" s="12" t="n">
-        <v>62000</v>
-      </c>
+      <c r="E132" s="12" t="n"/>
+      <c r="F132" s="12" t="n"/>
+      <c r="G132" s="12" t="n"/>
+      <c r="H132" s="12" t="n"/>
+      <c r="I132" s="12" t="n"/>
+      <c r="J132" s="12" t="n"/>
       <c r="K132" s="13">
         <f>E132+F132+G132+H132+I132+J132</f>
         <v/>
@@ -13347,24 +12269,12 @@
         <f>IFERROR(VLOOKUP(C133,▼売上原票!$A:$P,10,0),0)</f>
         <v/>
       </c>
-      <c r="E133" s="12" t="n">
-        <v>850000</v>
-      </c>
-      <c r="F133" s="12" t="n">
-        <v>248000</v>
-      </c>
-      <c r="G133" s="12" t="n">
-        <v>118000</v>
-      </c>
-      <c r="H133" s="12" t="n">
-        <v>580000</v>
-      </c>
-      <c r="I133" s="12" t="n">
-        <v>95000</v>
-      </c>
-      <c r="J133" s="12" t="n">
-        <v>62000</v>
-      </c>
+      <c r="E133" s="12" t="n"/>
+      <c r="F133" s="12" t="n"/>
+      <c r="G133" s="12" t="n"/>
+      <c r="H133" s="12" t="n"/>
+      <c r="I133" s="12" t="n"/>
+      <c r="J133" s="12" t="n"/>
       <c r="K133" s="13">
         <f>E133+F133+G133+H133+I133+J133</f>
         <v/>
@@ -13415,24 +12325,12 @@
         <f>IFERROR(VLOOKUP(C134,▼売上原票!$A:$P,10,0),0)</f>
         <v/>
       </c>
-      <c r="E134" s="12" t="n">
-        <v>850000</v>
-      </c>
-      <c r="F134" s="12" t="n">
-        <v>248000</v>
-      </c>
-      <c r="G134" s="12" t="n">
-        <v>118000</v>
-      </c>
-      <c r="H134" s="12" t="n">
-        <v>580000</v>
-      </c>
-      <c r="I134" s="12" t="n">
-        <v>95000</v>
-      </c>
-      <c r="J134" s="12" t="n">
-        <v>62000</v>
-      </c>
+      <c r="E134" s="12" t="n"/>
+      <c r="F134" s="12" t="n"/>
+      <c r="G134" s="12" t="n"/>
+      <c r="H134" s="12" t="n"/>
+      <c r="I134" s="12" t="n"/>
+      <c r="J134" s="12" t="n"/>
       <c r="K134" s="13">
         <f>E134+F134+G134+H134+I134+J134</f>
         <v/>
@@ -13483,24 +12381,12 @@
         <f>IFERROR(VLOOKUP(C135,▼売上原票!$A:$P,10,0),0)</f>
         <v/>
       </c>
-      <c r="E135" s="12" t="n">
-        <v>850000</v>
-      </c>
-      <c r="F135" s="12" t="n">
-        <v>248000</v>
-      </c>
-      <c r="G135" s="12" t="n">
-        <v>118000</v>
-      </c>
-      <c r="H135" s="12" t="n">
-        <v>580000</v>
-      </c>
-      <c r="I135" s="12" t="n">
-        <v>95000</v>
-      </c>
-      <c r="J135" s="12" t="n">
-        <v>62000</v>
-      </c>
+      <c r="E135" s="12" t="n"/>
+      <c r="F135" s="12" t="n"/>
+      <c r="G135" s="12" t="n"/>
+      <c r="H135" s="12" t="n"/>
+      <c r="I135" s="12" t="n"/>
+      <c r="J135" s="12" t="n"/>
       <c r="K135" s="13">
         <f>E135+F135+G135+H135+I135+J135</f>
         <v/>
@@ -13551,24 +12437,12 @@
         <f>IFERROR(VLOOKUP(C136,▼売上原票!$A:$P,10,0),0)</f>
         <v/>
       </c>
-      <c r="E136" s="12" t="n">
-        <v>850000</v>
-      </c>
-      <c r="F136" s="12" t="n">
-        <v>248000</v>
-      </c>
-      <c r="G136" s="12" t="n">
-        <v>118000</v>
-      </c>
-      <c r="H136" s="12" t="n">
-        <v>580000</v>
-      </c>
-      <c r="I136" s="12" t="n">
-        <v>95000</v>
-      </c>
-      <c r="J136" s="12" t="n">
-        <v>62000</v>
-      </c>
+      <c r="E136" s="12" t="n"/>
+      <c r="F136" s="12" t="n"/>
+      <c r="G136" s="12" t="n"/>
+      <c r="H136" s="12" t="n"/>
+      <c r="I136" s="12" t="n"/>
+      <c r="J136" s="12" t="n"/>
       <c r="K136" s="13">
         <f>E136+F136+G136+H136+I136+J136</f>
         <v/>
@@ -13619,24 +12493,12 @@
         <f>IFERROR(VLOOKUP(C137,▼売上原票!$A:$P,10,0),0)</f>
         <v/>
       </c>
-      <c r="E137" s="12" t="n">
-        <v>850000</v>
-      </c>
-      <c r="F137" s="12" t="n">
-        <v>248000</v>
-      </c>
-      <c r="G137" s="12" t="n">
-        <v>118000</v>
-      </c>
-      <c r="H137" s="12" t="n">
-        <v>580000</v>
-      </c>
-      <c r="I137" s="12" t="n">
-        <v>95000</v>
-      </c>
-      <c r="J137" s="12" t="n">
-        <v>62000</v>
-      </c>
+      <c r="E137" s="12" t="n"/>
+      <c r="F137" s="12" t="n"/>
+      <c r="G137" s="12" t="n"/>
+      <c r="H137" s="12" t="n"/>
+      <c r="I137" s="12" t="n"/>
+      <c r="J137" s="12" t="n"/>
       <c r="K137" s="13">
         <f>E137+F137+G137+H137+I137+J137</f>
         <v/>
@@ -13687,24 +12549,12 @@
         <f>IFERROR(VLOOKUP(C138,▼売上原票!$A:$P,10,0),0)</f>
         <v/>
       </c>
-      <c r="E138" s="12" t="n">
-        <v>850000</v>
-      </c>
-      <c r="F138" s="12" t="n">
-        <v>248000</v>
-      </c>
-      <c r="G138" s="12" t="n">
-        <v>118000</v>
-      </c>
-      <c r="H138" s="12" t="n">
-        <v>580000</v>
-      </c>
-      <c r="I138" s="12" t="n">
-        <v>95000</v>
-      </c>
-      <c r="J138" s="12" t="n">
-        <v>62000</v>
-      </c>
+      <c r="E138" s="12" t="n"/>
+      <c r="F138" s="12" t="n"/>
+      <c r="G138" s="12" t="n"/>
+      <c r="H138" s="12" t="n"/>
+      <c r="I138" s="12" t="n"/>
+      <c r="J138" s="12" t="n"/>
       <c r="K138" s="13">
         <f>E138+F138+G138+H138+I138+J138</f>
         <v/>
@@ -13755,24 +12605,12 @@
         <f>IFERROR(VLOOKUP(C139,▼売上原票!$A:$P,10,0),0)</f>
         <v/>
       </c>
-      <c r="E139" s="12" t="n">
-        <v>850000</v>
-      </c>
-      <c r="F139" s="12" t="n">
-        <v>248000</v>
-      </c>
-      <c r="G139" s="12" t="n">
-        <v>118000</v>
-      </c>
-      <c r="H139" s="12" t="n">
-        <v>580000</v>
-      </c>
-      <c r="I139" s="12" t="n">
-        <v>95000</v>
-      </c>
-      <c r="J139" s="12" t="n">
-        <v>62000</v>
-      </c>
+      <c r="E139" s="12" t="n"/>
+      <c r="F139" s="12" t="n"/>
+      <c r="G139" s="12" t="n"/>
+      <c r="H139" s="12" t="n"/>
+      <c r="I139" s="12" t="n"/>
+      <c r="J139" s="12" t="n"/>
       <c r="K139" s="13">
         <f>E139+F139+G139+H139+I139+J139</f>
         <v/>
@@ -13823,24 +12661,12 @@
         <f>IFERROR(VLOOKUP(C140,▼売上原票!$A:$P,10,0),0)</f>
         <v/>
       </c>
-      <c r="E140" s="12" t="n">
-        <v>850000</v>
-      </c>
-      <c r="F140" s="12" t="n">
-        <v>248000</v>
-      </c>
-      <c r="G140" s="12" t="n">
-        <v>118000</v>
-      </c>
-      <c r="H140" s="12" t="n">
-        <v>580000</v>
-      </c>
-      <c r="I140" s="12" t="n">
-        <v>95000</v>
-      </c>
-      <c r="J140" s="12" t="n">
-        <v>62000</v>
-      </c>
+      <c r="E140" s="12" t="n"/>
+      <c r="F140" s="12" t="n"/>
+      <c r="G140" s="12" t="n"/>
+      <c r="H140" s="12" t="n"/>
+      <c r="I140" s="12" t="n"/>
+      <c r="J140" s="12" t="n"/>
       <c r="K140" s="13">
         <f>E140+F140+G140+H140+I140+J140</f>
         <v/>
@@ -13891,24 +12717,12 @@
         <f>IFERROR(VLOOKUP(C141,▼売上原票!$A:$P,10,0),0)</f>
         <v/>
       </c>
-      <c r="E141" s="12" t="n">
-        <v>850000</v>
-      </c>
-      <c r="F141" s="12" t="n">
-        <v>248000</v>
-      </c>
-      <c r="G141" s="12" t="n">
-        <v>118000</v>
-      </c>
-      <c r="H141" s="12" t="n">
-        <v>580000</v>
-      </c>
-      <c r="I141" s="12" t="n">
-        <v>95000</v>
-      </c>
-      <c r="J141" s="12" t="n">
-        <v>62000</v>
-      </c>
+      <c r="E141" s="12" t="n"/>
+      <c r="F141" s="12" t="n"/>
+      <c r="G141" s="12" t="n"/>
+      <c r="H141" s="12" t="n"/>
+      <c r="I141" s="12" t="n"/>
+      <c r="J141" s="12" t="n"/>
       <c r="K141" s="13">
         <f>E141+F141+G141+H141+I141+J141</f>
         <v/>
@@ -13959,24 +12773,12 @@
         <f>IFERROR(VLOOKUP(C142,▼売上原票!$A:$P,10,0),0)</f>
         <v/>
       </c>
-      <c r="E142" s="12" t="n">
-        <v>850000</v>
-      </c>
-      <c r="F142" s="12" t="n">
-        <v>248000</v>
-      </c>
-      <c r="G142" s="12" t="n">
-        <v>118000</v>
-      </c>
-      <c r="H142" s="12" t="n">
-        <v>580000</v>
-      </c>
-      <c r="I142" s="12" t="n">
-        <v>95000</v>
-      </c>
-      <c r="J142" s="12" t="n">
-        <v>62000</v>
-      </c>
+      <c r="E142" s="12" t="n"/>
+      <c r="F142" s="12" t="n"/>
+      <c r="G142" s="12" t="n"/>
+      <c r="H142" s="12" t="n"/>
+      <c r="I142" s="12" t="n"/>
+      <c r="J142" s="12" t="n"/>
       <c r="K142" s="13">
         <f>E142+F142+G142+H142+I142+J142</f>
         <v/>
@@ -14027,24 +12829,12 @@
         <f>IFERROR(VLOOKUP(C143,▼売上原票!$A:$P,10,0),0)</f>
         <v/>
       </c>
-      <c r="E143" s="12" t="n">
-        <v>850000</v>
-      </c>
-      <c r="F143" s="12" t="n">
-        <v>248000</v>
-      </c>
-      <c r="G143" s="12" t="n">
-        <v>118000</v>
-      </c>
-      <c r="H143" s="12" t="n">
-        <v>580000</v>
-      </c>
-      <c r="I143" s="12" t="n">
-        <v>95000</v>
-      </c>
-      <c r="J143" s="12" t="n">
-        <v>62000</v>
-      </c>
+      <c r="E143" s="12" t="n"/>
+      <c r="F143" s="12" t="n"/>
+      <c r="G143" s="12" t="n"/>
+      <c r="H143" s="12" t="n"/>
+      <c r="I143" s="12" t="n"/>
+      <c r="J143" s="12" t="n"/>
       <c r="K143" s="13">
         <f>E143+F143+G143+H143+I143+J143</f>
         <v/>
@@ -14095,24 +12885,12 @@
         <f>IFERROR(VLOOKUP(C144,▼売上原票!$A:$P,10,0),0)</f>
         <v/>
       </c>
-      <c r="E144" s="12" t="n">
-        <v>850000</v>
-      </c>
-      <c r="F144" s="12" t="n">
-        <v>248000</v>
-      </c>
-      <c r="G144" s="12" t="n">
-        <v>118000</v>
-      </c>
-      <c r="H144" s="12" t="n">
-        <v>580000</v>
-      </c>
-      <c r="I144" s="12" t="n">
-        <v>95000</v>
-      </c>
-      <c r="J144" s="12" t="n">
-        <v>62000</v>
-      </c>
+      <c r="E144" s="12" t="n"/>
+      <c r="F144" s="12" t="n"/>
+      <c r="G144" s="12" t="n"/>
+      <c r="H144" s="12" t="n"/>
+      <c r="I144" s="12" t="n"/>
+      <c r="J144" s="12" t="n"/>
       <c r="K144" s="13">
         <f>E144+F144+G144+H144+I144+J144</f>
         <v/>
@@ -14163,24 +12941,12 @@
         <f>IFERROR(VLOOKUP(C145,▼売上原票!$A:$P,10,0),0)</f>
         <v/>
       </c>
-      <c r="E145" s="12" t="n">
-        <v>850000</v>
-      </c>
-      <c r="F145" s="12" t="n">
-        <v>248000</v>
-      </c>
-      <c r="G145" s="12" t="n">
-        <v>118000</v>
-      </c>
-      <c r="H145" s="12" t="n">
-        <v>580000</v>
-      </c>
-      <c r="I145" s="12" t="n">
-        <v>95000</v>
-      </c>
-      <c r="J145" s="12" t="n">
-        <v>62000</v>
-      </c>
+      <c r="E145" s="12" t="n"/>
+      <c r="F145" s="12" t="n"/>
+      <c r="G145" s="12" t="n"/>
+      <c r="H145" s="12" t="n"/>
+      <c r="I145" s="12" t="n"/>
+      <c r="J145" s="12" t="n"/>
       <c r="K145" s="13">
         <f>E145+F145+G145+H145+I145+J145</f>
         <v/>
@@ -14231,24 +12997,12 @@
         <f>IFERROR(VLOOKUP(C146,▼売上原票!$A:$P,10,0),0)</f>
         <v/>
       </c>
-      <c r="E146" s="12" t="n">
-        <v>850000</v>
-      </c>
-      <c r="F146" s="12" t="n">
-        <v>248000</v>
-      </c>
-      <c r="G146" s="12" t="n">
-        <v>118000</v>
-      </c>
-      <c r="H146" s="12" t="n">
-        <v>580000</v>
-      </c>
-      <c r="I146" s="12" t="n">
-        <v>95000</v>
-      </c>
-      <c r="J146" s="12" t="n">
-        <v>62000</v>
-      </c>
+      <c r="E146" s="12" t="n"/>
+      <c r="F146" s="12" t="n"/>
+      <c r="G146" s="12" t="n"/>
+      <c r="H146" s="12" t="n"/>
+      <c r="I146" s="12" t="n"/>
+      <c r="J146" s="12" t="n"/>
       <c r="K146" s="13">
         <f>E146+F146+G146+H146+I146+J146</f>
         <v/>
@@ -14299,24 +13053,12 @@
         <f>IFERROR(VLOOKUP(C147,▼売上原票!$A:$P,10,0),0)</f>
         <v/>
       </c>
-      <c r="E147" s="12" t="n">
-        <v>850000</v>
-      </c>
-      <c r="F147" s="12" t="n">
-        <v>248000</v>
-      </c>
-      <c r="G147" s="12" t="n">
-        <v>118000</v>
-      </c>
-      <c r="H147" s="12" t="n">
-        <v>580000</v>
-      </c>
-      <c r="I147" s="12" t="n">
-        <v>95000</v>
-      </c>
-      <c r="J147" s="12" t="n">
-        <v>62000</v>
-      </c>
+      <c r="E147" s="12" t="n"/>
+      <c r="F147" s="12" t="n"/>
+      <c r="G147" s="12" t="n"/>
+      <c r="H147" s="12" t="n"/>
+      <c r="I147" s="12" t="n"/>
+      <c r="J147" s="12" t="n"/>
       <c r="K147" s="13">
         <f>E147+F147+G147+H147+I147+J147</f>
         <v/>
@@ -14386,24 +13128,12 @@
         <f>IFERROR(VLOOKUP(C149,▼売上原票!$A:$P,11,0),0)</f>
         <v/>
       </c>
-      <c r="E149" s="12" t="n">
-        <v>280000</v>
-      </c>
-      <c r="F149" s="12" t="n">
-        <v>82000</v>
-      </c>
-      <c r="G149" s="12" t="n">
-        <v>38000</v>
-      </c>
-      <c r="H149" s="12" t="n">
-        <v>195000</v>
-      </c>
-      <c r="I149" s="12" t="n">
-        <v>32000</v>
-      </c>
-      <c r="J149" s="12" t="n">
-        <v>20000</v>
-      </c>
+      <c r="E149" s="12" t="n"/>
+      <c r="F149" s="12" t="n"/>
+      <c r="G149" s="12" t="n"/>
+      <c r="H149" s="12" t="n"/>
+      <c r="I149" s="12" t="n"/>
+      <c r="J149" s="12" t="n"/>
       <c r="K149" s="13">
         <f>E149+F149+G149+H149+I149+J149</f>
         <v/>
@@ -14455,24 +13185,12 @@
         <f>IFERROR(VLOOKUP(C150,▼売上原票!$A:$P,11,0),0)</f>
         <v/>
       </c>
-      <c r="E150" s="12" t="n">
-        <v>280000</v>
-      </c>
-      <c r="F150" s="12" t="n">
-        <v>82000</v>
-      </c>
-      <c r="G150" s="12" t="n">
-        <v>38000</v>
-      </c>
-      <c r="H150" s="12" t="n">
-        <v>195000</v>
-      </c>
-      <c r="I150" s="12" t="n">
-        <v>32000</v>
-      </c>
-      <c r="J150" s="12" t="n">
-        <v>20000</v>
-      </c>
+      <c r="E150" s="12" t="n"/>
+      <c r="F150" s="12" t="n"/>
+      <c r="G150" s="12" t="n"/>
+      <c r="H150" s="12" t="n"/>
+      <c r="I150" s="12" t="n"/>
+      <c r="J150" s="12" t="n"/>
       <c r="K150" s="13">
         <f>E150+F150+G150+H150+I150+J150</f>
         <v/>
@@ -14523,24 +13241,12 @@
         <f>IFERROR(VLOOKUP(C151,▼売上原票!$A:$P,11,0),0)</f>
         <v/>
       </c>
-      <c r="E151" s="12" t="n">
-        <v>280000</v>
-      </c>
-      <c r="F151" s="12" t="n">
-        <v>82000</v>
-      </c>
-      <c r="G151" s="12" t="n">
-        <v>38000</v>
-      </c>
-      <c r="H151" s="12" t="n">
-        <v>195000</v>
-      </c>
-      <c r="I151" s="12" t="n">
-        <v>32000</v>
-      </c>
-      <c r="J151" s="12" t="n">
-        <v>20000</v>
-      </c>
+      <c r="E151" s="12" t="n"/>
+      <c r="F151" s="12" t="n"/>
+      <c r="G151" s="12" t="n"/>
+      <c r="H151" s="12" t="n"/>
+      <c r="I151" s="12" t="n"/>
+      <c r="J151" s="12" t="n"/>
       <c r="K151" s="13">
         <f>E151+F151+G151+H151+I151+J151</f>
         <v/>
@@ -14591,24 +13297,12 @@
         <f>IFERROR(VLOOKUP(C152,▼売上原票!$A:$P,11,0),0)</f>
         <v/>
       </c>
-      <c r="E152" s="12" t="n">
-        <v>280000</v>
-      </c>
-      <c r="F152" s="12" t="n">
-        <v>82000</v>
-      </c>
-      <c r="G152" s="12" t="n">
-        <v>38000</v>
-      </c>
-      <c r="H152" s="12" t="n">
-        <v>195000</v>
-      </c>
-      <c r="I152" s="12" t="n">
-        <v>32000</v>
-      </c>
-      <c r="J152" s="12" t="n">
-        <v>20000</v>
-      </c>
+      <c r="E152" s="12" t="n"/>
+      <c r="F152" s="12" t="n"/>
+      <c r="G152" s="12" t="n"/>
+      <c r="H152" s="12" t="n"/>
+      <c r="I152" s="12" t="n"/>
+      <c r="J152" s="12" t="n"/>
       <c r="K152" s="13">
         <f>E152+F152+G152+H152+I152+J152</f>
         <v/>
@@ -14659,24 +13353,12 @@
         <f>IFERROR(VLOOKUP(C153,▼売上原票!$A:$P,11,0),0)</f>
         <v/>
       </c>
-      <c r="E153" s="12" t="n">
-        <v>280000</v>
-      </c>
-      <c r="F153" s="12" t="n">
-        <v>82000</v>
-      </c>
-      <c r="G153" s="12" t="n">
-        <v>38000</v>
-      </c>
-      <c r="H153" s="12" t="n">
-        <v>195000</v>
-      </c>
-      <c r="I153" s="12" t="n">
-        <v>32000</v>
-      </c>
-      <c r="J153" s="12" t="n">
-        <v>20000</v>
-      </c>
+      <c r="E153" s="12" t="n"/>
+      <c r="F153" s="12" t="n"/>
+      <c r="G153" s="12" t="n"/>
+      <c r="H153" s="12" t="n"/>
+      <c r="I153" s="12" t="n"/>
+      <c r="J153" s="12" t="n"/>
       <c r="K153" s="13">
         <f>E153+F153+G153+H153+I153+J153</f>
         <v/>
@@ -14727,24 +13409,12 @@
         <f>IFERROR(VLOOKUP(C154,▼売上原票!$A:$P,11,0),0)</f>
         <v/>
       </c>
-      <c r="E154" s="12" t="n">
-        <v>280000</v>
-      </c>
-      <c r="F154" s="12" t="n">
-        <v>82000</v>
-      </c>
-      <c r="G154" s="12" t="n">
-        <v>38000</v>
-      </c>
-      <c r="H154" s="12" t="n">
-        <v>195000</v>
-      </c>
-      <c r="I154" s="12" t="n">
-        <v>32000</v>
-      </c>
-      <c r="J154" s="12" t="n">
-        <v>20000</v>
-      </c>
+      <c r="E154" s="12" t="n"/>
+      <c r="F154" s="12" t="n"/>
+      <c r="G154" s="12" t="n"/>
+      <c r="H154" s="12" t="n"/>
+      <c r="I154" s="12" t="n"/>
+      <c r="J154" s="12" t="n"/>
       <c r="K154" s="13">
         <f>E154+F154+G154+H154+I154+J154</f>
         <v/>
@@ -14795,24 +13465,12 @@
         <f>IFERROR(VLOOKUP(C155,▼売上原票!$A:$P,11,0),0)</f>
         <v/>
       </c>
-      <c r="E155" s="12" t="n">
-        <v>280000</v>
-      </c>
-      <c r="F155" s="12" t="n">
-        <v>82000</v>
-      </c>
-      <c r="G155" s="12" t="n">
-        <v>38000</v>
-      </c>
-      <c r="H155" s="12" t="n">
-        <v>195000</v>
-      </c>
-      <c r="I155" s="12" t="n">
-        <v>32000</v>
-      </c>
-      <c r="J155" s="12" t="n">
-        <v>20000</v>
-      </c>
+      <c r="E155" s="12" t="n"/>
+      <c r="F155" s="12" t="n"/>
+      <c r="G155" s="12" t="n"/>
+      <c r="H155" s="12" t="n"/>
+      <c r="I155" s="12" t="n"/>
+      <c r="J155" s="12" t="n"/>
       <c r="K155" s="13">
         <f>E155+F155+G155+H155+I155+J155</f>
         <v/>
@@ -14863,24 +13521,12 @@
         <f>IFERROR(VLOOKUP(C156,▼売上原票!$A:$P,11,0),0)</f>
         <v/>
       </c>
-      <c r="E156" s="12" t="n">
-        <v>280000</v>
-      </c>
-      <c r="F156" s="12" t="n">
-        <v>82000</v>
-      </c>
-      <c r="G156" s="12" t="n">
-        <v>38000</v>
-      </c>
-      <c r="H156" s="12" t="n">
-        <v>195000</v>
-      </c>
-      <c r="I156" s="12" t="n">
-        <v>32000</v>
-      </c>
-      <c r="J156" s="12" t="n">
-        <v>20000</v>
-      </c>
+      <c r="E156" s="12" t="n"/>
+      <c r="F156" s="12" t="n"/>
+      <c r="G156" s="12" t="n"/>
+      <c r="H156" s="12" t="n"/>
+      <c r="I156" s="12" t="n"/>
+      <c r="J156" s="12" t="n"/>
       <c r="K156" s="13">
         <f>E156+F156+G156+H156+I156+J156</f>
         <v/>
@@ -14931,24 +13577,12 @@
         <f>IFERROR(VLOOKUP(C157,▼売上原票!$A:$P,11,0),0)</f>
         <v/>
       </c>
-      <c r="E157" s="12" t="n">
-        <v>280000</v>
-      </c>
-      <c r="F157" s="12" t="n">
-        <v>82000</v>
-      </c>
-      <c r="G157" s="12" t="n">
-        <v>38000</v>
-      </c>
-      <c r="H157" s="12" t="n">
-        <v>195000</v>
-      </c>
-      <c r="I157" s="12" t="n">
-        <v>32000</v>
-      </c>
-      <c r="J157" s="12" t="n">
-        <v>20000</v>
-      </c>
+      <c r="E157" s="12" t="n"/>
+      <c r="F157" s="12" t="n"/>
+      <c r="G157" s="12" t="n"/>
+      <c r="H157" s="12" t="n"/>
+      <c r="I157" s="12" t="n"/>
+      <c r="J157" s="12" t="n"/>
       <c r="K157" s="13">
         <f>E157+F157+G157+H157+I157+J157</f>
         <v/>
@@ -14999,24 +13633,12 @@
         <f>IFERROR(VLOOKUP(C158,▼売上原票!$A:$P,11,0),0)</f>
         <v/>
       </c>
-      <c r="E158" s="12" t="n">
-        <v>280000</v>
-      </c>
-      <c r="F158" s="12" t="n">
-        <v>82000</v>
-      </c>
-      <c r="G158" s="12" t="n">
-        <v>38000</v>
-      </c>
-      <c r="H158" s="12" t="n">
-        <v>195000</v>
-      </c>
-      <c r="I158" s="12" t="n">
-        <v>32000</v>
-      </c>
-      <c r="J158" s="12" t="n">
-        <v>20000</v>
-      </c>
+      <c r="E158" s="12" t="n"/>
+      <c r="F158" s="12" t="n"/>
+      <c r="G158" s="12" t="n"/>
+      <c r="H158" s="12" t="n"/>
+      <c r="I158" s="12" t="n"/>
+      <c r="J158" s="12" t="n"/>
       <c r="K158" s="13">
         <f>E158+F158+G158+H158+I158+J158</f>
         <v/>
@@ -15067,24 +13689,12 @@
         <f>IFERROR(VLOOKUP(C159,▼売上原票!$A:$P,11,0),0)</f>
         <v/>
       </c>
-      <c r="E159" s="12" t="n">
-        <v>280000</v>
-      </c>
-      <c r="F159" s="12" t="n">
-        <v>82000</v>
-      </c>
-      <c r="G159" s="12" t="n">
-        <v>38000</v>
-      </c>
-      <c r="H159" s="12" t="n">
-        <v>195000</v>
-      </c>
-      <c r="I159" s="12" t="n">
-        <v>32000</v>
-      </c>
-      <c r="J159" s="12" t="n">
-        <v>20000</v>
-      </c>
+      <c r="E159" s="12" t="n"/>
+      <c r="F159" s="12" t="n"/>
+      <c r="G159" s="12" t="n"/>
+      <c r="H159" s="12" t="n"/>
+      <c r="I159" s="12" t="n"/>
+      <c r="J159" s="12" t="n"/>
       <c r="K159" s="13">
         <f>E159+F159+G159+H159+I159+J159</f>
         <v/>
@@ -15135,24 +13745,12 @@
         <f>IFERROR(VLOOKUP(C160,▼売上原票!$A:$P,11,0),0)</f>
         <v/>
       </c>
-      <c r="E160" s="12" t="n">
-        <v>280000</v>
-      </c>
-      <c r="F160" s="12" t="n">
-        <v>82000</v>
-      </c>
-      <c r="G160" s="12" t="n">
-        <v>38000</v>
-      </c>
-      <c r="H160" s="12" t="n">
-        <v>195000</v>
-      </c>
-      <c r="I160" s="12" t="n">
-        <v>32000</v>
-      </c>
-      <c r="J160" s="12" t="n">
-        <v>20000</v>
-      </c>
+      <c r="E160" s="12" t="n"/>
+      <c r="F160" s="12" t="n"/>
+      <c r="G160" s="12" t="n"/>
+      <c r="H160" s="12" t="n"/>
+      <c r="I160" s="12" t="n"/>
+      <c r="J160" s="12" t="n"/>
       <c r="K160" s="13">
         <f>E160+F160+G160+H160+I160+J160</f>
         <v/>
@@ -15203,24 +13801,12 @@
         <f>IFERROR(VLOOKUP(C161,▼売上原票!$A:$P,11,0),0)</f>
         <v/>
       </c>
-      <c r="E161" s="12" t="n">
-        <v>280000</v>
-      </c>
-      <c r="F161" s="12" t="n">
-        <v>82000</v>
-      </c>
-      <c r="G161" s="12" t="n">
-        <v>38000</v>
-      </c>
-      <c r="H161" s="12" t="n">
-        <v>195000</v>
-      </c>
-      <c r="I161" s="12" t="n">
-        <v>32000</v>
-      </c>
-      <c r="J161" s="12" t="n">
-        <v>20000</v>
-      </c>
+      <c r="E161" s="12" t="n"/>
+      <c r="F161" s="12" t="n"/>
+      <c r="G161" s="12" t="n"/>
+      <c r="H161" s="12" t="n"/>
+      <c r="I161" s="12" t="n"/>
+      <c r="J161" s="12" t="n"/>
       <c r="K161" s="13">
         <f>E161+F161+G161+H161+I161+J161</f>
         <v/>
@@ -15271,24 +13857,12 @@
         <f>IFERROR(VLOOKUP(C162,▼売上原票!$A:$P,11,0),0)</f>
         <v/>
       </c>
-      <c r="E162" s="12" t="n">
-        <v>280000</v>
-      </c>
-      <c r="F162" s="12" t="n">
-        <v>82000</v>
-      </c>
-      <c r="G162" s="12" t="n">
-        <v>38000</v>
-      </c>
-      <c r="H162" s="12" t="n">
-        <v>195000</v>
-      </c>
-      <c r="I162" s="12" t="n">
-        <v>32000</v>
-      </c>
-      <c r="J162" s="12" t="n">
-        <v>20000</v>
-      </c>
+      <c r="E162" s="12" t="n"/>
+      <c r="F162" s="12" t="n"/>
+      <c r="G162" s="12" t="n"/>
+      <c r="H162" s="12" t="n"/>
+      <c r="I162" s="12" t="n"/>
+      <c r="J162" s="12" t="n"/>
       <c r="K162" s="13">
         <f>E162+F162+G162+H162+I162+J162</f>
         <v/>
@@ -15339,24 +13913,12 @@
         <f>IFERROR(VLOOKUP(C163,▼売上原票!$A:$P,11,0),0)</f>
         <v/>
       </c>
-      <c r="E163" s="12" t="n">
-        <v>280000</v>
-      </c>
-      <c r="F163" s="12" t="n">
-        <v>82000</v>
-      </c>
-      <c r="G163" s="12" t="n">
-        <v>38000</v>
-      </c>
-      <c r="H163" s="12" t="n">
-        <v>195000</v>
-      </c>
-      <c r="I163" s="12" t="n">
-        <v>32000</v>
-      </c>
-      <c r="J163" s="12" t="n">
-        <v>20000</v>
-      </c>
+      <c r="E163" s="12" t="n"/>
+      <c r="F163" s="12" t="n"/>
+      <c r="G163" s="12" t="n"/>
+      <c r="H163" s="12" t="n"/>
+      <c r="I163" s="12" t="n"/>
+      <c r="J163" s="12" t="n"/>
       <c r="K163" s="13">
         <f>E163+F163+G163+H163+I163+J163</f>
         <v/>
@@ -15407,24 +13969,12 @@
         <f>IFERROR(VLOOKUP(C164,▼売上原票!$A:$P,11,0),0)</f>
         <v/>
       </c>
-      <c r="E164" s="12" t="n">
-        <v>280000</v>
-      </c>
-      <c r="F164" s="12" t="n">
-        <v>82000</v>
-      </c>
-      <c r="G164" s="12" t="n">
-        <v>38000</v>
-      </c>
-      <c r="H164" s="12" t="n">
-        <v>195000</v>
-      </c>
-      <c r="I164" s="12" t="n">
-        <v>32000</v>
-      </c>
-      <c r="J164" s="12" t="n">
-        <v>20000</v>
-      </c>
+      <c r="E164" s="12" t="n"/>
+      <c r="F164" s="12" t="n"/>
+      <c r="G164" s="12" t="n"/>
+      <c r="H164" s="12" t="n"/>
+      <c r="I164" s="12" t="n"/>
+      <c r="J164" s="12" t="n"/>
       <c r="K164" s="13">
         <f>E164+F164+G164+H164+I164+J164</f>
         <v/>
@@ -15475,24 +14025,12 @@
         <f>IFERROR(VLOOKUP(C165,▼売上原票!$A:$P,11,0),0)</f>
         <v/>
       </c>
-      <c r="E165" s="12" t="n">
-        <v>280000</v>
-      </c>
-      <c r="F165" s="12" t="n">
-        <v>82000</v>
-      </c>
-      <c r="G165" s="12" t="n">
-        <v>38000</v>
-      </c>
-      <c r="H165" s="12" t="n">
-        <v>195000</v>
-      </c>
-      <c r="I165" s="12" t="n">
-        <v>32000</v>
-      </c>
-      <c r="J165" s="12" t="n">
-        <v>20000</v>
-      </c>
+      <c r="E165" s="12" t="n"/>
+      <c r="F165" s="12" t="n"/>
+      <c r="G165" s="12" t="n"/>
+      <c r="H165" s="12" t="n"/>
+      <c r="I165" s="12" t="n"/>
+      <c r="J165" s="12" t="n"/>
       <c r="K165" s="13">
         <f>E165+F165+G165+H165+I165+J165</f>
         <v/>
@@ -15562,22 +14100,12 @@
         <f>IFERROR(VLOOKUP(C167,▼売上原票!$A:$P,12,0),0)</f>
         <v/>
       </c>
-      <c r="E167" s="12" t="n">
-        <v>15000</v>
-      </c>
-      <c r="F167" s="12" t="n">
-        <v>4000</v>
-      </c>
-      <c r="G167" s="12" t="n">
-        <v>2000</v>
-      </c>
+      <c r="E167" s="12" t="n"/>
+      <c r="F167" s="12" t="n"/>
+      <c r="G167" s="12" t="n"/>
       <c r="H167" s="12" t="n"/>
-      <c r="I167" s="12" t="n">
-        <v>3000</v>
-      </c>
-      <c r="J167" s="12" t="n">
-        <v>2000</v>
-      </c>
+      <c r="I167" s="12" t="n"/>
+      <c r="J167" s="12" t="n"/>
       <c r="K167" s="13">
         <f>E167+F167+G167+H167+I167+J167</f>
         <v/>
@@ -15629,22 +14157,12 @@
         <f>IFERROR(VLOOKUP(C168,▼売上原票!$A:$P,12,0),0)</f>
         <v/>
       </c>
-      <c r="E168" s="12" t="n">
-        <v>15000</v>
-      </c>
-      <c r="F168" s="12" t="n">
-        <v>4000</v>
-      </c>
-      <c r="G168" s="12" t="n">
-        <v>2000</v>
-      </c>
+      <c r="E168" s="12" t="n"/>
+      <c r="F168" s="12" t="n"/>
+      <c r="G168" s="12" t="n"/>
       <c r="H168" s="12" t="n"/>
-      <c r="I168" s="12" t="n">
-        <v>3000</v>
-      </c>
-      <c r="J168" s="12" t="n">
-        <v>2000</v>
-      </c>
+      <c r="I168" s="12" t="n"/>
+      <c r="J168" s="12" t="n"/>
       <c r="K168" s="13">
         <f>E168+F168+G168+H168+I168+J168</f>
         <v/>
@@ -15695,22 +14213,12 @@
         <f>IFERROR(VLOOKUP(C169,▼売上原票!$A:$P,12,0),0)</f>
         <v/>
       </c>
-      <c r="E169" s="12" t="n">
-        <v>15000</v>
-      </c>
-      <c r="F169" s="12" t="n">
-        <v>4000</v>
-      </c>
-      <c r="G169" s="12" t="n">
-        <v>2000</v>
-      </c>
+      <c r="E169" s="12" t="n"/>
+      <c r="F169" s="12" t="n"/>
+      <c r="G169" s="12" t="n"/>
       <c r="H169" s="12" t="n"/>
-      <c r="I169" s="12" t="n">
-        <v>3000</v>
-      </c>
-      <c r="J169" s="12" t="n">
-        <v>2000</v>
-      </c>
+      <c r="I169" s="12" t="n"/>
+      <c r="J169" s="12" t="n"/>
       <c r="K169" s="13">
         <f>E169+F169+G169+H169+I169+J169</f>
         <v/>
@@ -15761,22 +14269,12 @@
         <f>IFERROR(VLOOKUP(C170,▼売上原票!$A:$P,12,0),0)</f>
         <v/>
       </c>
-      <c r="E170" s="12" t="n">
-        <v>15000</v>
-      </c>
-      <c r="F170" s="12" t="n">
-        <v>4000</v>
-      </c>
-      <c r="G170" s="12" t="n">
-        <v>2000</v>
-      </c>
+      <c r="E170" s="12" t="n"/>
+      <c r="F170" s="12" t="n"/>
+      <c r="G170" s="12" t="n"/>
       <c r="H170" s="12" t="n"/>
-      <c r="I170" s="12" t="n">
-        <v>3000</v>
-      </c>
-      <c r="J170" s="12" t="n">
-        <v>2000</v>
-      </c>
+      <c r="I170" s="12" t="n"/>
+      <c r="J170" s="12" t="n"/>
       <c r="K170" s="13">
         <f>E170+F170+G170+H170+I170+J170</f>
         <v/>
@@ -15827,22 +14325,12 @@
         <f>IFERROR(VLOOKUP(C171,▼売上原票!$A:$P,12,0),0)</f>
         <v/>
       </c>
-      <c r="E171" s="12" t="n">
-        <v>15000</v>
-      </c>
-      <c r="F171" s="12" t="n">
-        <v>4000</v>
-      </c>
-      <c r="G171" s="12" t="n">
-        <v>2000</v>
-      </c>
+      <c r="E171" s="12" t="n"/>
+      <c r="F171" s="12" t="n"/>
+      <c r="G171" s="12" t="n"/>
       <c r="H171" s="12" t="n"/>
-      <c r="I171" s="12" t="n">
-        <v>3000</v>
-      </c>
-      <c r="J171" s="12" t="n">
-        <v>2000</v>
-      </c>
+      <c r="I171" s="12" t="n"/>
+      <c r="J171" s="12" t="n"/>
       <c r="K171" s="13">
         <f>E171+F171+G171+H171+I171+J171</f>
         <v/>
@@ -15893,22 +14381,12 @@
         <f>IFERROR(VLOOKUP(C172,▼売上原票!$A:$P,12,0),0)</f>
         <v/>
       </c>
-      <c r="E172" s="12" t="n">
-        <v>15000</v>
-      </c>
-      <c r="F172" s="12" t="n">
-        <v>4000</v>
-      </c>
-      <c r="G172" s="12" t="n">
-        <v>2000</v>
-      </c>
+      <c r="E172" s="12" t="n"/>
+      <c r="F172" s="12" t="n"/>
+      <c r="G172" s="12" t="n"/>
       <c r="H172" s="12" t="n"/>
-      <c r="I172" s="12" t="n">
-        <v>3000</v>
-      </c>
-      <c r="J172" s="12" t="n">
-        <v>2000</v>
-      </c>
+      <c r="I172" s="12" t="n"/>
+      <c r="J172" s="12" t="n"/>
       <c r="K172" s="13">
         <f>E172+F172+G172+H172+I172+J172</f>
         <v/>
@@ -15959,22 +14437,12 @@
         <f>IFERROR(VLOOKUP(C173,▼売上原票!$A:$P,12,0),0)</f>
         <v/>
       </c>
-      <c r="E173" s="12" t="n">
-        <v>15000</v>
-      </c>
-      <c r="F173" s="12" t="n">
-        <v>4000</v>
-      </c>
-      <c r="G173" s="12" t="n">
-        <v>2000</v>
-      </c>
+      <c r="E173" s="12" t="n"/>
+      <c r="F173" s="12" t="n"/>
+      <c r="G173" s="12" t="n"/>
       <c r="H173" s="12" t="n"/>
-      <c r="I173" s="12" t="n">
-        <v>3000</v>
-      </c>
-      <c r="J173" s="12" t="n">
-        <v>2000</v>
-      </c>
+      <c r="I173" s="12" t="n"/>
+      <c r="J173" s="12" t="n"/>
       <c r="K173" s="13">
         <f>E173+F173+G173+H173+I173+J173</f>
         <v/>
@@ -16025,22 +14493,12 @@
         <f>IFERROR(VLOOKUP(C174,▼売上原票!$A:$P,12,0),0)</f>
         <v/>
       </c>
-      <c r="E174" s="12" t="n">
-        <v>15000</v>
-      </c>
-      <c r="F174" s="12" t="n">
-        <v>4000</v>
-      </c>
-      <c r="G174" s="12" t="n">
-        <v>2000</v>
-      </c>
+      <c r="E174" s="12" t="n"/>
+      <c r="F174" s="12" t="n"/>
+      <c r="G174" s="12" t="n"/>
       <c r="H174" s="12" t="n"/>
-      <c r="I174" s="12" t="n">
-        <v>3000</v>
-      </c>
-      <c r="J174" s="12" t="n">
-        <v>2000</v>
-      </c>
+      <c r="I174" s="12" t="n"/>
+      <c r="J174" s="12" t="n"/>
       <c r="K174" s="13">
         <f>E174+F174+G174+H174+I174+J174</f>
         <v/>
@@ -16091,22 +14549,12 @@
         <f>IFERROR(VLOOKUP(C175,▼売上原票!$A:$P,12,0),0)</f>
         <v/>
       </c>
-      <c r="E175" s="12" t="n">
-        <v>15000</v>
-      </c>
-      <c r="F175" s="12" t="n">
-        <v>4000</v>
-      </c>
-      <c r="G175" s="12" t="n">
-        <v>2000</v>
-      </c>
+      <c r="E175" s="12" t="n"/>
+      <c r="F175" s="12" t="n"/>
+      <c r="G175" s="12" t="n"/>
       <c r="H175" s="12" t="n"/>
-      <c r="I175" s="12" t="n">
-        <v>3000</v>
-      </c>
-      <c r="J175" s="12" t="n">
-        <v>2000</v>
-      </c>
+      <c r="I175" s="12" t="n"/>
+      <c r="J175" s="12" t="n"/>
       <c r="K175" s="13">
         <f>E175+F175+G175+H175+I175+J175</f>
         <v/>
@@ -16157,22 +14605,12 @@
         <f>IFERROR(VLOOKUP(C176,▼売上原票!$A:$P,12,0),0)</f>
         <v/>
       </c>
-      <c r="E176" s="12" t="n">
-        <v>15000</v>
-      </c>
-      <c r="F176" s="12" t="n">
-        <v>4000</v>
-      </c>
-      <c r="G176" s="12" t="n">
-        <v>2000</v>
-      </c>
+      <c r="E176" s="12" t="n"/>
+      <c r="F176" s="12" t="n"/>
+      <c r="G176" s="12" t="n"/>
       <c r="H176" s="12" t="n"/>
-      <c r="I176" s="12" t="n">
-        <v>3000</v>
-      </c>
-      <c r="J176" s="12" t="n">
-        <v>2000</v>
-      </c>
+      <c r="I176" s="12" t="n"/>
+      <c r="J176" s="12" t="n"/>
       <c r="K176" s="13">
         <f>E176+F176+G176+H176+I176+J176</f>
         <v/>
@@ -16223,22 +14661,12 @@
         <f>IFERROR(VLOOKUP(C177,▼売上原票!$A:$P,12,0),0)</f>
         <v/>
       </c>
-      <c r="E177" s="12" t="n">
-        <v>15000</v>
-      </c>
-      <c r="F177" s="12" t="n">
-        <v>4000</v>
-      </c>
-      <c r="G177" s="12" t="n">
-        <v>2000</v>
-      </c>
+      <c r="E177" s="12" t="n"/>
+      <c r="F177" s="12" t="n"/>
+      <c r="G177" s="12" t="n"/>
       <c r="H177" s="12" t="n"/>
-      <c r="I177" s="12" t="n">
-        <v>3000</v>
-      </c>
-      <c r="J177" s="12" t="n">
-        <v>2000</v>
-      </c>
+      <c r="I177" s="12" t="n"/>
+      <c r="J177" s="12" t="n"/>
       <c r="K177" s="13">
         <f>E177+F177+G177+H177+I177+J177</f>
         <v/>
@@ -16289,22 +14717,12 @@
         <f>IFERROR(VLOOKUP(C178,▼売上原票!$A:$P,12,0),0)</f>
         <v/>
       </c>
-      <c r="E178" s="12" t="n">
-        <v>15000</v>
-      </c>
-      <c r="F178" s="12" t="n">
-        <v>4000</v>
-      </c>
-      <c r="G178" s="12" t="n">
-        <v>2000</v>
-      </c>
+      <c r="E178" s="12" t="n"/>
+      <c r="F178" s="12" t="n"/>
+      <c r="G178" s="12" t="n"/>
       <c r="H178" s="12" t="n"/>
-      <c r="I178" s="12" t="n">
-        <v>3000</v>
-      </c>
-      <c r="J178" s="12" t="n">
-        <v>2000</v>
-      </c>
+      <c r="I178" s="12" t="n"/>
+      <c r="J178" s="12" t="n"/>
       <c r="K178" s="13">
         <f>E178+F178+G178+H178+I178+J178</f>
         <v/>
@@ -16355,22 +14773,12 @@
         <f>IFERROR(VLOOKUP(C179,▼売上原票!$A:$P,12,0),0)</f>
         <v/>
       </c>
-      <c r="E179" s="12" t="n">
-        <v>15000</v>
-      </c>
-      <c r="F179" s="12" t="n">
-        <v>4000</v>
-      </c>
-      <c r="G179" s="12" t="n">
-        <v>2000</v>
-      </c>
+      <c r="E179" s="12" t="n"/>
+      <c r="F179" s="12" t="n"/>
+      <c r="G179" s="12" t="n"/>
       <c r="H179" s="12" t="n"/>
-      <c r="I179" s="12" t="n">
-        <v>3000</v>
-      </c>
-      <c r="J179" s="12" t="n">
-        <v>2000</v>
-      </c>
+      <c r="I179" s="12" t="n"/>
+      <c r="J179" s="12" t="n"/>
       <c r="K179" s="13">
         <f>E179+F179+G179+H179+I179+J179</f>
         <v/>
@@ -16421,22 +14829,12 @@
         <f>IFERROR(VLOOKUP(C180,▼売上原票!$A:$P,12,0),0)</f>
         <v/>
       </c>
-      <c r="E180" s="12" t="n">
-        <v>15000</v>
-      </c>
-      <c r="F180" s="12" t="n">
-        <v>4000</v>
-      </c>
-      <c r="G180" s="12" t="n">
-        <v>2000</v>
-      </c>
+      <c r="E180" s="12" t="n"/>
+      <c r="F180" s="12" t="n"/>
+      <c r="G180" s="12" t="n"/>
       <c r="H180" s="12" t="n"/>
-      <c r="I180" s="12" t="n">
-        <v>3000</v>
-      </c>
-      <c r="J180" s="12" t="n">
-        <v>2000</v>
-      </c>
+      <c r="I180" s="12" t="n"/>
+      <c r="J180" s="12" t="n"/>
       <c r="K180" s="13">
         <f>E180+F180+G180+H180+I180+J180</f>
         <v/>
@@ -16487,22 +14885,12 @@
         <f>IFERROR(VLOOKUP(C181,▼売上原票!$A:$P,12,0),0)</f>
         <v/>
       </c>
-      <c r="E181" s="12" t="n">
-        <v>15000</v>
-      </c>
-      <c r="F181" s="12" t="n">
-        <v>4000</v>
-      </c>
-      <c r="G181" s="12" t="n">
-        <v>2000</v>
-      </c>
+      <c r="E181" s="12" t="n"/>
+      <c r="F181" s="12" t="n"/>
+      <c r="G181" s="12" t="n"/>
       <c r="H181" s="12" t="n"/>
-      <c r="I181" s="12" t="n">
-        <v>3000</v>
-      </c>
-      <c r="J181" s="12" t="n">
-        <v>2000</v>
-      </c>
+      <c r="I181" s="12" t="n"/>
+      <c r="J181" s="12" t="n"/>
       <c r="K181" s="13">
         <f>E181+F181+G181+H181+I181+J181</f>
         <v/>
@@ -16553,22 +14941,12 @@
         <f>IFERROR(VLOOKUP(C182,▼売上原票!$A:$P,12,0),0)</f>
         <v/>
       </c>
-      <c r="E182" s="12" t="n">
-        <v>15000</v>
-      </c>
-      <c r="F182" s="12" t="n">
-        <v>4000</v>
-      </c>
-      <c r="G182" s="12" t="n">
-        <v>2000</v>
-      </c>
+      <c r="E182" s="12" t="n"/>
+      <c r="F182" s="12" t="n"/>
+      <c r="G182" s="12" t="n"/>
       <c r="H182" s="12" t="n"/>
-      <c r="I182" s="12" t="n">
-        <v>3000</v>
-      </c>
-      <c r="J182" s="12" t="n">
-        <v>2000</v>
-      </c>
+      <c r="I182" s="12" t="n"/>
+      <c r="J182" s="12" t="n"/>
       <c r="K182" s="13">
         <f>E182+F182+G182+H182+I182+J182</f>
         <v/>
@@ -16619,22 +14997,12 @@
         <f>IFERROR(VLOOKUP(C183,▼売上原票!$A:$P,12,0),0)</f>
         <v/>
       </c>
-      <c r="E183" s="12" t="n">
-        <v>15000</v>
-      </c>
-      <c r="F183" s="12" t="n">
-        <v>4000</v>
-      </c>
-      <c r="G183" s="12" t="n">
-        <v>2000</v>
-      </c>
+      <c r="E183" s="12" t="n"/>
+      <c r="F183" s="12" t="n"/>
+      <c r="G183" s="12" t="n"/>
       <c r="H183" s="12" t="n"/>
-      <c r="I183" s="12" t="n">
-        <v>3000</v>
-      </c>
-      <c r="J183" s="12" t="n">
-        <v>2000</v>
-      </c>
+      <c r="I183" s="12" t="n"/>
+      <c r="J183" s="12" t="n"/>
       <c r="K183" s="13">
         <f>E183+F183+G183+H183+I183+J183</f>
         <v/>
@@ -16704,22 +15072,12 @@
         <f>IFERROR(VLOOKUP(C185,▼売上原票!$A:$P,13,0),0)</f>
         <v/>
       </c>
-      <c r="E185" s="12" t="n">
-        <v>35000</v>
-      </c>
-      <c r="F185" s="12" t="n">
-        <v>10000</v>
-      </c>
-      <c r="G185" s="12" t="n">
-        <v>5000</v>
-      </c>
+      <c r="E185" s="12" t="n"/>
+      <c r="F185" s="12" t="n"/>
+      <c r="G185" s="12" t="n"/>
       <c r="H185" s="12" t="n"/>
-      <c r="I185" s="12" t="n">
-        <v>8000</v>
-      </c>
-      <c r="J185" s="12" t="n">
-        <v>5000</v>
-      </c>
+      <c r="I185" s="12" t="n"/>
+      <c r="J185" s="12" t="n"/>
       <c r="K185" s="13">
         <f>E185+F185+G185+H185+I185+J185</f>
         <v/>
@@ -16771,22 +15129,12 @@
         <f>IFERROR(VLOOKUP(C186,▼売上原票!$A:$P,13,0),0)</f>
         <v/>
       </c>
-      <c r="E186" s="12" t="n">
-        <v>35000</v>
-      </c>
-      <c r="F186" s="12" t="n">
-        <v>10000</v>
-      </c>
-      <c r="G186" s="12" t="n">
-        <v>5000</v>
-      </c>
+      <c r="E186" s="12" t="n"/>
+      <c r="F186" s="12" t="n"/>
+      <c r="G186" s="12" t="n"/>
       <c r="H186" s="12" t="n"/>
-      <c r="I186" s="12" t="n">
-        <v>8000</v>
-      </c>
-      <c r="J186" s="12" t="n">
-        <v>5000</v>
-      </c>
+      <c r="I186" s="12" t="n"/>
+      <c r="J186" s="12" t="n"/>
       <c r="K186" s="13">
         <f>E186+F186+G186+H186+I186+J186</f>
         <v/>
@@ -16837,22 +15185,12 @@
         <f>IFERROR(VLOOKUP(C187,▼売上原票!$A:$P,13,0),0)</f>
         <v/>
       </c>
-      <c r="E187" s="12" t="n">
-        <v>35000</v>
-      </c>
-      <c r="F187" s="12" t="n">
-        <v>10000</v>
-      </c>
-      <c r="G187" s="12" t="n">
-        <v>5000</v>
-      </c>
+      <c r="E187" s="12" t="n"/>
+      <c r="F187" s="12" t="n"/>
+      <c r="G187" s="12" t="n"/>
       <c r="H187" s="12" t="n"/>
-      <c r="I187" s="12" t="n">
-        <v>8000</v>
-      </c>
-      <c r="J187" s="12" t="n">
-        <v>5000</v>
-      </c>
+      <c r="I187" s="12" t="n"/>
+      <c r="J187" s="12" t="n"/>
       <c r="K187" s="13">
         <f>E187+F187+G187+H187+I187+J187</f>
         <v/>
@@ -16903,22 +15241,12 @@
         <f>IFERROR(VLOOKUP(C188,▼売上原票!$A:$P,13,0),0)</f>
         <v/>
       </c>
-      <c r="E188" s="12" t="n">
-        <v>35000</v>
-      </c>
-      <c r="F188" s="12" t="n">
-        <v>10000</v>
-      </c>
-      <c r="G188" s="12" t="n">
-        <v>5000</v>
-      </c>
+      <c r="E188" s="12" t="n"/>
+      <c r="F188" s="12" t="n"/>
+      <c r="G188" s="12" t="n"/>
       <c r="H188" s="12" t="n"/>
-      <c r="I188" s="12" t="n">
-        <v>8000</v>
-      </c>
-      <c r="J188" s="12" t="n">
-        <v>5000</v>
-      </c>
+      <c r="I188" s="12" t="n"/>
+      <c r="J188" s="12" t="n"/>
       <c r="K188" s="13">
         <f>E188+F188+G188+H188+I188+J188</f>
         <v/>
@@ -16969,22 +15297,12 @@
         <f>IFERROR(VLOOKUP(C189,▼売上原票!$A:$P,13,0),0)</f>
         <v/>
       </c>
-      <c r="E189" s="12" t="n">
-        <v>35000</v>
-      </c>
-      <c r="F189" s="12" t="n">
-        <v>10000</v>
-      </c>
-      <c r="G189" s="12" t="n">
-        <v>5000</v>
-      </c>
+      <c r="E189" s="12" t="n"/>
+      <c r="F189" s="12" t="n"/>
+      <c r="G189" s="12" t="n"/>
       <c r="H189" s="12" t="n"/>
-      <c r="I189" s="12" t="n">
-        <v>8000</v>
-      </c>
-      <c r="J189" s="12" t="n">
-        <v>5000</v>
-      </c>
+      <c r="I189" s="12" t="n"/>
+      <c r="J189" s="12" t="n"/>
       <c r="K189" s="13">
         <f>E189+F189+G189+H189+I189+J189</f>
         <v/>
@@ -17035,22 +15353,12 @@
         <f>IFERROR(VLOOKUP(C190,▼売上原票!$A:$P,13,0),0)</f>
         <v/>
       </c>
-      <c r="E190" s="12" t="n">
-        <v>35000</v>
-      </c>
-      <c r="F190" s="12" t="n">
-        <v>10000</v>
-      </c>
-      <c r="G190" s="12" t="n">
-        <v>5000</v>
-      </c>
+      <c r="E190" s="12" t="n"/>
+      <c r="F190" s="12" t="n"/>
+      <c r="G190" s="12" t="n"/>
       <c r="H190" s="12" t="n"/>
-      <c r="I190" s="12" t="n">
-        <v>8000</v>
-      </c>
-      <c r="J190" s="12" t="n">
-        <v>5000</v>
-      </c>
+      <c r="I190" s="12" t="n"/>
+      <c r="J190" s="12" t="n"/>
       <c r="K190" s="13">
         <f>E190+F190+G190+H190+I190+J190</f>
         <v/>
@@ -17101,22 +15409,12 @@
         <f>IFERROR(VLOOKUP(C191,▼売上原票!$A:$P,13,0),0)</f>
         <v/>
       </c>
-      <c r="E191" s="12" t="n">
-        <v>35000</v>
-      </c>
-      <c r="F191" s="12" t="n">
-        <v>10000</v>
-      </c>
-      <c r="G191" s="12" t="n">
-        <v>5000</v>
-      </c>
+      <c r="E191" s="12" t="n"/>
+      <c r="F191" s="12" t="n"/>
+      <c r="G191" s="12" t="n"/>
       <c r="H191" s="12" t="n"/>
-      <c r="I191" s="12" t="n">
-        <v>8000</v>
-      </c>
-      <c r="J191" s="12" t="n">
-        <v>5000</v>
-      </c>
+      <c r="I191" s="12" t="n"/>
+      <c r="J191" s="12" t="n"/>
       <c r="K191" s="13">
         <f>E191+F191+G191+H191+I191+J191</f>
         <v/>
@@ -17167,22 +15465,12 @@
         <f>IFERROR(VLOOKUP(C192,▼売上原票!$A:$P,13,0),0)</f>
         <v/>
       </c>
-      <c r="E192" s="12" t="n">
-        <v>35000</v>
-      </c>
-      <c r="F192" s="12" t="n">
-        <v>10000</v>
-      </c>
-      <c r="G192" s="12" t="n">
-        <v>5000</v>
-      </c>
+      <c r="E192" s="12" t="n"/>
+      <c r="F192" s="12" t="n"/>
+      <c r="G192" s="12" t="n"/>
       <c r="H192" s="12" t="n"/>
-      <c r="I192" s="12" t="n">
-        <v>8000</v>
-      </c>
-      <c r="J192" s="12" t="n">
-        <v>5000</v>
-      </c>
+      <c r="I192" s="12" t="n"/>
+      <c r="J192" s="12" t="n"/>
       <c r="K192" s="13">
         <f>E192+F192+G192+H192+I192+J192</f>
         <v/>
@@ -17233,22 +15521,12 @@
         <f>IFERROR(VLOOKUP(C193,▼売上原票!$A:$P,13,0),0)</f>
         <v/>
       </c>
-      <c r="E193" s="12" t="n">
-        <v>35000</v>
-      </c>
-      <c r="F193" s="12" t="n">
-        <v>10000</v>
-      </c>
-      <c r="G193" s="12" t="n">
-        <v>5000</v>
-      </c>
+      <c r="E193" s="12" t="n"/>
+      <c r="F193" s="12" t="n"/>
+      <c r="G193" s="12" t="n"/>
       <c r="H193" s="12" t="n"/>
-      <c r="I193" s="12" t="n">
-        <v>8000</v>
-      </c>
-      <c r="J193" s="12" t="n">
-        <v>5000</v>
-      </c>
+      <c r="I193" s="12" t="n"/>
+      <c r="J193" s="12" t="n"/>
       <c r="K193" s="13">
         <f>E193+F193+G193+H193+I193+J193</f>
         <v/>
@@ -17299,22 +15577,12 @@
         <f>IFERROR(VLOOKUP(C194,▼売上原票!$A:$P,13,0),0)</f>
         <v/>
       </c>
-      <c r="E194" s="12" t="n">
-        <v>35000</v>
-      </c>
-      <c r="F194" s="12" t="n">
-        <v>10000</v>
-      </c>
-      <c r="G194" s="12" t="n">
-        <v>5000</v>
-      </c>
+      <c r="E194" s="12" t="n"/>
+      <c r="F194" s="12" t="n"/>
+      <c r="G194" s="12" t="n"/>
       <c r="H194" s="12" t="n"/>
-      <c r="I194" s="12" t="n">
-        <v>8000</v>
-      </c>
-      <c r="J194" s="12" t="n">
-        <v>5000</v>
-      </c>
+      <c r="I194" s="12" t="n"/>
+      <c r="J194" s="12" t="n"/>
       <c r="K194" s="13">
         <f>E194+F194+G194+H194+I194+J194</f>
         <v/>
@@ -17365,22 +15633,12 @@
         <f>IFERROR(VLOOKUP(C195,▼売上原票!$A:$P,13,0),0)</f>
         <v/>
       </c>
-      <c r="E195" s="12" t="n">
-        <v>35000</v>
-      </c>
-      <c r="F195" s="12" t="n">
-        <v>10000</v>
-      </c>
-      <c r="G195" s="12" t="n">
-        <v>5000</v>
-      </c>
+      <c r="E195" s="12" t="n"/>
+      <c r="F195" s="12" t="n"/>
+      <c r="G195" s="12" t="n"/>
       <c r="H195" s="12" t="n"/>
-      <c r="I195" s="12" t="n">
-        <v>8000</v>
-      </c>
-      <c r="J195" s="12" t="n">
-        <v>5000</v>
-      </c>
+      <c r="I195" s="12" t="n"/>
+      <c r="J195" s="12" t="n"/>
       <c r="K195" s="13">
         <f>E195+F195+G195+H195+I195+J195</f>
         <v/>
@@ -17431,22 +15689,12 @@
         <f>IFERROR(VLOOKUP(C196,▼売上原票!$A:$P,13,0),0)</f>
         <v/>
       </c>
-      <c r="E196" s="12" t="n">
-        <v>35000</v>
-      </c>
-      <c r="F196" s="12" t="n">
-        <v>10000</v>
-      </c>
-      <c r="G196" s="12" t="n">
-        <v>5000</v>
-      </c>
+      <c r="E196" s="12" t="n"/>
+      <c r="F196" s="12" t="n"/>
+      <c r="G196" s="12" t="n"/>
       <c r="H196" s="12" t="n"/>
-      <c r="I196" s="12" t="n">
-        <v>8000</v>
-      </c>
-      <c r="J196" s="12" t="n">
-        <v>5000</v>
-      </c>
+      <c r="I196" s="12" t="n"/>
+      <c r="J196" s="12" t="n"/>
       <c r="K196" s="13">
         <f>E196+F196+G196+H196+I196+J196</f>
         <v/>
@@ -17497,22 +15745,12 @@
         <f>IFERROR(VLOOKUP(C197,▼売上原票!$A:$P,13,0),0)</f>
         <v/>
       </c>
-      <c r="E197" s="12" t="n">
-        <v>35000</v>
-      </c>
-      <c r="F197" s="12" t="n">
-        <v>10000</v>
-      </c>
-      <c r="G197" s="12" t="n">
-        <v>5000</v>
-      </c>
+      <c r="E197" s="12" t="n"/>
+      <c r="F197" s="12" t="n"/>
+      <c r="G197" s="12" t="n"/>
       <c r="H197" s="12" t="n"/>
-      <c r="I197" s="12" t="n">
-        <v>8000</v>
-      </c>
-      <c r="J197" s="12" t="n">
-        <v>5000</v>
-      </c>
+      <c r="I197" s="12" t="n"/>
+      <c r="J197" s="12" t="n"/>
       <c r="K197" s="13">
         <f>E197+F197+G197+H197+I197+J197</f>
         <v/>
@@ -17563,22 +15801,12 @@
         <f>IFERROR(VLOOKUP(C198,▼売上原票!$A:$P,13,0),0)</f>
         <v/>
       </c>
-      <c r="E198" s="12" t="n">
-        <v>35000</v>
-      </c>
-      <c r="F198" s="12" t="n">
-        <v>10000</v>
-      </c>
-      <c r="G198" s="12" t="n">
-        <v>5000</v>
-      </c>
+      <c r="E198" s="12" t="n"/>
+      <c r="F198" s="12" t="n"/>
+      <c r="G198" s="12" t="n"/>
       <c r="H198" s="12" t="n"/>
-      <c r="I198" s="12" t="n">
-        <v>8000</v>
-      </c>
-      <c r="J198" s="12" t="n">
-        <v>5000</v>
-      </c>
+      <c r="I198" s="12" t="n"/>
+      <c r="J198" s="12" t="n"/>
       <c r="K198" s="13">
         <f>E198+F198+G198+H198+I198+J198</f>
         <v/>
@@ -17629,22 +15857,12 @@
         <f>IFERROR(VLOOKUP(C199,▼売上原票!$A:$P,13,0),0)</f>
         <v/>
       </c>
-      <c r="E199" s="12" t="n">
-        <v>35000</v>
-      </c>
-      <c r="F199" s="12" t="n">
-        <v>10000</v>
-      </c>
-      <c r="G199" s="12" t="n">
-        <v>5000</v>
-      </c>
+      <c r="E199" s="12" t="n"/>
+      <c r="F199" s="12" t="n"/>
+      <c r="G199" s="12" t="n"/>
       <c r="H199" s="12" t="n"/>
-      <c r="I199" s="12" t="n">
-        <v>8000</v>
-      </c>
-      <c r="J199" s="12" t="n">
-        <v>5000</v>
-      </c>
+      <c r="I199" s="12" t="n"/>
+      <c r="J199" s="12" t="n"/>
       <c r="K199" s="13">
         <f>E199+F199+G199+H199+I199+J199</f>
         <v/>
@@ -17695,22 +15913,12 @@
         <f>IFERROR(VLOOKUP(C200,▼売上原票!$A:$P,13,0),0)</f>
         <v/>
       </c>
-      <c r="E200" s="12" t="n">
-        <v>35000</v>
-      </c>
-      <c r="F200" s="12" t="n">
-        <v>10000</v>
-      </c>
-      <c r="G200" s="12" t="n">
-        <v>5000</v>
-      </c>
+      <c r="E200" s="12" t="n"/>
+      <c r="F200" s="12" t="n"/>
+      <c r="G200" s="12" t="n"/>
       <c r="H200" s="12" t="n"/>
-      <c r="I200" s="12" t="n">
-        <v>8000</v>
-      </c>
-      <c r="J200" s="12" t="n">
-        <v>5000</v>
-      </c>
+      <c r="I200" s="12" t="n"/>
+      <c r="J200" s="12" t="n"/>
       <c r="K200" s="13">
         <f>E200+F200+G200+H200+I200+J200</f>
         <v/>
@@ -17761,22 +15969,12 @@
         <f>IFERROR(VLOOKUP(C201,▼売上原票!$A:$P,13,0),0)</f>
         <v/>
       </c>
-      <c r="E201" s="12" t="n">
-        <v>35000</v>
-      </c>
-      <c r="F201" s="12" t="n">
-        <v>10000</v>
-      </c>
-      <c r="G201" s="12" t="n">
-        <v>5000</v>
-      </c>
+      <c r="E201" s="12" t="n"/>
+      <c r="F201" s="12" t="n"/>
+      <c r="G201" s="12" t="n"/>
       <c r="H201" s="12" t="n"/>
-      <c r="I201" s="12" t="n">
-        <v>8000</v>
-      </c>
-      <c r="J201" s="12" t="n">
-        <v>5000</v>
-      </c>
+      <c r="I201" s="12" t="n"/>
+      <c r="J201" s="12" t="n"/>
       <c r="K201" s="13">
         <f>E201+F201+G201+H201+I201+J201</f>
         <v/>

--- a/sacure_採算管理_v4_ルート別案件別.xlsx
+++ b/sacure_採算管理_v4_ルート別案件別.xlsx
@@ -5352,7 +5352,10 @@
         <f>IFERROR(VLOOKUP(C5,▼売上原票!$A:$P,3,0),0)</f>
         <v/>
       </c>
-      <c r="E5" s="12" t="n"/>
+      <c r="E5" s="32">
+        <f>SUMPRODUCT((▼従業員マスター!$A$6:$A$300="本社")*(▼従業員マスター!$G$6:$G$300="直接")*▼従業員マスター!$F$6:$F$300)</f>
+        <v/>
+      </c>
       <c r="F5" s="12" t="n"/>
       <c r="G5" s="12" t="n"/>
       <c r="H5" s="12" t="n"/>
@@ -5409,7 +5412,10 @@
         <f>IFERROR(VLOOKUP(C6,▼売上原票!$A:$P,3,0),0)</f>
         <v/>
       </c>
-      <c r="E6" s="12" t="n"/>
+      <c r="E6" s="32">
+        <f>SUMPRODUCT((▼従業員マスター!$A$6:$A$300="本社")*(▼従業員マスター!$G$6:$G$300="直接")*▼従業員マスター!$F$6:$F$300)</f>
+        <v/>
+      </c>
       <c r="F6" s="12" t="n"/>
       <c r="G6" s="12" t="n"/>
       <c r="H6" s="12" t="n"/>
@@ -5465,7 +5471,10 @@
         <f>IFERROR(VLOOKUP(C7,▼売上原票!$A:$P,3,0),0)</f>
         <v/>
       </c>
-      <c r="E7" s="12" t="n"/>
+      <c r="E7" s="32">
+        <f>SUMPRODUCT((▼従業員マスター!$A$6:$A$300="本社")*(▼従業員マスター!$G$6:$G$300="直接")*▼従業員マスター!$F$6:$F$300)</f>
+        <v/>
+      </c>
       <c r="F7" s="12" t="n"/>
       <c r="G7" s="12" t="n"/>
       <c r="H7" s="12" t="n"/>
@@ -5521,7 +5530,10 @@
         <f>IFERROR(VLOOKUP(C8,▼売上原票!$A:$P,3,0),0)</f>
         <v/>
       </c>
-      <c r="E8" s="12" t="n"/>
+      <c r="E8" s="32">
+        <f>SUMPRODUCT((▼従業員マスター!$A$6:$A$300="本社")*(▼従業員マスター!$G$6:$G$300="直接")*▼従業員マスター!$F$6:$F$300)</f>
+        <v/>
+      </c>
       <c r="F8" s="12" t="n"/>
       <c r="G8" s="12" t="n"/>
       <c r="H8" s="12" t="n"/>
@@ -5577,7 +5589,10 @@
         <f>IFERROR(VLOOKUP(C9,▼売上原票!$A:$P,3,0),0)</f>
         <v/>
       </c>
-      <c r="E9" s="12" t="n"/>
+      <c r="E9" s="32">
+        <f>SUMPRODUCT((▼従業員マスター!$A$6:$A$300="本社")*(▼従業員マスター!$G$6:$G$300="直接")*▼従業員マスター!$F$6:$F$300)</f>
+        <v/>
+      </c>
       <c r="F9" s="12" t="n"/>
       <c r="G9" s="12" t="n"/>
       <c r="H9" s="12" t="n"/>
@@ -5633,7 +5648,10 @@
         <f>IFERROR(VLOOKUP(C10,▼売上原票!$A:$P,3,0),0)</f>
         <v/>
       </c>
-      <c r="E10" s="12" t="n"/>
+      <c r="E10" s="32">
+        <f>SUMPRODUCT((▼従業員マスター!$A$6:$A$300="本社")*(▼従業員マスター!$G$6:$G$300="直接")*▼従業員マスター!$F$6:$F$300)</f>
+        <v/>
+      </c>
       <c r="F10" s="12" t="n"/>
       <c r="G10" s="12" t="n"/>
       <c r="H10" s="12" t="n"/>
@@ -5689,7 +5707,10 @@
         <f>IFERROR(VLOOKUP(C11,▼売上原票!$A:$P,3,0),0)</f>
         <v/>
       </c>
-      <c r="E11" s="12" t="n"/>
+      <c r="E11" s="32">
+        <f>SUMPRODUCT((▼従業員マスター!$A$6:$A$300="本社")*(▼従業員マスター!$G$6:$G$300="直接")*▼従業員マスター!$F$6:$F$300)</f>
+        <v/>
+      </c>
       <c r="F11" s="12" t="n"/>
       <c r="G11" s="12" t="n"/>
       <c r="H11" s="12" t="n"/>
@@ -5745,7 +5766,10 @@
         <f>IFERROR(VLOOKUP(C12,▼売上原票!$A:$P,3,0),0)</f>
         <v/>
       </c>
-      <c r="E12" s="12" t="n"/>
+      <c r="E12" s="32">
+        <f>SUMPRODUCT((▼従業員マスター!$A$6:$A$300="本社")*(▼従業員マスター!$G$6:$G$300="直接")*▼従業員マスター!$F$6:$F$300)</f>
+        <v/>
+      </c>
       <c r="F12" s="12" t="n"/>
       <c r="G12" s="12" t="n"/>
       <c r="H12" s="12" t="n"/>
@@ -5801,7 +5825,10 @@
         <f>IFERROR(VLOOKUP(C13,▼売上原票!$A:$P,3,0),0)</f>
         <v/>
       </c>
-      <c r="E13" s="12" t="n"/>
+      <c r="E13" s="32">
+        <f>SUMPRODUCT((▼従業員マスター!$A$6:$A$300="本社")*(▼従業員マスター!$G$6:$G$300="直接")*▼従業員マスター!$F$6:$F$300)</f>
+        <v/>
+      </c>
       <c r="F13" s="12" t="n"/>
       <c r="G13" s="12" t="n"/>
       <c r="H13" s="12" t="n"/>
@@ -5857,7 +5884,10 @@
         <f>IFERROR(VLOOKUP(C14,▼売上原票!$A:$P,3,0),0)</f>
         <v/>
       </c>
-      <c r="E14" s="12" t="n"/>
+      <c r="E14" s="32">
+        <f>SUMPRODUCT((▼従業員マスター!$A$6:$A$300="本社")*(▼従業員マスター!$G$6:$G$300="直接")*▼従業員マスター!$F$6:$F$300)</f>
+        <v/>
+      </c>
       <c r="F14" s="12" t="n"/>
       <c r="G14" s="12" t="n"/>
       <c r="H14" s="12" t="n"/>
@@ -5913,7 +5943,10 @@
         <f>IFERROR(VLOOKUP(C15,▼売上原票!$A:$P,3,0),0)</f>
         <v/>
       </c>
-      <c r="E15" s="12" t="n"/>
+      <c r="E15" s="32">
+        <f>SUMPRODUCT((▼従業員マスター!$A$6:$A$300="本社")*(▼従業員マスター!$G$6:$G$300="直接")*▼従業員マスター!$F$6:$F$300)</f>
+        <v/>
+      </c>
       <c r="F15" s="12" t="n"/>
       <c r="G15" s="12" t="n"/>
       <c r="H15" s="12" t="n"/>
@@ -5969,7 +6002,10 @@
         <f>IFERROR(VLOOKUP(C16,▼売上原票!$A:$P,3,0),0)</f>
         <v/>
       </c>
-      <c r="E16" s="12" t="n"/>
+      <c r="E16" s="32">
+        <f>SUMPRODUCT((▼従業員マスター!$A$6:$A$300="本社")*(▼従業員マスター!$G$6:$G$300="直接")*▼従業員マスター!$F$6:$F$300)</f>
+        <v/>
+      </c>
       <c r="F16" s="12" t="n"/>
       <c r="G16" s="12" t="n"/>
       <c r="H16" s="12" t="n"/>
@@ -6025,7 +6061,10 @@
         <f>IFERROR(VLOOKUP(C17,▼売上原票!$A:$P,3,0),0)</f>
         <v/>
       </c>
-      <c r="E17" s="12" t="n"/>
+      <c r="E17" s="32">
+        <f>SUMPRODUCT((▼従業員マスター!$A$6:$A$300="本社")*(▼従業員マスター!$G$6:$G$300="直接")*▼従業員マスター!$F$6:$F$300)</f>
+        <v/>
+      </c>
       <c r="F17" s="12" t="n"/>
       <c r="G17" s="12" t="n"/>
       <c r="H17" s="12" t="n"/>
@@ -6081,7 +6120,10 @@
         <f>IFERROR(VLOOKUP(C18,▼売上原票!$A:$P,3,0),0)</f>
         <v/>
       </c>
-      <c r="E18" s="12" t="n"/>
+      <c r="E18" s="32">
+        <f>SUMPRODUCT((▼従業員マスター!$A$6:$A$300="本社")*(▼従業員マスター!$G$6:$G$300="直接")*▼従業員マスター!$F$6:$F$300)</f>
+        <v/>
+      </c>
       <c r="F18" s="12" t="n"/>
       <c r="G18" s="12" t="n"/>
       <c r="H18" s="12" t="n"/>
@@ -6137,7 +6179,10 @@
         <f>IFERROR(VLOOKUP(C19,▼売上原票!$A:$P,3,0),0)</f>
         <v/>
       </c>
-      <c r="E19" s="12" t="n"/>
+      <c r="E19" s="32">
+        <f>SUMPRODUCT((▼従業員マスター!$A$6:$A$300="本社")*(▼従業員マスター!$G$6:$G$300="直接")*▼従業員マスター!$F$6:$F$300)</f>
+        <v/>
+      </c>
       <c r="F19" s="12" t="n"/>
       <c r="G19" s="12" t="n"/>
       <c r="H19" s="12" t="n"/>
@@ -6193,7 +6238,10 @@
         <f>IFERROR(VLOOKUP(C20,▼売上原票!$A:$P,3,0),0)</f>
         <v/>
       </c>
-      <c r="E20" s="12" t="n"/>
+      <c r="E20" s="32">
+        <f>SUMPRODUCT((▼従業員マスター!$A$6:$A$300="本社")*(▼従業員マスター!$G$6:$G$300="直接")*▼従業員マスター!$F$6:$F$300)</f>
+        <v/>
+      </c>
       <c r="F20" s="12" t="n"/>
       <c r="G20" s="12" t="n"/>
       <c r="H20" s="12" t="n"/>
@@ -6249,7 +6297,10 @@
         <f>IFERROR(VLOOKUP(C21,▼売上原票!$A:$P,3,0),0)</f>
         <v/>
       </c>
-      <c r="E21" s="12" t="n"/>
+      <c r="E21" s="32">
+        <f>SUMPRODUCT((▼従業員マスター!$A$6:$A$300="本社")*(▼従業員マスター!$G$6:$G$300="直接")*▼従業員マスター!$F$6:$F$300)</f>
+        <v/>
+      </c>
       <c r="F21" s="12" t="n"/>
       <c r="G21" s="12" t="n"/>
       <c r="H21" s="12" t="n"/>
@@ -6324,7 +6375,10 @@
         <f>IFERROR(VLOOKUP(C23,▼売上原票!$A:$P,4,0),0)</f>
         <v/>
       </c>
-      <c r="E23" s="12" t="n"/>
+      <c r="E23" s="32">
+        <f>SUMPRODUCT((▼従業員マスター!$A$6:$A$300="埼玉")*(▼従業員マスター!$G$6:$G$300="直接")*▼従業員マスター!$F$6:$F$300)</f>
+        <v/>
+      </c>
       <c r="F23" s="12" t="n"/>
       <c r="G23" s="12" t="n"/>
       <c r="H23" s="12" t="n"/>
@@ -6381,7 +6435,10 @@
         <f>IFERROR(VLOOKUP(C24,▼売上原票!$A:$P,4,0),0)</f>
         <v/>
       </c>
-      <c r="E24" s="12" t="n"/>
+      <c r="E24" s="32">
+        <f>SUMPRODUCT((▼従業員マスター!$A$6:$A$300="埼玉")*(▼従業員マスター!$G$6:$G$300="直接")*▼従業員マスター!$F$6:$F$300)</f>
+        <v/>
+      </c>
       <c r="F24" s="12" t="n"/>
       <c r="G24" s="12" t="n"/>
       <c r="H24" s="12" t="n"/>
@@ -6437,7 +6494,10 @@
         <f>IFERROR(VLOOKUP(C25,▼売上原票!$A:$P,4,0),0)</f>
         <v/>
       </c>
-      <c r="E25" s="12" t="n"/>
+      <c r="E25" s="32">
+        <f>SUMPRODUCT((▼従業員マスター!$A$6:$A$300="埼玉")*(▼従業員マスター!$G$6:$G$300="直接")*▼従業員マスター!$F$6:$F$300)</f>
+        <v/>
+      </c>
       <c r="F25" s="12" t="n"/>
       <c r="G25" s="12" t="n"/>
       <c r="H25" s="12" t="n"/>
@@ -6493,7 +6553,10 @@
         <f>IFERROR(VLOOKUP(C26,▼売上原票!$A:$P,4,0),0)</f>
         <v/>
       </c>
-      <c r="E26" s="12" t="n"/>
+      <c r="E26" s="32">
+        <f>SUMPRODUCT((▼従業員マスター!$A$6:$A$300="埼玉")*(▼従業員マスター!$G$6:$G$300="直接")*▼従業員マスター!$F$6:$F$300)</f>
+        <v/>
+      </c>
       <c r="F26" s="12" t="n"/>
       <c r="G26" s="12" t="n"/>
       <c r="H26" s="12" t="n"/>
@@ -6549,7 +6612,10 @@
         <f>IFERROR(VLOOKUP(C27,▼売上原票!$A:$P,4,0),0)</f>
         <v/>
       </c>
-      <c r="E27" s="12" t="n"/>
+      <c r="E27" s="32">
+        <f>SUMPRODUCT((▼従業員マスター!$A$6:$A$300="埼玉")*(▼従業員マスター!$G$6:$G$300="直接")*▼従業員マスター!$F$6:$F$300)</f>
+        <v/>
+      </c>
       <c r="F27" s="12" t="n"/>
       <c r="G27" s="12" t="n"/>
       <c r="H27" s="12" t="n"/>
@@ -6605,7 +6671,10 @@
         <f>IFERROR(VLOOKUP(C28,▼売上原票!$A:$P,4,0),0)</f>
         <v/>
       </c>
-      <c r="E28" s="12" t="n"/>
+      <c r="E28" s="32">
+        <f>SUMPRODUCT((▼従業員マスター!$A$6:$A$300="埼玉")*(▼従業員マスター!$G$6:$G$300="直接")*▼従業員マスター!$F$6:$F$300)</f>
+        <v/>
+      </c>
       <c r="F28" s="12" t="n"/>
       <c r="G28" s="12" t="n"/>
       <c r="H28" s="12" t="n"/>
@@ -6661,7 +6730,10 @@
         <f>IFERROR(VLOOKUP(C29,▼売上原票!$A:$P,4,0),0)</f>
         <v/>
       </c>
-      <c r="E29" s="12" t="n"/>
+      <c r="E29" s="32">
+        <f>SUMPRODUCT((▼従業員マスター!$A$6:$A$300="埼玉")*(▼従業員マスター!$G$6:$G$300="直接")*▼従業員マスター!$F$6:$F$300)</f>
+        <v/>
+      </c>
       <c r="F29" s="12" t="n"/>
       <c r="G29" s="12" t="n"/>
       <c r="H29" s="12" t="n"/>
@@ -6717,7 +6789,10 @@
         <f>IFERROR(VLOOKUP(C30,▼売上原票!$A:$P,4,0),0)</f>
         <v/>
       </c>
-      <c r="E30" s="12" t="n"/>
+      <c r="E30" s="32">
+        <f>SUMPRODUCT((▼従業員マスター!$A$6:$A$300="埼玉")*(▼従業員マスター!$G$6:$G$300="直接")*▼従業員マスター!$F$6:$F$300)</f>
+        <v/>
+      </c>
       <c r="F30" s="12" t="n"/>
       <c r="G30" s="12" t="n"/>
       <c r="H30" s="12" t="n"/>
@@ -6773,7 +6848,10 @@
         <f>IFERROR(VLOOKUP(C31,▼売上原票!$A:$P,4,0),0)</f>
         <v/>
       </c>
-      <c r="E31" s="12" t="n"/>
+      <c r="E31" s="32">
+        <f>SUMPRODUCT((▼従業員マスター!$A$6:$A$300="埼玉")*(▼従業員マスター!$G$6:$G$300="直接")*▼従業員マスター!$F$6:$F$300)</f>
+        <v/>
+      </c>
       <c r="F31" s="12" t="n"/>
       <c r="G31" s="12" t="n"/>
       <c r="H31" s="12" t="n"/>
@@ -6829,7 +6907,10 @@
         <f>IFERROR(VLOOKUP(C32,▼売上原票!$A:$P,4,0),0)</f>
         <v/>
       </c>
-      <c r="E32" s="12" t="n"/>
+      <c r="E32" s="32">
+        <f>SUMPRODUCT((▼従業員マスター!$A$6:$A$300="埼玉")*(▼従業員マスター!$G$6:$G$300="直接")*▼従業員マスター!$F$6:$F$300)</f>
+        <v/>
+      </c>
       <c r="F32" s="12" t="n"/>
       <c r="G32" s="12" t="n"/>
       <c r="H32" s="12" t="n"/>
@@ -6885,7 +6966,10 @@
         <f>IFERROR(VLOOKUP(C33,▼売上原票!$A:$P,4,0),0)</f>
         <v/>
       </c>
-      <c r="E33" s="12" t="n"/>
+      <c r="E33" s="32">
+        <f>SUMPRODUCT((▼従業員マスター!$A$6:$A$300="埼玉")*(▼従業員マスター!$G$6:$G$300="直接")*▼従業員マスター!$F$6:$F$300)</f>
+        <v/>
+      </c>
       <c r="F33" s="12" t="n"/>
       <c r="G33" s="12" t="n"/>
       <c r="H33" s="12" t="n"/>
@@ -6941,7 +7025,10 @@
         <f>IFERROR(VLOOKUP(C34,▼売上原票!$A:$P,4,0),0)</f>
         <v/>
       </c>
-      <c r="E34" s="12" t="n"/>
+      <c r="E34" s="32">
+        <f>SUMPRODUCT((▼従業員マスター!$A$6:$A$300="埼玉")*(▼従業員マスター!$G$6:$G$300="直接")*▼従業員マスター!$F$6:$F$300)</f>
+        <v/>
+      </c>
       <c r="F34" s="12" t="n"/>
       <c r="G34" s="12" t="n"/>
       <c r="H34" s="12" t="n"/>
@@ -6997,7 +7084,10 @@
         <f>IFERROR(VLOOKUP(C35,▼売上原票!$A:$P,4,0),0)</f>
         <v/>
       </c>
-      <c r="E35" s="12" t="n"/>
+      <c r="E35" s="32">
+        <f>SUMPRODUCT((▼従業員マスター!$A$6:$A$300="埼玉")*(▼従業員マスター!$G$6:$G$300="直接")*▼従業員マスター!$F$6:$F$300)</f>
+        <v/>
+      </c>
       <c r="F35" s="12" t="n"/>
       <c r="G35" s="12" t="n"/>
       <c r="H35" s="12" t="n"/>
@@ -7053,7 +7143,10 @@
         <f>IFERROR(VLOOKUP(C36,▼売上原票!$A:$P,4,0),0)</f>
         <v/>
       </c>
-      <c r="E36" s="12" t="n"/>
+      <c r="E36" s="32">
+        <f>SUMPRODUCT((▼従業員マスター!$A$6:$A$300="埼玉")*(▼従業員マスター!$G$6:$G$300="直接")*▼従業員マスター!$F$6:$F$300)</f>
+        <v/>
+      </c>
       <c r="F36" s="12" t="n"/>
       <c r="G36" s="12" t="n"/>
       <c r="H36" s="12" t="n"/>
@@ -7109,7 +7202,10 @@
         <f>IFERROR(VLOOKUP(C37,▼売上原票!$A:$P,4,0),0)</f>
         <v/>
       </c>
-      <c r="E37" s="12" t="n"/>
+      <c r="E37" s="32">
+        <f>SUMPRODUCT((▼従業員マスター!$A$6:$A$300="埼玉")*(▼従業員マスター!$G$6:$G$300="直接")*▼従業員マスター!$F$6:$F$300)</f>
+        <v/>
+      </c>
       <c r="F37" s="12" t="n"/>
       <c r="G37" s="12" t="n"/>
       <c r="H37" s="12" t="n"/>
@@ -7165,7 +7261,10 @@
         <f>IFERROR(VLOOKUP(C38,▼売上原票!$A:$P,4,0),0)</f>
         <v/>
       </c>
-      <c r="E38" s="12" t="n"/>
+      <c r="E38" s="32">
+        <f>SUMPRODUCT((▼従業員マスター!$A$6:$A$300="埼玉")*(▼従業員マスター!$G$6:$G$300="直接")*▼従業員マスター!$F$6:$F$300)</f>
+        <v/>
+      </c>
       <c r="F38" s="12" t="n"/>
       <c r="G38" s="12" t="n"/>
       <c r="H38" s="12" t="n"/>
@@ -7221,7 +7320,10 @@
         <f>IFERROR(VLOOKUP(C39,▼売上原票!$A:$P,4,0),0)</f>
         <v/>
       </c>
-      <c r="E39" s="12" t="n"/>
+      <c r="E39" s="32">
+        <f>SUMPRODUCT((▼従業員マスター!$A$6:$A$300="埼玉")*(▼従業員マスター!$G$6:$G$300="直接")*▼従業員マスター!$F$6:$F$300)</f>
+        <v/>
+      </c>
       <c r="F39" s="12" t="n"/>
       <c r="G39" s="12" t="n"/>
       <c r="H39" s="12" t="n"/>
@@ -12156,7 +12258,10 @@
         <f>IFERROR(VLOOKUP(C131,▼売上原票!$A:$P,10,0),0)</f>
         <v/>
       </c>
-      <c r="E131" s="12" t="n"/>
+      <c r="E131" s="32">
+        <f>SUMPRODUCT((▼従業員マスター!$A$6:$A$300="板橋")*(▼従業員マスター!$G$6:$G$300="直接")*▼従業員マスター!$F$6:$F$300)</f>
+        <v/>
+      </c>
       <c r="F131" s="12" t="n"/>
       <c r="G131" s="12" t="n"/>
       <c r="H131" s="12" t="n"/>
@@ -12213,7 +12318,10 @@
         <f>IFERROR(VLOOKUP(C132,▼売上原票!$A:$P,10,0),0)</f>
         <v/>
       </c>
-      <c r="E132" s="12" t="n"/>
+      <c r="E132" s="32">
+        <f>SUMPRODUCT((▼従業員マスター!$A$6:$A$300="板橋")*(▼従業員マスター!$G$6:$G$300="直接")*▼従業員マスター!$F$6:$F$300)</f>
+        <v/>
+      </c>
       <c r="F132" s="12" t="n"/>
       <c r="G132" s="12" t="n"/>
       <c r="H132" s="12" t="n"/>
@@ -12269,7 +12377,10 @@
         <f>IFERROR(VLOOKUP(C133,▼売上原票!$A:$P,10,0),0)</f>
         <v/>
       </c>
-      <c r="E133" s="12" t="n"/>
+      <c r="E133" s="32">
+        <f>SUMPRODUCT((▼従業員マスター!$A$6:$A$300="板橋")*(▼従業員マスター!$G$6:$G$300="直接")*▼従業員マスター!$F$6:$F$300)</f>
+        <v/>
+      </c>
       <c r="F133" s="12" t="n"/>
       <c r="G133" s="12" t="n"/>
       <c r="H133" s="12" t="n"/>
@@ -12325,7 +12436,10 @@
         <f>IFERROR(VLOOKUP(C134,▼売上原票!$A:$P,10,0),0)</f>
         <v/>
       </c>
-      <c r="E134" s="12" t="n"/>
+      <c r="E134" s="32">
+        <f>SUMPRODUCT((▼従業員マスター!$A$6:$A$300="板橋")*(▼従業員マスター!$G$6:$G$300="直接")*▼従業員マスター!$F$6:$F$300)</f>
+        <v/>
+      </c>
       <c r="F134" s="12" t="n"/>
       <c r="G134" s="12" t="n"/>
       <c r="H134" s="12" t="n"/>
@@ -12381,7 +12495,10 @@
         <f>IFERROR(VLOOKUP(C135,▼売上原票!$A:$P,10,0),0)</f>
         <v/>
       </c>
-      <c r="E135" s="12" t="n"/>
+      <c r="E135" s="32">
+        <f>SUMPRODUCT((▼従業員マスター!$A$6:$A$300="板橋")*(▼従業員マスター!$G$6:$G$300="直接")*▼従業員マスター!$F$6:$F$300)</f>
+        <v/>
+      </c>
       <c r="F135" s="12" t="n"/>
       <c r="G135" s="12" t="n"/>
       <c r="H135" s="12" t="n"/>
@@ -12437,7 +12554,10 @@
         <f>IFERROR(VLOOKUP(C136,▼売上原票!$A:$P,10,0),0)</f>
         <v/>
       </c>
-      <c r="E136" s="12" t="n"/>
+      <c r="E136" s="32">
+        <f>SUMPRODUCT((▼従業員マスター!$A$6:$A$300="板橋")*(▼従業員マスター!$G$6:$G$300="直接")*▼従業員マスター!$F$6:$F$300)</f>
+        <v/>
+      </c>
       <c r="F136" s="12" t="n"/>
       <c r="G136" s="12" t="n"/>
       <c r="H136" s="12" t="n"/>
@@ -12493,7 +12613,10 @@
         <f>IFERROR(VLOOKUP(C137,▼売上原票!$A:$P,10,0),0)</f>
         <v/>
       </c>
-      <c r="E137" s="12" t="n"/>
+      <c r="E137" s="32">
+        <f>SUMPRODUCT((▼従業員マスター!$A$6:$A$300="板橋")*(▼従業員マスター!$G$6:$G$300="直接")*▼従業員マスター!$F$6:$F$300)</f>
+        <v/>
+      </c>
       <c r="F137" s="12" t="n"/>
       <c r="G137" s="12" t="n"/>
       <c r="H137" s="12" t="n"/>
@@ -12549,7 +12672,10 @@
         <f>IFERROR(VLOOKUP(C138,▼売上原票!$A:$P,10,0),0)</f>
         <v/>
       </c>
-      <c r="E138" s="12" t="n"/>
+      <c r="E138" s="32">
+        <f>SUMPRODUCT((▼従業員マスター!$A$6:$A$300="板橋")*(▼従業員マスター!$G$6:$G$300="直接")*▼従業員マスター!$F$6:$F$300)</f>
+        <v/>
+      </c>
       <c r="F138" s="12" t="n"/>
       <c r="G138" s="12" t="n"/>
       <c r="H138" s="12" t="n"/>
@@ -12605,7 +12731,10 @@
         <f>IFERROR(VLOOKUP(C139,▼売上原票!$A:$P,10,0),0)</f>
         <v/>
       </c>
-      <c r="E139" s="12" t="n"/>
+      <c r="E139" s="32">
+        <f>SUMPRODUCT((▼従業員マスター!$A$6:$A$300="板橋")*(▼従業員マスター!$G$6:$G$300="直接")*▼従業員マスター!$F$6:$F$300)</f>
+        <v/>
+      </c>
       <c r="F139" s="12" t="n"/>
       <c r="G139" s="12" t="n"/>
       <c r="H139" s="12" t="n"/>
@@ -12661,7 +12790,10 @@
         <f>IFERROR(VLOOKUP(C140,▼売上原票!$A:$P,10,0),0)</f>
         <v/>
       </c>
-      <c r="E140" s="12" t="n"/>
+      <c r="E140" s="32">
+        <f>SUMPRODUCT((▼従業員マスター!$A$6:$A$300="板橋")*(▼従業員マスター!$G$6:$G$300="直接")*▼従業員マスター!$F$6:$F$300)</f>
+        <v/>
+      </c>
       <c r="F140" s="12" t="n"/>
       <c r="G140" s="12" t="n"/>
       <c r="H140" s="12" t="n"/>
@@ -12717,7 +12849,10 @@
         <f>IFERROR(VLOOKUP(C141,▼売上原票!$A:$P,10,0),0)</f>
         <v/>
       </c>
-      <c r="E141" s="12" t="n"/>
+      <c r="E141" s="32">
+        <f>SUMPRODUCT((▼従業員マスター!$A$6:$A$300="板橋")*(▼従業員マスター!$G$6:$G$300="直接")*▼従業員マスター!$F$6:$F$300)</f>
+        <v/>
+      </c>
       <c r="F141" s="12" t="n"/>
       <c r="G141" s="12" t="n"/>
       <c r="H141" s="12" t="n"/>
@@ -12773,7 +12908,10 @@
         <f>IFERROR(VLOOKUP(C142,▼売上原票!$A:$P,10,0),0)</f>
         <v/>
       </c>
-      <c r="E142" s="12" t="n"/>
+      <c r="E142" s="32">
+        <f>SUMPRODUCT((▼従業員マスター!$A$6:$A$300="板橋")*(▼従業員マスター!$G$6:$G$300="直接")*▼従業員マスター!$F$6:$F$300)</f>
+        <v/>
+      </c>
       <c r="F142" s="12" t="n"/>
       <c r="G142" s="12" t="n"/>
       <c r="H142" s="12" t="n"/>
@@ -12829,7 +12967,10 @@
         <f>IFERROR(VLOOKUP(C143,▼売上原票!$A:$P,10,0),0)</f>
         <v/>
       </c>
-      <c r="E143" s="12" t="n"/>
+      <c r="E143" s="32">
+        <f>SUMPRODUCT((▼従業員マスター!$A$6:$A$300="板橋")*(▼従業員マスター!$G$6:$G$300="直接")*▼従業員マスター!$F$6:$F$300)</f>
+        <v/>
+      </c>
       <c r="F143" s="12" t="n"/>
       <c r="G143" s="12" t="n"/>
       <c r="H143" s="12" t="n"/>
@@ -12885,7 +13026,10 @@
         <f>IFERROR(VLOOKUP(C144,▼売上原票!$A:$P,10,0),0)</f>
         <v/>
       </c>
-      <c r="E144" s="12" t="n"/>
+      <c r="E144" s="32">
+        <f>SUMPRODUCT((▼従業員マスター!$A$6:$A$300="板橋")*(▼従業員マスター!$G$6:$G$300="直接")*▼従業員マスター!$F$6:$F$300)</f>
+        <v/>
+      </c>
       <c r="F144" s="12" t="n"/>
       <c r="G144" s="12" t="n"/>
       <c r="H144" s="12" t="n"/>
@@ -12941,7 +13085,10 @@
         <f>IFERROR(VLOOKUP(C145,▼売上原票!$A:$P,10,0),0)</f>
         <v/>
       </c>
-      <c r="E145" s="12" t="n"/>
+      <c r="E145" s="32">
+        <f>SUMPRODUCT((▼従業員マスター!$A$6:$A$300="板橋")*(▼従業員マスター!$G$6:$G$300="直接")*▼従業員マスター!$F$6:$F$300)</f>
+        <v/>
+      </c>
       <c r="F145" s="12" t="n"/>
       <c r="G145" s="12" t="n"/>
       <c r="H145" s="12" t="n"/>
@@ -12997,7 +13144,10 @@
         <f>IFERROR(VLOOKUP(C146,▼売上原票!$A:$P,10,0),0)</f>
         <v/>
       </c>
-      <c r="E146" s="12" t="n"/>
+      <c r="E146" s="32">
+        <f>SUMPRODUCT((▼従業員マスター!$A$6:$A$300="板橋")*(▼従業員マスター!$G$6:$G$300="直接")*▼従業員マスター!$F$6:$F$300)</f>
+        <v/>
+      </c>
       <c r="F146" s="12" t="n"/>
       <c r="G146" s="12" t="n"/>
       <c r="H146" s="12" t="n"/>
@@ -13053,7 +13203,10 @@
         <f>IFERROR(VLOOKUP(C147,▼売上原票!$A:$P,10,0),0)</f>
         <v/>
       </c>
-      <c r="E147" s="12" t="n"/>
+      <c r="E147" s="32">
+        <f>SUMPRODUCT((▼従業員マスター!$A$6:$A$300="板橋")*(▼従業員マスター!$G$6:$G$300="直接")*▼従業員マスター!$F$6:$F$300)</f>
+        <v/>
+      </c>
       <c r="F147" s="12" t="n"/>
       <c r="G147" s="12" t="n"/>
       <c r="H147" s="12" t="n"/>
@@ -13128,7 +13281,10 @@
         <f>IFERROR(VLOOKUP(C149,▼売上原票!$A:$P,11,0),0)</f>
         <v/>
       </c>
-      <c r="E149" s="12" t="n"/>
+      <c r="E149" s="32">
+        <f>SUMPRODUCT((▼従業員マスター!$A$6:$A$300="新横浜")*(▼従業員マスター!$G$6:$G$300="直接")*▼従業員マスター!$F$6:$F$300)</f>
+        <v/>
+      </c>
       <c r="F149" s="12" t="n"/>
       <c r="G149" s="12" t="n"/>
       <c r="H149" s="12" t="n"/>
@@ -13185,7 +13341,10 @@
         <f>IFERROR(VLOOKUP(C150,▼売上原票!$A:$P,11,0),0)</f>
         <v/>
       </c>
-      <c r="E150" s="12" t="n"/>
+      <c r="E150" s="32">
+        <f>SUMPRODUCT((▼従業員マスター!$A$6:$A$300="新横浜")*(▼従業員マスター!$G$6:$G$300="直接")*▼従業員マスター!$F$6:$F$300)</f>
+        <v/>
+      </c>
       <c r="F150" s="12" t="n"/>
       <c r="G150" s="12" t="n"/>
       <c r="H150" s="12" t="n"/>
@@ -13241,7 +13400,10 @@
         <f>IFERROR(VLOOKUP(C151,▼売上原票!$A:$P,11,0),0)</f>
         <v/>
       </c>
-      <c r="E151" s="12" t="n"/>
+      <c r="E151" s="32">
+        <f>SUMPRODUCT((▼従業員マスター!$A$6:$A$300="新横浜")*(▼従業員マスター!$G$6:$G$300="直接")*▼従業員マスター!$F$6:$F$300)</f>
+        <v/>
+      </c>
       <c r="F151" s="12" t="n"/>
       <c r="G151" s="12" t="n"/>
       <c r="H151" s="12" t="n"/>
@@ -13297,7 +13459,10 @@
         <f>IFERROR(VLOOKUP(C152,▼売上原票!$A:$P,11,0),0)</f>
         <v/>
       </c>
-      <c r="E152" s="12" t="n"/>
+      <c r="E152" s="32">
+        <f>SUMPRODUCT((▼従業員マスター!$A$6:$A$300="新横浜")*(▼従業員マスター!$G$6:$G$300="直接")*▼従業員マスター!$F$6:$F$300)</f>
+        <v/>
+      </c>
       <c r="F152" s="12" t="n"/>
       <c r="G152" s="12" t="n"/>
       <c r="H152" s="12" t="n"/>
@@ -13353,7 +13518,10 @@
         <f>IFERROR(VLOOKUP(C153,▼売上原票!$A:$P,11,0),0)</f>
         <v/>
       </c>
-      <c r="E153" s="12" t="n"/>
+      <c r="E153" s="32">
+        <f>SUMPRODUCT((▼従業員マスター!$A$6:$A$300="新横浜")*(▼従業員マスター!$G$6:$G$300="直接")*▼従業員マスター!$F$6:$F$300)</f>
+        <v/>
+      </c>
       <c r="F153" s="12" t="n"/>
       <c r="G153" s="12" t="n"/>
       <c r="H153" s="12" t="n"/>
@@ -13409,7 +13577,10 @@
         <f>IFERROR(VLOOKUP(C154,▼売上原票!$A:$P,11,0),0)</f>
         <v/>
       </c>
-      <c r="E154" s="12" t="n"/>
+      <c r="E154" s="32">
+        <f>SUMPRODUCT((▼従業員マスター!$A$6:$A$300="新横浜")*(▼従業員マスター!$G$6:$G$300="直接")*▼従業員マスター!$F$6:$F$300)</f>
+        <v/>
+      </c>
       <c r="F154" s="12" t="n"/>
       <c r="G154" s="12" t="n"/>
       <c r="H154" s="12" t="n"/>
@@ -13465,7 +13636,10 @@
         <f>IFERROR(VLOOKUP(C155,▼売上原票!$A:$P,11,0),0)</f>
         <v/>
       </c>
-      <c r="E155" s="12" t="n"/>
+      <c r="E155" s="32">
+        <f>SUMPRODUCT((▼従業員マスター!$A$6:$A$300="新横浜")*(▼従業員マスター!$G$6:$G$300="直接")*▼従業員マスター!$F$6:$F$300)</f>
+        <v/>
+      </c>
       <c r="F155" s="12" t="n"/>
       <c r="G155" s="12" t="n"/>
       <c r="H155" s="12" t="n"/>
@@ -13521,7 +13695,10 @@
         <f>IFERROR(VLOOKUP(C156,▼売上原票!$A:$P,11,0),0)</f>
         <v/>
       </c>
-      <c r="E156" s="12" t="n"/>
+      <c r="E156" s="32">
+        <f>SUMPRODUCT((▼従業員マスター!$A$6:$A$300="新横浜")*(▼従業員マスター!$G$6:$G$300="直接")*▼従業員マスター!$F$6:$F$300)</f>
+        <v/>
+      </c>
       <c r="F156" s="12" t="n"/>
       <c r="G156" s="12" t="n"/>
       <c r="H156" s="12" t="n"/>
@@ -13577,7 +13754,10 @@
         <f>IFERROR(VLOOKUP(C157,▼売上原票!$A:$P,11,0),0)</f>
         <v/>
       </c>
-      <c r="E157" s="12" t="n"/>
+      <c r="E157" s="32">
+        <f>SUMPRODUCT((▼従業員マスター!$A$6:$A$300="新横浜")*(▼従業員マスター!$G$6:$G$300="直接")*▼従業員マスター!$F$6:$F$300)</f>
+        <v/>
+      </c>
       <c r="F157" s="12" t="n"/>
       <c r="G157" s="12" t="n"/>
       <c r="H157" s="12" t="n"/>
@@ -13633,7 +13813,10 @@
         <f>IFERROR(VLOOKUP(C158,▼売上原票!$A:$P,11,0),0)</f>
         <v/>
       </c>
-      <c r="E158" s="12" t="n"/>
+      <c r="E158" s="32">
+        <f>SUMPRODUCT((▼従業員マスター!$A$6:$A$300="新横浜")*(▼従業員マスター!$G$6:$G$300="直接")*▼従業員マスター!$F$6:$F$300)</f>
+        <v/>
+      </c>
       <c r="F158" s="12" t="n"/>
       <c r="G158" s="12" t="n"/>
       <c r="H158" s="12" t="n"/>
@@ -13689,7 +13872,10 @@
         <f>IFERROR(VLOOKUP(C159,▼売上原票!$A:$P,11,0),0)</f>
         <v/>
       </c>
-      <c r="E159" s="12" t="n"/>
+      <c r="E159" s="32">
+        <f>SUMPRODUCT((▼従業員マスター!$A$6:$A$300="新横浜")*(▼従業員マスター!$G$6:$G$300="直接")*▼従業員マスター!$F$6:$F$300)</f>
+        <v/>
+      </c>
       <c r="F159" s="12" t="n"/>
       <c r="G159" s="12" t="n"/>
       <c r="H159" s="12" t="n"/>
@@ -13745,7 +13931,10 @@
         <f>IFERROR(VLOOKUP(C160,▼売上原票!$A:$P,11,0),0)</f>
         <v/>
       </c>
-      <c r="E160" s="12" t="n"/>
+      <c r="E160" s="32">
+        <f>SUMPRODUCT((▼従業員マスター!$A$6:$A$300="新横浜")*(▼従業員マスター!$G$6:$G$300="直接")*▼従業員マスター!$F$6:$F$300)</f>
+        <v/>
+      </c>
       <c r="F160" s="12" t="n"/>
       <c r="G160" s="12" t="n"/>
       <c r="H160" s="12" t="n"/>
@@ -13801,7 +13990,10 @@
         <f>IFERROR(VLOOKUP(C161,▼売上原票!$A:$P,11,0),0)</f>
         <v/>
       </c>
-      <c r="E161" s="12" t="n"/>
+      <c r="E161" s="32">
+        <f>SUMPRODUCT((▼従業員マスター!$A$6:$A$300="新横浜")*(▼従業員マスター!$G$6:$G$300="直接")*▼従業員マスター!$F$6:$F$300)</f>
+        <v/>
+      </c>
       <c r="F161" s="12" t="n"/>
       <c r="G161" s="12" t="n"/>
       <c r="H161" s="12" t="n"/>
@@ -13857,7 +14049,10 @@
         <f>IFERROR(VLOOKUP(C162,▼売上原票!$A:$P,11,0),0)</f>
         <v/>
       </c>
-      <c r="E162" s="12" t="n"/>
+      <c r="E162" s="32">
+        <f>SUMPRODUCT((▼従業員マスター!$A$6:$A$300="新横浜")*(▼従業員マスター!$G$6:$G$300="直接")*▼従業員マスター!$F$6:$F$300)</f>
+        <v/>
+      </c>
       <c r="F162" s="12" t="n"/>
       <c r="G162" s="12" t="n"/>
       <c r="H162" s="12" t="n"/>
@@ -13913,7 +14108,10 @@
         <f>IFERROR(VLOOKUP(C163,▼売上原票!$A:$P,11,0),0)</f>
         <v/>
       </c>
-      <c r="E163" s="12" t="n"/>
+      <c r="E163" s="32">
+        <f>SUMPRODUCT((▼従業員マスター!$A$6:$A$300="新横浜")*(▼従業員マスター!$G$6:$G$300="直接")*▼従業員マスター!$F$6:$F$300)</f>
+        <v/>
+      </c>
       <c r="F163" s="12" t="n"/>
       <c r="G163" s="12" t="n"/>
       <c r="H163" s="12" t="n"/>
@@ -13969,7 +14167,10 @@
         <f>IFERROR(VLOOKUP(C164,▼売上原票!$A:$P,11,0),0)</f>
         <v/>
       </c>
-      <c r="E164" s="12" t="n"/>
+      <c r="E164" s="32">
+        <f>SUMPRODUCT((▼従業員マスター!$A$6:$A$300="新横浜")*(▼従業員マスター!$G$6:$G$300="直接")*▼従業員マスター!$F$6:$F$300)</f>
+        <v/>
+      </c>
       <c r="F164" s="12" t="n"/>
       <c r="G164" s="12" t="n"/>
       <c r="H164" s="12" t="n"/>
@@ -14025,7 +14226,10 @@
         <f>IFERROR(VLOOKUP(C165,▼売上原票!$A:$P,11,0),0)</f>
         <v/>
       </c>
-      <c r="E165" s="12" t="n"/>
+      <c r="E165" s="32">
+        <f>SUMPRODUCT((▼従業員マスター!$A$6:$A$300="新横浜")*(▼従業員マスター!$G$6:$G$300="直接")*▼従業員マスター!$F$6:$F$300)</f>
+        <v/>
+      </c>
       <c r="F165" s="12" t="n"/>
       <c r="G165" s="12" t="n"/>
       <c r="H165" s="12" t="n"/>

--- a/sacure_採算管理_v4_ルート別案件別.xlsx
+++ b/sacure_採算管理_v4_ルート別案件別.xlsx
@@ -6066,7 +6066,9 @@
         <v/>
       </c>
       <c r="F17" s="12" t="n"/>
-      <c r="G17" s="12" t="n"/>
+      <c r="G17" s="32" t="n">
+        <v>977440</v>
+      </c>
       <c r="H17" s="12" t="n"/>
       <c r="I17" s="12" t="n"/>
       <c r="J17" s="12" t="n"/>
@@ -6125,7 +6127,9 @@
         <v/>
       </c>
       <c r="F18" s="12" t="n"/>
-      <c r="G18" s="12" t="n"/>
+      <c r="G18" s="32" t="n">
+        <v>738100</v>
+      </c>
       <c r="H18" s="12" t="n"/>
       <c r="I18" s="12" t="n"/>
       <c r="J18" s="12" t="n"/>
@@ -6184,7 +6188,9 @@
         <v/>
       </c>
       <c r="F19" s="12" t="n"/>
-      <c r="G19" s="12" t="n"/>
+      <c r="G19" s="32" t="n">
+        <v>461270</v>
+      </c>
       <c r="H19" s="12" t="n"/>
       <c r="I19" s="12" t="n"/>
       <c r="J19" s="12" t="n"/>
@@ -6243,7 +6249,9 @@
         <v/>
       </c>
       <c r="F20" s="12" t="n"/>
-      <c r="G20" s="12" t="n"/>
+      <c r="G20" s="32" t="n">
+        <v>1135153</v>
+      </c>
       <c r="H20" s="12" t="n"/>
       <c r="I20" s="12" t="n"/>
       <c r="J20" s="12" t="n"/>
@@ -6302,7 +6310,9 @@
         <v/>
       </c>
       <c r="F21" s="12" t="n"/>
-      <c r="G21" s="12" t="n"/>
+      <c r="G21" s="32" t="n">
+        <v>644910</v>
+      </c>
       <c r="H21" s="12" t="n"/>
       <c r="I21" s="12" t="n"/>
       <c r="J21" s="12" t="n"/>
@@ -7089,7 +7099,9 @@
         <v/>
       </c>
       <c r="F35" s="12" t="n"/>
-      <c r="G35" s="12" t="n"/>
+      <c r="G35" s="32" t="n">
+        <v>2575300</v>
+      </c>
       <c r="H35" s="12" t="n"/>
       <c r="I35" s="12" t="n"/>
       <c r="J35" s="12" t="n"/>
@@ -7148,7 +7160,9 @@
         <v/>
       </c>
       <c r="F36" s="12" t="n"/>
-      <c r="G36" s="12" t="n"/>
+      <c r="G36" s="32" t="n">
+        <v>1621800</v>
+      </c>
       <c r="H36" s="12" t="n"/>
       <c r="I36" s="12" t="n"/>
       <c r="J36" s="12" t="n"/>
@@ -7207,7 +7221,9 @@
         <v/>
       </c>
       <c r="F37" s="12" t="n"/>
-      <c r="G37" s="12" t="n"/>
+      <c r="G37" s="32" t="n">
+        <v>1418360</v>
+      </c>
       <c r="H37" s="12" t="n"/>
       <c r="I37" s="12" t="n"/>
       <c r="J37" s="12" t="n"/>
@@ -7266,7 +7282,9 @@
         <v/>
       </c>
       <c r="F38" s="12" t="n"/>
-      <c r="G38" s="12" t="n"/>
+      <c r="G38" s="32" t="n">
+        <v>593300</v>
+      </c>
       <c r="H38" s="12" t="n"/>
       <c r="I38" s="12" t="n"/>
       <c r="J38" s="12" t="n"/>
@@ -12972,7 +12990,9 @@
         <v/>
       </c>
       <c r="F143" s="12" t="n"/>
-      <c r="G143" s="12" t="n"/>
+      <c r="G143" s="32" t="n">
+        <v>245127</v>
+      </c>
       <c r="H143" s="12" t="n"/>
       <c r="I143" s="12" t="n"/>
       <c r="J143" s="12" t="n"/>
@@ -13090,7 +13110,9 @@
         <v/>
       </c>
       <c r="F145" s="12" t="n"/>
-      <c r="G145" s="12" t="n"/>
+      <c r="G145" s="32" t="n">
+        <v>231930</v>
+      </c>
       <c r="H145" s="12" t="n"/>
       <c r="I145" s="12" t="n"/>
       <c r="J145" s="12" t="n"/>
@@ -13149,7 +13171,9 @@
         <v/>
       </c>
       <c r="F146" s="12" t="n"/>
-      <c r="G146" s="12" t="n"/>
+      <c r="G146" s="32" t="n">
+        <v>960116</v>
+      </c>
       <c r="H146" s="12" t="n"/>
       <c r="I146" s="12" t="n"/>
       <c r="J146" s="12" t="n"/>
@@ -13208,7 +13232,9 @@
         <v/>
       </c>
       <c r="F147" s="12" t="n"/>
-      <c r="G147" s="12" t="n"/>
+      <c r="G147" s="32" t="n">
+        <v>443847</v>
+      </c>
       <c r="H147" s="12" t="n"/>
       <c r="I147" s="12" t="n"/>
       <c r="J147" s="12" t="n"/>
@@ -13995,7 +14021,9 @@
         <v/>
       </c>
       <c r="F161" s="12" t="n"/>
-      <c r="G161" s="12" t="n"/>
+      <c r="G161" s="32" t="n">
+        <v>420575</v>
+      </c>
       <c r="H161" s="12" t="n"/>
       <c r="I161" s="12" t="n"/>
       <c r="J161" s="12" t="n"/>
@@ -14054,7 +14082,9 @@
         <v/>
       </c>
       <c r="F162" s="12" t="n"/>
-      <c r="G162" s="12" t="n"/>
+      <c r="G162" s="32" t="n">
+        <v>185340</v>
+      </c>
       <c r="H162" s="12" t="n"/>
       <c r="I162" s="12" t="n"/>
       <c r="J162" s="12" t="n"/>
@@ -14113,7 +14143,9 @@
         <v/>
       </c>
       <c r="F163" s="12" t="n"/>
-      <c r="G163" s="12" t="n"/>
+      <c r="G163" s="32" t="n">
+        <v>197900</v>
+      </c>
       <c r="H163" s="12" t="n"/>
       <c r="I163" s="12" t="n"/>
       <c r="J163" s="12" t="n"/>
@@ -14172,7 +14204,9 @@
         <v/>
       </c>
       <c r="F164" s="12" t="n"/>
-      <c r="G164" s="12" t="n"/>
+      <c r="G164" s="32" t="n">
+        <v>66750</v>
+      </c>
       <c r="H164" s="12" t="n"/>
       <c r="I164" s="12" t="n"/>
       <c r="J164" s="12" t="n"/>

--- a/sacure_採算管理_v4_ルート別案件別.xlsx
+++ b/sacure_採算管理_v4_ルート別案件別.xlsx
@@ -5947,7 +5947,9 @@
         <f>SUMPRODUCT((▼従業員マスター!$A$6:$A$300="本社")*(▼従業員マスター!$G$6:$G$300="直接")*▼従業員マスター!$F$6:$F$300)</f>
         <v/>
       </c>
-      <c r="F15" s="12" t="n"/>
+      <c r="F15" s="32" t="n">
+        <v>713584</v>
+      </c>
       <c r="G15" s="12" t="n"/>
       <c r="H15" s="12" t="n"/>
       <c r="I15" s="12" t="n"/>
@@ -6006,7 +6008,9 @@
         <f>SUMPRODUCT((▼従業員マスター!$A$6:$A$300="本社")*(▼従業員マスター!$G$6:$G$300="直接")*▼従業員マスター!$F$6:$F$300)</f>
         <v/>
       </c>
-      <c r="F16" s="12" t="n"/>
+      <c r="F16" s="32" t="n">
+        <v>779796</v>
+      </c>
       <c r="G16" s="12" t="n"/>
       <c r="H16" s="12" t="n"/>
       <c r="I16" s="12" t="n"/>
@@ -6065,7 +6069,9 @@
         <f>SUMPRODUCT((▼従業員マスター!$A$6:$A$300="本社")*(▼従業員マスター!$G$6:$G$300="直接")*▼従業員マスター!$F$6:$F$300)</f>
         <v/>
       </c>
-      <c r="F17" s="12" t="n"/>
+      <c r="F17" s="32" t="n">
+        <v>990322</v>
+      </c>
       <c r="G17" s="32" t="n">
         <v>977440</v>
       </c>
@@ -6980,7 +6986,9 @@
         <f>SUMPRODUCT((▼従業員マスター!$A$6:$A$300="埼玉")*(▼従業員マスター!$G$6:$G$300="直接")*▼従業員マスター!$F$6:$F$300)</f>
         <v/>
       </c>
-      <c r="F33" s="12" t="n"/>
+      <c r="F33" s="32" t="n">
+        <v>1236618</v>
+      </c>
       <c r="G33" s="12" t="n"/>
       <c r="H33" s="12" t="n"/>
       <c r="I33" s="12" t="n"/>
@@ -7039,7 +7047,9 @@
         <f>SUMPRODUCT((▼従業員マスター!$A$6:$A$300="埼玉")*(▼従業員マスター!$G$6:$G$300="直接")*▼従業員マスター!$F$6:$F$300)</f>
         <v/>
       </c>
-      <c r="F34" s="12" t="n"/>
+      <c r="F34" s="32" t="n">
+        <v>1284802</v>
+      </c>
       <c r="G34" s="12" t="n"/>
       <c r="H34" s="12" t="n"/>
       <c r="I34" s="12" t="n"/>
@@ -7098,7 +7108,9 @@
         <f>SUMPRODUCT((▼従業員マスター!$A$6:$A$300="埼玉")*(▼従業員マスター!$G$6:$G$300="直接")*▼従業員マスター!$F$6:$F$300)</f>
         <v/>
       </c>
-      <c r="F35" s="12" t="n"/>
+      <c r="F35" s="32" t="n">
+        <v>1639924</v>
+      </c>
       <c r="G35" s="32" t="n">
         <v>2575300</v>
       </c>
@@ -8950,7 +8962,9 @@
         <v/>
       </c>
       <c r="E69" s="12" t="n"/>
-      <c r="F69" s="12" t="n"/>
+      <c r="F69" s="32" t="n">
+        <v>63684</v>
+      </c>
       <c r="G69" s="12" t="n"/>
       <c r="H69" s="12" t="n"/>
       <c r="I69" s="12" t="n"/>
@@ -9006,7 +9020,9 @@
         <v/>
       </c>
       <c r="E70" s="12" t="n"/>
-      <c r="F70" s="12" t="n"/>
+      <c r="F70" s="32" t="n">
+        <v>5336</v>
+      </c>
       <c r="G70" s="12" t="n"/>
       <c r="H70" s="12" t="n"/>
       <c r="I70" s="12" t="n"/>
@@ -9062,7 +9078,9 @@
         <v/>
       </c>
       <c r="E71" s="12" t="n"/>
-      <c r="F71" s="12" t="n"/>
+      <c r="F71" s="32" t="n">
+        <v>11682</v>
+      </c>
       <c r="G71" s="12" t="n"/>
       <c r="H71" s="12" t="n"/>
       <c r="I71" s="12" t="n"/>
@@ -12871,7 +12889,9 @@
         <f>SUMPRODUCT((▼従業員マスター!$A$6:$A$300="板橋")*(▼従業員マスター!$G$6:$G$300="直接")*▼従業員マスター!$F$6:$F$300)</f>
         <v/>
       </c>
-      <c r="F141" s="12" t="n"/>
+      <c r="F141" s="32" t="n">
+        <v>482319</v>
+      </c>
       <c r="G141" s="12" t="n"/>
       <c r="H141" s="12" t="n"/>
       <c r="I141" s="12" t="n"/>
@@ -12930,7 +12950,9 @@
         <f>SUMPRODUCT((▼従業員マスター!$A$6:$A$300="板橋")*(▼従業員マスター!$G$6:$G$300="直接")*▼従業員マスター!$F$6:$F$300)</f>
         <v/>
       </c>
-      <c r="F142" s="12" t="n"/>
+      <c r="F142" s="32" t="n">
+        <v>555271</v>
+      </c>
       <c r="G142" s="12" t="n"/>
       <c r="H142" s="12" t="n"/>
       <c r="I142" s="12" t="n"/>
@@ -12989,7 +13011,9 @@
         <f>SUMPRODUCT((▼従業員マスター!$A$6:$A$300="板橋")*(▼従業員マスター!$G$6:$G$300="直接")*▼従業員マスター!$F$6:$F$300)</f>
         <v/>
       </c>
-      <c r="F143" s="12" t="n"/>
+      <c r="F143" s="32" t="n">
+        <v>571056</v>
+      </c>
       <c r="G143" s="32" t="n">
         <v>245127</v>
       </c>
@@ -13902,7 +13926,9 @@
         <f>SUMPRODUCT((▼従業員マスター!$A$6:$A$300="新横浜")*(▼従業員マスター!$G$6:$G$300="直接")*▼従業員マスター!$F$6:$F$300)</f>
         <v/>
       </c>
-      <c r="F159" s="12" t="n"/>
+      <c r="F159" s="32" t="n">
+        <v>102837</v>
+      </c>
       <c r="G159" s="12" t="n"/>
       <c r="H159" s="12" t="n"/>
       <c r="I159" s="12" t="n"/>
@@ -13961,7 +13987,9 @@
         <f>SUMPRODUCT((▼従業員マスター!$A$6:$A$300="新横浜")*(▼従業員マスター!$G$6:$G$300="直接")*▼従業員マスター!$F$6:$F$300)</f>
         <v/>
       </c>
-      <c r="F160" s="12" t="n"/>
+      <c r="F160" s="32" t="n">
+        <v>83756</v>
+      </c>
       <c r="G160" s="12" t="n"/>
       <c r="H160" s="12" t="n"/>
       <c r="I160" s="12" t="n"/>
@@ -14020,7 +14048,9 @@
         <f>SUMPRODUCT((▼従業員マスター!$A$6:$A$300="新横浜")*(▼従業員マスター!$G$6:$G$300="直接")*▼従業員マスター!$F$6:$F$300)</f>
         <v/>
       </c>
-      <c r="F161" s="12" t="n"/>
+      <c r="F161" s="32" t="n">
+        <v>92914</v>
+      </c>
       <c r="G161" s="32" t="n">
         <v>420575</v>
       </c>
